--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 45.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 45.xlsx
@@ -526,8 +526,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -570,7 +568,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -674,8 +672,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -705,6 +701,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-302.203</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2.72644e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-81.66800000000001</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.3324985672437418</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.7394414943525438</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.361079132107822</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.201343800322297</v>
+      </c>
+      <c r="J2" t="n">
+        <v>22.28309065067079</v>
+      </c>
+      <c r="K2" t="n">
+        <v>86.23659232903233</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 15.203x + -8360.981</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>480.9179802226254</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>32722752.40087609</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>4.76354489356448e-07</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.9151183199761981</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-264.968</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2.70903e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-82.346</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.6659572099321607</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.048833820776525</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.586446990618198</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.345168482408644</v>
+      </c>
+      <c r="J3" t="n">
+        <v>25.39547829567944</v>
+      </c>
+      <c r="K3" t="n">
+        <v>86.70513271440362</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 17.370x + -9099.215</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>467.4573120364058</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>184552953.7433971</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>4.383445486220268e-07</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.9266667270381466</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-259.959</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.70055e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-82.53400000000001</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.2065994235832161</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.6908149256288911</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.464748598532261</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.374217128379251</v>
+      </c>
+      <c r="J4" t="n">
+        <v>26.27564491304693</v>
+      </c>
+      <c r="K4" t="n">
+        <v>86.68945551792773</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 17.288x + -8852.895</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>454.0172810323862</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>3786.052574500075</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.329909910929096e-06</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8414651222984563</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-249.0699999999999</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.69345e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-82.68600000000001</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.6912967279279655</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.198611813223144</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.778678856535083</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.59988802737649</v>
+      </c>
+      <c r="J5" t="n">
+        <v>28.11678770011679</v>
+      </c>
+      <c r="K5" t="n">
+        <v>86.9522145457658</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 18.781x + -9578.119</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>437.8876006493587</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>3750.519568057159</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.369126947661995e-06</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8634281974415232</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-242.599</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.69164e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-82.818</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.5585690423399794</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.031679730211049</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.876525158797712</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.557353394756368</v>
+      </c>
+      <c r="J6" t="n">
+        <v>28.68694396703544</v>
+      </c>
+      <c r="K6" t="n">
+        <v>87.00985416806904</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 19.144x + -9651.182</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>452.6898605286162</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>372708633.2520003</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>4.145001707610471e-07</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.9341455687278762</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-243.597</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.68755e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-82.883</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.2829153481239688</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.030556376765423</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.715617314790859</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.399803562555813</v>
+      </c>
+      <c r="J7" t="n">
+        <v>28.28943105105307</v>
+      </c>
+      <c r="K7" t="n">
+        <v>86.9539854200394</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 18.792x + -9335.074</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>448.2409320277739</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>213847128.618784</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>4.107660705107558e-07</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.935303220497161</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-239.779</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.68598e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-82.98399999999999</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.3906853287052123</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.8914368621230316</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.468883588348177</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.182733189467243</v>
+      </c>
+      <c r="J8" t="n">
+        <v>28.13442189504315</v>
+      </c>
+      <c r="K8" t="n">
+        <v>86.97806735020897</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 18.942x + -9296.229</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>443.9565030544216</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>181463160.9333132</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>4.064278669403648e-07</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.9368215071807625</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-240.252</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.6826e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-83.051</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.1343551314808551</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.6300344017212653</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.495542216537642</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.470749574069002</v>
+      </c>
+      <c r="J9" t="n">
+        <v>29.05839633211262</v>
+      </c>
+      <c r="K9" t="n">
+        <v>86.92254155876262</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 18.600x + -9000.956</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>439.8959858391522</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>239754015.1150077</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>4.030579782766424e-07</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.9379010583485747</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-234.1440000000001</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.67996e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-83.143</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.3960606103374492</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.107020323807981</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.75865263571295</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.651354532909224</v>
+      </c>
+      <c r="J10" t="n">
+        <v>30.14161298387466</v>
+      </c>
+      <c r="K10" t="n">
+        <v>87.11025620574966</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 19.810x + -9552.484</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>436.1400784512594</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>178248817.8884017</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>3.991627777082239e-07</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.9392278592739676</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-235.8550000000001</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.67899e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-83.182</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.3126472516318443</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.8809811551360011</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.651890857807161</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.515392565456309</v>
+      </c>
+      <c r="J11" t="n">
+        <v>29.56037493256354</v>
+      </c>
+      <c r="K11" t="n">
+        <v>87.0544119031679</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 19.434x + -9255.033</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>432.6308624506758</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>118712714.3928932</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>3.972024883721081e-07</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.9399227166687285</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-232.321</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2.67688e-07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-83.258</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.3193440510416889</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.123988181618426</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.585267034946885</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.58428996961779</v>
+      </c>
+      <c r="J12" t="n">
+        <v>30.44305894452784</v>
+      </c>
+      <c r="K12" t="n">
+        <v>87.11923817397374</v>
+      </c>
+      <c r="W12" t="n">
+        <v>11</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>y = 19.872x + -9391.599</t>
+        </is>
+      </c>
+      <c r="Y12" t="n">
+        <v>429.2544068328343</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>117731880.7618263</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>3.941020955067442e-07</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.9409913259040812</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-229.193</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2.67488e-07</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-83.316</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.5158624171801967</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.280873663322011</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.604421231636899</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2.575176920347626</v>
+      </c>
+      <c r="J13" t="n">
+        <v>29.97653689912666</v>
+      </c>
+      <c r="K13" t="n">
+        <v>87.23740857856555</v>
+      </c>
+      <c r="W13" t="n">
+        <v>12</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>y = 20.724x + -9755.401</t>
+        </is>
+      </c>
+      <c r="Y13" t="n">
+        <v>426.0092985316125</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>115910342.4364102</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>3.916201313707369e-07</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.9418383531316091</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-226.787</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2.67391e-07</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-83.373</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.9861774126466745</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.304360260794313</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.874176311080603</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2.810718427190251</v>
+      </c>
+      <c r="J14" t="n">
+        <v>31.00984725168055</v>
+      </c>
+      <c r="K14" t="n">
+        <v>87.29760709754886</v>
+      </c>
+      <c r="W14" t="n">
+        <v>13</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>y = 21.186x + -9907.356</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
+        <v>422.7582751157986</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>115113235.4057532</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>3.894681968248368e-07</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.9426184644425313</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-228.5439999999999</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2.67161e-07</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-83.43300000000001</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.1390085439308156</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.641765336270207</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.526971169942958</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.211514049010288</v>
+      </c>
+      <c r="J15" t="n">
+        <v>29.73296890354945</v>
+      </c>
+      <c r="K15" t="n">
+        <v>87.14788086539058</v>
+      </c>
+      <c r="W15" t="n">
+        <v>14</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>y = 20.072x + -9230.947</t>
+        </is>
+      </c>
+      <c r="Y15" t="n">
+        <v>419.5445726516589</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>228489614.6300777</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>3.870198928759991e-07</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.943446300867181</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-227.6300000000001</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2.67154e-07</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-83.488</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.7845881925667021</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.367119214563877</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.248802712732471</v>
+      </c>
+      <c r="J16" t="n">
+        <v>30.00706656580175</v>
+      </c>
+      <c r="K16" t="n">
+        <v>87.11724320036751</v>
+      </c>
+      <c r="W16" t="n">
+        <v>15</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>y = 19.859x + -9039.395</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>416.4026218088894</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>113897961.7652397</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>3.852111742265167e-07</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.9441457628753107</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-220.461</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2.67023e-07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-83.565</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.5472777647383407</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1.097982380007562</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.639998117077041</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2.663054796785869</v>
+      </c>
+      <c r="J17" t="n">
+        <v>31.83879823197438</v>
+      </c>
+      <c r="K17" t="n">
+        <v>87.32277914582281</v>
+      </c>
+      <c r="W17" t="n">
+        <v>16</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>y = 21.386x + -9725.303</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>413.2448694439817</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>225034438.3059394</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>3.824649422397493e-07</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.9451590446040621</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-220.907</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2.66962e-07</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-83.611</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.2356551103359827</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.103637347044258</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.725787522674725</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.554197738215202</v>
+      </c>
+      <c r="J18" t="n">
+        <v>31.97879886202891</v>
+      </c>
+      <c r="K18" t="n">
+        <v>87.28332486828249</v>
+      </c>
+      <c r="W18" t="n">
+        <v>17</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>y = 21.075x + -9479.464</t>
+        </is>
+      </c>
+      <c r="Y18" t="n">
+        <v>410.0939754555842</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>111547416.8222765</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>3.80791102093921e-07</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.9457842968523634</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-220.714</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2.66831e-07</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-83.63800000000001</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.6330550368265632</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1.105393231135166</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.821768013626504</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2.646129527231523</v>
+      </c>
+      <c r="J19" t="n">
+        <v>31.71668794179721</v>
+      </c>
+      <c r="K19" t="n">
+        <v>87.35643336487306</v>
+      </c>
+      <c r="W19" t="n">
+        <v>18</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>y = 21.658x + -9689.716</t>
+        </is>
+      </c>
+      <c r="Y19" t="n">
+        <v>406.9299068987231</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>166188766.2632105</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>3.795864383290239e-07</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.9461987923542072</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-220.716</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2.6676e-07</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-83.705</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.2173800541936653</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.5995250439238596</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.575355738175434</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.35627503580692</v>
+      </c>
+      <c r="J20" t="n">
+        <v>31.15370010076809</v>
+      </c>
+      <c r="K20" t="n">
+        <v>87.23143930517391</v>
+      </c>
+      <c r="W20" t="n">
+        <v>19</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>y = 20.679x + -9112.604</t>
+        </is>
+      </c>
+      <c r="Y20" t="n">
+        <v>403.8097827662983</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>110186319.4424782</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>3.773386297485312e-07</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.9470588941999227</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-215.333</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2.66757e-07</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-83.786</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.2509158592886808</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.8856038118946071</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.654938574216668</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.552729536040805</v>
+      </c>
+      <c r="J21" t="n">
+        <v>33.03580469276218</v>
+      </c>
+      <c r="K21" t="n">
+        <v>87.32353763478508</v>
+      </c>
+      <c r="W21" t="n">
+        <v>20</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>y = 21.392x + -9365.318</t>
+        </is>
+      </c>
+      <c r="Y21" t="n">
+        <v>400.5999790302465</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>174014444.5471484</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>3.749404704529664e-07</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.9480103435088878</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-213.279</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2.66694e-07</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-83.834</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.4855452567875742</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1.096834607655973</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.769976167413208</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2.541987523060316</v>
+      </c>
+      <c r="J22" t="n">
+        <v>32.85722396609565</v>
+      </c>
+      <c r="K22" t="n">
+        <v>87.38723037836647</v>
+      </c>
+      <c r="W22" t="n">
+        <v>21</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>y = 21.914x + -9532.753</t>
+        </is>
+      </c>
+      <c r="Y22" t="n">
+        <v>397.4150777577553</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>108186090.8757237</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>3.73254825807647e-07</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.9486615081080416</v>
       </c>
     </row>
   </sheetData>
@@ -822,8 +1910,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -866,7 +1952,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -970,8 +2056,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1001,6 +2085,526 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-460.1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2.79854e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-78.821</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.5481798751735231</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.7263531403530465</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.179289579195842</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.896337896148187</v>
+      </c>
+      <c r="J2" t="n">
+        <v>13.24664818956317</v>
+      </c>
+      <c r="K2" t="n">
+        <v>84.60611152146957</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 10.591x + -6757.919</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>536.6848260996646</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>589286338.9800715</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>6.871695977063213e-07</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8642186898387478</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-364.144</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2.81243e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-80.351</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.5418256152046087</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.9010682330957922</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.475204226091361</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.33219979671676</v>
+      </c>
+      <c r="J3" t="n">
+        <v>17.23871188001938</v>
+      </c>
+      <c r="K3" t="n">
+        <v>85.66777575705275</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 13.200x + -7718.584</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>512.4986315999361</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>48174490.39845841</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>5.584673222971136e-07</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8960328445951323</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-319.514</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.78511e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-81.10299999999999</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.0275019636966087</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.5816810453513427</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.475904541060932</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.069702158372602</v>
+      </c>
+      <c r="J4" t="n">
+        <v>19.65098299046176</v>
+      </c>
+      <c r="K4" t="n">
+        <v>86.06107784966113</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 14.523x + -8224.408</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>503.443943654204</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>37943666.38081218</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>5.082483036017803e-07</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.9086717044287616</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-292.909</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.76359e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-81.548</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.2203867314408416</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.7012511749719063</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.426403407443023</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.056537876143126</v>
+      </c>
+      <c r="J5" t="n">
+        <v>21.90434294057446</v>
+      </c>
+      <c r="K5" t="n">
+        <v>86.35405494977601</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 15.694x + -8750.737</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>497.1263969792354</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>36136651.60595468</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>4.812910557211444e-07</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.9156698053745044</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-277.218</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.74397e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-81.848</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.3164895967107017</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.9415504384226792</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.506193361917312</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.216134587374894</v>
+      </c>
+      <c r="J6" t="n">
+        <v>23.84829695047509</v>
+      </c>
+      <c r="K6" t="n">
+        <v>86.56163916493065</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 16.644x + -9159.621</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>491.2163573691311</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>134309084.697485</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>4.631455767424235e-07</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.9203777368027308</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-267.169</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.73123e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-82.081</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.7123332046212697</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.37181600158045</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.207625158007089</v>
+      </c>
+      <c r="J7" t="n">
+        <v>25.18493337408912</v>
+      </c>
+      <c r="K7" t="n">
+        <v>86.62097055897429</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 16.937x + -9169.790</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>485.4364083442069</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>265477180.1549042</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>4.500455495922638e-07</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.9239989877368346</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-255.1600000000001</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.71946e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-82.276</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.5263140168972354</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.466862357593779</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.551702448414602</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.379554499254712</v>
+      </c>
+      <c r="J8" t="n">
+        <v>26.2906876890817</v>
+      </c>
+      <c r="K8" t="n">
+        <v>86.88720245361314</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 18.388x + -9885.402</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>479.7942909356152</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>131023940.34062</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>4.389724878764684e-07</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.9271133873023493</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-251.974</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.71109e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-82.44199999999999</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.07132121822165173</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.6796286447944158</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.403179545867203</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.237145134177287</v>
+      </c>
+      <c r="J9" t="n">
+        <v>27.30665783007737</v>
+      </c>
+      <c r="K9" t="n">
+        <v>86.74861304721674</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 17.603x + -9258.924</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>464.4180728158482</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>3892.381706851974</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.172201301024176e-06</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8860525156364467</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-247.93</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.70458e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-82.56999999999999</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.1163231533897849</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.6260359228828783</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.327437304529981</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.16106049180579</v>
+      </c>
+      <c r="J10" t="n">
+        <v>27.57286682831236</v>
+      </c>
+      <c r="K10" t="n">
+        <v>86.80272453991049</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 17.902x + -9296.457</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>450.9331247486803</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3850.192004271824</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>9.042976841967091e-07</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.9131653180518182</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-235.55</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.69936e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-82.73699999999999</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.2728817483206419</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.9138021539933532</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.630666832634549</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.235788488584801</v>
+      </c>
+      <c r="J11" t="n">
+        <v>28.88389101858023</v>
+      </c>
+      <c r="K11" t="n">
+        <v>87.04481260445652</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 19.371x + -10002.052</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>451.1993374767339</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>7672.813938747323</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>3.584885292294679e-07</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.9999959218011779</v>
       </c>
     </row>
   </sheetData>
@@ -1014,7 +2618,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1118,8 +2722,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1149,6 +2751,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-332.0350000000001</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2.76224e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-81.25700000000001</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.330533986844334</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.5877378281273548</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.298060770326512</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.010056679955588</v>
+      </c>
+      <c r="J2" t="n">
+        <v>19.28371356972924</v>
+      </c>
+      <c r="K2" t="n">
+        <v>85.95626256722102</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 14.145x + -7763.767</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>480.2951757214407</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>58206032.58323675</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>4.992013584057573e-07</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.9101550712502147</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-280.237</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2.73656e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-82.15600000000001</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.08386181951354808</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.6501778611598134</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.29584434663318</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.223420237279577</v>
+      </c>
+      <c r="J3" t="n">
+        <v>23.83488154240947</v>
+      </c>
+      <c r="K3" t="n">
+        <v>86.48127321041933</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 16.263x + -8434.634</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>466.0520934308912</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>516752350.111385</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>4.480406649797358e-07</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.9249675534955195</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-257.74</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.7226e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-82.504</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.1348066623443797</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.740179005066733</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.480561527749616</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.313516128215868</v>
+      </c>
+      <c r="J4" t="n">
+        <v>26.24863934026049</v>
+      </c>
+      <c r="K4" t="n">
+        <v>86.78649210241561</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 17.811x + -9104.597</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>440.2287237932851</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>3771.878876273001</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>9.89915647613028e-07</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.9048746537960295</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-258.3969999999999</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.71316e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-82.673</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.59305345371442</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1.713764778757748</v>
+      </c>
+      <c r="J5" t="n">
+        <v>25.21912274842513</v>
+      </c>
+      <c r="K5" t="n">
+        <v>86.35824109805462</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 15.712x + -7782.179</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>455.2898977755081</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>233476585.7749151</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>4.214796704370467e-07</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.9328901449854846</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-239.8799999999999</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.70379e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-82.851</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.3779501970894521</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.030186041264169</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.767613475431259</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.52143372850762</v>
+      </c>
+      <c r="J6" t="n">
+        <v>29.13872742400114</v>
+      </c>
+      <c r="K6" t="n">
+        <v>87.01682231696586</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 19.189x + -9593.137</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>450.9861210411568</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>126545179.3254542</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>4.129222500315576e-07</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.9354617326991671</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-231.3179999999999</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.69961e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-82.991</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.448810581471758</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.128325434466154</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.581702138578309</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.476534749288193</v>
+      </c>
+      <c r="J7" t="n">
+        <v>30.31672463756461</v>
+      </c>
+      <c r="K7" t="n">
+        <v>87.11128161283676</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 19.818x + -9806.389</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>446.8889649155186</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>122458875.3100242</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>4.067916761251468e-07</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.9374812448816695</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-228.917</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.69501e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-83.08</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.4950521832648156</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.9881042457549121</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.67893185350079</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.517252900989067</v>
+      </c>
+      <c r="J8" t="n">
+        <v>30.77767099983682</v>
+      </c>
+      <c r="K8" t="n">
+        <v>87.15781820780296</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 20.143x + -9869.027</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>442.8712218178521</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>122392902.8602818</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>4.024624242343295e-07</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.9388505881348892</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-225.077</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.69065e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-83.175</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.4777027867347912</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.956899369371179</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.699034982422144</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.490957032654544</v>
+      </c>
+      <c r="J9" t="n">
+        <v>31.46402998335893</v>
+      </c>
+      <c r="K9" t="n">
+        <v>87.21211455630632</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 20.535x + -9966.374</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>439.1164588465697</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>358891114.3223209</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>3.981809757220652e-07</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.9402256101603299</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-219.884</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.68862e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-83.27500000000001</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.5569813971787919</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.9256174962347529</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.624419420570391</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.511422546735022</v>
+      </c>
+      <c r="J10" t="n">
+        <v>31.88114884056025</v>
+      </c>
+      <c r="K10" t="n">
+        <v>87.25805920057836</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 20.880x + -10037.105</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>435.6279289492796</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>135088959.5285163</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>3.942594878233831e-07</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.9416011267882688</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-220.128</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.685e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-83.33</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.3114787340900936</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.9543286886739243</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.720521367487621</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.638531994005457</v>
+      </c>
+      <c r="J11" t="n">
+        <v>32.48496036065949</v>
+      </c>
+      <c r="K11" t="n">
+        <v>87.23514555078835</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 20.707x + -9852.044</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>432.426126761333</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>353362037.112519</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>3.915712377291921e-07</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.9424435530314343</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-218.152</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2.68248e-07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-83.396</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.2604359614596863</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.6804501382612789</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.486805657384116</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.327269215728609</v>
+      </c>
+      <c r="J12" t="n">
+        <v>31.64516494426261</v>
+      </c>
+      <c r="K12" t="n">
+        <v>87.22943828442875</v>
+      </c>
+      <c r="W12" t="n">
+        <v>11</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>y = 20.664x + -9738.147</t>
+        </is>
+      </c>
+      <c r="Y12" t="n">
+        <v>429.3655616654337</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>350392262.7494087</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>3.887829210702251e-07</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.9433874120046737</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-212.123</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2.68049e-07</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-83.486</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.2269760579253861</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.9987665889543645</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.602335496143361</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2.626349416462623</v>
+      </c>
+      <c r="J13" t="n">
+        <v>33.86317524998702</v>
+      </c>
+      <c r="K13" t="n">
+        <v>87.3222287501108</v>
+      </c>
+      <c r="W13" t="n">
+        <v>12</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>y = 21.381x + -10018.553</t>
+        </is>
+      </c>
+      <c r="Y13" t="n">
+        <v>426.3164300355821</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>580420486.7926364</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>3.855688000858838e-07</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.944520693151338</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-210.152</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2.6773e-07</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-83.53700000000001</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.6305025851687559</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.9964186962867626</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.912712004248301</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2.683603967450868</v>
+      </c>
+      <c r="J14" t="n">
+        <v>33.97227132522889</v>
+      </c>
+      <c r="K14" t="n">
+        <v>87.41672760765853</v>
+      </c>
+      <c r="W14" t="n">
+        <v>13</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>y = 22.165x + -10335.154</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
+        <v>423.2760786268939</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>119273868.8902068</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>3.831347269447549e-07</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.9453085696818081</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-216.568</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2.67571e-07</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-83.574</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.01892620484260812</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.208705692684379</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.0716699838771</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.940687293254324</v>
+      </c>
+      <c r="J15" t="n">
+        <v>31.05210348518892</v>
+      </c>
+      <c r="K15" t="n">
+        <v>87.08785412480184</v>
+      </c>
+      <c r="W15" t="n">
+        <v>14</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>y = 19.658x + -8970.084</t>
+        </is>
+      </c>
+      <c r="Y15" t="n">
+        <v>420.1909075974667</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>114419301.9815577</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>3.815828381615512e-07</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.9458411130672405</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-211.1</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2.67374e-07</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-83.628</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.1876909474431176</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.8003300417552056</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.61157141227288</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.526243468095973</v>
+      </c>
+      <c r="J16" t="n">
+        <v>33.83314000141182</v>
+      </c>
+      <c r="K16" t="n">
+        <v>87.32531571405592</v>
+      </c>
+      <c r="W16" t="n">
+        <v>15</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>y = 21.406x + -9770.702</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>417.1214845417246</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>170335906.1875667</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>3.79570601572069e-07</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.9465298135882735</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-207.197</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2.67279e-07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-83.69</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.2957751868366115</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.9636503420793484</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.634190566495614</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2.392784020934656</v>
+      </c>
+      <c r="J17" t="n">
+        <v>33.49245672902483</v>
+      </c>
+      <c r="K17" t="n">
+        <v>87.44751334825065</v>
+      </c>
+      <c r="W17" t="n">
+        <v>16</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>y = 22.432x + -10197.687</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>414.0538608169979</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>189662324.7506776</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>3.774134290660462e-07</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.947336461795603</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-203.219</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2.67075e-07</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-83.759</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.5951039828724957</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.073613451235428</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.874587208278521</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.748564575002348</v>
+      </c>
+      <c r="J18" t="n">
+        <v>35.30980551628979</v>
+      </c>
+      <c r="K18" t="n">
+        <v>87.52417100540225</v>
+      </c>
+      <c r="W18" t="n">
+        <v>17</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>y = 23.128x + -10453.667</t>
+        </is>
+      </c>
+      <c r="Y18" t="n">
+        <v>411.0115831455041</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>335463998.5325902</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>3.75005320023306e-07</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.948182704905459</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-205.833</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2.66953e-07</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-83.803</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.1242211930156695</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.631517199390349</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.431943269044873</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2.321296160162953</v>
+      </c>
+      <c r="J19" t="n">
+        <v>33.81777975569447</v>
+      </c>
+      <c r="K19" t="n">
+        <v>87.37354170745235</v>
+      </c>
+      <c r="W19" t="n">
+        <v>18</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>y = 21.800x + -9699.760</t>
+        </is>
+      </c>
+      <c r="Y19" t="n">
+        <v>407.8691435991047</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>166791579.8430284</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>3.733618963832413e-07</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.9487873349115972</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-205.568</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2.66861e-07</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-83.834</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.3188206966877221</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.7984307653834289</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.671405747267264</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.27978211544319</v>
+      </c>
+      <c r="J20" t="n">
+        <v>33.65501553687267</v>
+      </c>
+      <c r="K20" t="n">
+        <v>87.44335165990118</v>
+      </c>
+      <c r="W20" t="n">
+        <v>19</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>y = 22.396x + -9910.234</t>
+        </is>
+      </c>
+      <c r="Y20" t="n">
+        <v>404.7743525593904</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>220966175.5117127</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>3.722562336146518e-07</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.9491914304127851</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-200.7020000000001</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2.66724e-07</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-83.895</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.7173799805031622</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1.316235481668363</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.739407420553176</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.618405736056628</v>
+      </c>
+      <c r="J21" t="n">
+        <v>34.88228354389916</v>
+      </c>
+      <c r="K21" t="n">
+        <v>87.6263570578039</v>
+      </c>
+      <c r="W21" t="n">
+        <v>20</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>y = 24.125x + -10659.979</t>
+        </is>
+      </c>
+      <c r="Y21" t="n">
+        <v>401.6864719294056</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>218430394.4754781</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>3.70075288371997e-07</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.9500074306874754</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-199.958</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2.66594e-07</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-83.96599999999999</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.4115843471558466</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.9389535320322314</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.611043353358093</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2.606017068382955</v>
+      </c>
+      <c r="J22" t="n">
+        <v>36.02166506229121</v>
+      </c>
+      <c r="K22" t="n">
+        <v>87.50042163574763</v>
+      </c>
+      <c r="W22" t="n">
+        <v>21</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>y = 22.908x + -9967.246</t>
+        </is>
+      </c>
+      <c r="Y22" t="n">
+        <v>398.5548574235218</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>433419073.6183606</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>3.67800067085379e-07</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.9508641339490165</v>
       </c>
     </row>
   </sheetData>
@@ -1162,7 +3856,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1266,8 +3960,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1297,6 +3989,526 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-562.266</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2.84316e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-77.22</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.08978648883415256</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.4588389627428508</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.967997851505038</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.680153160535744</v>
+      </c>
+      <c r="J2" t="n">
+        <v>10.51397226609207</v>
+      </c>
+      <c r="K2" t="n">
+        <v>83.2286754759028</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 8.422x + -5594.038</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>543.1549205509359</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>186265100.5781556</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>9.000562484580156e-07</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8262717331236198</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-405.046</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2.87624e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-79.655</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.3596651333256907</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.7502398108834016</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.458388893159746</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.304195474805894</v>
+      </c>
+      <c r="J3" t="n">
+        <v>15.06963432387406</v>
+      </c>
+      <c r="K3" t="n">
+        <v>85.0734179252637</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 11.601x + -6793.990</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>510.9396929138588</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>280770929.6339918</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>6.244166002873013e-07</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8826192676113127</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-350.2140000000001</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.84392e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-80.584</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.4120581683184186</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.7372488032528489</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.3682177871806</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.171282251502486</v>
+      </c>
+      <c r="J4" t="n">
+        <v>17.43515295685487</v>
+      </c>
+      <c r="K4" t="n">
+        <v>85.68063584767771</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 13.240x + -7493.782</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>500.6049367462784</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>53375387.1332188</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>5.527798103117413e-07</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8991624134218938</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-313.629</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.81587e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-81.169</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.2220249874761634</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.8108045526750352</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.575293000320209</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.21423370452061</v>
+      </c>
+      <c r="J5" t="n">
+        <v>19.9532080972912</v>
+      </c>
+      <c r="K5" t="n">
+        <v>86.08381995169948</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 14.608x + -8129.460</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>494.0450278191379</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>46786109.65925075</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>5.137677306838621e-07</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.9086276890544402</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-293.726</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.79529e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-81.532</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.2913970905464736</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.753727737783691</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.54670286844977</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.167709406308663</v>
+      </c>
+      <c r="J6" t="n">
+        <v>21.73132486399051</v>
+      </c>
+      <c r="K6" t="n">
+        <v>86.32011709446074</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 15.549x + -8528.743</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>487.943646383955</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>33367211.02390506</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>4.901749361239819e-07</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.9145916029816222</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-278.4590000000001</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.78141e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-81.807</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.4629487547650173</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.044311552568128</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.66867415449035</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.49605929445957</v>
+      </c>
+      <c r="J7" t="n">
+        <v>23.85104886284417</v>
+      </c>
+      <c r="K7" t="n">
+        <v>86.52516603865126</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 16.469x + -8919.202</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>481.8661609590969</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>792603942.9823534</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>4.73924482176603e-07</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.9189140062896058</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-264.2569999999999</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.76923e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-82.05200000000001</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.7921775406142562</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.013640151941362</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.876557889961799</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.37590768450577</v>
+      </c>
+      <c r="J8" t="n">
+        <v>24.90528374330481</v>
+      </c>
+      <c r="K8" t="n">
+        <v>86.72920435807227</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 17.498x + -9365.715</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>475.8994573007008</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>130349566.0779665</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>4.59654215334174e-07</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.9228651803233946</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-259.361</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.75833e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-82.236</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.2993758409746031</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.9043058464767185</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.591753687542244</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.306192192620498</v>
+      </c>
+      <c r="J9" t="n">
+        <v>25.07201326729235</v>
+      </c>
+      <c r="K9" t="n">
+        <v>86.72363030343634</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 17.469x + -9178.008</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>470.2342682494343</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>192582098.4404453</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>4.488018763383606e-07</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.9258881672677145</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-248.358</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.75131e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-82.438</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.1965352671732684</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.8598913346408041</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.621214801029556</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.558268819927799</v>
+      </c>
+      <c r="J10" t="n">
+        <v>27.73301992254679</v>
+      </c>
+      <c r="K10" t="n">
+        <v>86.82480654129405</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 18.026x + -9343.367</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>443.8763524390018</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3816.204478538165</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.679564945875143e-06</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.826458868524758</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-243.711</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.74475e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-82.578</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.3162668118101436</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.9570668073881924</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.68957947960506</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.411477381060497</v>
+      </c>
+      <c r="J11" t="n">
+        <v>28.05607358596687</v>
+      </c>
+      <c r="K11" t="n">
+        <v>86.88813597581999</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 18.394x + -9412.102</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>439.9090000652595</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>3778.608686157441</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.073043167800002e-06</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8926826976604159</v>
       </c>
     </row>
   </sheetData>
@@ -1310,7 +4522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1414,8 +4626,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1445,6 +4655,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-402.6819999999999</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2.93977e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-79.83799999999999</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.2391044109163905</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.7136005494002059</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.243429740364458</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.049380985192579</v>
+      </c>
+      <c r="J2" t="n">
+        <v>14.65458637159623</v>
+      </c>
+      <c r="K2" t="n">
+        <v>84.97403041664072</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 11.371x + -6270.930</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>480.7329810792613</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>74281673.71447983</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>6.10816213591845e-07</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8894009714299091</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-304.586</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2.84886e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-81.52</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.4649729785824099</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.9275681081264546</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.623548140619627</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.307936484269805</v>
+      </c>
+      <c r="J3" t="n">
+        <v>20.57984087140361</v>
+      </c>
+      <c r="K3" t="n">
+        <v>86.21937729737456</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 15.133x + -7908.508</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>466.6743280794358</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1146789125.444086</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>4.93953090122737e-07</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.9163984231004559</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-275.384</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.81455e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-82.027</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.5400442856502823</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.004924751475929</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.562905831973823</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.46533442115506</v>
+      </c>
+      <c r="J4" t="n">
+        <v>23.42731796260284</v>
+      </c>
+      <c r="K4" t="n">
+        <v>86.56353036166978</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 16.653x + -8555.418</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>441.7462578815397</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>3784.671871658175</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>9.920763789529094e-07</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8841076497048745</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-261.417</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.79294e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-82.303</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.3643220811514742</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.9542164653254016</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.706124634932756</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.557466640050853</v>
+      </c>
+      <c r="J5" t="n">
+        <v>25.57066790162908</v>
+      </c>
+      <c r="K5" t="n">
+        <v>86.69176337968138</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 17.300x + -8769.938</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>456.5841396445374</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>124610153.8380714</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>4.478528728625239e-07</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.9281369151662501</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-250.0599999999999</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.78271e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-82.5</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.4038505141133135</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.191843074366935</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.61408324282019</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.427137666739247</v>
+      </c>
+      <c r="J6" t="n">
+        <v>26.19734474223249</v>
+      </c>
+      <c r="K6" t="n">
+        <v>86.86121345923347</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 18.236x + -9162.047</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>452.2941937652293</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>370159327.3551711</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>4.379485607529913e-07</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.9309405666265033</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-244.102</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.77066e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-82.661</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.1492253332338421</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.7377444389760996</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.550429218871968</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.420052258613789</v>
+      </c>
+      <c r="J7" t="n">
+        <v>26.8792209452552</v>
+      </c>
+      <c r="K7" t="n">
+        <v>86.86744460857412</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 18.272x + -9049.733</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>447.9608253751574</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>170780600.7147736</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>4.290502484936856e-07</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.9333986982988465</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-239.6659999999999</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.76493e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-82.78700000000001</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.07170453227870047</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.9006459460884192</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.410516855309734</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.356001495963845</v>
+      </c>
+      <c r="J8" t="n">
+        <v>27.71404091806502</v>
+      </c>
+      <c r="K8" t="n">
+        <v>86.86641320059545</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 18.266x + -8927.371</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>443.8211181574397</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>363229513.4700153</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>4.22975977742907e-07</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.9352353544685039</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-234.5579999999999</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.75846e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-82.91</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.04359110091901515</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.6539034218664624</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.507416497338782</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.093907073931078</v>
+      </c>
+      <c r="J9" t="n">
+        <v>27.72395612532735</v>
+      </c>
+      <c r="K9" t="n">
+        <v>86.91368979123239</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 18.547x + -8965.883</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>439.9561516169117</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>723148207.1356236</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>4.170676493982838e-07</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.9370133824139422</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-227.726</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.75517e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-83.04600000000001</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.04799330266948247</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.5089520950458595</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.328541868980331</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.276765500046405</v>
+      </c>
+      <c r="J10" t="n">
+        <v>29.34774855306356</v>
+      </c>
+      <c r="K10" t="n">
+        <v>86.94806930354042</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 18.756x + -8968.914</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>436.3600211278208</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>358460681.8910872</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>4.115320442145009e-07</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.9388208224766018</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-226.396</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.74867e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-83.09099999999999</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.251142230750293</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.001559869725202</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.617462083210003</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.388396257881872</v>
+      </c>
+      <c r="J11" t="n">
+        <v>29.59671202286416</v>
+      </c>
+      <c r="K11" t="n">
+        <v>87.11608184377877</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 19.851x + -9466.038</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>432.97046668927</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>236014137.9245085</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>4.083913633849018e-07</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.9396582439700497</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-218.4560000000001</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2.74698e-07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-83.209</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.538528885055742</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.197607868959394</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.673785067309329</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.645207520751798</v>
+      </c>
+      <c r="J12" t="n">
+        <v>31.71356509395545</v>
+      </c>
+      <c r="K12" t="n">
+        <v>87.22113248913811</v>
+      </c>
+      <c r="W12" t="n">
+        <v>11</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>y = 20.602x + -9759.613</t>
+        </is>
+      </c>
+      <c r="Y12" t="n">
+        <v>429.7823712461693</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>117324768.0826236</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>4.040091939319597e-07</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.9411799777512009</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-218.275</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2.74453e-07</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-83.25700000000001</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.3159914689799611</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.7606565528292796</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.532980626709601</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2.379374168915587</v>
+      </c>
+      <c r="J13" t="n">
+        <v>30.45819316920828</v>
+      </c>
+      <c r="K13" t="n">
+        <v>87.20388616141652</v>
+      </c>
+      <c r="W13" t="n">
+        <v>12</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>y = 20.475x + -9605.001</t>
+        </is>
+      </c>
+      <c r="Y13" t="n">
+        <v>426.7265578770754</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>116197004.0089286</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>4.017211680390725e-07</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.9419093952397858</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-216.824</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2.74151e-07</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-83.309</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.6882018617424399</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.240996384041292</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.838074607032267</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2.844247579126824</v>
+      </c>
+      <c r="J14" t="n">
+        <v>32.33648522574576</v>
+      </c>
+      <c r="K14" t="n">
+        <v>87.28877204326189</v>
+      </c>
+      <c r="W14" t="n">
+        <v>13</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>y = 21.117x + -9858.038</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
+        <v>423.717404171028</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>174275636.4765854</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>3.993079744260538e-07</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.9426626894254309</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-211.552</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2.73748e-07</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-83.417</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.3134838763771157</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.042939328728132</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.762795303259463</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.697678128525368</v>
+      </c>
+      <c r="J15" t="n">
+        <v>33.13060500710547</v>
+      </c>
+      <c r="K15" t="n">
+        <v>87.27853165704568</v>
+      </c>
+      <c r="W15" t="n">
+        <v>14</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>y = 21.037x + -9717.500</t>
+        </is>
+      </c>
+      <c r="Y15" t="n">
+        <v>420.8301510651199</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>118699947.6321774</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>3.950350635438924e-07</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.9440599332315927</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-210.8699999999999</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2.73534e-07</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-83.444</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.8348889911401127</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.162140258504048</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.817230276788898</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.500076677676967</v>
+      </c>
+      <c r="J16" t="n">
+        <v>32.04735124593791</v>
+      </c>
+      <c r="K16" t="n">
+        <v>87.37663320905385</v>
+      </c>
+      <c r="W16" t="n">
+        <v>15</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>y = 21.825x + -10047.448</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>417.8883155073642</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>113886404.4804137</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>3.936691830738516e-07</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.9444756568646714</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-209.307</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2.73386e-07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-83.521</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.1647945491312554</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.9837396176996254</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.647799806128335</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2.36922966697612</v>
+      </c>
+      <c r="J17" t="n">
+        <v>32.74818385103877</v>
+      </c>
+      <c r="K17" t="n">
+        <v>87.29573909794998</v>
+      </c>
+      <c r="W17" t="n">
+        <v>16</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>y = 21.171x + -9621.750</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>414.9342646853236</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>225863530.1406434</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>3.909898706607735e-07</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.9454196979458092</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-205.398</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2.73301e-07</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-83.593</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.3214774842710523</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.209466696147226</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.839286975016417</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.696931366100376</v>
+      </c>
+      <c r="J18" t="n">
+        <v>34.32470239710515</v>
+      </c>
+      <c r="K18" t="n">
+        <v>87.36062890868665</v>
+      </c>
+      <c r="W18" t="n">
+        <v>17</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>y = 21.693x + -9796.621</t>
+        </is>
+      </c>
+      <c r="Y18" t="n">
+        <v>411.9720116088964</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>224301672.8987534</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>3.885281668279745e-07</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.9463227911538287</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-206.718</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2.73065e-07</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-83.61199999999999</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.4950083851407024</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1.175182459718676</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.651556081778543</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2.664032826976464</v>
+      </c>
+      <c r="J19" t="n">
+        <v>33.45708075385323</v>
+      </c>
+      <c r="K19" t="n">
+        <v>87.42040333435118</v>
+      </c>
+      <c r="W19" t="n">
+        <v>18</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>y = 22.196x + -9966.494</t>
+        </is>
+      </c>
+      <c r="Y19" t="n">
+        <v>408.9261837758424</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>336717429.4957645</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>3.872646030629363e-07</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.9467052719556901</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-203.48</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2.73002e-07</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-83.694</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.3197724061545827</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.7992640451359035</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.667099980053784</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.35736918713577</v>
+      </c>
+      <c r="J20" t="n">
+        <v>33.04256991738124</v>
+      </c>
+      <c r="K20" t="n">
+        <v>87.36357714126802</v>
+      </c>
+      <c r="W20" t="n">
+        <v>19</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>y = 21.717x + -9633.625</t>
+        </is>
+      </c>
+      <c r="Y20" t="n">
+        <v>405.9261632735991</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>167472087.5035553</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>3.846101172966364e-07</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.9476994654770635</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-202.8820000000001</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2.7283e-07</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-83.73999999999999</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.1456315529338118</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.8252817968348364</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.68344162422929</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.325128961003513</v>
+      </c>
+      <c r="J21" t="n">
+        <v>33.18595231170661</v>
+      </c>
+      <c r="K21" t="n">
+        <v>87.37559569964908</v>
+      </c>
+      <c r="W21" t="n">
+        <v>20</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>y = 21.817x + -9599.512</t>
+        </is>
+      </c>
+      <c r="Y21" t="n">
+        <v>402.8799496509758</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>164336307.8858424</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>3.8283198706333e-07</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.948311996810812</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-202.72</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2.72657e-07</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-83.786</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.3344382195167493</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.8663366712060335</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.660336650775057</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2.628745819131058</v>
+      </c>
+      <c r="J22" t="n">
+        <v>34.60014319776201</v>
+      </c>
+      <c r="K22" t="n">
+        <v>87.39131217537374</v>
+      </c>
+      <c r="W22" t="n">
+        <v>21</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>y = 21.948x + -9575.315</t>
+        </is>
+      </c>
+      <c r="Y22" t="n">
+        <v>399.8123011185766</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>435006457.8718216</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>3.81027561082448e-07</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.9489411211194251</v>
       </c>
     </row>
   </sheetData>
@@ -1562,8 +5864,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1606,7 +5906,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1710,8 +6010,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1741,6 +6039,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-366.1239999999999</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2.90962e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-80.413</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.05632165463573149</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.6030178703272474</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.291296933946665</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.092727964739502</v>
+      </c>
+      <c r="J2" t="n">
+        <v>16.61522318530226</v>
+      </c>
+      <c r="K2" t="n">
+        <v>85.36780758400076</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 12.342x + -6748.483</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>481.3169627103698</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>16419334.8726047</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>5.669450557150221e-07</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8989682063270243</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-296.5</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2.84504e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-81.617</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.3018543265036266</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.7948109934005042</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.450497006712002</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.347110374287388</v>
+      </c>
+      <c r="J3" t="n">
+        <v>21.37036557361384</v>
+      </c>
+      <c r="K3" t="n">
+        <v>86.24270524471871</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 15.227x + -7954.308</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>468.5931932505256</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>159877891.2432903</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>4.873475088148432e-07</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.9182314914725673</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-273.1660000000001</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.81687e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-82.045</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.0543188916675581</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.9187364282398158</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.498707011918256</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.289753805255692</v>
+      </c>
+      <c r="J4" t="n">
+        <v>23.14132603398336</v>
+      </c>
+      <c r="K4" t="n">
+        <v>86.49591963575499</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 16.331x + -8381.350</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>442.0128795856027</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>3801.263534749723</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.062851142884898e-06</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.9015750434924876</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-257.358</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.80065e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-82.316</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.2822353297111492</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.9998832862542856</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.644037359117712</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.466855875220816</v>
+      </c>
+      <c r="J5" t="n">
+        <v>25.6597756595014</v>
+      </c>
+      <c r="K5" t="n">
+        <v>86.70390905726283</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 17.364x + -8819.308</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>458.1390253610684</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>250286990.6666235</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>4.477011926842336e-07</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.9286061019103289</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-247.627</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.78988e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-82.503</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.4369707905749145</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.9786950025844137</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.598157331735448</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.490136468821365</v>
+      </c>
+      <c r="J6" t="n">
+        <v>26.90238682115092</v>
+      </c>
+      <c r="K6" t="n">
+        <v>86.82408465951286</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 18.022x + -9051.571</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>453.4836180409301</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>185543068.2052857</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>4.378649357911211e-07</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.9313778756816655</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-238.378</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.78413e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-82.687</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.1281494067318574</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.7198944617762969</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.488134384064884</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.441531922837453</v>
+      </c>
+      <c r="J7" t="n">
+        <v>27.99171628122713</v>
+      </c>
+      <c r="K7" t="n">
+        <v>86.84822348474556</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 18.161x + -8990.707</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>449.0052073497969</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>122834849.4659618</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>4.295566039130984e-07</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.9339426762883472</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-237.4060000000001</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.77561e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-82.736</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.8914811866735203</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.257392073300633</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.862314840617542</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.422520428958181</v>
+      </c>
+      <c r="J8" t="n">
+        <v>27.77002464045712</v>
+      </c>
+      <c r="K8" t="n">
+        <v>87.07437942212684</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 19.567x + -9667.665</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>444.7540789640374</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>181863100.6548848</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>4.254248137776638e-07</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.9349760936115415</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-231.886</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.77305e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-82.873</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.3707102807844357</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.042678878766388</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.664121299461529</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.452585515216535</v>
+      </c>
+      <c r="J9" t="n">
+        <v>28.84182331349882</v>
+      </c>
+      <c r="K9" t="n">
+        <v>87.01837713022248</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 19.199x + -9336.990</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>440.9192743489919</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>163536237.4030253</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>4.197342568742096e-07</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.9368559410857729</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-228.221</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.76884e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-82.96899999999999</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.3011969081534984</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.064876016727608</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.729454618817764</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.321924199199953</v>
+      </c>
+      <c r="J10" t="n">
+        <v>29.13686104294803</v>
+      </c>
+      <c r="K10" t="n">
+        <v>87.05324217330423</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 19.427x + -9355.329</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>437.2768084047943</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>180768141.8999214</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>4.153048812850813e-07</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.9382300766782647</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-223.821</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.76525e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-83.074</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.1863187019911016</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.785036998776084</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.603038143482963</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.366914462988277</v>
+      </c>
+      <c r="J11" t="n">
+        <v>29.90548607814235</v>
+      </c>
+      <c r="K11" t="n">
+        <v>87.05817622417544</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 19.459x + -9268.528</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>433.926388333696</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>354594046.7493199</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>4.108080852274275e-07</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.939677337286614</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-219.738</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2.76262e-07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-83.155</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.2965496547716178</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.17144045888976</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.619530577406423</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.461145959607075</v>
+      </c>
+      <c r="J12" t="n">
+        <v>30.46447517675472</v>
+      </c>
+      <c r="K12" t="n">
+        <v>87.16366452366474</v>
+      </c>
+      <c r="W12" t="n">
+        <v>11</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>y = 20.184x + -9562.297</t>
+        </is>
+      </c>
+      <c r="Y12" t="n">
+        <v>430.7946570849169</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>176191282.6818075</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>4.07338253062954e-07</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.9408160193881694</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-216.857</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2.76021e-07</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-83.23</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.2612641244370062</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.8618077240652429</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.57390425567196</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2.491843768907402</v>
+      </c>
+      <c r="J13" t="n">
+        <v>31.51168575287774</v>
+      </c>
+      <c r="K13" t="n">
+        <v>87.15239682727612</v>
+      </c>
+      <c r="W13" t="n">
+        <v>12</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>y = 20.104x + -9433.777</t>
+        </is>
+      </c>
+      <c r="Y13" t="n">
+        <v>427.7582624629842</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>582235796.8971089</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>4.042887200040525e-07</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.941817274399396</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-214.232</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2.75885e-07</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-83.29600000000001</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.3627986000509496</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.006275397997277</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.489633957647103</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2.341879768411624</v>
+      </c>
+      <c r="J14" t="n">
+        <v>31.02200798893481</v>
+      </c>
+      <c r="K14" t="n">
+        <v>87.22555644851892</v>
+      </c>
+      <c r="W14" t="n">
+        <v>13</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>y = 20.635x + -9622.311</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
+        <v>424.742500254259</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>231370192.64752</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>4.016765652232231e-07</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.9427223175330037</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-221.498</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2.75449e-07</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-83.358</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.5284105134071867</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.645140983711813</v>
+      </c>
+      <c r="J15" t="n">
+        <v>28.54794017829548</v>
+      </c>
+      <c r="K15" t="n">
+        <v>86.68831508228989</v>
+      </c>
+      <c r="W15" t="n">
+        <v>14</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>y = 17.282x + -7835.620</t>
+        </is>
+      </c>
+      <c r="Y15" t="n">
+        <v>421.7272234711429</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>459203866.0416507</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>3.987137550482963e-07</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.9436113417893272</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-211.868</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2.75362e-07</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-83.404</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.2567416298007419</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.039574621431789</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.901466951544447</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.654389688558586</v>
+      </c>
+      <c r="J16" t="n">
+        <v>32.82564847444672</v>
+      </c>
+      <c r="K16" t="n">
+        <v>87.26625806343664</v>
+      </c>
+      <c r="W16" t="n">
+        <v>15</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>y = 20.943x + -9609.411</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>418.6073312970457</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>341638582.3541558</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>3.968436105843079e-07</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.9442829336644935</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-209.069</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2.75127e-07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-83.46299999999999</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.6545810269870269</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1.373625820132056</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.855074542768117</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2.859874240445463</v>
+      </c>
+      <c r="J17" t="n">
+        <v>33.53952021722319</v>
+      </c>
+      <c r="K17" t="n">
+        <v>87.36962013998401</v>
+      </c>
+      <c r="W17" t="n">
+        <v>16</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>y = 21.767x + -9943.823</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>415.4988262863592</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>678122195.9628119</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>3.944747448839126e-07</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.9450593510380562</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-208.9879999999999</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2.752e-07</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-83.532</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.01972741828231752</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.6329222072146139</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.359612831196749</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.342528833365068</v>
+      </c>
+      <c r="J18" t="n">
+        <v>31.92717052037846</v>
+      </c>
+      <c r="K18" t="n">
+        <v>87.20830633647073</v>
+      </c>
+      <c r="W18" t="n">
+        <v>17</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>y = 20.507x + -9214.628</t>
+        </is>
+      </c>
+      <c r="Y18" t="n">
+        <v>412.3408510988346</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1009164193.7573</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>3.922775108507422e-07</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.9459407386960953</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-201.794</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2.75054e-07</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-83.613</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.6193574318054983</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1.224288964249634</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.757157908479477</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2.812775319975381</v>
+      </c>
+      <c r="J19" t="n">
+        <v>34.53731380715769</v>
+      </c>
+      <c r="K19" t="n">
+        <v>87.43245571536816</v>
+      </c>
+      <c r="W19" t="n">
+        <v>18</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>y = 22.300x + -10016.940</t>
+        </is>
+      </c>
+      <c r="Y19" t="n">
+        <v>409.146220039869</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>111675322.944287</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>3.89463031729073e-07</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.9469428626333418</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-205.635</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2.74906e-07</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-83.65000000000001</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.06680426372917281</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.6254671828461726</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.558258670953845</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.418485407083224</v>
+      </c>
+      <c r="J20" t="n">
+        <v>33.6102473676049</v>
+      </c>
+      <c r="K20" t="n">
+        <v>87.24302465416277</v>
+      </c>
+      <c r="W20" t="n">
+        <v>19</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>y = 20.766x + -9168.850</t>
+        </is>
+      </c>
+      <c r="Y20" t="n">
+        <v>405.8704923241809</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>331483536.4798995</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>3.879106575621827e-07</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.9474793052485463</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-204.341</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2.74804e-07</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-83.673</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.5907969911891308</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1.248602594578701</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.661483957986553</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.549052190523509</v>
+      </c>
+      <c r="J21" t="n">
+        <v>33.20916565104123</v>
+      </c>
+      <c r="K21" t="n">
+        <v>87.42690252177401</v>
+      </c>
+      <c r="W21" t="n">
+        <v>20</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>y = 22.252x + -9813.809</t>
+        </is>
+      </c>
+      <c r="Y21" t="n">
+        <v>402.6115395092147</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>328927971.9372172</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>3.868962096896977e-07</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.9478246627882296</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-203.105</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2.74796e-07</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-83.76000000000001</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.6192578126582722</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.366398932951824</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2.324959367663667</v>
+      </c>
+      <c r="J22" t="n">
+        <v>33.37604744936927</v>
+      </c>
+      <c r="K22" t="n">
+        <v>87.27172274305212</v>
+      </c>
+      <c r="W22" t="n">
+        <v>21</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>y = 20.985x + -9099.908</t>
+        </is>
+      </c>
+      <c r="Y22" t="n">
+        <v>399.4009964319251</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>163014039.1037835</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>3.84126071669241e-07</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.948902603725772</v>
       </c>
     </row>
   </sheetData>
@@ -1754,7 +7144,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1858,8 +7248,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1889,6 +7277,526 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-493.3709999999999</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2.85579e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-78.413</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.2263665679697882</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.6638822971646808</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.293211094585357</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.919426546576553</v>
+      </c>
+      <c r="J2" t="n">
+        <v>12.17773641243749</v>
+      </c>
+      <c r="K2" t="n">
+        <v>84.08290098419012</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 9.649x + -5985.534</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>517.0072749278866</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>424364260.9700205</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>7.372089456214138e-07</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8567990274930191</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-369.8169999999999</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2.84088e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-80.55500000000001</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.551288982656042</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.208455215704146</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.165342448054973</v>
+      </c>
+      <c r="J3" t="n">
+        <v>16.81992527759554</v>
+      </c>
+      <c r="K3" t="n">
+        <v>85.38886327510725</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 12.399x + -6817.849</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>487.5256646728903</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>401099383.0753671</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>5.505983538172226e-07</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8996711595776918</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-316.712</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.80278e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-81.40900000000001</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.06199560623364564</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.7243401381040071</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.279808995644383</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.217647669909073</v>
+      </c>
+      <c r="J4" t="n">
+        <v>20.02949988549155</v>
+      </c>
+      <c r="K4" t="n">
+        <v>86.04545356274795</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 14.466x + -7736.705</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>477.6740464688352</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>264626087.1599844</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>4.957459364143968e-07</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.9133416400144007</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-290.949</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.77441e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-81.84999999999999</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.1304386430923389</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.8333450844142718</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.58987825015285</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.428335461406494</v>
+      </c>
+      <c r="J5" t="n">
+        <v>22.85414558827944</v>
+      </c>
+      <c r="K5" t="n">
+        <v>86.37443048586742</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 15.782x + -8310.461</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>470.9872411527926</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>257756903.5772153</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>4.690264968634016e-07</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.9201326074386598</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-272.147</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.75699e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-82.163</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.3225886190486932</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.9964592631470622</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.757523654227942</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.356567263269973</v>
+      </c>
+      <c r="J6" t="n">
+        <v>24.3758272005061</v>
+      </c>
+      <c r="K6" t="n">
+        <v>86.62510124543059</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 16.957x + -8818.705</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>464.8602776880605</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>254079897.3065849</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>4.517866403552614e-07</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.9248175910051529</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-261.033</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.74648e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-82.39400000000001</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.540467568610694</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.127642102626859</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.53951753724565</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.347522683678398</v>
+      </c>
+      <c r="J7" t="n">
+        <v>25.41078565163649</v>
+      </c>
+      <c r="K7" t="n">
+        <v>86.73955288943954</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 17.554x + -8990.702</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>440.5670897046683</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>3760.852508810734</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.58174486006174e-06</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8362733134808182</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-249.523</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.7384e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-82.613</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.3803279486330484</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.010963154993154</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.642251469051127</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.451493371399361</v>
+      </c>
+      <c r="J8" t="n">
+        <v>27.78480334468127</v>
+      </c>
+      <c r="K8" t="n">
+        <v>86.83360894459653</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 18.077x + -9110.545</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>452.7456342089746</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>246904518.6869225</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>4.294520224850721e-07</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.9314217339739586</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-251.2169999999999</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.73324e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-82.708</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.1068662504930662</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.7170961197232232</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.338398208661787</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.16448637641308</v>
+      </c>
+      <c r="J9" t="n">
+        <v>26.71414690001193</v>
+      </c>
+      <c r="K9" t="n">
+        <v>86.75578467338379</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 17.642x + -8721.405</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>447.0348010388421</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>121838407.0186928</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>4.240480861238635e-07</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.9330733490802984</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-244.867</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.73061e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-82.834</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.4841724412663034</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.8789033583930339</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.561033290041177</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.231645556879763</v>
+      </c>
+      <c r="J10" t="n">
+        <v>27.03093700069163</v>
+      </c>
+      <c r="K10" t="n">
+        <v>86.88368510113125</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 18.368x + -8980.525</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>441.8132763859897</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>126501952.0246875</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>4.183775092728076e-07</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.9349609149016714</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-238.592</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.72774e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-82.97799999999999</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.08315385594277053</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.7646753249610921</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.466099350365916</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.373176587681221</v>
+      </c>
+      <c r="J11" t="n">
+        <v>28.8931875628394</v>
+      </c>
+      <c r="K11" t="n">
+        <v>86.86890944232314</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 18.281x + -8798.414</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>437.2092957584164</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>357233911.4357943</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>4.123806631877916e-07</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.9369762446723572</v>
       </c>
     </row>
   </sheetData>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 45.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 45.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -528,12 +528,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -543,7 +543,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -555,6 +555,526 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-273.0309999999999</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2.64063e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-82.324</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.4924579293767634</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.000017234335748</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.556010042998564</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.39825309898576</v>
+      </c>
+      <c r="J2" t="n">
+        <v>25.68537325146842</v>
+      </c>
+      <c r="K2" t="n">
+        <v>86.78874740645739</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>y = 17.824x + -9599.322</t>
+        </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-9599.322190146206</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>479.6053667238517</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>273.0309999999999</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>4.26998522159083e-07</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.9268023972871524</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-253.042</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2.631e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-82.649</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.407323822046795</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.9823134680563622</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.596583349940528</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.523729445795916</v>
+      </c>
+      <c r="J3" t="n">
+        <v>28.66566303413096</v>
+      </c>
+      <c r="K3" t="n">
+        <v>86.94581505152189</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>y = 18.742x + -9898.387</t>
+        </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-9898.387345826271</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>451.5456264712489</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>253.042</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.643783049026739e-06</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8272660883542078</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-244.425</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.6245e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-82.824</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.3142806937342108</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.9343354005925628</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.48290245110116</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.273660235496234</v>
+      </c>
+      <c r="J4" t="n">
+        <v>29.27699521926877</v>
+      </c>
+      <c r="K4" t="n">
+        <v>87.01709364146427</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>y = 19.191x + -9985.675</t>
+        </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-9985.674568337905</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>446.2200620584686</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>244.425</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.351528210561691e-06</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8650685767984596</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-237.049</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.62147e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-82.971</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.3739565358041708</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.8913275871117444</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.557116324463475</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.389893365360842</v>
+      </c>
+      <c r="J5" t="n">
+        <v>30.37546324776115</v>
+      </c>
+      <c r="K5" t="n">
+        <v>87.09139200699965</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>y = 19.682x + -10105.935</t>
+        </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-10105.93471235811</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>444.7545958425873</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>237.049</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>3.588868257132026e-07</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.9999755699729936</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-232.828</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.61719e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-83.101</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.1972190940341653</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.7763665983516556</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.288509687719331</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.056046379524496</v>
+      </c>
+      <c r="J6" t="n">
+        <v>30.40908416249143</v>
+      </c>
+      <c r="K6" t="n">
+        <v>87.05450951659333</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>y = 19.435x + -9813.146</t>
+        </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-9813.14555680553</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>457.025911920714</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>232.828</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>3.916622015651721e-07</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.9384871503513036</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-226.1440000000001</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.61617e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-83.221</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.2593616930651583</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.8290005632814033</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.408463332803359</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.172567118839585</v>
+      </c>
+      <c r="J7" t="n">
+        <v>31.3206243398632</v>
+      </c>
+      <c r="K7" t="n">
+        <v>87.196205066275</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>y = 20.419x + -10212.241</t>
+        </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-10212.2407737871</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>452.1017489174236</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>226.1440000000001</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>3.870928133099566e-07</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.940198540333773</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-222.697</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.61431e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-83.304</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.6319168900716478</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.8630939836095451</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.493971249342138</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.44281625196101</v>
+      </c>
+      <c r="J8" t="n">
+        <v>32.69220281666847</v>
+      </c>
+      <c r="K8" t="n">
+        <v>87.27092498551941</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>y = 20.979x + -10390.983</t>
+        </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-10390.98297151223</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>447.5255461435086</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>222.697</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>3.837286484855732e-07</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.9414129971822996</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-232.307</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.6122e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-83.35299999999999</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.7986966776689637</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.791538494521635</v>
+      </c>
+      <c r="J9" t="n">
+        <v>30.10285341389156</v>
+      </c>
+      <c r="K9" t="n">
+        <v>86.75953266883968</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>y = 17.662x + -8486.175</t>
+        </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-8486.174645203593</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>443.1919386320271</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>232.307</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>3.8122141057872e-07</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.9423048378955623</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-223.849</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.61242e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-83.407</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.1202899337352879</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.000500774910222</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.456274285465032</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.337962751536113</v>
+      </c>
+      <c r="J10" t="n">
+        <v>32.18886212165614</v>
+      </c>
+      <c r="K10" t="n">
+        <v>87.24643305816566</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>y = 20.792x + -10047.856</t>
+        </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-10047.85629252543</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>438.9914340641202</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>223.849</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>3.792017074982107e-07</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.943130388630344</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-217.3030000000001</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.61085e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-83.509</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.2858294528696655</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.9502442901448466</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.518586120627437</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.44874768511965</v>
+      </c>
+      <c r="J11" t="n">
+        <v>33.15944773050924</v>
+      </c>
+      <c r="K11" t="n">
+        <v>87.36798349326666</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>y = 21.753x + -10438.648</t>
+        </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-10438.64831531955</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>435.0729141741307</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>217.3030000000001</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>3.755259302377786e-07</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.9445047767300254</v>
       </c>
     </row>
   </sheetData>
@@ -674,12 +1194,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -689,7 +1209,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -734,19 +1254,19 @@
       <c r="K2" t="n">
         <v>86.23659232903233</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 15.203x + -8360.981</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-8360.98103653289</v>
       </c>
       <c r="Y2" t="n">
         <v>480.9179802226254</v>
       </c>
       <c r="Z2" t="n">
-        <v>32722752.40087609</v>
+        <v>302.203</v>
       </c>
       <c r="AA2" t="n">
         <v>4.76354489356448e-07</v>
@@ -786,19 +1306,19 @@
       <c r="K3" t="n">
         <v>86.70513271440362</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 17.370x + -9099.215</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-9099.215171842827</v>
       </c>
       <c r="Y3" t="n">
         <v>467.4573120364058</v>
       </c>
       <c r="Z3" t="n">
-        <v>184552953.7433971</v>
+        <v>264.968</v>
       </c>
       <c r="AA3" t="n">
         <v>4.383445486220268e-07</v>
@@ -838,19 +1358,19 @@
       <c r="K4" t="n">
         <v>86.68945551792773</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 17.288x + -8852.895</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-8852.895054964198</v>
       </c>
       <c r="Y4" t="n">
         <v>454.0172810323862</v>
       </c>
       <c r="Z4" t="n">
-        <v>3786.052574500075</v>
+        <v>259.959</v>
       </c>
       <c r="AA4" t="n">
         <v>1.329909910929096e-06</v>
@@ -890,19 +1410,19 @@
       <c r="K5" t="n">
         <v>86.9522145457658</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 18.781x + -9578.119</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-9578.119360771974</v>
       </c>
       <c r="Y5" t="n">
         <v>437.8876006493587</v>
       </c>
       <c r="Z5" t="n">
-        <v>3750.519568057159</v>
+        <v>249.0699999999999</v>
       </c>
       <c r="AA5" t="n">
         <v>1.369126947661995e-06</v>
@@ -942,19 +1462,19 @@
       <c r="K6" t="n">
         <v>87.00985416806904</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 19.144x + -9651.182</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-9651.181865898097</v>
       </c>
       <c r="Y6" t="n">
         <v>452.6898605286162</v>
       </c>
       <c r="Z6" t="n">
-        <v>372708633.2520003</v>
+        <v>242.599</v>
       </c>
       <c r="AA6" t="n">
         <v>4.145001707610471e-07</v>
@@ -994,19 +1514,19 @@
       <c r="K7" t="n">
         <v>86.9539854200394</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 18.792x + -9335.074</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-9335.073827635899</v>
       </c>
       <c r="Y7" t="n">
         <v>448.2409320277739</v>
       </c>
       <c r="Z7" t="n">
-        <v>213847128.618784</v>
+        <v>243.597</v>
       </c>
       <c r="AA7" t="n">
         <v>4.107660705107558e-07</v>
@@ -1046,19 +1566,19 @@
       <c r="K8" t="n">
         <v>86.97806735020897</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 18.942x + -9296.229</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-9296.228995134883</v>
       </c>
       <c r="Y8" t="n">
         <v>443.9565030544216</v>
       </c>
       <c r="Z8" t="n">
-        <v>181463160.9333132</v>
+        <v>239.779</v>
       </c>
       <c r="AA8" t="n">
         <v>4.064278669403648e-07</v>
@@ -1098,19 +1618,19 @@
       <c r="K9" t="n">
         <v>86.92254155876262</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 18.600x + -9000.956</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-9000.956083669631</v>
       </c>
       <c r="Y9" t="n">
         <v>439.8959858391522</v>
       </c>
       <c r="Z9" t="n">
-        <v>239754015.1150077</v>
+        <v>240.252</v>
       </c>
       <c r="AA9" t="n">
         <v>4.030579782766424e-07</v>
@@ -1150,19 +1670,19 @@
       <c r="K10" t="n">
         <v>87.11025620574966</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 19.810x + -9552.484</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-9552.484276580579</v>
       </c>
       <c r="Y10" t="n">
         <v>436.1400784512594</v>
       </c>
       <c r="Z10" t="n">
-        <v>178248817.8884017</v>
+        <v>234.1440000000001</v>
       </c>
       <c r="AA10" t="n">
         <v>3.991627777082239e-07</v>
@@ -1202,19 +1722,19 @@
       <c r="K11" t="n">
         <v>87.0544119031679</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 19.434x + -9255.033</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-9255.033440822186</v>
       </c>
       <c r="Y11" t="n">
         <v>432.6308624506758</v>
       </c>
       <c r="Z11" t="n">
-        <v>118712714.3928932</v>
+        <v>235.8550000000001</v>
       </c>
       <c r="AA11" t="n">
         <v>3.972024883721081e-07</v>
@@ -1254,19 +1774,19 @@
       <c r="K12" t="n">
         <v>87.11923817397374</v>
       </c>
-      <c r="W12" t="n">
-        <v>11</v>
-      </c>
-      <c r="X12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>y = 19.872x + -9391.599</t>
         </is>
+      </c>
+      <c r="X12" t="n">
+        <v>-9391.598627738556</v>
       </c>
       <c r="Y12" t="n">
         <v>429.2544068328343</v>
       </c>
       <c r="Z12" t="n">
-        <v>117731880.7618263</v>
+        <v>232.321</v>
       </c>
       <c r="AA12" t="n">
         <v>3.941020955067442e-07</v>
@@ -1306,19 +1826,19 @@
       <c r="K13" t="n">
         <v>87.23740857856555</v>
       </c>
-      <c r="W13" t="n">
-        <v>12</v>
-      </c>
-      <c r="X13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>y = 20.724x + -9755.401</t>
         </is>
+      </c>
+      <c r="X13" t="n">
+        <v>-9755.401357545546</v>
       </c>
       <c r="Y13" t="n">
         <v>426.0092985316125</v>
       </c>
       <c r="Z13" t="n">
-        <v>115910342.4364102</v>
+        <v>229.193</v>
       </c>
       <c r="AA13" t="n">
         <v>3.916201313707369e-07</v>
@@ -1358,19 +1878,19 @@
       <c r="K14" t="n">
         <v>87.29760709754886</v>
       </c>
-      <c r="W14" t="n">
-        <v>13</v>
-      </c>
-      <c r="X14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>y = 21.186x + -9907.356</t>
         </is>
+      </c>
+      <c r="X14" t="n">
+        <v>-9907.355670692714</v>
       </c>
       <c r="Y14" t="n">
         <v>422.7582751157986</v>
       </c>
       <c r="Z14" t="n">
-        <v>115113235.4057532</v>
+        <v>226.787</v>
       </c>
       <c r="AA14" t="n">
         <v>3.894681968248368e-07</v>
@@ -1410,19 +1930,19 @@
       <c r="K15" t="n">
         <v>87.14788086539058</v>
       </c>
-      <c r="W15" t="n">
-        <v>14</v>
-      </c>
-      <c r="X15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>y = 20.072x + -9230.947</t>
         </is>
+      </c>
+      <c r="X15" t="n">
+        <v>-9230.947039114715</v>
       </c>
       <c r="Y15" t="n">
         <v>419.5445726516589</v>
       </c>
       <c r="Z15" t="n">
-        <v>228489614.6300777</v>
+        <v>228.5439999999999</v>
       </c>
       <c r="AA15" t="n">
         <v>3.870198928759991e-07</v>
@@ -1462,19 +1982,19 @@
       <c r="K16" t="n">
         <v>87.11724320036751</v>
       </c>
-      <c r="W16" t="n">
-        <v>15</v>
-      </c>
-      <c r="X16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>y = 19.859x + -9039.395</t>
         </is>
+      </c>
+      <c r="X16" t="n">
+        <v>-9039.394937021554</v>
       </c>
       <c r="Y16" t="n">
         <v>416.4026218088894</v>
       </c>
       <c r="Z16" t="n">
-        <v>113897961.7652397</v>
+        <v>227.6300000000001</v>
       </c>
       <c r="AA16" t="n">
         <v>3.852111742265167e-07</v>
@@ -1514,19 +2034,19 @@
       <c r="K17" t="n">
         <v>87.32277914582281</v>
       </c>
-      <c r="W17" t="n">
-        <v>16</v>
-      </c>
-      <c r="X17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>y = 21.386x + -9725.303</t>
         </is>
+      </c>
+      <c r="X17" t="n">
+        <v>-9725.303200891476</v>
       </c>
       <c r="Y17" t="n">
         <v>413.2448694439817</v>
       </c>
       <c r="Z17" t="n">
-        <v>225034438.3059394</v>
+        <v>220.461</v>
       </c>
       <c r="AA17" t="n">
         <v>3.824649422397493e-07</v>
@@ -1566,19 +2086,19 @@
       <c r="K18" t="n">
         <v>87.28332486828249</v>
       </c>
-      <c r="W18" t="n">
-        <v>17</v>
-      </c>
-      <c r="X18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>y = 21.075x + -9479.464</t>
         </is>
+      </c>
+      <c r="X18" t="n">
+        <v>-9479.464339063117</v>
       </c>
       <c r="Y18" t="n">
         <v>410.0939754555842</v>
       </c>
       <c r="Z18" t="n">
-        <v>111547416.8222765</v>
+        <v>220.907</v>
       </c>
       <c r="AA18" t="n">
         <v>3.80791102093921e-07</v>
@@ -1618,19 +2138,19 @@
       <c r="K19" t="n">
         <v>87.35643336487306</v>
       </c>
-      <c r="W19" t="n">
-        <v>18</v>
-      </c>
-      <c r="X19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>y = 21.658x + -9689.716</t>
         </is>
+      </c>
+      <c r="X19" t="n">
+        <v>-9689.716375442036</v>
       </c>
       <c r="Y19" t="n">
         <v>406.9299068987231</v>
       </c>
       <c r="Z19" t="n">
-        <v>166188766.2632105</v>
+        <v>220.714</v>
       </c>
       <c r="AA19" t="n">
         <v>3.795864383290239e-07</v>
@@ -1670,19 +2190,19 @@
       <c r="K20" t="n">
         <v>87.23143930517391</v>
       </c>
-      <c r="W20" t="n">
-        <v>19</v>
-      </c>
-      <c r="X20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>y = 20.679x + -9112.604</t>
         </is>
+      </c>
+      <c r="X20" t="n">
+        <v>-9112.604359247525</v>
       </c>
       <c r="Y20" t="n">
         <v>403.8097827662983</v>
       </c>
       <c r="Z20" t="n">
-        <v>110186319.4424782</v>
+        <v>220.716</v>
       </c>
       <c r="AA20" t="n">
         <v>3.773386297485312e-07</v>
@@ -1722,19 +2242,19 @@
       <c r="K21" t="n">
         <v>87.32353763478508</v>
       </c>
-      <c r="W21" t="n">
-        <v>20</v>
-      </c>
-      <c r="X21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>y = 21.392x + -9365.318</t>
         </is>
+      </c>
+      <c r="X21" t="n">
+        <v>-9365.318451994282</v>
       </c>
       <c r="Y21" t="n">
         <v>400.5999790302465</v>
       </c>
       <c r="Z21" t="n">
-        <v>174014444.5471484</v>
+        <v>215.333</v>
       </c>
       <c r="AA21" t="n">
         <v>3.749404704529664e-07</v>
@@ -1774,19 +2294,19 @@
       <c r="K22" t="n">
         <v>87.38723037836647</v>
       </c>
-      <c r="W22" t="n">
-        <v>21</v>
-      </c>
-      <c r="X22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>y = 21.914x + -9532.753</t>
         </is>
+      </c>
+      <c r="X22" t="n">
+        <v>-9532.753076700101</v>
       </c>
       <c r="Y22" t="n">
         <v>397.4150777577553</v>
       </c>
       <c r="Z22" t="n">
-        <v>108186090.8757237</v>
+        <v>213.279</v>
       </c>
       <c r="AA22" t="n">
         <v>3.73254825807647e-07</v>
@@ -1806,7 +2326,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1912,12 +2432,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -1927,7 +2447,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -1939,6 +2459,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-347.697</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2.76249e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-80.96899999999999</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.04343039752405262</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.8418040515083883</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.314491415637336</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.038407936820749</v>
+      </c>
+      <c r="J2" t="n">
+        <v>18.18260956816588</v>
+      </c>
+      <c r="K2" t="n">
+        <v>85.87600810476651</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>y = 13.869x + -7751.373</t>
+        </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-7751.373462847805</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>489.3266483925309</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>347.697</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>5.117874468168567e-07</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.9064835283478637</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-271.207</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2.69663e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-82.26900000000001</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.1914147981042067</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.8150916579859183</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.315918381934325</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.255889295085648</v>
+      </c>
+      <c r="J3" t="n">
+        <v>25.20742870161399</v>
+      </c>
+      <c r="K3" t="n">
+        <v>86.68721616396195</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>y = 17.276x + -9142.691</t>
+        </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-9142.691276745545</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>473.6761094560357</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>271.207</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>4.361934590012305e-07</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.9268027198490548</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-245.1329999999999</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.67466e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-82.681</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.2646475862435225</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.8565699563484701</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.522194353988355</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.446073873217861</v>
+      </c>
+      <c r="J4" t="n">
+        <v>28.77049235878962</v>
+      </c>
+      <c r="K4" t="n">
+        <v>86.97475332453027</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>y = 18.922x + -9826.408</t>
+        </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-9826.40835573673</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>443.9702341850466</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>245.1329999999999</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.663103739688245e-06</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8227840406122269</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-233.96</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.66165e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-82.895</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.3351661003685886</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.8756985218762945</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.568373431022961</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.506700597572104</v>
+      </c>
+      <c r="J5" t="n">
+        <v>30.56301410612685</v>
+      </c>
+      <c r="K5" t="n">
+        <v>87.10637500562872</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>y = 19.784x + -10144.972</t>
+        </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-10144.97169018693</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>461.9480378828465</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>233.96</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>4.05022007432776e-07</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.9359848204513325</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-226.484</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.65327e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-83.065</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.1508564917214077</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.799194061895109</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.418053411067973</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.272384411112472</v>
+      </c>
+      <c r="J6" t="n">
+        <v>31.22483142127902</v>
+      </c>
+      <c r="K6" t="n">
+        <v>87.093586354596</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>y = 19.697x + -9944.378</t>
+        </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-9944.378389610323</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>457.2780540802589</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>226.484</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>3.974253091366641e-07</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.9383576063960247</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-225.373</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.64548e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-83.139</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.2463480940070178</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.9326952380695922</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.429578443016108</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.372350245621452</v>
+      </c>
+      <c r="J7" t="n">
+        <v>31.30864612221542</v>
+      </c>
+      <c r="K7" t="n">
+        <v>87.208357009784</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>y = 20.508x + -10269.293</t>
+        </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-10269.29342203443</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>452.8080354240732</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>225.373</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>3.930978807543943e-07</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.9395936313795407</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-223.033</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.64146e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-83.236</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.105649314740603</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.625763532184045</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.355536378971123</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.164654493749005</v>
+      </c>
+      <c r="J8" t="n">
+        <v>31.128494022466</v>
+      </c>
+      <c r="K8" t="n">
+        <v>87.15669685568162</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>y = 20.135x + -9938.274</t>
+        </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-9938.273876717878</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>448.5791766810402</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>223.033</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>3.888280687482529e-07</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.9410154735253821</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-214.4809999999999</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.63749e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-83.346</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.4360353487768501</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.120755714236871</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.501267766137637</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.447572537638714</v>
+      </c>
+      <c r="J9" t="n">
+        <v>32.95742830739476</v>
+      </c>
+      <c r="K9" t="n">
+        <v>87.39384097181849</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>y = 21.970x + -10810.293</t>
+        </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-10810.29347620989</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>444.5332927489689</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>214.4809999999999</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>3.844328084949008e-07</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.9425036085232681</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-213.393</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.63693e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-83.42400000000001</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.4194633037955159</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.8070032550269018</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.533721079263632</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.586691077604846</v>
+      </c>
+      <c r="J10" t="n">
+        <v>34.42595728458807</v>
+      </c>
+      <c r="K10" t="n">
+        <v>87.33204245290545</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>y = 21.460x + -10413.433</t>
+        </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-10413.43311909305</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>440.5873702632053</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>213.393</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>3.815704047326536e-07</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.9435980953403028</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-209.535</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.63424e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-83.505</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.3467271827384857</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.9828524000414398</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.640047320023245</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.434250549018704</v>
+      </c>
+      <c r="J11" t="n">
+        <v>34.5404099508481</v>
+      </c>
+      <c r="K11" t="n">
+        <v>87.42074980966801</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>y = 22.199x + -10691.841</t>
+        </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-10691.8405558676</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>436.8161075249475</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>209.535</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>3.783203121129007e-07</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.9447429738066498</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-208.582</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2.63247e-07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-83.556</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.4731264239234456</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.152051875921184</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.74960963116658</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.73274829544289</v>
+      </c>
+      <c r="J12" t="n">
+        <v>35.06571559413162</v>
+      </c>
+      <c r="K12" t="n">
+        <v>87.46809368424151</v>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>y = 22.615x + -10800.427</t>
+        </is>
+      </c>
+      <c r="X12" t="n">
+        <v>-10800.42748218264</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>433.1057700019758</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>208.582</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>3.76118759844843e-07</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.9455323355146705</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-213.7740000000001</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2.6306e-07</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-83.574</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.2326338549762718</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.6982633161749783</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.307001351254357</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2.189353317246665</v>
+      </c>
+      <c r="J13" t="n">
+        <v>32.80302195309584</v>
+      </c>
+      <c r="K13" t="n">
+        <v>87.34812609311159</v>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>y = 21.590x + -10161.857</t>
+        </is>
+      </c>
+      <c r="X13" t="n">
+        <v>-10161.85739058252</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>429.4439812672068</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>213.7740000000001</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>3.749219490547249e-07</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.9459274276735616</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-206.2859999999999</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2.6299e-07</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-83.66200000000001</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.6826025157403757</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.156997170608582</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.916585457249574</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2.980092831894027</v>
+      </c>
+      <c r="J14" t="n">
+        <v>35.58622275389752</v>
+      </c>
+      <c r="K14" t="n">
+        <v>87.54149542254061</v>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>y = 23.291x + -10932.964</t>
+        </is>
+      </c>
+      <c r="X14" t="n">
+        <v>-10932.96353878005</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>425.9360495064776</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>206.2859999999999</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>3.720419380982052e-07</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.9470460350531218</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-210.5310000000001</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2.62701e-07</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-83.7</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.8436189222789908</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.499790380353879</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.287454373889161</v>
+      </c>
+      <c r="J15" t="n">
+        <v>33.92203510076359</v>
+      </c>
+      <c r="K15" t="n">
+        <v>87.37337984018964</v>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>y = 21.798x + -10062.847</t>
+        </is>
+      </c>
+      <c r="X15" t="n">
+        <v>-10062.84740667248</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>422.5053683915358</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>210.5310000000001</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>3.700733224478628e-07</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.9477029872925168</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-206.84</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2.62774e-07</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-83.77200000000001</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.1429580418353057</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.7701281964330922</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.374109121272471</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.28657479494855</v>
+      </c>
+      <c r="J16" t="n">
+        <v>34.64877437114263</v>
+      </c>
+      <c r="K16" t="n">
+        <v>87.41554703304374</v>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>y = 22.154x + -10140.976</t>
+        </is>
+      </c>
+      <c r="X16" t="n">
+        <v>-10140.97625424357</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>419.1506147717284</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>206.84</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>3.680147787927724e-07</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.9485785014736785</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-212.756</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2.62665e-07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-83.81999999999999</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.6061579902784883</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.729433694712073</v>
+      </c>
+      <c r="J17" t="n">
+        <v>32.14037607902404</v>
+      </c>
+      <c r="K17" t="n">
+        <v>87.00610323156411</v>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>y = 19.120x + -8545.573</t>
+        </is>
+      </c>
+      <c r="X17" t="n">
+        <v>-8545.572680046193</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>415.8752996081886</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>212.756</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>3.662335020716312e-07</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.949257850232058</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-202.6950000000001</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2.62561e-07</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-83.878</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.3912048887978243</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.8700773857977739</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.657233547782414</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.501819561359755</v>
+      </c>
+      <c r="J18" t="n">
+        <v>35.6105177428725</v>
+      </c>
+      <c r="K18" t="n">
+        <v>87.54195876112072</v>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>y = 23.295x + -10518.961</t>
+        </is>
+      </c>
+      <c r="X18" t="n">
+        <v>-10518.96137799515</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>412.6466910559025</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>202.6950000000001</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>3.643023645097892e-07</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.9499978075269191</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-201.413</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2.62665e-07</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-83.913</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.5333541823910142</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1.075086740893133</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.811626083946722</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2.572617737686896</v>
+      </c>
+      <c r="J19" t="n">
+        <v>35.61814551247041</v>
+      </c>
+      <c r="K19" t="n">
+        <v>87.61957944655116</v>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>y = 24.056x + -10802.088</t>
+        </is>
+      </c>
+      <c r="X19" t="n">
+        <v>-10802.08755314234</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>409.4551609776633</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>201.413</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>3.633735453588941e-07</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.9504444312633231</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-202.188</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2.62544e-07</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-83.959</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.2908092961987711</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.8500583952511908</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.679482118302269</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.599995524394957</v>
+      </c>
+      <c r="J20" t="n">
+        <v>36.11289913370867</v>
+      </c>
+      <c r="K20" t="n">
+        <v>87.54282346394551</v>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>y = 23.303x + -10333.879</t>
+        </is>
+      </c>
+      <c r="X20" t="n">
+        <v>-10333.87876575362</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>406.3600839261352</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>202.188</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>3.617354002147274e-07</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.9510637144779559</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-201.159</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2.62416e-07</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-84.01300000000001</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.1072777898928834</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.7640302041180881</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.46361278669187</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.205173163820537</v>
+      </c>
+      <c r="J21" t="n">
+        <v>35.41312290823187</v>
+      </c>
+      <c r="K21" t="n">
+        <v>87.52906141133336</v>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>y = 23.173x + -10176.646</t>
+        </is>
+      </c>
+      <c r="X21" t="n">
+        <v>-10176.64596798434</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>403.2808176775151</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>201.159</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>3.599258221389223e-07</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.9517534265592323</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-203.246</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2.62309e-07</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-84.02</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.2293604959594025</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.8844101444669695</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.560549621133494</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2.407839855706039</v>
+      </c>
+      <c r="J22" t="n">
+        <v>34.74501701540667</v>
+      </c>
+      <c r="K22" t="n">
+        <v>87.58295513147668</v>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>y = 23.691x + -10345.331</t>
+        </is>
+      </c>
+      <c r="X22" t="n">
+        <v>-10345.33052685845</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>400.2005045956716</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>203.246</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>3.594996674257935e-07</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.9518836743788911</v>
       </c>
     </row>
   </sheetData>
@@ -2058,12 +3670,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -2073,7 +3685,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -2118,19 +3730,19 @@
       <c r="K2" t="n">
         <v>84.60611152146957</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 10.591x + -6757.919</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-6757.919165589063</v>
       </c>
       <c r="Y2" t="n">
         <v>536.6848260996646</v>
       </c>
       <c r="Z2" t="n">
-        <v>589286338.9800715</v>
+        <v>460.1</v>
       </c>
       <c r="AA2" t="n">
         <v>6.871695977063213e-07</v>
@@ -2170,19 +3782,19 @@
       <c r="K3" t="n">
         <v>85.66777575705275</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 13.200x + -7718.584</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-7718.58434488335</v>
       </c>
       <c r="Y3" t="n">
         <v>512.4986315999361</v>
       </c>
       <c r="Z3" t="n">
-        <v>48174490.39845841</v>
+        <v>364.144</v>
       </c>
       <c r="AA3" t="n">
         <v>5.584673222971136e-07</v>
@@ -2222,19 +3834,19 @@
       <c r="K4" t="n">
         <v>86.06107784966113</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 14.523x + -8224.408</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-8224.407501363354</v>
       </c>
       <c r="Y4" t="n">
         <v>503.443943654204</v>
       </c>
       <c r="Z4" t="n">
-        <v>37943666.38081218</v>
+        <v>319.514</v>
       </c>
       <c r="AA4" t="n">
         <v>5.082483036017803e-07</v>
@@ -2274,19 +3886,19 @@
       <c r="K5" t="n">
         <v>86.35405494977601</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 15.694x + -8750.737</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-8750.737407184411</v>
       </c>
       <c r="Y5" t="n">
         <v>497.1263969792354</v>
       </c>
       <c r="Z5" t="n">
-        <v>36136651.60595468</v>
+        <v>292.909</v>
       </c>
       <c r="AA5" t="n">
         <v>4.812910557211444e-07</v>
@@ -2326,19 +3938,19 @@
       <c r="K6" t="n">
         <v>86.56163916493065</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 16.644x + -9159.621</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-9159.621420920957</v>
       </c>
       <c r="Y6" t="n">
         <v>491.2163573691311</v>
       </c>
       <c r="Z6" t="n">
-        <v>134309084.697485</v>
+        <v>277.218</v>
       </c>
       <c r="AA6" t="n">
         <v>4.631455767424235e-07</v>
@@ -2378,19 +3990,19 @@
       <c r="K7" t="n">
         <v>86.62097055897429</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 16.937x + -9169.790</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-9169.78964253145</v>
       </c>
       <c r="Y7" t="n">
         <v>485.4364083442069</v>
       </c>
       <c r="Z7" t="n">
-        <v>265477180.1549042</v>
+        <v>267.169</v>
       </c>
       <c r="AA7" t="n">
         <v>4.500455495922638e-07</v>
@@ -2430,19 +4042,19 @@
       <c r="K8" t="n">
         <v>86.88720245361314</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 18.388x + -9885.402</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-9885.402018134655</v>
       </c>
       <c r="Y8" t="n">
         <v>479.7942909356152</v>
       </c>
       <c r="Z8" t="n">
-        <v>131023940.34062</v>
+        <v>255.1600000000001</v>
       </c>
       <c r="AA8" t="n">
         <v>4.389724878764684e-07</v>
@@ -2482,19 +4094,19 @@
       <c r="K9" t="n">
         <v>86.74861304721674</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 17.603x + -9258.924</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-9258.92408894535</v>
       </c>
       <c r="Y9" t="n">
         <v>464.4180728158482</v>
       </c>
       <c r="Z9" t="n">
-        <v>3892.381706851974</v>
+        <v>251.974</v>
       </c>
       <c r="AA9" t="n">
         <v>1.172201301024176e-06</v>
@@ -2534,19 +4146,19 @@
       <c r="K10" t="n">
         <v>86.80272453991049</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 17.902x + -9296.457</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-9296.456844935376</v>
       </c>
       <c r="Y10" t="n">
         <v>450.9331247486803</v>
       </c>
       <c r="Z10" t="n">
-        <v>3850.192004271824</v>
+        <v>247.93</v>
       </c>
       <c r="AA10" t="n">
         <v>9.042976841967091e-07</v>
@@ -2586,19 +4198,19 @@
       <c r="K11" t="n">
         <v>87.04481260445652</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 19.371x + -10002.052</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-10002.05164744971</v>
       </c>
       <c r="Y11" t="n">
         <v>451.1993374767339</v>
       </c>
       <c r="Z11" t="n">
-        <v>7672.813938747323</v>
+        <v>235.55</v>
       </c>
       <c r="AA11" t="n">
         <v>3.584885292294679e-07</v>
@@ -2724,12 +4336,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -2739,7 +4351,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -2784,19 +4396,19 @@
       <c r="K2" t="n">
         <v>85.95626256722102</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 14.145x + -7763.767</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-7763.767418940207</v>
       </c>
       <c r="Y2" t="n">
         <v>480.2951757214407</v>
       </c>
       <c r="Z2" t="n">
-        <v>58206032.58323675</v>
+        <v>332.0350000000001</v>
       </c>
       <c r="AA2" t="n">
         <v>4.992013584057573e-07</v>
@@ -2836,19 +4448,19 @@
       <c r="K3" t="n">
         <v>86.48127321041933</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 16.263x + -8434.634</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-8434.634266655097</v>
       </c>
       <c r="Y3" t="n">
         <v>466.0520934308912</v>
       </c>
       <c r="Z3" t="n">
-        <v>516752350.111385</v>
+        <v>280.237</v>
       </c>
       <c r="AA3" t="n">
         <v>4.480406649797358e-07</v>
@@ -2888,19 +4500,19 @@
       <c r="K4" t="n">
         <v>86.78649210241561</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 17.811x + -9104.597</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-9104.597151980255</v>
       </c>
       <c r="Y4" t="n">
         <v>440.2287237932851</v>
       </c>
       <c r="Z4" t="n">
-        <v>3771.878876273001</v>
+        <v>257.74</v>
       </c>
       <c r="AA4" t="n">
         <v>9.89915647613028e-07</v>
@@ -2940,19 +4552,19 @@
       <c r="K5" t="n">
         <v>86.35824109805462</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 15.712x + -7782.179</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-7782.179053414251</v>
       </c>
       <c r="Y5" t="n">
         <v>455.2898977755081</v>
       </c>
       <c r="Z5" t="n">
-        <v>233476585.7749151</v>
+        <v>258.3969999999999</v>
       </c>
       <c r="AA5" t="n">
         <v>4.214796704370467e-07</v>
@@ -2992,19 +4604,19 @@
       <c r="K6" t="n">
         <v>87.01682231696586</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 19.189x + -9593.137</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-9593.136762940996</v>
       </c>
       <c r="Y6" t="n">
         <v>450.9861210411568</v>
       </c>
       <c r="Z6" t="n">
-        <v>126545179.3254542</v>
+        <v>239.8799999999999</v>
       </c>
       <c r="AA6" t="n">
         <v>4.129222500315576e-07</v>
@@ -3044,19 +4656,19 @@
       <c r="K7" t="n">
         <v>87.11128161283676</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 19.818x + -9806.389</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-9806.389472830584</v>
       </c>
       <c r="Y7" t="n">
         <v>446.8889649155186</v>
       </c>
       <c r="Z7" t="n">
-        <v>122458875.3100242</v>
+        <v>231.3179999999999</v>
       </c>
       <c r="AA7" t="n">
         <v>4.067916761251468e-07</v>
@@ -3096,19 +4708,19 @@
       <c r="K8" t="n">
         <v>87.15781820780296</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 20.143x + -9869.027</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-9869.027485010618</v>
       </c>
       <c r="Y8" t="n">
         <v>442.8712218178521</v>
       </c>
       <c r="Z8" t="n">
-        <v>122392902.8602818</v>
+        <v>228.917</v>
       </c>
       <c r="AA8" t="n">
         <v>4.024624242343295e-07</v>
@@ -3148,19 +4760,19 @@
       <c r="K9" t="n">
         <v>87.21211455630632</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 20.535x + -9966.374</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-9966.373567261111</v>
       </c>
       <c r="Y9" t="n">
         <v>439.1164588465697</v>
       </c>
       <c r="Z9" t="n">
-        <v>358891114.3223209</v>
+        <v>225.077</v>
       </c>
       <c r="AA9" t="n">
         <v>3.981809757220652e-07</v>
@@ -3200,19 +4812,19 @@
       <c r="K10" t="n">
         <v>87.25805920057836</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 20.880x + -10037.105</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-10037.10526332246</v>
       </c>
       <c r="Y10" t="n">
         <v>435.6279289492796</v>
       </c>
       <c r="Z10" t="n">
-        <v>135088959.5285163</v>
+        <v>219.884</v>
       </c>
       <c r="AA10" t="n">
         <v>3.942594878233831e-07</v>
@@ -3252,19 +4864,19 @@
       <c r="K11" t="n">
         <v>87.23514555078835</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 20.707x + -9852.044</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-9852.044214779651</v>
       </c>
       <c r="Y11" t="n">
         <v>432.426126761333</v>
       </c>
       <c r="Z11" t="n">
-        <v>353362037.112519</v>
+        <v>220.128</v>
       </c>
       <c r="AA11" t="n">
         <v>3.915712377291921e-07</v>
@@ -3304,19 +4916,19 @@
       <c r="K12" t="n">
         <v>87.22943828442875</v>
       </c>
-      <c r="W12" t="n">
-        <v>11</v>
-      </c>
-      <c r="X12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>y = 20.664x + -9738.147</t>
         </is>
+      </c>
+      <c r="X12" t="n">
+        <v>-9738.146833238899</v>
       </c>
       <c r="Y12" t="n">
         <v>429.3655616654337</v>
       </c>
       <c r="Z12" t="n">
-        <v>350392262.7494087</v>
+        <v>218.152</v>
       </c>
       <c r="AA12" t="n">
         <v>3.887829210702251e-07</v>
@@ -3356,19 +4968,19 @@
       <c r="K13" t="n">
         <v>87.3222287501108</v>
       </c>
-      <c r="W13" t="n">
-        <v>12</v>
-      </c>
-      <c r="X13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>y = 21.381x + -10018.553</t>
         </is>
+      </c>
+      <c r="X13" t="n">
+        <v>-10018.55328220722</v>
       </c>
       <c r="Y13" t="n">
         <v>426.3164300355821</v>
       </c>
       <c r="Z13" t="n">
-        <v>580420486.7926364</v>
+        <v>212.123</v>
       </c>
       <c r="AA13" t="n">
         <v>3.855688000858838e-07</v>
@@ -3408,19 +5020,19 @@
       <c r="K14" t="n">
         <v>87.41672760765853</v>
       </c>
-      <c r="W14" t="n">
-        <v>13</v>
-      </c>
-      <c r="X14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>y = 22.165x + -10335.154</t>
         </is>
+      </c>
+      <c r="X14" t="n">
+        <v>-10335.15395494345</v>
       </c>
       <c r="Y14" t="n">
         <v>423.2760786268939</v>
       </c>
       <c r="Z14" t="n">
-        <v>119273868.8902068</v>
+        <v>210.152</v>
       </c>
       <c r="AA14" t="n">
         <v>3.831347269447549e-07</v>
@@ -3460,19 +5072,19 @@
       <c r="K15" t="n">
         <v>87.08785412480184</v>
       </c>
-      <c r="W15" t="n">
-        <v>14</v>
-      </c>
-      <c r="X15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>y = 19.658x + -8970.084</t>
         </is>
+      </c>
+      <c r="X15" t="n">
+        <v>-8970.084037679289</v>
       </c>
       <c r="Y15" t="n">
         <v>420.1909075974667</v>
       </c>
       <c r="Z15" t="n">
-        <v>114419301.9815577</v>
+        <v>216.568</v>
       </c>
       <c r="AA15" t="n">
         <v>3.815828381615512e-07</v>
@@ -3512,19 +5124,19 @@
       <c r="K16" t="n">
         <v>87.32531571405592</v>
       </c>
-      <c r="W16" t="n">
-        <v>15</v>
-      </c>
-      <c r="X16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>y = 21.406x + -9770.702</t>
         </is>
+      </c>
+      <c r="X16" t="n">
+        <v>-9770.701640971984</v>
       </c>
       <c r="Y16" t="n">
         <v>417.1214845417246</v>
       </c>
       <c r="Z16" t="n">
-        <v>170335906.1875667</v>
+        <v>211.1</v>
       </c>
       <c r="AA16" t="n">
         <v>3.79570601572069e-07</v>
@@ -3564,19 +5176,19 @@
       <c r="K17" t="n">
         <v>87.44751334825065</v>
       </c>
-      <c r="W17" t="n">
-        <v>16</v>
-      </c>
-      <c r="X17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>y = 22.432x + -10197.687</t>
         </is>
+      </c>
+      <c r="X17" t="n">
+        <v>-10197.68748450432</v>
       </c>
       <c r="Y17" t="n">
         <v>414.0538608169979</v>
       </c>
       <c r="Z17" t="n">
-        <v>189662324.7506776</v>
+        <v>207.197</v>
       </c>
       <c r="AA17" t="n">
         <v>3.774134290660462e-07</v>
@@ -3616,19 +5228,19 @@
       <c r="K18" t="n">
         <v>87.52417100540225</v>
       </c>
-      <c r="W18" t="n">
-        <v>17</v>
-      </c>
-      <c r="X18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>y = 23.128x + -10453.667</t>
         </is>
+      </c>
+      <c r="X18" t="n">
+        <v>-10453.6666009086</v>
       </c>
       <c r="Y18" t="n">
         <v>411.0115831455041</v>
       </c>
       <c r="Z18" t="n">
-        <v>335463998.5325902</v>
+        <v>203.219</v>
       </c>
       <c r="AA18" t="n">
         <v>3.75005320023306e-07</v>
@@ -3668,19 +5280,19 @@
       <c r="K19" t="n">
         <v>87.37354170745235</v>
       </c>
-      <c r="W19" t="n">
-        <v>18</v>
-      </c>
-      <c r="X19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>y = 21.800x + -9699.760</t>
         </is>
+      </c>
+      <c r="X19" t="n">
+        <v>-9699.759956167509</v>
       </c>
       <c r="Y19" t="n">
         <v>407.8691435991047</v>
       </c>
       <c r="Z19" t="n">
-        <v>166791579.8430284</v>
+        <v>205.833</v>
       </c>
       <c r="AA19" t="n">
         <v>3.733618963832413e-07</v>
@@ -3720,19 +5332,19 @@
       <c r="K20" t="n">
         <v>87.44335165990118</v>
       </c>
-      <c r="W20" t="n">
-        <v>19</v>
-      </c>
-      <c r="X20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>y = 22.396x + -9910.234</t>
         </is>
+      </c>
+      <c r="X20" t="n">
+        <v>-9910.233625440118</v>
       </c>
       <c r="Y20" t="n">
         <v>404.7743525593904</v>
       </c>
       <c r="Z20" t="n">
-        <v>220966175.5117127</v>
+        <v>205.568</v>
       </c>
       <c r="AA20" t="n">
         <v>3.722562336146518e-07</v>
@@ -3772,19 +5384,19 @@
       <c r="K21" t="n">
         <v>87.6263570578039</v>
       </c>
-      <c r="W21" t="n">
-        <v>20</v>
-      </c>
-      <c r="X21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>y = 24.125x + -10659.979</t>
         </is>
+      </c>
+      <c r="X21" t="n">
+        <v>-10659.97893321486</v>
       </c>
       <c r="Y21" t="n">
         <v>401.6864719294056</v>
       </c>
       <c r="Z21" t="n">
-        <v>218430394.4754781</v>
+        <v>200.7020000000001</v>
       </c>
       <c r="AA21" t="n">
         <v>3.70075288371997e-07</v>
@@ -3824,19 +5436,19 @@
       <c r="K22" t="n">
         <v>87.50042163574763</v>
       </c>
-      <c r="W22" t="n">
-        <v>21</v>
-      </c>
-      <c r="X22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>y = 22.908x + -9967.246</t>
         </is>
+      </c>
+      <c r="X22" t="n">
+        <v>-9967.246164742723</v>
       </c>
       <c r="Y22" t="n">
         <v>398.5548574235218</v>
       </c>
       <c r="Z22" t="n">
-        <v>433419073.6183606</v>
+        <v>199.958</v>
       </c>
       <c r="AA22" t="n">
         <v>3.67800067085379e-07</v>
@@ -3962,12 +5574,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -3977,7 +5589,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -4022,19 +5634,19 @@
       <c r="K2" t="n">
         <v>83.2286754759028</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 8.422x + -5594.038</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-5594.038148614398</v>
       </c>
       <c r="Y2" t="n">
         <v>543.1549205509359</v>
       </c>
       <c r="Z2" t="n">
-        <v>186265100.5781556</v>
+        <v>562.266</v>
       </c>
       <c r="AA2" t="n">
         <v>9.000562484580156e-07</v>
@@ -4074,19 +5686,19 @@
       <c r="K3" t="n">
         <v>85.0734179252637</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 11.601x + -6793.990</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-6793.990321478196</v>
       </c>
       <c r="Y3" t="n">
         <v>510.9396929138588</v>
       </c>
       <c r="Z3" t="n">
-        <v>280770929.6339918</v>
+        <v>405.046</v>
       </c>
       <c r="AA3" t="n">
         <v>6.244166002873013e-07</v>
@@ -4126,19 +5738,19 @@
       <c r="K4" t="n">
         <v>85.68063584767771</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 13.240x + -7493.782</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-7493.781817736216</v>
       </c>
       <c r="Y4" t="n">
         <v>500.6049367462784</v>
       </c>
       <c r="Z4" t="n">
-        <v>53375387.1332188</v>
+        <v>350.2140000000001</v>
       </c>
       <c r="AA4" t="n">
         <v>5.527798103117413e-07</v>
@@ -4178,19 +5790,19 @@
       <c r="K5" t="n">
         <v>86.08381995169948</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 14.608x + -8129.460</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-8129.460176005873</v>
       </c>
       <c r="Y5" t="n">
         <v>494.0450278191379</v>
       </c>
       <c r="Z5" t="n">
-        <v>46786109.65925075</v>
+        <v>313.629</v>
       </c>
       <c r="AA5" t="n">
         <v>5.137677306838621e-07</v>
@@ -4230,19 +5842,19 @@
       <c r="K6" t="n">
         <v>86.32011709446074</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 15.549x + -8528.743</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-8528.742698678667</v>
       </c>
       <c r="Y6" t="n">
         <v>487.943646383955</v>
       </c>
       <c r="Z6" t="n">
-        <v>33367211.02390506</v>
+        <v>293.726</v>
       </c>
       <c r="AA6" t="n">
         <v>4.901749361239819e-07</v>
@@ -4282,19 +5894,19 @@
       <c r="K7" t="n">
         <v>86.52516603865126</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 16.469x + -8919.202</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-8919.202352188366</v>
       </c>
       <c r="Y7" t="n">
         <v>481.8661609590969</v>
       </c>
       <c r="Z7" t="n">
-        <v>792603942.9823534</v>
+        <v>278.4590000000001</v>
       </c>
       <c r="AA7" t="n">
         <v>4.73924482176603e-07</v>
@@ -4334,19 +5946,19 @@
       <c r="K8" t="n">
         <v>86.72920435807227</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 17.498x + -9365.715</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-9365.715433468496</v>
       </c>
       <c r="Y8" t="n">
         <v>475.8994573007008</v>
       </c>
       <c r="Z8" t="n">
-        <v>130349566.0779665</v>
+        <v>264.2569999999999</v>
       </c>
       <c r="AA8" t="n">
         <v>4.59654215334174e-07</v>
@@ -4386,19 +5998,19 @@
       <c r="K9" t="n">
         <v>86.72363030343634</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 17.469x + -9178.008</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-9178.008238206097</v>
       </c>
       <c r="Y9" t="n">
         <v>470.2342682494343</v>
       </c>
       <c r="Z9" t="n">
-        <v>192582098.4404453</v>
+        <v>259.361</v>
       </c>
       <c r="AA9" t="n">
         <v>4.488018763383606e-07</v>
@@ -4438,19 +6050,19 @@
       <c r="K10" t="n">
         <v>86.82480654129405</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 18.026x + -9343.367</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-9343.367392363531</v>
       </c>
       <c r="Y10" t="n">
         <v>443.8763524390018</v>
       </c>
       <c r="Z10" t="n">
-        <v>3816.204478538165</v>
+        <v>248.358</v>
       </c>
       <c r="AA10" t="n">
         <v>1.679564945875143e-06</v>
@@ -4490,19 +6102,19 @@
       <c r="K11" t="n">
         <v>86.88813597581999</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 18.394x + -9412.102</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-9412.102212550497</v>
       </c>
       <c r="Y11" t="n">
         <v>439.9090000652595</v>
       </c>
       <c r="Z11" t="n">
-        <v>3778.608686157441</v>
+        <v>243.711</v>
       </c>
       <c r="AA11" t="n">
         <v>1.073043167800002e-06</v>
@@ -4628,12 +6240,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -4643,7 +6255,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -4688,19 +6300,19 @@
       <c r="K2" t="n">
         <v>84.97403041664072</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 11.371x + -6270.930</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-6270.929668642305</v>
       </c>
       <c r="Y2" t="n">
         <v>480.7329810792613</v>
       </c>
       <c r="Z2" t="n">
-        <v>74281673.71447983</v>
+        <v>402.6819999999999</v>
       </c>
       <c r="AA2" t="n">
         <v>6.10816213591845e-07</v>
@@ -4740,19 +6352,19 @@
       <c r="K3" t="n">
         <v>86.21937729737456</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 15.133x + -7908.508</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-7908.507524896489</v>
       </c>
       <c r="Y3" t="n">
         <v>466.6743280794358</v>
       </c>
       <c r="Z3" t="n">
-        <v>1146789125.444086</v>
+        <v>304.586</v>
       </c>
       <c r="AA3" t="n">
         <v>4.93953090122737e-07</v>
@@ -4792,19 +6404,19 @@
       <c r="K4" t="n">
         <v>86.56353036166978</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 16.653x + -8555.418</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-8555.417740161829</v>
       </c>
       <c r="Y4" t="n">
         <v>441.7462578815397</v>
       </c>
       <c r="Z4" t="n">
-        <v>3784.671871658175</v>
+        <v>275.384</v>
       </c>
       <c r="AA4" t="n">
         <v>9.920763789529094e-07</v>
@@ -4844,19 +6456,19 @@
       <c r="K5" t="n">
         <v>86.69176337968138</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 17.300x + -8769.938</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-8769.937580096921</v>
       </c>
       <c r="Y5" t="n">
         <v>456.5841396445374</v>
       </c>
       <c r="Z5" t="n">
-        <v>124610153.8380714</v>
+        <v>261.417</v>
       </c>
       <c r="AA5" t="n">
         <v>4.478528728625239e-07</v>
@@ -4896,19 +6508,19 @@
       <c r="K6" t="n">
         <v>86.86121345923347</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 18.236x + -9162.047</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-9162.047188881685</v>
       </c>
       <c r="Y6" t="n">
         <v>452.2941937652293</v>
       </c>
       <c r="Z6" t="n">
-        <v>370159327.3551711</v>
+        <v>250.0599999999999</v>
       </c>
       <c r="AA6" t="n">
         <v>4.379485607529913e-07</v>
@@ -4948,19 +6560,19 @@
       <c r="K7" t="n">
         <v>86.86744460857412</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 18.272x + -9049.733</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-9049.732686986781</v>
       </c>
       <c r="Y7" t="n">
         <v>447.9608253751574</v>
       </c>
       <c r="Z7" t="n">
-        <v>170780600.7147736</v>
+        <v>244.102</v>
       </c>
       <c r="AA7" t="n">
         <v>4.290502484936856e-07</v>
@@ -5000,19 +6612,19 @@
       <c r="K8" t="n">
         <v>86.86641320059545</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 18.266x + -8927.371</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-8927.370516560044</v>
       </c>
       <c r="Y8" t="n">
         <v>443.8211181574397</v>
       </c>
       <c r="Z8" t="n">
-        <v>363229513.4700153</v>
+        <v>239.6659999999999</v>
       </c>
       <c r="AA8" t="n">
         <v>4.22975977742907e-07</v>
@@ -5052,19 +6664,19 @@
       <c r="K9" t="n">
         <v>86.91368979123239</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 18.547x + -8965.883</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-8965.882849277941</v>
       </c>
       <c r="Y9" t="n">
         <v>439.9561516169117</v>
       </c>
       <c r="Z9" t="n">
-        <v>723148207.1356236</v>
+        <v>234.5579999999999</v>
       </c>
       <c r="AA9" t="n">
         <v>4.170676493982838e-07</v>
@@ -5104,19 +6716,19 @@
       <c r="K10" t="n">
         <v>86.94806930354042</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 18.756x + -8968.914</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-8968.913603131734</v>
       </c>
       <c r="Y10" t="n">
         <v>436.3600211278208</v>
       </c>
       <c r="Z10" t="n">
-        <v>358460681.8910872</v>
+        <v>227.726</v>
       </c>
       <c r="AA10" t="n">
         <v>4.115320442145009e-07</v>
@@ -5156,19 +6768,19 @@
       <c r="K11" t="n">
         <v>87.11608184377877</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 19.851x + -9466.038</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-9466.037951180724</v>
       </c>
       <c r="Y11" t="n">
         <v>432.97046668927</v>
       </c>
       <c r="Z11" t="n">
-        <v>236014137.9245085</v>
+        <v>226.396</v>
       </c>
       <c r="AA11" t="n">
         <v>4.083913633849018e-07</v>
@@ -5208,19 +6820,19 @@
       <c r="K12" t="n">
         <v>87.22113248913811</v>
       </c>
-      <c r="W12" t="n">
-        <v>11</v>
-      </c>
-      <c r="X12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>y = 20.602x + -9759.613</t>
         </is>
+      </c>
+      <c r="X12" t="n">
+        <v>-9759.613103107598</v>
       </c>
       <c r="Y12" t="n">
         <v>429.7823712461693</v>
       </c>
       <c r="Z12" t="n">
-        <v>117324768.0826236</v>
+        <v>218.4560000000001</v>
       </c>
       <c r="AA12" t="n">
         <v>4.040091939319597e-07</v>
@@ -5260,19 +6872,19 @@
       <c r="K13" t="n">
         <v>87.20388616141652</v>
       </c>
-      <c r="W13" t="n">
-        <v>12</v>
-      </c>
-      <c r="X13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>y = 20.475x + -9605.001</t>
         </is>
+      </c>
+      <c r="X13" t="n">
+        <v>-9605.001358597106</v>
       </c>
       <c r="Y13" t="n">
         <v>426.7265578770754</v>
       </c>
       <c r="Z13" t="n">
-        <v>116197004.0089286</v>
+        <v>218.275</v>
       </c>
       <c r="AA13" t="n">
         <v>4.017211680390725e-07</v>
@@ -5312,19 +6924,19 @@
       <c r="K14" t="n">
         <v>87.28877204326189</v>
       </c>
-      <c r="W14" t="n">
-        <v>13</v>
-      </c>
-      <c r="X14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>y = 21.117x + -9858.038</t>
         </is>
+      </c>
+      <c r="X14" t="n">
+        <v>-9858.038022428444</v>
       </c>
       <c r="Y14" t="n">
         <v>423.717404171028</v>
       </c>
       <c r="Z14" t="n">
-        <v>174275636.4765854</v>
+        <v>216.824</v>
       </c>
       <c r="AA14" t="n">
         <v>3.993079744260538e-07</v>
@@ -5364,19 +6976,19 @@
       <c r="K15" t="n">
         <v>87.27853165704568</v>
       </c>
-      <c r="W15" t="n">
-        <v>14</v>
-      </c>
-      <c r="X15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>y = 21.037x + -9717.500</t>
         </is>
+      </c>
+      <c r="X15" t="n">
+        <v>-9717.500210802407</v>
       </c>
       <c r="Y15" t="n">
         <v>420.8301510651199</v>
       </c>
       <c r="Z15" t="n">
-        <v>118699947.6321774</v>
+        <v>211.552</v>
       </c>
       <c r="AA15" t="n">
         <v>3.950350635438924e-07</v>
@@ -5416,19 +7028,19 @@
       <c r="K16" t="n">
         <v>87.37663320905385</v>
       </c>
-      <c r="W16" t="n">
-        <v>15</v>
-      </c>
-      <c r="X16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>y = 21.825x + -10047.448</t>
         </is>
+      </c>
+      <c r="X16" t="n">
+        <v>-10047.4484867406</v>
       </c>
       <c r="Y16" t="n">
         <v>417.8883155073642</v>
       </c>
       <c r="Z16" t="n">
-        <v>113886404.4804137</v>
+        <v>210.8699999999999</v>
       </c>
       <c r="AA16" t="n">
         <v>3.936691830738516e-07</v>
@@ -5468,19 +7080,19 @@
       <c r="K17" t="n">
         <v>87.29573909794998</v>
       </c>
-      <c r="W17" t="n">
-        <v>16</v>
-      </c>
-      <c r="X17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>y = 21.171x + -9621.750</t>
         </is>
+      </c>
+      <c r="X17" t="n">
+        <v>-9621.749888657463</v>
       </c>
       <c r="Y17" t="n">
         <v>414.9342646853236</v>
       </c>
       <c r="Z17" t="n">
-        <v>225863530.1406434</v>
+        <v>209.307</v>
       </c>
       <c r="AA17" t="n">
         <v>3.909898706607735e-07</v>
@@ -5520,19 +7132,19 @@
       <c r="K18" t="n">
         <v>87.36062890868665</v>
       </c>
-      <c r="W18" t="n">
-        <v>17</v>
-      </c>
-      <c r="X18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>y = 21.693x + -9796.621</t>
         </is>
+      </c>
+      <c r="X18" t="n">
+        <v>-9796.620626035796</v>
       </c>
       <c r="Y18" t="n">
         <v>411.9720116088964</v>
       </c>
       <c r="Z18" t="n">
-        <v>224301672.8987534</v>
+        <v>205.398</v>
       </c>
       <c r="AA18" t="n">
         <v>3.885281668279745e-07</v>
@@ -5572,19 +7184,19 @@
       <c r="K19" t="n">
         <v>87.42040333435118</v>
       </c>
-      <c r="W19" t="n">
-        <v>18</v>
-      </c>
-      <c r="X19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>y = 22.196x + -9966.494</t>
         </is>
+      </c>
+      <c r="X19" t="n">
+        <v>-9966.493890533791</v>
       </c>
       <c r="Y19" t="n">
         <v>408.9261837758424</v>
       </c>
       <c r="Z19" t="n">
-        <v>336717429.4957645</v>
+        <v>206.718</v>
       </c>
       <c r="AA19" t="n">
         <v>3.872646030629363e-07</v>
@@ -5624,19 +7236,19 @@
       <c r="K20" t="n">
         <v>87.36357714126802</v>
       </c>
-      <c r="W20" t="n">
-        <v>19</v>
-      </c>
-      <c r="X20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>y = 21.717x + -9633.625</t>
         </is>
+      </c>
+      <c r="X20" t="n">
+        <v>-9633.625039364226</v>
       </c>
       <c r="Y20" t="n">
         <v>405.9261632735991</v>
       </c>
       <c r="Z20" t="n">
-        <v>167472087.5035553</v>
+        <v>203.48</v>
       </c>
       <c r="AA20" t="n">
         <v>3.846101172966364e-07</v>
@@ -5676,19 +7288,19 @@
       <c r="K21" t="n">
         <v>87.37559569964908</v>
       </c>
-      <c r="W21" t="n">
-        <v>20</v>
-      </c>
-      <c r="X21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>y = 21.817x + -9599.512</t>
         </is>
+      </c>
+      <c r="X21" t="n">
+        <v>-9599.512453267755</v>
       </c>
       <c r="Y21" t="n">
         <v>402.8799496509758</v>
       </c>
       <c r="Z21" t="n">
-        <v>164336307.8858424</v>
+        <v>202.8820000000001</v>
       </c>
       <c r="AA21" t="n">
         <v>3.8283198706333e-07</v>
@@ -5728,19 +7340,19 @@
       <c r="K22" t="n">
         <v>87.39131217537374</v>
       </c>
-      <c r="W22" t="n">
-        <v>21</v>
-      </c>
-      <c r="X22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>y = 21.948x + -9575.315</t>
         </is>
+      </c>
+      <c r="X22" t="n">
+        <v>-9575.315285342263</v>
       </c>
       <c r="Y22" t="n">
         <v>399.8123011185766</v>
       </c>
       <c r="Z22" t="n">
-        <v>435006457.8718216</v>
+        <v>202.72</v>
       </c>
       <c r="AA22" t="n">
         <v>3.81027561082448e-07</v>
@@ -5866,12 +7478,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -5881,7 +7493,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -6012,12 +7624,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -6027,7 +7639,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -6072,19 +7684,19 @@
       <c r="K2" t="n">
         <v>85.36780758400076</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 12.342x + -6748.483</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-6748.482591283335</v>
       </c>
       <c r="Y2" t="n">
         <v>481.3169627103698</v>
       </c>
       <c r="Z2" t="n">
-        <v>16419334.8726047</v>
+        <v>366.1239999999999</v>
       </c>
       <c r="AA2" t="n">
         <v>5.669450557150221e-07</v>
@@ -6124,19 +7736,19 @@
       <c r="K3" t="n">
         <v>86.24270524471871</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 15.227x + -7954.308</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-7954.308330172933</v>
       </c>
       <c r="Y3" t="n">
         <v>468.5931932505256</v>
       </c>
       <c r="Z3" t="n">
-        <v>159877891.2432903</v>
+        <v>296.5</v>
       </c>
       <c r="AA3" t="n">
         <v>4.873475088148432e-07</v>
@@ -6176,19 +7788,19 @@
       <c r="K4" t="n">
         <v>86.49591963575499</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 16.331x + -8381.350</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-8381.349611913041</v>
       </c>
       <c r="Y4" t="n">
         <v>442.0128795856027</v>
       </c>
       <c r="Z4" t="n">
-        <v>3801.263534749723</v>
+        <v>273.1660000000001</v>
       </c>
       <c r="AA4" t="n">
         <v>1.062851142884898e-06</v>
@@ -6228,19 +7840,19 @@
       <c r="K5" t="n">
         <v>86.70390905726283</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 17.364x + -8819.308</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-8819.308046089296</v>
       </c>
       <c r="Y5" t="n">
         <v>458.1390253610684</v>
       </c>
       <c r="Z5" t="n">
-        <v>250286990.6666235</v>
+        <v>257.358</v>
       </c>
       <c r="AA5" t="n">
         <v>4.477011926842336e-07</v>
@@ -6280,19 +7892,19 @@
       <c r="K6" t="n">
         <v>86.82408465951286</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 18.022x + -9051.571</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-9051.57053567746</v>
       </c>
       <c r="Y6" t="n">
         <v>453.4836180409301</v>
       </c>
       <c r="Z6" t="n">
-        <v>185543068.2052857</v>
+        <v>247.627</v>
       </c>
       <c r="AA6" t="n">
         <v>4.378649357911211e-07</v>
@@ -6332,19 +7944,19 @@
       <c r="K7" t="n">
         <v>86.84822348474556</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 18.161x + -8990.707</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-8990.707432323008</v>
       </c>
       <c r="Y7" t="n">
         <v>449.0052073497969</v>
       </c>
       <c r="Z7" t="n">
-        <v>122834849.4659618</v>
+        <v>238.378</v>
       </c>
       <c r="AA7" t="n">
         <v>4.295566039130984e-07</v>
@@ -6384,19 +7996,19 @@
       <c r="K8" t="n">
         <v>87.07437942212684</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 19.567x + -9667.665</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-9667.665045701837</v>
       </c>
       <c r="Y8" t="n">
         <v>444.7540789640374</v>
       </c>
       <c r="Z8" t="n">
-        <v>181863100.6548848</v>
+        <v>237.4060000000001</v>
       </c>
       <c r="AA8" t="n">
         <v>4.254248137776638e-07</v>
@@ -6436,19 +8048,19 @@
       <c r="K9" t="n">
         <v>87.01837713022248</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 19.199x + -9336.990</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-9336.989697992338</v>
       </c>
       <c r="Y9" t="n">
         <v>440.9192743489919</v>
       </c>
       <c r="Z9" t="n">
-        <v>163536237.4030253</v>
+        <v>231.886</v>
       </c>
       <c r="AA9" t="n">
         <v>4.197342568742096e-07</v>
@@ -6488,19 +8100,19 @@
       <c r="K10" t="n">
         <v>87.05324217330423</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 19.427x + -9355.329</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-9355.328574205456</v>
       </c>
       <c r="Y10" t="n">
         <v>437.2768084047943</v>
       </c>
       <c r="Z10" t="n">
-        <v>180768141.8999214</v>
+        <v>228.221</v>
       </c>
       <c r="AA10" t="n">
         <v>4.153048812850813e-07</v>
@@ -6540,19 +8152,19 @@
       <c r="K11" t="n">
         <v>87.05817622417544</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 19.459x + -9268.528</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-9268.527996519775</v>
       </c>
       <c r="Y11" t="n">
         <v>433.926388333696</v>
       </c>
       <c r="Z11" t="n">
-        <v>354594046.7493199</v>
+        <v>223.821</v>
       </c>
       <c r="AA11" t="n">
         <v>4.108080852274275e-07</v>
@@ -6592,19 +8204,19 @@
       <c r="K12" t="n">
         <v>87.16366452366474</v>
       </c>
-      <c r="W12" t="n">
-        <v>11</v>
-      </c>
-      <c r="X12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>y = 20.184x + -9562.297</t>
         </is>
+      </c>
+      <c r="X12" t="n">
+        <v>-9562.296871914776</v>
       </c>
       <c r="Y12" t="n">
         <v>430.7946570849169</v>
       </c>
       <c r="Z12" t="n">
-        <v>176191282.6818075</v>
+        <v>219.738</v>
       </c>
       <c r="AA12" t="n">
         <v>4.07338253062954e-07</v>
@@ -6644,19 +8256,19 @@
       <c r="K13" t="n">
         <v>87.15239682727612</v>
       </c>
-      <c r="W13" t="n">
-        <v>12</v>
-      </c>
-      <c r="X13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>y = 20.104x + -9433.777</t>
         </is>
+      </c>
+      <c r="X13" t="n">
+        <v>-9433.776914746522</v>
       </c>
       <c r="Y13" t="n">
         <v>427.7582624629842</v>
       </c>
       <c r="Z13" t="n">
-        <v>582235796.8971089</v>
+        <v>216.857</v>
       </c>
       <c r="AA13" t="n">
         <v>4.042887200040525e-07</v>
@@ -6696,19 +8308,19 @@
       <c r="K14" t="n">
         <v>87.22555644851892</v>
       </c>
-      <c r="W14" t="n">
-        <v>13</v>
-      </c>
-      <c r="X14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>y = 20.635x + -9622.311</t>
         </is>
+      </c>
+      <c r="X14" t="n">
+        <v>-9622.311120797718</v>
       </c>
       <c r="Y14" t="n">
         <v>424.742500254259</v>
       </c>
       <c r="Z14" t="n">
-        <v>231370192.64752</v>
+        <v>214.232</v>
       </c>
       <c r="AA14" t="n">
         <v>4.016765652232231e-07</v>
@@ -6748,19 +8360,19 @@
       <c r="K15" t="n">
         <v>86.68831508228989</v>
       </c>
-      <c r="W15" t="n">
-        <v>14</v>
-      </c>
-      <c r="X15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>y = 17.282x + -7835.620</t>
         </is>
+      </c>
+      <c r="X15" t="n">
+        <v>-7835.619852268862</v>
       </c>
       <c r="Y15" t="n">
         <v>421.7272234711429</v>
       </c>
       <c r="Z15" t="n">
-        <v>459203866.0416507</v>
+        <v>221.498</v>
       </c>
       <c r="AA15" t="n">
         <v>3.987137550482963e-07</v>
@@ -6800,19 +8412,19 @@
       <c r="K16" t="n">
         <v>87.26625806343664</v>
       </c>
-      <c r="W16" t="n">
-        <v>15</v>
-      </c>
-      <c r="X16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>y = 20.943x + -9609.411</t>
         </is>
+      </c>
+      <c r="X16" t="n">
+        <v>-9609.411179678706</v>
       </c>
       <c r="Y16" t="n">
         <v>418.6073312970457</v>
       </c>
       <c r="Z16" t="n">
-        <v>341638582.3541558</v>
+        <v>211.868</v>
       </c>
       <c r="AA16" t="n">
         <v>3.968436105843079e-07</v>
@@ -6852,19 +8464,19 @@
       <c r="K17" t="n">
         <v>87.36962013998401</v>
       </c>
-      <c r="W17" t="n">
-        <v>16</v>
-      </c>
-      <c r="X17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>y = 21.767x + -9943.823</t>
         </is>
+      </c>
+      <c r="X17" t="n">
+        <v>-9943.823040689851</v>
       </c>
       <c r="Y17" t="n">
         <v>415.4988262863592</v>
       </c>
       <c r="Z17" t="n">
-        <v>678122195.9628119</v>
+        <v>209.069</v>
       </c>
       <c r="AA17" t="n">
         <v>3.944747448839126e-07</v>
@@ -6904,19 +8516,19 @@
       <c r="K18" t="n">
         <v>87.20830633647073</v>
       </c>
-      <c r="W18" t="n">
-        <v>17</v>
-      </c>
-      <c r="X18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>y = 20.507x + -9214.628</t>
         </is>
+      </c>
+      <c r="X18" t="n">
+        <v>-9214.62778707721</v>
       </c>
       <c r="Y18" t="n">
         <v>412.3408510988346</v>
       </c>
       <c r="Z18" t="n">
-        <v>1009164193.7573</v>
+        <v>208.9879999999999</v>
       </c>
       <c r="AA18" t="n">
         <v>3.922775108507422e-07</v>
@@ -6956,19 +8568,19 @@
       <c r="K19" t="n">
         <v>87.43245571536816</v>
       </c>
-      <c r="W19" t="n">
-        <v>18</v>
-      </c>
-      <c r="X19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>y = 22.300x + -10016.940</t>
         </is>
+      </c>
+      <c r="X19" t="n">
+        <v>-10016.93989251047</v>
       </c>
       <c r="Y19" t="n">
         <v>409.146220039869</v>
       </c>
       <c r="Z19" t="n">
-        <v>111675322.944287</v>
+        <v>201.794</v>
       </c>
       <c r="AA19" t="n">
         <v>3.89463031729073e-07</v>
@@ -7008,19 +8620,19 @@
       <c r="K20" t="n">
         <v>87.24302465416277</v>
       </c>
-      <c r="W20" t="n">
-        <v>19</v>
-      </c>
-      <c r="X20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>y = 20.766x + -9168.850</t>
         </is>
+      </c>
+      <c r="X20" t="n">
+        <v>-9168.849542788153</v>
       </c>
       <c r="Y20" t="n">
         <v>405.8704923241809</v>
       </c>
       <c r="Z20" t="n">
-        <v>331483536.4798995</v>
+        <v>205.635</v>
       </c>
       <c r="AA20" t="n">
         <v>3.879106575621827e-07</v>
@@ -7060,19 +8672,19 @@
       <c r="K21" t="n">
         <v>87.42690252177401</v>
       </c>
-      <c r="W21" t="n">
-        <v>20</v>
-      </c>
-      <c r="X21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>y = 22.252x + -9813.809</t>
         </is>
+      </c>
+      <c r="X21" t="n">
+        <v>-9813.809394455837</v>
       </c>
       <c r="Y21" t="n">
         <v>402.6115395092147</v>
       </c>
       <c r="Z21" t="n">
-        <v>328927971.9372172</v>
+        <v>204.341</v>
       </c>
       <c r="AA21" t="n">
         <v>3.868962096896977e-07</v>
@@ -7112,19 +8724,19 @@
       <c r="K22" t="n">
         <v>87.27172274305212</v>
       </c>
-      <c r="W22" t="n">
-        <v>21</v>
-      </c>
-      <c r="X22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>y = 20.985x + -9099.908</t>
         </is>
+      </c>
+      <c r="X22" t="n">
+        <v>-9099.907935646037</v>
       </c>
       <c r="Y22" t="n">
         <v>399.4009964319251</v>
       </c>
       <c r="Z22" t="n">
-        <v>163014039.1037835</v>
+        <v>203.105</v>
       </c>
       <c r="AA22" t="n">
         <v>3.84126071669241e-07</v>
@@ -7250,12 +8862,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -7265,7 +8877,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -7310,19 +8922,19 @@
       <c r="K2" t="n">
         <v>84.08290098419012</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 9.649x + -5985.534</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-5985.534406047734</v>
       </c>
       <c r="Y2" t="n">
         <v>517.0072749278866</v>
       </c>
       <c r="Z2" t="n">
-        <v>424364260.9700205</v>
+        <v>493.3709999999999</v>
       </c>
       <c r="AA2" t="n">
         <v>7.372089456214138e-07</v>
@@ -7362,19 +8974,19 @@
       <c r="K3" t="n">
         <v>85.38886327510725</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 12.399x + -6817.849</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-6817.848939904364</v>
       </c>
       <c r="Y3" t="n">
         <v>487.5256646728903</v>
       </c>
       <c r="Z3" t="n">
-        <v>401099383.0753671</v>
+        <v>369.8169999999999</v>
       </c>
       <c r="AA3" t="n">
         <v>5.505983538172226e-07</v>
@@ -7414,19 +9026,19 @@
       <c r="K4" t="n">
         <v>86.04545356274795</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 14.466x + -7736.705</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-7736.704617183487</v>
       </c>
       <c r="Y4" t="n">
         <v>477.6740464688352</v>
       </c>
       <c r="Z4" t="n">
-        <v>264626087.1599844</v>
+        <v>316.712</v>
       </c>
       <c r="AA4" t="n">
         <v>4.957459364143968e-07</v>
@@ -7466,19 +9078,19 @@
       <c r="K5" t="n">
         <v>86.37443048586742</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 15.782x + -8310.461</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-8310.46069717217</v>
       </c>
       <c r="Y5" t="n">
         <v>470.9872411527926</v>
       </c>
       <c r="Z5" t="n">
-        <v>257756903.5772153</v>
+        <v>290.949</v>
       </c>
       <c r="AA5" t="n">
         <v>4.690264968634016e-07</v>
@@ -7518,19 +9130,19 @@
       <c r="K6" t="n">
         <v>86.62510124543059</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 16.957x + -8818.705</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-8818.705085613392</v>
       </c>
       <c r="Y6" t="n">
         <v>464.8602776880605</v>
       </c>
       <c r="Z6" t="n">
-        <v>254079897.3065849</v>
+        <v>272.147</v>
       </c>
       <c r="AA6" t="n">
         <v>4.517866403552614e-07</v>
@@ -7570,19 +9182,19 @@
       <c r="K7" t="n">
         <v>86.73955288943954</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 17.554x + -8990.702</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-8990.702303374113</v>
       </c>
       <c r="Y7" t="n">
         <v>440.5670897046683</v>
       </c>
       <c r="Z7" t="n">
-        <v>3760.852508810734</v>
+        <v>261.033</v>
       </c>
       <c r="AA7" t="n">
         <v>1.58174486006174e-06</v>
@@ -7622,19 +9234,19 @@
       <c r="K8" t="n">
         <v>86.83360894459653</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 18.077x + -9110.545</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-9110.545228760877</v>
       </c>
       <c r="Y8" t="n">
         <v>452.7456342089746</v>
       </c>
       <c r="Z8" t="n">
-        <v>246904518.6869225</v>
+        <v>249.523</v>
       </c>
       <c r="AA8" t="n">
         <v>4.294520224850721e-07</v>
@@ -7674,19 +9286,19 @@
       <c r="K9" t="n">
         <v>86.75578467338379</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 17.642x + -8721.405</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-8721.405395930318</v>
       </c>
       <c r="Y9" t="n">
         <v>447.0348010388421</v>
       </c>
       <c r="Z9" t="n">
-        <v>121838407.0186928</v>
+        <v>251.2169999999999</v>
       </c>
       <c r="AA9" t="n">
         <v>4.240480861238635e-07</v>
@@ -7726,19 +9338,19 @@
       <c r="K10" t="n">
         <v>86.88368510113125</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 18.368x + -8980.525</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-8980.525195986682</v>
       </c>
       <c r="Y10" t="n">
         <v>441.8132763859897</v>
       </c>
       <c r="Z10" t="n">
-        <v>126501952.0246875</v>
+        <v>244.867</v>
       </c>
       <c r="AA10" t="n">
         <v>4.183775092728076e-07</v>
@@ -7778,19 +9390,19 @@
       <c r="K11" t="n">
         <v>86.86890944232314</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 18.281x + -8798.414</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-8798.41393372084</v>
       </c>
       <c r="Y11" t="n">
         <v>437.2092957584164</v>
       </c>
       <c r="Z11" t="n">
-        <v>357233911.4357943</v>
+        <v>238.592</v>
       </c>
       <c r="AA11" t="n">
         <v>4.123806631877916e-07</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 45.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 45.xlsx
@@ -528,12 +528,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -588,10 +588,8 @@
       <c r="K2" t="n">
         <v>86.78874740645739</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 17.824x + -9599.322</t>
-        </is>
+      <c r="W2" t="n">
+        <v>17.82350396332755</v>
       </c>
       <c r="X2" t="n">
         <v>-9599.322190146206</v>
@@ -600,7 +598,7 @@
         <v>479.6053667238517</v>
       </c>
       <c r="Z2" t="n">
-        <v>273.0309999999999</v>
+        <v>149743442.3326762</v>
       </c>
       <c r="AA2" t="n">
         <v>4.26998522159083e-07</v>
@@ -640,10 +638,8 @@
       <c r="K3" t="n">
         <v>86.94581505152189</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 18.742x + -9898.387</t>
-        </is>
+      <c r="W3" t="n">
+        <v>18.7419890496679</v>
       </c>
       <c r="X3" t="n">
         <v>-9898.387345826271</v>
@@ -652,7 +648,7 @@
         <v>451.5456264712489</v>
       </c>
       <c r="Z3" t="n">
-        <v>253.042</v>
+        <v>3879.482615407804</v>
       </c>
       <c r="AA3" t="n">
         <v>1.643783049026739e-06</v>
@@ -692,10 +688,8 @@
       <c r="K4" t="n">
         <v>87.01709364146427</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 19.191x + -9985.675</t>
-        </is>
+      <c r="W4" t="n">
+        <v>19.19068129526032</v>
       </c>
       <c r="X4" t="n">
         <v>-9985.674568337905</v>
@@ -704,7 +698,7 @@
         <v>446.2200620584686</v>
       </c>
       <c r="Z4" t="n">
-        <v>244.425</v>
+        <v>3829.841406571698</v>
       </c>
       <c r="AA4" t="n">
         <v>1.351528210561691e-06</v>
@@ -744,10 +738,8 @@
       <c r="K5" t="n">
         <v>87.09139200699965</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 19.682x + -10105.935</t>
-        </is>
+      <c r="W5" t="n">
+        <v>19.68176973497182</v>
       </c>
       <c r="X5" t="n">
         <v>-10105.93471235811</v>
@@ -756,7 +748,7 @@
         <v>444.7545958425873</v>
       </c>
       <c r="Z5" t="n">
-        <v>237.049</v>
+        <v>7629.382468145198</v>
       </c>
       <c r="AA5" t="n">
         <v>3.588868257132026e-07</v>
@@ -796,10 +788,8 @@
       <c r="K6" t="n">
         <v>87.05450951659333</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 19.435x + -9813.146</t>
-        </is>
+      <c r="W6" t="n">
+        <v>19.43489429606497</v>
       </c>
       <c r="X6" t="n">
         <v>-9813.14555680553</v>
@@ -808,7 +798,7 @@
         <v>457.025911920714</v>
       </c>
       <c r="Z6" t="n">
-        <v>232.828</v>
+        <v>746705934.7151682</v>
       </c>
       <c r="AA6" t="n">
         <v>3.916622015651721e-07</v>
@@ -848,10 +838,8 @@
       <c r="K7" t="n">
         <v>87.196205066275</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 20.419x + -10212.241</t>
-        </is>
+      <c r="W7" t="n">
+        <v>20.41876762439064</v>
       </c>
       <c r="X7" t="n">
         <v>-10212.2407737871</v>
@@ -860,7 +848,7 @@
         <v>452.1017489174236</v>
       </c>
       <c r="Z7" t="n">
-        <v>226.1440000000001</v>
+        <v>184651142.0570834</v>
       </c>
       <c r="AA7" t="n">
         <v>3.870928133099566e-07</v>
@@ -900,10 +888,8 @@
       <c r="K8" t="n">
         <v>87.27092498551941</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 20.979x + -10390.983</t>
-        </is>
+      <c r="W8" t="n">
+        <v>20.97869894262035</v>
       </c>
       <c r="X8" t="n">
         <v>-10390.98297151223</v>
@@ -912,7 +898,7 @@
         <v>447.5255461435086</v>
       </c>
       <c r="Z8" t="n">
-        <v>222.697</v>
+        <v>186251969.6700453</v>
       </c>
       <c r="AA8" t="n">
         <v>3.837286484855732e-07</v>
@@ -952,10 +938,8 @@
       <c r="K9" t="n">
         <v>86.75953266883968</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 17.662x + -8486.175</t>
-        </is>
+      <c r="W9" t="n">
+        <v>17.66247594942411</v>
       </c>
       <c r="X9" t="n">
         <v>-8486.174645203593</v>
@@ -964,7 +948,7 @@
         <v>443.1919386320271</v>
       </c>
       <c r="Z9" t="n">
-        <v>232.307</v>
+        <v>603072528.4740071</v>
       </c>
       <c r="AA9" t="n">
         <v>3.8122141057872e-07</v>
@@ -1004,10 +988,8 @@
       <c r="K10" t="n">
         <v>87.24643305816566</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 20.792x + -10047.856</t>
-        </is>
+      <c r="W10" t="n">
+        <v>20.79181762396264</v>
       </c>
       <c r="X10" t="n">
         <v>-10047.85629252543</v>
@@ -1016,7 +998,7 @@
         <v>438.9914340641202</v>
       </c>
       <c r="Z10" t="n">
-        <v>223.849</v>
+        <v>239030133.4983007</v>
       </c>
       <c r="AA10" t="n">
         <v>3.792017074982107e-07</v>
@@ -1056,10 +1038,8 @@
       <c r="K11" t="n">
         <v>87.36798349326666</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 21.753x + -10438.648</t>
-        </is>
+      <c r="W11" t="n">
+        <v>21.7534620588097</v>
       </c>
       <c r="X11" t="n">
         <v>-10438.64831531955</v>
@@ -1068,7 +1048,7 @@
         <v>435.0729141741307</v>
       </c>
       <c r="Z11" t="n">
-        <v>217.3030000000001</v>
+        <v>118307610.4016054</v>
       </c>
       <c r="AA11" t="n">
         <v>3.755259302377786e-07</v>
@@ -1194,12 +1174,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -1254,10 +1234,8 @@
       <c r="K2" t="n">
         <v>86.23659232903233</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 15.203x + -8360.981</t>
-        </is>
+      <c r="W2" t="n">
+        <v>15.20254047159887</v>
       </c>
       <c r="X2" t="n">
         <v>-8360.98103653289</v>
@@ -1266,7 +1244,7 @@
         <v>480.9179802226254</v>
       </c>
       <c r="Z2" t="n">
-        <v>302.203</v>
+        <v>32722752.40087609</v>
       </c>
       <c r="AA2" t="n">
         <v>4.76354489356448e-07</v>
@@ -1306,10 +1284,8 @@
       <c r="K3" t="n">
         <v>86.70513271440362</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 17.370x + -9099.215</t>
-        </is>
+      <c r="W3" t="n">
+        <v>17.37023136307375</v>
       </c>
       <c r="X3" t="n">
         <v>-9099.215171842827</v>
@@ -1318,7 +1294,7 @@
         <v>467.4573120364058</v>
       </c>
       <c r="Z3" t="n">
-        <v>264.968</v>
+        <v>184552953.7433971</v>
       </c>
       <c r="AA3" t="n">
         <v>4.383445486220268e-07</v>
@@ -1358,10 +1334,8 @@
       <c r="K4" t="n">
         <v>86.68945551792773</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 17.288x + -8852.895</t>
-        </is>
+      <c r="W4" t="n">
+        <v>17.28779197790907</v>
       </c>
       <c r="X4" t="n">
         <v>-8852.895054964198</v>
@@ -1370,7 +1344,7 @@
         <v>454.0172810323862</v>
       </c>
       <c r="Z4" t="n">
-        <v>259.959</v>
+        <v>3786.052574500075</v>
       </c>
       <c r="AA4" t="n">
         <v>1.329909910929096e-06</v>
@@ -1410,10 +1384,8 @@
       <c r="K5" t="n">
         <v>86.9522145457658</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 18.781x + -9578.119</t>
-        </is>
+      <c r="W5" t="n">
+        <v>18.78141653552514</v>
       </c>
       <c r="X5" t="n">
         <v>-9578.119360771974</v>
@@ -1422,7 +1394,7 @@
         <v>437.8876006493587</v>
       </c>
       <c r="Z5" t="n">
-        <v>249.0699999999999</v>
+        <v>3750.519568057159</v>
       </c>
       <c r="AA5" t="n">
         <v>1.369126947661995e-06</v>
@@ -1462,10 +1434,8 @@
       <c r="K6" t="n">
         <v>87.00985416806904</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 19.144x + -9651.182</t>
-        </is>
+      <c r="W6" t="n">
+        <v>19.1441343721385</v>
       </c>
       <c r="X6" t="n">
         <v>-9651.181865898097</v>
@@ -1474,7 +1444,7 @@
         <v>452.6898605286162</v>
       </c>
       <c r="Z6" t="n">
-        <v>242.599</v>
+        <v>372708633.2520003</v>
       </c>
       <c r="AA6" t="n">
         <v>4.145001707610471e-07</v>
@@ -1514,10 +1484,8 @@
       <c r="K7" t="n">
         <v>86.9539854200394</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 18.792x + -9335.074</t>
-        </is>
+      <c r="W7" t="n">
+        <v>18.79235618526171</v>
       </c>
       <c r="X7" t="n">
         <v>-9335.073827635899</v>
@@ -1526,7 +1494,7 @@
         <v>448.2409320277739</v>
       </c>
       <c r="Z7" t="n">
-        <v>243.597</v>
+        <v>213847128.618784</v>
       </c>
       <c r="AA7" t="n">
         <v>4.107660705107558e-07</v>
@@ -1566,10 +1534,8 @@
       <c r="K8" t="n">
         <v>86.97806735020897</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 18.942x + -9296.229</t>
-        </is>
+      <c r="W8" t="n">
+        <v>18.94239482524619</v>
       </c>
       <c r="X8" t="n">
         <v>-9296.228995134883</v>
@@ -1578,7 +1544,7 @@
         <v>443.9565030544216</v>
       </c>
       <c r="Z8" t="n">
-        <v>239.779</v>
+        <v>181463160.9333132</v>
       </c>
       <c r="AA8" t="n">
         <v>4.064278669403648e-07</v>
@@ -1618,10 +1584,8 @@
       <c r="K9" t="n">
         <v>86.92254155876262</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 18.600x + -9000.956</t>
-        </is>
+      <c r="W9" t="n">
+        <v>18.59998158003243</v>
       </c>
       <c r="X9" t="n">
         <v>-9000.956083669631</v>
@@ -1630,7 +1594,7 @@
         <v>439.8959858391522</v>
       </c>
       <c r="Z9" t="n">
-        <v>240.252</v>
+        <v>239754015.1150077</v>
       </c>
       <c r="AA9" t="n">
         <v>4.030579782766424e-07</v>
@@ -1670,10 +1634,8 @@
       <c r="K10" t="n">
         <v>87.11025620574966</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 19.810x + -9552.484</t>
-        </is>
+      <c r="W10" t="n">
+        <v>19.81047228239968</v>
       </c>
       <c r="X10" t="n">
         <v>-9552.484276580579</v>
@@ -1682,7 +1644,7 @@
         <v>436.1400784512594</v>
       </c>
       <c r="Z10" t="n">
-        <v>234.1440000000001</v>
+        <v>178248817.8884017</v>
       </c>
       <c r="AA10" t="n">
         <v>3.991627777082239e-07</v>
@@ -1722,10 +1684,8 @@
       <c r="K11" t="n">
         <v>87.0544119031679</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 19.434x + -9255.033</t>
-        </is>
+      <c r="W11" t="n">
+        <v>19.43424910969891</v>
       </c>
       <c r="X11" t="n">
         <v>-9255.033440822186</v>
@@ -1734,7 +1694,7 @@
         <v>432.6308624506758</v>
       </c>
       <c r="Z11" t="n">
-        <v>235.8550000000001</v>
+        <v>118712714.3928932</v>
       </c>
       <c r="AA11" t="n">
         <v>3.972024883721081e-07</v>
@@ -1774,10 +1734,8 @@
       <c r="K12" t="n">
         <v>87.11923817397374</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = 19.872x + -9391.599</t>
-        </is>
+      <c r="W12" t="n">
+        <v>19.87234434365108</v>
       </c>
       <c r="X12" t="n">
         <v>-9391.598627738556</v>
@@ -1786,7 +1744,7 @@
         <v>429.2544068328343</v>
       </c>
       <c r="Z12" t="n">
-        <v>232.321</v>
+        <v>117731880.7618263</v>
       </c>
       <c r="AA12" t="n">
         <v>3.941020955067442e-07</v>
@@ -1826,10 +1784,8 @@
       <c r="K13" t="n">
         <v>87.23740857856555</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = 20.724x + -9755.401</t>
-        </is>
+      <c r="W13" t="n">
+        <v>20.72379271336019</v>
       </c>
       <c r="X13" t="n">
         <v>-9755.401357545546</v>
@@ -1838,7 +1794,7 @@
         <v>426.0092985316125</v>
       </c>
       <c r="Z13" t="n">
-        <v>229.193</v>
+        <v>115910342.4364102</v>
       </c>
       <c r="AA13" t="n">
         <v>3.916201313707369e-07</v>
@@ -1878,10 +1834,8 @@
       <c r="K14" t="n">
         <v>87.29760709754886</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = 21.186x + -9907.356</t>
-        </is>
+      <c r="W14" t="n">
+        <v>21.18614449045294</v>
       </c>
       <c r="X14" t="n">
         <v>-9907.355670692714</v>
@@ -1890,7 +1844,7 @@
         <v>422.7582751157986</v>
       </c>
       <c r="Z14" t="n">
-        <v>226.787</v>
+        <v>115113235.4057532</v>
       </c>
       <c r="AA14" t="n">
         <v>3.894681968248368e-07</v>
@@ -1930,10 +1884,8 @@
       <c r="K15" t="n">
         <v>87.14788086539058</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = 20.072x + -9230.947</t>
-        </is>
+      <c r="W15" t="n">
+        <v>20.07224940566364</v>
       </c>
       <c r="X15" t="n">
         <v>-9230.947039114715</v>
@@ -1942,7 +1894,7 @@
         <v>419.5445726516589</v>
       </c>
       <c r="Z15" t="n">
-        <v>228.5439999999999</v>
+        <v>228489614.6300777</v>
       </c>
       <c r="AA15" t="n">
         <v>3.870198928759991e-07</v>
@@ -1982,10 +1934,8 @@
       <c r="K16" t="n">
         <v>87.11724320036751</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = 19.859x + -9039.395</t>
-        </is>
+      <c r="W16" t="n">
+        <v>19.85856873896583</v>
       </c>
       <c r="X16" t="n">
         <v>-9039.394937021554</v>
@@ -1994,7 +1944,7 @@
         <v>416.4026218088894</v>
       </c>
       <c r="Z16" t="n">
-        <v>227.6300000000001</v>
+        <v>113897961.7652397</v>
       </c>
       <c r="AA16" t="n">
         <v>3.852111742265167e-07</v>
@@ -2034,10 +1984,8 @@
       <c r="K17" t="n">
         <v>87.32277914582281</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = 21.386x + -9725.303</t>
-        </is>
+      <c r="W17" t="n">
+        <v>21.38563744612662</v>
       </c>
       <c r="X17" t="n">
         <v>-9725.303200891476</v>
@@ -2046,7 +1994,7 @@
         <v>413.2448694439817</v>
       </c>
       <c r="Z17" t="n">
-        <v>220.461</v>
+        <v>225034438.3059394</v>
       </c>
       <c r="AA17" t="n">
         <v>3.824649422397493e-07</v>
@@ -2086,10 +2034,8 @@
       <c r="K18" t="n">
         <v>87.28332486828249</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = 21.075x + -9479.464</t>
-        </is>
+      <c r="W18" t="n">
+        <v>21.07459792476552</v>
       </c>
       <c r="X18" t="n">
         <v>-9479.464339063117</v>
@@ -2098,7 +2044,7 @@
         <v>410.0939754555842</v>
       </c>
       <c r="Z18" t="n">
-        <v>220.907</v>
+        <v>111547416.8222765</v>
       </c>
       <c r="AA18" t="n">
         <v>3.80791102093921e-07</v>
@@ -2138,10 +2084,8 @@
       <c r="K19" t="n">
         <v>87.35643336487306</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = 21.658x + -9689.716</t>
-        </is>
+      <c r="W19" t="n">
+        <v>21.65828387251652</v>
       </c>
       <c r="X19" t="n">
         <v>-9689.716375442036</v>
@@ -2150,7 +2094,7 @@
         <v>406.9299068987231</v>
       </c>
       <c r="Z19" t="n">
-        <v>220.714</v>
+        <v>166188766.2632105</v>
       </c>
       <c r="AA19" t="n">
         <v>3.795864383290239e-07</v>
@@ -2190,10 +2134,8 @@
       <c r="K20" t="n">
         <v>87.23143930517391</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = 20.679x + -9112.604</t>
-        </is>
+      <c r="W20" t="n">
+        <v>20.67904089367934</v>
       </c>
       <c r="X20" t="n">
         <v>-9112.604359247525</v>
@@ -2202,7 +2144,7 @@
         <v>403.8097827662983</v>
       </c>
       <c r="Z20" t="n">
-        <v>220.716</v>
+        <v>110186319.4424782</v>
       </c>
       <c r="AA20" t="n">
         <v>3.773386297485312e-07</v>
@@ -2242,10 +2184,8 @@
       <c r="K21" t="n">
         <v>87.32353763478508</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = 21.392x + -9365.318</t>
-        </is>
+      <c r="W21" t="n">
+        <v>21.39170680144206</v>
       </c>
       <c r="X21" t="n">
         <v>-9365.318451994282</v>
@@ -2254,7 +2194,7 @@
         <v>400.5999790302465</v>
       </c>
       <c r="Z21" t="n">
-        <v>215.333</v>
+        <v>174014444.5471484</v>
       </c>
       <c r="AA21" t="n">
         <v>3.749404704529664e-07</v>
@@ -2294,10 +2234,8 @@
       <c r="K22" t="n">
         <v>87.38723037836647</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = 21.914x + -9532.753</t>
-        </is>
+      <c r="W22" t="n">
+        <v>21.91393308703115</v>
       </c>
       <c r="X22" t="n">
         <v>-9532.753076700101</v>
@@ -2306,7 +2244,7 @@
         <v>397.4150777577553</v>
       </c>
       <c r="Z22" t="n">
-        <v>213.279</v>
+        <v>108186090.8757237</v>
       </c>
       <c r="AA22" t="n">
         <v>3.73254825807647e-07</v>
@@ -2432,12 +2370,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -2492,10 +2430,8 @@
       <c r="K2" t="n">
         <v>85.87600810476651</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 13.869x + -7751.373</t>
-        </is>
+      <c r="W2" t="n">
+        <v>13.86928060524225</v>
       </c>
       <c r="X2" t="n">
         <v>-7751.373462847805</v>
@@ -2504,7 +2440,7 @@
         <v>489.3266483925309</v>
       </c>
       <c r="Z2" t="n">
-        <v>347.697</v>
+        <v>107266965.1809667</v>
       </c>
       <c r="AA2" t="n">
         <v>5.117874468168567e-07</v>
@@ -2544,10 +2480,8 @@
       <c r="K3" t="n">
         <v>86.68721616396195</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 17.276x + -9142.691</t>
-        </is>
+      <c r="W3" t="n">
+        <v>17.27607983040949</v>
       </c>
       <c r="X3" t="n">
         <v>-9142.691276745545</v>
@@ -2556,7 +2490,7 @@
         <v>473.6761094560357</v>
       </c>
       <c r="Z3" t="n">
-        <v>271.207</v>
+        <v>193739339.0518807</v>
       </c>
       <c r="AA3" t="n">
         <v>4.361934590012305e-07</v>
@@ -2596,10 +2530,8 @@
       <c r="K4" t="n">
         <v>86.97475332453027</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 18.922x + -9826.408</t>
-        </is>
+      <c r="W4" t="n">
+        <v>18.92160570492989</v>
       </c>
       <c r="X4" t="n">
         <v>-9826.40835573673</v>
@@ -2608,7 +2540,7 @@
         <v>443.9702341850466</v>
       </c>
       <c r="Z4" t="n">
-        <v>245.1329999999999</v>
+        <v>3830.162915425468</v>
       </c>
       <c r="AA4" t="n">
         <v>1.663103739688245e-06</v>
@@ -2648,10 +2580,8 @@
       <c r="K5" t="n">
         <v>87.10637500562872</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 19.784x + -10144.972</t>
-        </is>
+      <c r="W5" t="n">
+        <v>19.7838554817209</v>
       </c>
       <c r="X5" t="n">
         <v>-10144.97169018693</v>
@@ -2660,7 +2590,7 @@
         <v>461.9480378828465</v>
       </c>
       <c r="Z5" t="n">
-        <v>233.96</v>
+        <v>188865975.5467272</v>
       </c>
       <c r="AA5" t="n">
         <v>4.05022007432776e-07</v>
@@ -2700,10 +2630,8 @@
       <c r="K6" t="n">
         <v>87.093586354596</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 19.697x + -9944.378</t>
-        </is>
+      <c r="W6" t="n">
+        <v>19.69665505777763</v>
       </c>
       <c r="X6" t="n">
         <v>-9944.378389610323</v>
@@ -2712,7 +2640,7 @@
         <v>457.2780540802589</v>
       </c>
       <c r="Z6" t="n">
-        <v>226.484</v>
+        <v>186916035.996489</v>
       </c>
       <c r="AA6" t="n">
         <v>3.974253091366641e-07</v>
@@ -2752,10 +2680,8 @@
       <c r="K7" t="n">
         <v>87.208357009784</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 20.508x + -10269.293</t>
-        </is>
+      <c r="W7" t="n">
+        <v>20.50779169331176</v>
       </c>
       <c r="X7" t="n">
         <v>-10269.29342203443</v>
@@ -2764,7 +2690,7 @@
         <v>452.8080354240732</v>
       </c>
       <c r="Z7" t="n">
-        <v>225.373</v>
+        <v>370275443.9422262</v>
       </c>
       <c r="AA7" t="n">
         <v>3.930978807543943e-07</v>
@@ -2804,10 +2730,8 @@
       <c r="K8" t="n">
         <v>87.15669685568162</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 20.135x + -9938.274</t>
-        </is>
+      <c r="W8" t="n">
+        <v>20.1345885083383</v>
       </c>
       <c r="X8" t="n">
         <v>-9938.273876717878</v>
@@ -2816,7 +2740,7 @@
         <v>448.5791766810402</v>
       </c>
       <c r="Z8" t="n">
-        <v>223.033</v>
+        <v>122673713.7347551</v>
       </c>
       <c r="AA8" t="n">
         <v>3.888280687482529e-07</v>
@@ -2856,10 +2780,8 @@
       <c r="K9" t="n">
         <v>87.39384097181849</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 21.970x + -10810.293</t>
-        </is>
+      <c r="W9" t="n">
+        <v>21.96959541256436</v>
       </c>
       <c r="X9" t="n">
         <v>-10810.29347620989</v>
@@ -2868,7 +2790,7 @@
         <v>444.5332927489689</v>
       </c>
       <c r="Z9" t="n">
-        <v>214.4809999999999</v>
+        <v>968286450.4794898</v>
       </c>
       <c r="AA9" t="n">
         <v>3.844328084949008e-07</v>
@@ -2908,10 +2830,8 @@
       <c r="K10" t="n">
         <v>87.33204245290545</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 21.460x + -10413.433</t>
-        </is>
+      <c r="W10" t="n">
+        <v>21.45999765158652</v>
       </c>
       <c r="X10" t="n">
         <v>-10413.43311909305</v>
@@ -2920,7 +2840,7 @@
         <v>440.5873702632053</v>
       </c>
       <c r="Z10" t="n">
-        <v>213.393</v>
+        <v>184768244.8321308</v>
       </c>
       <c r="AA10" t="n">
         <v>3.815704047326536e-07</v>
@@ -2960,10 +2880,8 @@
       <c r="K11" t="n">
         <v>87.42074980966801</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 22.199x + -10691.841</t>
-        </is>
+      <c r="W11" t="n">
+        <v>22.19911493592852</v>
       </c>
       <c r="X11" t="n">
         <v>-10691.8405558676</v>
@@ -2972,7 +2890,7 @@
         <v>436.8161075249475</v>
       </c>
       <c r="Z11" t="n">
-        <v>209.535</v>
+        <v>356645226.2740096</v>
       </c>
       <c r="AA11" t="n">
         <v>3.783203121129007e-07</v>
@@ -3012,10 +2930,8 @@
       <c r="K12" t="n">
         <v>87.46809368424151</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = 22.615x + -10800.427</t>
-        </is>
+      <c r="W12" t="n">
+        <v>22.6147702364912</v>
       </c>
       <c r="X12" t="n">
         <v>-10800.42748218264</v>
@@ -3024,7 +2940,7 @@
         <v>433.1057700019758</v>
       </c>
       <c r="Z12" t="n">
-        <v>208.582</v>
+        <v>117833105.0114324</v>
       </c>
       <c r="AA12" t="n">
         <v>3.76118759844843e-07</v>
@@ -3064,10 +2980,8 @@
       <c r="K13" t="n">
         <v>87.34812609311159</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = 21.590x + -10161.857</t>
-        </is>
+      <c r="W13" t="n">
+        <v>21.59034050245337</v>
       </c>
       <c r="X13" t="n">
         <v>-10161.85739058252</v>
@@ -3076,7 +2990,7 @@
         <v>429.4439812672068</v>
       </c>
       <c r="Z13" t="n">
-        <v>213.7740000000001</v>
+        <v>175380791.5834915</v>
       </c>
       <c r="AA13" t="n">
         <v>3.749219490547249e-07</v>
@@ -3116,10 +3030,8 @@
       <c r="K14" t="n">
         <v>87.54149542254061</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = 23.291x + -10932.964</t>
-        </is>
+      <c r="W14" t="n">
+        <v>23.29082960857156</v>
       </c>
       <c r="X14" t="n">
         <v>-10932.96353878005</v>
@@ -3128,7 +3040,7 @@
         <v>425.9360495064776</v>
       </c>
       <c r="Z14" t="n">
-        <v>206.2859999999999</v>
+        <v>231850658.248151</v>
       </c>
       <c r="AA14" t="n">
         <v>3.720419380982052e-07</v>
@@ -3168,10 +3080,8 @@
       <c r="K15" t="n">
         <v>87.37337984018964</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = 21.798x + -10062.847</t>
-        </is>
+      <c r="W15" t="n">
+        <v>21.79821705208842</v>
       </c>
       <c r="X15" t="n">
         <v>-10062.84740667248</v>
@@ -3180,7 +3090,7 @@
         <v>422.5053683915358</v>
       </c>
       <c r="Z15" t="n">
-        <v>210.5310000000001</v>
+        <v>115035712.5850869</v>
       </c>
       <c r="AA15" t="n">
         <v>3.700733224478628e-07</v>
@@ -3220,10 +3130,8 @@
       <c r="K16" t="n">
         <v>87.41554703304374</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = 22.154x + -10140.976</t>
-        </is>
+      <c r="W16" t="n">
+        <v>22.15436528183677</v>
       </c>
       <c r="X16" t="n">
         <v>-10140.97625424357</v>
@@ -3232,7 +3140,7 @@
         <v>419.1506147717284</v>
       </c>
       <c r="Z16" t="n">
-        <v>206.84</v>
+        <v>194254551.8520578</v>
       </c>
       <c r="AA16" t="n">
         <v>3.680147787927724e-07</v>
@@ -3272,10 +3180,8 @@
       <c r="K17" t="n">
         <v>87.00610323156411</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = 19.120x + -8545.573</t>
-        </is>
+      <c r="W17" t="n">
+        <v>19.12010580011504</v>
       </c>
       <c r="X17" t="n">
         <v>-8545.572680046193</v>
@@ -3284,7 +3190,7 @@
         <v>415.8752996081886</v>
       </c>
       <c r="Z17" t="n">
-        <v>212.756</v>
+        <v>113149192.4884365</v>
       </c>
       <c r="AA17" t="n">
         <v>3.662335020716312e-07</v>
@@ -3324,10 +3230,8 @@
       <c r="K18" t="n">
         <v>87.54195876112072</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = 23.295x + -10518.961</t>
-        </is>
+      <c r="W18" t="n">
+        <v>23.29522530219045</v>
       </c>
       <c r="X18" t="n">
         <v>-10518.96137799515</v>
@@ -3336,7 +3240,7 @@
         <v>412.6466910559025</v>
       </c>
       <c r="Z18" t="n">
-        <v>202.6950000000001</v>
+        <v>224736200.9780773</v>
       </c>
       <c r="AA18" t="n">
         <v>3.643023645097892e-07</v>
@@ -3376,10 +3280,8 @@
       <c r="K19" t="n">
         <v>87.61957944655116</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = 24.056x + -10802.088</t>
-        </is>
+      <c r="W19" t="n">
+        <v>24.05575344467231</v>
       </c>
       <c r="X19" t="n">
         <v>-10802.08755314234</v>
@@ -3388,7 +3290,7 @@
         <v>409.4551609776633</v>
       </c>
       <c r="Z19" t="n">
-        <v>201.413</v>
+        <v>222919474.3622769</v>
       </c>
       <c r="AA19" t="n">
         <v>3.633735453588941e-07</v>
@@ -3428,10 +3330,8 @@
       <c r="K20" t="n">
         <v>87.54282346394551</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = 23.303x + -10333.879</t>
-        </is>
+      <c r="W20" t="n">
+        <v>23.30343316986745</v>
       </c>
       <c r="X20" t="n">
         <v>-10333.87876575362</v>
@@ -3440,7 +3340,7 @@
         <v>406.3600839261352</v>
       </c>
       <c r="Z20" t="n">
-        <v>202.188</v>
+        <v>663848237.5938212</v>
       </c>
       <c r="AA20" t="n">
         <v>3.617354002147274e-07</v>
@@ -3480,10 +3380,8 @@
       <c r="K21" t="n">
         <v>87.52906141133336</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = 23.173x + -10176.646</t>
-        </is>
+      <c r="W21" t="n">
+        <v>23.17348346630436</v>
       </c>
       <c r="X21" t="n">
         <v>-10176.64596798434</v>
@@ -3492,7 +3390,7 @@
         <v>403.2808176775151</v>
       </c>
       <c r="Z21" t="n">
-        <v>201.159</v>
+        <v>109812062.8511681</v>
       </c>
       <c r="AA21" t="n">
         <v>3.599258221389223e-07</v>
@@ -3532,10 +3430,8 @@
       <c r="K22" t="n">
         <v>87.58295513147668</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = 23.691x + -10345.331</t>
-        </is>
+      <c r="W22" t="n">
+        <v>23.69082520203667</v>
       </c>
       <c r="X22" t="n">
         <v>-10345.33052685845</v>
@@ -3544,7 +3440,7 @@
         <v>400.2005045956716</v>
       </c>
       <c r="Z22" t="n">
-        <v>203.246</v>
+        <v>870186794.0575885</v>
       </c>
       <c r="AA22" t="n">
         <v>3.594996674257935e-07</v>
@@ -3670,12 +3566,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -3730,10 +3626,8 @@
       <c r="K2" t="n">
         <v>84.60611152146957</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 10.591x + -6757.919</t>
-        </is>
+      <c r="W2" t="n">
+        <v>10.5909525989069</v>
       </c>
       <c r="X2" t="n">
         <v>-6757.919165589063</v>
@@ -3742,7 +3636,7 @@
         <v>536.6848260996646</v>
       </c>
       <c r="Z2" t="n">
-        <v>460.1</v>
+        <v>589286338.9800715</v>
       </c>
       <c r="AA2" t="n">
         <v>6.871695977063213e-07</v>
@@ -3782,10 +3676,8 @@
       <c r="K3" t="n">
         <v>85.66777575705275</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 13.200x + -7718.584</t>
-        </is>
+      <c r="W3" t="n">
+        <v>13.20027447754708</v>
       </c>
       <c r="X3" t="n">
         <v>-7718.58434488335</v>
@@ -3794,7 +3686,7 @@
         <v>512.4986315999361</v>
       </c>
       <c r="Z3" t="n">
-        <v>364.144</v>
+        <v>48174490.39845841</v>
       </c>
       <c r="AA3" t="n">
         <v>5.584673222971136e-07</v>
@@ -3834,10 +3726,8 @@
       <c r="K4" t="n">
         <v>86.06107784966113</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 14.523x + -8224.408</t>
-        </is>
+      <c r="W4" t="n">
+        <v>14.52313237965902</v>
       </c>
       <c r="X4" t="n">
         <v>-8224.407501363354</v>
@@ -3846,7 +3736,7 @@
         <v>503.443943654204</v>
       </c>
       <c r="Z4" t="n">
-        <v>319.514</v>
+        <v>37943666.38081218</v>
       </c>
       <c r="AA4" t="n">
         <v>5.082483036017803e-07</v>
@@ -3886,10 +3776,8 @@
       <c r="K5" t="n">
         <v>86.35405494977601</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 15.694x + -8750.737</t>
-        </is>
+      <c r="W5" t="n">
+        <v>15.6937152902109</v>
       </c>
       <c r="X5" t="n">
         <v>-8750.737407184411</v>
@@ -3898,7 +3786,7 @@
         <v>497.1263969792354</v>
       </c>
       <c r="Z5" t="n">
-        <v>292.909</v>
+        <v>36136651.60595468</v>
       </c>
       <c r="AA5" t="n">
         <v>4.812910557211444e-07</v>
@@ -3938,10 +3826,8 @@
       <c r="K6" t="n">
         <v>86.56163916493065</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 16.644x + -9159.621</t>
-        </is>
+      <c r="W6" t="n">
+        <v>16.64368175398435</v>
       </c>
       <c r="X6" t="n">
         <v>-9159.621420920957</v>
@@ -3950,7 +3836,7 @@
         <v>491.2163573691311</v>
       </c>
       <c r="Z6" t="n">
-        <v>277.218</v>
+        <v>134309084.697485</v>
       </c>
       <c r="AA6" t="n">
         <v>4.631455767424235e-07</v>
@@ -3990,10 +3876,8 @@
       <c r="K7" t="n">
         <v>86.62097055897429</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 16.937x + -9169.790</t>
-        </is>
+      <c r="W7" t="n">
+        <v>16.93662005737464</v>
       </c>
       <c r="X7" t="n">
         <v>-9169.78964253145</v>
@@ -4002,7 +3886,7 @@
         <v>485.4364083442069</v>
       </c>
       <c r="Z7" t="n">
-        <v>267.169</v>
+        <v>265477180.1549042</v>
       </c>
       <c r="AA7" t="n">
         <v>4.500455495922638e-07</v>
@@ -4042,10 +3926,8 @@
       <c r="K8" t="n">
         <v>86.88720245361314</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 18.388x + -9885.402</t>
-        </is>
+      <c r="W8" t="n">
+        <v>18.38840987531621</v>
       </c>
       <c r="X8" t="n">
         <v>-9885.402018134655</v>
@@ -4054,7 +3936,7 @@
         <v>479.7942909356152</v>
       </c>
       <c r="Z8" t="n">
-        <v>255.1600000000001</v>
+        <v>131023940.34062</v>
       </c>
       <c r="AA8" t="n">
         <v>4.389724878764684e-07</v>
@@ -4094,10 +3976,8 @@
       <c r="K9" t="n">
         <v>86.74861304721674</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 17.603x + -9258.924</t>
-        </is>
+      <c r="W9" t="n">
+        <v>17.60303050451797</v>
       </c>
       <c r="X9" t="n">
         <v>-9258.92408894535</v>
@@ -4106,7 +3986,7 @@
         <v>464.4180728158482</v>
       </c>
       <c r="Z9" t="n">
-        <v>251.974</v>
+        <v>3892.381706851974</v>
       </c>
       <c r="AA9" t="n">
         <v>1.172201301024176e-06</v>
@@ -4146,10 +4026,8 @@
       <c r="K10" t="n">
         <v>86.80272453991049</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 17.902x + -9296.457</t>
-        </is>
+      <c r="W10" t="n">
+        <v>17.90158382468181</v>
       </c>
       <c r="X10" t="n">
         <v>-9296.456844935376</v>
@@ -4158,7 +4036,7 @@
         <v>450.9331247486803</v>
       </c>
       <c r="Z10" t="n">
-        <v>247.93</v>
+        <v>3850.192004271824</v>
       </c>
       <c r="AA10" t="n">
         <v>9.042976841967091e-07</v>
@@ -4198,10 +4076,8 @@
       <c r="K11" t="n">
         <v>87.04481260445652</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 19.371x + -10002.052</t>
-        </is>
+      <c r="W11" t="n">
+        <v>19.37100952744106</v>
       </c>
       <c r="X11" t="n">
         <v>-10002.05164744971</v>
@@ -4210,7 +4086,7 @@
         <v>451.1993374767339</v>
       </c>
       <c r="Z11" t="n">
-        <v>235.55</v>
+        <v>7672.813938747323</v>
       </c>
       <c r="AA11" t="n">
         <v>3.584885292294679e-07</v>
@@ -4336,12 +4212,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -4396,10 +4272,8 @@
       <c r="K2" t="n">
         <v>85.95626256722102</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 14.145x + -7763.767</t>
-        </is>
+      <c r="W2" t="n">
+        <v>14.14548245783472</v>
       </c>
       <c r="X2" t="n">
         <v>-7763.767418940207</v>
@@ -4408,7 +4282,7 @@
         <v>480.2951757214407</v>
       </c>
       <c r="Z2" t="n">
-        <v>332.0350000000001</v>
+        <v>58206032.58323675</v>
       </c>
       <c r="AA2" t="n">
         <v>4.992013584057573e-07</v>
@@ -4448,10 +4322,8 @@
       <c r="K3" t="n">
         <v>86.48127321041933</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 16.263x + -8434.634</t>
-        </is>
+      <c r="W3" t="n">
+        <v>16.26262353659398</v>
       </c>
       <c r="X3" t="n">
         <v>-8434.634266655097</v>
@@ -4460,7 +4332,7 @@
         <v>466.0520934308912</v>
       </c>
       <c r="Z3" t="n">
-        <v>280.237</v>
+        <v>516752350.111385</v>
       </c>
       <c r="AA3" t="n">
         <v>4.480406649797358e-07</v>
@@ -4500,10 +4372,8 @@
       <c r="K4" t="n">
         <v>86.78649210241561</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 17.811x + -9104.597</t>
-        </is>
+      <c r="W4" t="n">
+        <v>17.81096882872391</v>
       </c>
       <c r="X4" t="n">
         <v>-9104.597151980255</v>
@@ -4512,7 +4382,7 @@
         <v>440.2287237932851</v>
       </c>
       <c r="Z4" t="n">
-        <v>257.74</v>
+        <v>3771.878876273001</v>
       </c>
       <c r="AA4" t="n">
         <v>9.89915647613028e-07</v>
@@ -4552,10 +4422,8 @@
       <c r="K5" t="n">
         <v>86.35824109805462</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 15.712x + -7782.179</t>
-        </is>
+      <c r="W5" t="n">
+        <v>15.71180374738322</v>
       </c>
       <c r="X5" t="n">
         <v>-7782.179053414251</v>
@@ -4564,7 +4432,7 @@
         <v>455.2898977755081</v>
       </c>
       <c r="Z5" t="n">
-        <v>258.3969999999999</v>
+        <v>233476585.7749151</v>
       </c>
       <c r="AA5" t="n">
         <v>4.214796704370467e-07</v>
@@ -4604,10 +4472,8 @@
       <c r="K6" t="n">
         <v>87.01682231696586</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 19.189x + -9593.137</t>
-        </is>
+      <c r="W6" t="n">
+        <v>19.1889327159228</v>
       </c>
       <c r="X6" t="n">
         <v>-9593.136762940996</v>
@@ -4616,7 +4482,7 @@
         <v>450.9861210411568</v>
       </c>
       <c r="Z6" t="n">
-        <v>239.8799999999999</v>
+        <v>126545179.3254542</v>
       </c>
       <c r="AA6" t="n">
         <v>4.129222500315576e-07</v>
@@ -4656,10 +4522,8 @@
       <c r="K7" t="n">
         <v>87.11128161283676</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 19.818x + -9806.389</t>
-        </is>
+      <c r="W7" t="n">
+        <v>19.81751633429429</v>
       </c>
       <c r="X7" t="n">
         <v>-9806.389472830584</v>
@@ -4668,7 +4532,7 @@
         <v>446.8889649155186</v>
       </c>
       <c r="Z7" t="n">
-        <v>231.3179999999999</v>
+        <v>122458875.3100242</v>
       </c>
       <c r="AA7" t="n">
         <v>4.067916761251468e-07</v>
@@ -4708,10 +4572,8 @@
       <c r="K8" t="n">
         <v>87.15781820780296</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 20.143x + -9869.027</t>
-        </is>
+      <c r="W8" t="n">
+        <v>20.14254544709857</v>
       </c>
       <c r="X8" t="n">
         <v>-9869.027485010618</v>
@@ -4720,7 +4582,7 @@
         <v>442.8712218178521</v>
       </c>
       <c r="Z8" t="n">
-        <v>228.917</v>
+        <v>122392902.8602818</v>
       </c>
       <c r="AA8" t="n">
         <v>4.024624242343295e-07</v>
@@ -4760,10 +4622,8 @@
       <c r="K9" t="n">
         <v>87.21211455630632</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 20.535x + -9966.374</t>
-        </is>
+      <c r="W9" t="n">
+        <v>20.53547611323334</v>
       </c>
       <c r="X9" t="n">
         <v>-9966.373567261111</v>
@@ -4772,7 +4632,7 @@
         <v>439.1164588465697</v>
       </c>
       <c r="Z9" t="n">
-        <v>225.077</v>
+        <v>358891114.3223209</v>
       </c>
       <c r="AA9" t="n">
         <v>3.981809757220652e-07</v>
@@ -4812,10 +4672,8 @@
       <c r="K10" t="n">
         <v>87.25805920057836</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 20.880x + -10037.105</t>
-        </is>
+      <c r="W10" t="n">
+        <v>20.88011291202754</v>
       </c>
       <c r="X10" t="n">
         <v>-10037.10526332246</v>
@@ -4824,7 +4682,7 @@
         <v>435.6279289492796</v>
       </c>
       <c r="Z10" t="n">
-        <v>219.884</v>
+        <v>135088959.5285163</v>
       </c>
       <c r="AA10" t="n">
         <v>3.942594878233831e-07</v>
@@ -4864,10 +4722,8 @@
       <c r="K11" t="n">
         <v>87.23514555078835</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 20.707x + -9852.044</t>
-        </is>
+      <c r="W11" t="n">
+        <v>20.70680400200393</v>
       </c>
       <c r="X11" t="n">
         <v>-9852.044214779651</v>
@@ -4876,7 +4732,7 @@
         <v>432.426126761333</v>
       </c>
       <c r="Z11" t="n">
-        <v>220.128</v>
+        <v>353362037.112519</v>
       </c>
       <c r="AA11" t="n">
         <v>3.915712377291921e-07</v>
@@ -4916,10 +4772,8 @@
       <c r="K12" t="n">
         <v>87.22943828442875</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = 20.664x + -9738.147</t>
-        </is>
+      <c r="W12" t="n">
+        <v>20.66408230488827</v>
       </c>
       <c r="X12" t="n">
         <v>-9738.146833238899</v>
@@ -4928,7 +4782,7 @@
         <v>429.3655616654337</v>
       </c>
       <c r="Z12" t="n">
-        <v>218.152</v>
+        <v>350392262.7494087</v>
       </c>
       <c r="AA12" t="n">
         <v>3.887829210702251e-07</v>
@@ -4968,10 +4822,8 @@
       <c r="K13" t="n">
         <v>87.3222287501108</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = 21.381x + -10018.553</t>
-        </is>
+      <c r="W13" t="n">
+        <v>21.38123538406983</v>
       </c>
       <c r="X13" t="n">
         <v>-10018.55328220722</v>
@@ -4980,7 +4832,7 @@
         <v>426.3164300355821</v>
       </c>
       <c r="Z13" t="n">
-        <v>212.123</v>
+        <v>580420486.7926364</v>
       </c>
       <c r="AA13" t="n">
         <v>3.855688000858838e-07</v>
@@ -5020,10 +4872,8 @@
       <c r="K14" t="n">
         <v>87.41672760765853</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = 22.165x + -10335.154</t>
-        </is>
+      <c r="W14" t="n">
+        <v>22.16450373431897</v>
       </c>
       <c r="X14" t="n">
         <v>-10335.15395494345</v>
@@ -5032,7 +4882,7 @@
         <v>423.2760786268939</v>
       </c>
       <c r="Z14" t="n">
-        <v>210.152</v>
+        <v>119273868.8902068</v>
       </c>
       <c r="AA14" t="n">
         <v>3.831347269447549e-07</v>
@@ -5072,10 +4922,8 @@
       <c r="K15" t="n">
         <v>87.08785412480184</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = 19.658x + -8970.084</t>
-        </is>
+      <c r="W15" t="n">
+        <v>19.65781776517757</v>
       </c>
       <c r="X15" t="n">
         <v>-8970.084037679289</v>
@@ -5084,7 +4932,7 @@
         <v>420.1909075974667</v>
       </c>
       <c r="Z15" t="n">
-        <v>216.568</v>
+        <v>114419301.9815577</v>
       </c>
       <c r="AA15" t="n">
         <v>3.815828381615512e-07</v>
@@ -5124,10 +4972,8 @@
       <c r="K16" t="n">
         <v>87.32531571405592</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = 21.406x + -9770.702</t>
-        </is>
+      <c r="W16" t="n">
+        <v>21.4059483032814</v>
       </c>
       <c r="X16" t="n">
         <v>-9770.701640971984</v>
@@ -5136,7 +4982,7 @@
         <v>417.1214845417246</v>
       </c>
       <c r="Z16" t="n">
-        <v>211.1</v>
+        <v>170335906.1875667</v>
       </c>
       <c r="AA16" t="n">
         <v>3.79570601572069e-07</v>
@@ -5176,10 +5022,8 @@
       <c r="K17" t="n">
         <v>87.44751334825065</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = 22.432x + -10197.687</t>
-        </is>
+      <c r="W17" t="n">
+        <v>22.43219200770721</v>
       </c>
       <c r="X17" t="n">
         <v>-10197.68748450432</v>
@@ -5188,7 +5032,7 @@
         <v>414.0538608169979</v>
       </c>
       <c r="Z17" t="n">
-        <v>207.197</v>
+        <v>189662324.7506776</v>
       </c>
       <c r="AA17" t="n">
         <v>3.774134290660462e-07</v>
@@ -5228,10 +5072,8 @@
       <c r="K18" t="n">
         <v>87.52417100540225</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = 23.128x + -10453.667</t>
-        </is>
+      <c r="W18" t="n">
+        <v>23.12765295142246</v>
       </c>
       <c r="X18" t="n">
         <v>-10453.6666009086</v>
@@ -5240,7 +5082,7 @@
         <v>411.0115831455041</v>
       </c>
       <c r="Z18" t="n">
-        <v>203.219</v>
+        <v>335463998.5325902</v>
       </c>
       <c r="AA18" t="n">
         <v>3.75005320023306e-07</v>
@@ -5280,10 +5122,8 @@
       <c r="K19" t="n">
         <v>87.37354170745235</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = 21.800x + -9699.760</t>
-        </is>
+      <c r="W19" t="n">
+        <v>21.79956234889971</v>
       </c>
       <c r="X19" t="n">
         <v>-9699.759956167509</v>
@@ -5292,7 +5132,7 @@
         <v>407.8691435991047</v>
       </c>
       <c r="Z19" t="n">
-        <v>205.833</v>
+        <v>166791579.8430284</v>
       </c>
       <c r="AA19" t="n">
         <v>3.733618963832413e-07</v>
@@ -5332,10 +5172,8 @@
       <c r="K20" t="n">
         <v>87.44335165990118</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = 22.396x + -9910.234</t>
-        </is>
+      <c r="W20" t="n">
+        <v>22.39562869768338</v>
       </c>
       <c r="X20" t="n">
         <v>-9910.233625440118</v>
@@ -5344,7 +5182,7 @@
         <v>404.7743525593904</v>
       </c>
       <c r="Z20" t="n">
-        <v>205.568</v>
+        <v>220966175.5117127</v>
       </c>
       <c r="AA20" t="n">
         <v>3.722562336146518e-07</v>
@@ -5384,10 +5222,8 @@
       <c r="K21" t="n">
         <v>87.6263570578039</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = 24.125x + -10659.979</t>
-        </is>
+      <c r="W21" t="n">
+        <v>24.12452033487193</v>
       </c>
       <c r="X21" t="n">
         <v>-10659.97893321486</v>
@@ -5396,7 +5232,7 @@
         <v>401.6864719294056</v>
       </c>
       <c r="Z21" t="n">
-        <v>200.7020000000001</v>
+        <v>218430394.4754781</v>
       </c>
       <c r="AA21" t="n">
         <v>3.70075288371997e-07</v>
@@ -5436,10 +5272,8 @@
       <c r="K22" t="n">
         <v>87.50042163574763</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = 22.908x + -9967.246</t>
-        </is>
+      <c r="W22" t="n">
+        <v>22.90763392616027</v>
       </c>
       <c r="X22" t="n">
         <v>-9967.246164742723</v>
@@ -5448,7 +5282,7 @@
         <v>398.5548574235218</v>
       </c>
       <c r="Z22" t="n">
-        <v>199.958</v>
+        <v>433419073.6183606</v>
       </c>
       <c r="AA22" t="n">
         <v>3.67800067085379e-07</v>
@@ -5574,12 +5408,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -5634,10 +5468,8 @@
       <c r="K2" t="n">
         <v>83.2286754759028</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 8.422x + -5594.038</t>
-        </is>
+      <c r="W2" t="n">
+        <v>8.422101355625013</v>
       </c>
       <c r="X2" t="n">
         <v>-5594.038148614398</v>
@@ -5646,7 +5478,7 @@
         <v>543.1549205509359</v>
       </c>
       <c r="Z2" t="n">
-        <v>562.266</v>
+        <v>186265100.5781556</v>
       </c>
       <c r="AA2" t="n">
         <v>9.000562484580156e-07</v>
@@ -5686,10 +5518,8 @@
       <c r="K3" t="n">
         <v>85.0734179252637</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 11.601x + -6793.990</t>
-        </is>
+      <c r="W3" t="n">
+        <v>11.60124906408612</v>
       </c>
       <c r="X3" t="n">
         <v>-6793.990321478196</v>
@@ -5698,7 +5528,7 @@
         <v>510.9396929138588</v>
       </c>
       <c r="Z3" t="n">
-        <v>405.046</v>
+        <v>280770929.6339918</v>
       </c>
       <c r="AA3" t="n">
         <v>6.244166002873013e-07</v>
@@ -5738,10 +5568,8 @@
       <c r="K4" t="n">
         <v>85.68063584767771</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 13.240x + -7493.782</t>
-        </is>
+      <c r="W4" t="n">
+        <v>13.23972577131781</v>
       </c>
       <c r="X4" t="n">
         <v>-7493.781817736216</v>
@@ -5750,7 +5578,7 @@
         <v>500.6049367462784</v>
       </c>
       <c r="Z4" t="n">
-        <v>350.2140000000001</v>
+        <v>53375387.1332188</v>
       </c>
       <c r="AA4" t="n">
         <v>5.527798103117413e-07</v>
@@ -5790,10 +5618,8 @@
       <c r="K5" t="n">
         <v>86.08381995169948</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 14.608x + -8129.460</t>
-        </is>
+      <c r="W5" t="n">
+        <v>14.60773689230128</v>
       </c>
       <c r="X5" t="n">
         <v>-8129.460176005873</v>
@@ -5802,7 +5628,7 @@
         <v>494.0450278191379</v>
       </c>
       <c r="Z5" t="n">
-        <v>313.629</v>
+        <v>46786109.65925075</v>
       </c>
       <c r="AA5" t="n">
         <v>5.137677306838621e-07</v>
@@ -5842,10 +5668,8 @@
       <c r="K6" t="n">
         <v>86.32011709446074</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 15.549x + -8528.743</t>
-        </is>
+      <c r="W6" t="n">
+        <v>15.54858614599184</v>
       </c>
       <c r="X6" t="n">
         <v>-8528.742698678667</v>
@@ -5854,7 +5678,7 @@
         <v>487.943646383955</v>
       </c>
       <c r="Z6" t="n">
-        <v>293.726</v>
+        <v>33367211.02390506</v>
       </c>
       <c r="AA6" t="n">
         <v>4.901749361239819e-07</v>
@@ -5894,10 +5718,8 @@
       <c r="K7" t="n">
         <v>86.52516603865126</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 16.469x + -8919.202</t>
-        </is>
+      <c r="W7" t="n">
+        <v>16.46856123014045</v>
       </c>
       <c r="X7" t="n">
         <v>-8919.202352188366</v>
@@ -5906,7 +5728,7 @@
         <v>481.8661609590969</v>
       </c>
       <c r="Z7" t="n">
-        <v>278.4590000000001</v>
+        <v>792603942.9823534</v>
       </c>
       <c r="AA7" t="n">
         <v>4.73924482176603e-07</v>
@@ -5946,10 +5768,8 @@
       <c r="K8" t="n">
         <v>86.72920435807227</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 17.498x + -9365.715</t>
-        </is>
+      <c r="W8" t="n">
+        <v>17.49835000588874</v>
       </c>
       <c r="X8" t="n">
         <v>-9365.715433468496</v>
@@ -5958,7 +5778,7 @@
         <v>475.8994573007008</v>
       </c>
       <c r="Z8" t="n">
-        <v>264.2569999999999</v>
+        <v>130349566.0779665</v>
       </c>
       <c r="AA8" t="n">
         <v>4.59654215334174e-07</v>
@@ -5998,10 +5818,8 @@
       <c r="K9" t="n">
         <v>86.72363030343634</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 17.469x + -9178.008</t>
-        </is>
+      <c r="W9" t="n">
+        <v>17.46851540983855</v>
       </c>
       <c r="X9" t="n">
         <v>-9178.008238206097</v>
@@ -6010,7 +5828,7 @@
         <v>470.2342682494343</v>
       </c>
       <c r="Z9" t="n">
-        <v>259.361</v>
+        <v>192582098.4404453</v>
       </c>
       <c r="AA9" t="n">
         <v>4.488018763383606e-07</v>
@@ -6050,10 +5868,8 @@
       <c r="K10" t="n">
         <v>86.82480654129405</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 18.026x + -9343.367</t>
-        </is>
+      <c r="W10" t="n">
+        <v>18.02633899289433</v>
       </c>
       <c r="X10" t="n">
         <v>-9343.367392363531</v>
@@ -6062,7 +5878,7 @@
         <v>443.8763524390018</v>
       </c>
       <c r="Z10" t="n">
-        <v>248.358</v>
+        <v>3816.204478538165</v>
       </c>
       <c r="AA10" t="n">
         <v>1.679564945875143e-06</v>
@@ -6102,10 +5918,8 @@
       <c r="K11" t="n">
         <v>86.88813597581999</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 18.394x + -9412.102</t>
-        </is>
+      <c r="W11" t="n">
+        <v>18.39393704756781</v>
       </c>
       <c r="X11" t="n">
         <v>-9412.102212550497</v>
@@ -6114,7 +5928,7 @@
         <v>439.9090000652595</v>
       </c>
       <c r="Z11" t="n">
-        <v>243.711</v>
+        <v>3778.608686157441</v>
       </c>
       <c r="AA11" t="n">
         <v>1.073043167800002e-06</v>
@@ -6240,12 +6054,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -6300,10 +6114,8 @@
       <c r="K2" t="n">
         <v>84.97403041664072</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 11.371x + -6270.930</t>
-        </is>
+      <c r="W2" t="n">
+        <v>11.37069061908078</v>
       </c>
       <c r="X2" t="n">
         <v>-6270.929668642305</v>
@@ -6312,7 +6124,7 @@
         <v>480.7329810792613</v>
       </c>
       <c r="Z2" t="n">
-        <v>402.6819999999999</v>
+        <v>74281673.71447983</v>
       </c>
       <c r="AA2" t="n">
         <v>6.10816213591845e-07</v>
@@ -6352,10 +6164,8 @@
       <c r="K3" t="n">
         <v>86.21937729737456</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 15.133x + -7908.508</t>
-        </is>
+      <c r="W3" t="n">
+        <v>15.13311587404684</v>
       </c>
       <c r="X3" t="n">
         <v>-7908.507524896489</v>
@@ -6364,7 +6174,7 @@
         <v>466.6743280794358</v>
       </c>
       <c r="Z3" t="n">
-        <v>304.586</v>
+        <v>1146789125.444086</v>
       </c>
       <c r="AA3" t="n">
         <v>4.93953090122737e-07</v>
@@ -6404,10 +6214,8 @@
       <c r="K4" t="n">
         <v>86.56353036166978</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 16.653x + -8555.418</t>
-        </is>
+      <c r="W4" t="n">
+        <v>16.6528633143862</v>
       </c>
       <c r="X4" t="n">
         <v>-8555.417740161829</v>
@@ -6416,7 +6224,7 @@
         <v>441.7462578815397</v>
       </c>
       <c r="Z4" t="n">
-        <v>275.384</v>
+        <v>3784.671871658175</v>
       </c>
       <c r="AA4" t="n">
         <v>9.920763789529094e-07</v>
@@ -6456,10 +6264,8 @@
       <c r="K5" t="n">
         <v>86.69176337968138</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 17.300x + -8769.938</t>
-        </is>
+      <c r="W5" t="n">
+        <v>17.29987900364074</v>
       </c>
       <c r="X5" t="n">
         <v>-8769.937580096921</v>
@@ -6468,7 +6274,7 @@
         <v>456.5841396445374</v>
       </c>
       <c r="Z5" t="n">
-        <v>261.417</v>
+        <v>124610153.8380714</v>
       </c>
       <c r="AA5" t="n">
         <v>4.478528728625239e-07</v>
@@ -6508,10 +6314,8 @@
       <c r="K6" t="n">
         <v>86.86121345923347</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 18.236x + -9162.047</t>
-        </is>
+      <c r="W6" t="n">
+        <v>18.23585350489639</v>
       </c>
       <c r="X6" t="n">
         <v>-9162.047188881685</v>
@@ -6520,7 +6324,7 @@
         <v>452.2941937652293</v>
       </c>
       <c r="Z6" t="n">
-        <v>250.0599999999999</v>
+        <v>370159327.3551711</v>
       </c>
       <c r="AA6" t="n">
         <v>4.379485607529913e-07</v>
@@ -6560,10 +6364,8 @@
       <c r="K7" t="n">
         <v>86.86744460857412</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 18.272x + -9049.733</t>
-        </is>
+      <c r="W7" t="n">
+        <v>18.27220011263456</v>
       </c>
       <c r="X7" t="n">
         <v>-9049.732686986781</v>
@@ -6572,7 +6374,7 @@
         <v>447.9608253751574</v>
       </c>
       <c r="Z7" t="n">
-        <v>244.102</v>
+        <v>170780600.7147736</v>
       </c>
       <c r="AA7" t="n">
         <v>4.290502484936856e-07</v>
@@ -6612,10 +6414,8 @@
       <c r="K8" t="n">
         <v>86.86641320059545</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 18.266x + -8927.371</t>
-        </is>
+      <c r="W8" t="n">
+        <v>18.26617388483119</v>
       </c>
       <c r="X8" t="n">
         <v>-8927.370516560044</v>
@@ -6624,7 +6424,7 @@
         <v>443.8211181574397</v>
       </c>
       <c r="Z8" t="n">
-        <v>239.6659999999999</v>
+        <v>363229513.4700153</v>
       </c>
       <c r="AA8" t="n">
         <v>4.22975977742907e-07</v>
@@ -6664,10 +6464,8 @@
       <c r="K9" t="n">
         <v>86.91368979123239</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 18.547x + -8965.883</t>
-        </is>
+      <c r="W9" t="n">
+        <v>18.5465325606511</v>
       </c>
       <c r="X9" t="n">
         <v>-8965.882849277941</v>
@@ -6676,7 +6474,7 @@
         <v>439.9561516169117</v>
       </c>
       <c r="Z9" t="n">
-        <v>234.5579999999999</v>
+        <v>723148207.1356236</v>
       </c>
       <c r="AA9" t="n">
         <v>4.170676493982838e-07</v>
@@ -6716,10 +6514,8 @@
       <c r="K10" t="n">
         <v>86.94806930354042</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 18.756x + -8968.914</t>
-        </is>
+      <c r="W10" t="n">
+        <v>18.75585872139407</v>
       </c>
       <c r="X10" t="n">
         <v>-8968.913603131734</v>
@@ -6728,7 +6524,7 @@
         <v>436.3600211278208</v>
       </c>
       <c r="Z10" t="n">
-        <v>227.726</v>
+        <v>358460681.8910872</v>
       </c>
       <c r="AA10" t="n">
         <v>4.115320442145009e-07</v>
@@ -6768,10 +6564,8 @@
       <c r="K11" t="n">
         <v>87.11608184377877</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 19.851x + -9466.038</t>
-        </is>
+      <c r="W11" t="n">
+        <v>19.85055815957696</v>
       </c>
       <c r="X11" t="n">
         <v>-9466.037951180724</v>
@@ -6780,7 +6574,7 @@
         <v>432.97046668927</v>
       </c>
       <c r="Z11" t="n">
-        <v>226.396</v>
+        <v>236014137.9245085</v>
       </c>
       <c r="AA11" t="n">
         <v>4.083913633849018e-07</v>
@@ -6820,10 +6614,8 @@
       <c r="K12" t="n">
         <v>87.22113248913811</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = 20.602x + -9759.613</t>
-        </is>
+      <c r="W12" t="n">
+        <v>20.60222261724563</v>
       </c>
       <c r="X12" t="n">
         <v>-9759.613103107598</v>
@@ -6832,7 +6624,7 @@
         <v>429.7823712461693</v>
       </c>
       <c r="Z12" t="n">
-        <v>218.4560000000001</v>
+        <v>117324768.0826236</v>
       </c>
       <c r="AA12" t="n">
         <v>4.040091939319597e-07</v>
@@ -6872,10 +6664,8 @@
       <c r="K13" t="n">
         <v>87.20388616141652</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = 20.475x + -9605.001</t>
-        </is>
+      <c r="W13" t="n">
+        <v>20.47494874847089</v>
       </c>
       <c r="X13" t="n">
         <v>-9605.001358597106</v>
@@ -6884,7 +6674,7 @@
         <v>426.7265578770754</v>
       </c>
       <c r="Z13" t="n">
-        <v>218.275</v>
+        <v>116197004.0089286</v>
       </c>
       <c r="AA13" t="n">
         <v>4.017211680390725e-07</v>
@@ -6924,10 +6714,8 @@
       <c r="K14" t="n">
         <v>87.28877204326189</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = 21.117x + -9858.038</t>
-        </is>
+      <c r="W14" t="n">
+        <v>21.11700272736227</v>
       </c>
       <c r="X14" t="n">
         <v>-9858.038022428444</v>
@@ -6936,7 +6724,7 @@
         <v>423.717404171028</v>
       </c>
       <c r="Z14" t="n">
-        <v>216.824</v>
+        <v>174275636.4765854</v>
       </c>
       <c r="AA14" t="n">
         <v>3.993079744260538e-07</v>
@@ -6976,10 +6764,8 @@
       <c r="K15" t="n">
         <v>87.27853165704568</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = 21.037x + -9717.500</t>
-        </is>
+      <c r="W15" t="n">
+        <v>21.03742435549335</v>
       </c>
       <c r="X15" t="n">
         <v>-9717.500210802407</v>
@@ -6988,7 +6774,7 @@
         <v>420.8301510651199</v>
       </c>
       <c r="Z15" t="n">
-        <v>211.552</v>
+        <v>118699947.6321774</v>
       </c>
       <c r="AA15" t="n">
         <v>3.950350635438924e-07</v>
@@ -7028,10 +6814,8 @@
       <c r="K16" t="n">
         <v>87.37663320905385</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = 21.825x + -10047.448</t>
-        </is>
+      <c r="W16" t="n">
+        <v>21.82528800418178</v>
       </c>
       <c r="X16" t="n">
         <v>-10047.4484867406</v>
@@ -7040,7 +6824,7 @@
         <v>417.8883155073642</v>
       </c>
       <c r="Z16" t="n">
-        <v>210.8699999999999</v>
+        <v>113886404.4804137</v>
       </c>
       <c r="AA16" t="n">
         <v>3.936691830738516e-07</v>
@@ -7080,10 +6864,8 @@
       <c r="K17" t="n">
         <v>87.29573909794998</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = 21.171x + -9621.750</t>
-        </is>
+      <c r="W17" t="n">
+        <v>21.17148818119123</v>
       </c>
       <c r="X17" t="n">
         <v>-9621.749888657463</v>
@@ -7092,7 +6874,7 @@
         <v>414.9342646853236</v>
       </c>
       <c r="Z17" t="n">
-        <v>209.307</v>
+        <v>225863530.1406434</v>
       </c>
       <c r="AA17" t="n">
         <v>3.909898706607735e-07</v>
@@ -7132,10 +6914,8 @@
       <c r="K18" t="n">
         <v>87.36062890868665</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = 21.693x + -9796.621</t>
-        </is>
+      <c r="W18" t="n">
+        <v>21.69276074669611</v>
       </c>
       <c r="X18" t="n">
         <v>-9796.620626035796</v>
@@ -7144,7 +6924,7 @@
         <v>411.9720116088964</v>
       </c>
       <c r="Z18" t="n">
-        <v>205.398</v>
+        <v>224301672.8987534</v>
       </c>
       <c r="AA18" t="n">
         <v>3.885281668279745e-07</v>
@@ -7184,10 +6964,8 @@
       <c r="K19" t="n">
         <v>87.42040333435118</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = 22.196x + -9966.494</t>
-        </is>
+      <c r="W19" t="n">
+        <v>22.19612925718187</v>
       </c>
       <c r="X19" t="n">
         <v>-9966.493890533791</v>
@@ -7196,7 +6974,7 @@
         <v>408.9261837758424</v>
       </c>
       <c r="Z19" t="n">
-        <v>206.718</v>
+        <v>336717429.4957645</v>
       </c>
       <c r="AA19" t="n">
         <v>3.872646030629363e-07</v>
@@ -7236,10 +7014,8 @@
       <c r="K20" t="n">
         <v>87.36357714126802</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = 21.717x + -9633.625</t>
-        </is>
+      <c r="W20" t="n">
+        <v>21.71705344331145</v>
       </c>
       <c r="X20" t="n">
         <v>-9633.625039364226</v>
@@ -7248,7 +7024,7 @@
         <v>405.9261632735991</v>
       </c>
       <c r="Z20" t="n">
-        <v>203.48</v>
+        <v>167472087.5035553</v>
       </c>
       <c r="AA20" t="n">
         <v>3.846101172966364e-07</v>
@@ -7288,10 +7064,8 @@
       <c r="K21" t="n">
         <v>87.37559569964908</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = 21.817x + -9599.512</t>
-        </is>
+      <c r="W21" t="n">
+        <v>21.81664770973818</v>
       </c>
       <c r="X21" t="n">
         <v>-9599.512453267755</v>
@@ -7300,7 +7074,7 @@
         <v>402.8799496509758</v>
       </c>
       <c r="Z21" t="n">
-        <v>202.8820000000001</v>
+        <v>164336307.8858424</v>
       </c>
       <c r="AA21" t="n">
         <v>3.8283198706333e-07</v>
@@ -7340,10 +7114,8 @@
       <c r="K22" t="n">
         <v>87.39131217537374</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = 21.948x + -9575.315</t>
-        </is>
+      <c r="W22" t="n">
+        <v>21.94826922092168</v>
       </c>
       <c r="X22" t="n">
         <v>-9575.315285342263</v>
@@ -7352,7 +7124,7 @@
         <v>399.8123011185766</v>
       </c>
       <c r="Z22" t="n">
-        <v>202.72</v>
+        <v>435006457.8718216</v>
       </c>
       <c r="AA22" t="n">
         <v>3.81027561082448e-07</v>
@@ -7478,12 +7250,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -7624,12 +7396,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -7684,10 +7456,8 @@
       <c r="K2" t="n">
         <v>85.36780758400076</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 12.342x + -6748.483</t>
-        </is>
+      <c r="W2" t="n">
+        <v>12.34208059193906</v>
       </c>
       <c r="X2" t="n">
         <v>-6748.482591283335</v>
@@ -7696,7 +7466,7 @@
         <v>481.3169627103698</v>
       </c>
       <c r="Z2" t="n">
-        <v>366.1239999999999</v>
+        <v>16419334.8726047</v>
       </c>
       <c r="AA2" t="n">
         <v>5.669450557150221e-07</v>
@@ -7736,10 +7506,8 @@
       <c r="K3" t="n">
         <v>86.24270524471871</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 15.227x + -7954.308</t>
-        </is>
+      <c r="W3" t="n">
+        <v>15.22734540983481</v>
       </c>
       <c r="X3" t="n">
         <v>-7954.308330172933</v>
@@ -7748,7 +7516,7 @@
         <v>468.5931932505256</v>
       </c>
       <c r="Z3" t="n">
-        <v>296.5</v>
+        <v>159877891.2432903</v>
       </c>
       <c r="AA3" t="n">
         <v>4.873475088148432e-07</v>
@@ -7788,10 +7556,8 @@
       <c r="K4" t="n">
         <v>86.49591963575499</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 16.331x + -8381.350</t>
-        </is>
+      <c r="W4" t="n">
+        <v>16.33076923701559</v>
       </c>
       <c r="X4" t="n">
         <v>-8381.349611913041</v>
@@ -7800,7 +7566,7 @@
         <v>442.0128795856027</v>
       </c>
       <c r="Z4" t="n">
-        <v>273.1660000000001</v>
+        <v>3801.263534749723</v>
       </c>
       <c r="AA4" t="n">
         <v>1.062851142884898e-06</v>
@@ -7840,10 +7606,8 @@
       <c r="K5" t="n">
         <v>86.70390905726283</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 17.364x + -8819.308</t>
-        </is>
+      <c r="W5" t="n">
+        <v>17.36376851073928</v>
       </c>
       <c r="X5" t="n">
         <v>-8819.308046089296</v>
@@ -7852,7 +7616,7 @@
         <v>458.1390253610684</v>
       </c>
       <c r="Z5" t="n">
-        <v>257.358</v>
+        <v>250286990.6666235</v>
       </c>
       <c r="AA5" t="n">
         <v>4.477011926842336e-07</v>
@@ -7892,10 +7656,8 @@
       <c r="K6" t="n">
         <v>86.82408465951286</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 18.022x + -9051.571</t>
-        </is>
+      <c r="W6" t="n">
+        <v>18.02223322550936</v>
       </c>
       <c r="X6" t="n">
         <v>-9051.57053567746</v>
@@ -7904,7 +7666,7 @@
         <v>453.4836180409301</v>
       </c>
       <c r="Z6" t="n">
-        <v>247.627</v>
+        <v>185543068.2052857</v>
       </c>
       <c r="AA6" t="n">
         <v>4.378649357911211e-07</v>
@@ -7944,10 +7706,8 @@
       <c r="K7" t="n">
         <v>86.84822348474556</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 18.161x + -8990.707</t>
-        </is>
+      <c r="W7" t="n">
+        <v>18.16054395931161</v>
       </c>
       <c r="X7" t="n">
         <v>-8990.707432323008</v>
@@ -7956,7 +7716,7 @@
         <v>449.0052073497969</v>
       </c>
       <c r="Z7" t="n">
-        <v>238.378</v>
+        <v>122834849.4659618</v>
       </c>
       <c r="AA7" t="n">
         <v>4.295566039130984e-07</v>
@@ -7996,10 +7756,8 @@
       <c r="K8" t="n">
         <v>87.07437942212684</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 19.567x + -9667.665</t>
-        </is>
+      <c r="W8" t="n">
+        <v>19.56712211995582</v>
       </c>
       <c r="X8" t="n">
         <v>-9667.665045701837</v>
@@ -8008,7 +7766,7 @@
         <v>444.7540789640374</v>
       </c>
       <c r="Z8" t="n">
-        <v>237.4060000000001</v>
+        <v>181863100.6548848</v>
       </c>
       <c r="AA8" t="n">
         <v>4.254248137776638e-07</v>
@@ -8048,10 +7806,8 @@
       <c r="K9" t="n">
         <v>87.01837713022248</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 19.199x + -9336.990</t>
-        </is>
+      <c r="W9" t="n">
+        <v>19.19895718333372</v>
       </c>
       <c r="X9" t="n">
         <v>-9336.989697992338</v>
@@ -8060,7 +7816,7 @@
         <v>440.9192743489919</v>
       </c>
       <c r="Z9" t="n">
-        <v>231.886</v>
+        <v>163536237.4030253</v>
       </c>
       <c r="AA9" t="n">
         <v>4.197342568742096e-07</v>
@@ -8100,10 +7856,8 @@
       <c r="K10" t="n">
         <v>87.05324217330423</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 19.427x + -9355.329</t>
-        </is>
+      <c r="W10" t="n">
+        <v>19.42652097738906</v>
       </c>
       <c r="X10" t="n">
         <v>-9355.328574205456</v>
@@ -8112,7 +7866,7 @@
         <v>437.2768084047943</v>
       </c>
       <c r="Z10" t="n">
-        <v>228.221</v>
+        <v>180768141.8999214</v>
       </c>
       <c r="AA10" t="n">
         <v>4.153048812850813e-07</v>
@@ -8152,10 +7906,8 @@
       <c r="K11" t="n">
         <v>87.05817622417544</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 19.459x + -9268.528</t>
-        </is>
+      <c r="W11" t="n">
+        <v>19.4591607757565</v>
       </c>
       <c r="X11" t="n">
         <v>-9268.527996519775</v>
@@ -8164,7 +7916,7 @@
         <v>433.926388333696</v>
       </c>
       <c r="Z11" t="n">
-        <v>223.821</v>
+        <v>354594046.7493199</v>
       </c>
       <c r="AA11" t="n">
         <v>4.108080852274275e-07</v>
@@ -8204,10 +7956,8 @@
       <c r="K12" t="n">
         <v>87.16366452366474</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = 20.184x + -9562.297</t>
-        </is>
+      <c r="W12" t="n">
+        <v>20.18413181362069</v>
       </c>
       <c r="X12" t="n">
         <v>-9562.296871914776</v>
@@ -8216,7 +7966,7 @@
         <v>430.7946570849169</v>
       </c>
       <c r="Z12" t="n">
-        <v>219.738</v>
+        <v>176191282.6818075</v>
       </c>
       <c r="AA12" t="n">
         <v>4.07338253062954e-07</v>
@@ -8256,10 +8006,8 @@
       <c r="K13" t="n">
         <v>87.15239682727612</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = 20.104x + -9433.777</t>
-        </is>
+      <c r="W13" t="n">
+        <v>20.10413422417657</v>
       </c>
       <c r="X13" t="n">
         <v>-9433.776914746522</v>
@@ -8268,7 +8016,7 @@
         <v>427.7582624629842</v>
       </c>
       <c r="Z13" t="n">
-        <v>216.857</v>
+        <v>582235796.8971089</v>
       </c>
       <c r="AA13" t="n">
         <v>4.042887200040525e-07</v>
@@ -8308,10 +8056,8 @@
       <c r="K14" t="n">
         <v>87.22555644851892</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = 20.635x + -9622.311</t>
-        </is>
+      <c r="W14" t="n">
+        <v>20.63512520391754</v>
       </c>
       <c r="X14" t="n">
         <v>-9622.311120797718</v>
@@ -8320,7 +8066,7 @@
         <v>424.742500254259</v>
       </c>
       <c r="Z14" t="n">
-        <v>214.232</v>
+        <v>231370192.64752</v>
       </c>
       <c r="AA14" t="n">
         <v>4.016765652232231e-07</v>
@@ -8360,10 +8106,8 @@
       <c r="K15" t="n">
         <v>86.68831508228989</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = 17.282x + -7835.620</t>
-        </is>
+      <c r="W15" t="n">
+        <v>17.2818253563226</v>
       </c>
       <c r="X15" t="n">
         <v>-7835.619852268862</v>
@@ -8372,7 +8116,7 @@
         <v>421.7272234711429</v>
       </c>
       <c r="Z15" t="n">
-        <v>221.498</v>
+        <v>459203866.0416507</v>
       </c>
       <c r="AA15" t="n">
         <v>3.987137550482963e-07</v>
@@ -8412,10 +8156,8 @@
       <c r="K16" t="n">
         <v>87.26625806343664</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = 20.943x + -9609.411</t>
-        </is>
+      <c r="W16" t="n">
+        <v>20.94283077297428</v>
       </c>
       <c r="X16" t="n">
         <v>-9609.411179678706</v>
@@ -8424,7 +8166,7 @@
         <v>418.6073312970457</v>
       </c>
       <c r="Z16" t="n">
-        <v>211.868</v>
+        <v>341638582.3541558</v>
       </c>
       <c r="AA16" t="n">
         <v>3.968436105843079e-07</v>
@@ -8464,10 +8206,8 @@
       <c r="K17" t="n">
         <v>87.36962013998401</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = 21.767x + -9943.823</t>
-        </is>
+      <c r="W17" t="n">
+        <v>21.76701631896348</v>
       </c>
       <c r="X17" t="n">
         <v>-9943.823040689851</v>
@@ -8476,7 +8216,7 @@
         <v>415.4988262863592</v>
       </c>
       <c r="Z17" t="n">
-        <v>209.069</v>
+        <v>678122195.9628119</v>
       </c>
       <c r="AA17" t="n">
         <v>3.944747448839126e-07</v>
@@ -8516,10 +8256,8 @@
       <c r="K18" t="n">
         <v>87.20830633647073</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = 20.507x + -9214.628</t>
-        </is>
+      <c r="W18" t="n">
+        <v>20.50741885717805</v>
       </c>
       <c r="X18" t="n">
         <v>-9214.62778707721</v>
@@ -8528,7 +8266,7 @@
         <v>412.3408510988346</v>
       </c>
       <c r="Z18" t="n">
-        <v>208.9879999999999</v>
+        <v>1009164193.7573</v>
       </c>
       <c r="AA18" t="n">
         <v>3.922775108507422e-07</v>
@@ -8568,10 +8306,8 @@
       <c r="K19" t="n">
         <v>87.43245571536816</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = 22.300x + -10016.940</t>
-        </is>
+      <c r="W19" t="n">
+        <v>22.30046132747842</v>
       </c>
       <c r="X19" t="n">
         <v>-10016.93989251047</v>
@@ -8580,7 +8316,7 @@
         <v>409.146220039869</v>
       </c>
       <c r="Z19" t="n">
-        <v>201.794</v>
+        <v>111675322.944287</v>
       </c>
       <c r="AA19" t="n">
         <v>3.89463031729073e-07</v>
@@ -8620,10 +8356,8 @@
       <c r="K20" t="n">
         <v>87.24302465416277</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = 20.766x + -9168.850</t>
-        </is>
+      <c r="W20" t="n">
+        <v>20.76607339002453</v>
       </c>
       <c r="X20" t="n">
         <v>-9168.849542788153</v>
@@ -8632,7 +8366,7 @@
         <v>405.8704923241809</v>
       </c>
       <c r="Z20" t="n">
-        <v>205.635</v>
+        <v>331483536.4798995</v>
       </c>
       <c r="AA20" t="n">
         <v>3.879106575621827e-07</v>
@@ -8672,10 +8406,8 @@
       <c r="K21" t="n">
         <v>87.42690252177401</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = 22.252x + -9813.809</t>
-        </is>
+      <c r="W21" t="n">
+        <v>22.25226847656322</v>
       </c>
       <c r="X21" t="n">
         <v>-9813.809394455837</v>
@@ -8684,7 +8416,7 @@
         <v>402.6115395092147</v>
       </c>
       <c r="Z21" t="n">
-        <v>204.341</v>
+        <v>328927971.9372172</v>
       </c>
       <c r="AA21" t="n">
         <v>3.868962096896977e-07</v>
@@ -8724,10 +8456,8 @@
       <c r="K22" t="n">
         <v>87.27172274305212</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = 20.985x + -9099.908</t>
-        </is>
+      <c r="W22" t="n">
+        <v>20.98484247191181</v>
       </c>
       <c r="X22" t="n">
         <v>-9099.907935646037</v>
@@ -8736,7 +8466,7 @@
         <v>399.4009964319251</v>
       </c>
       <c r="Z22" t="n">
-        <v>203.105</v>
+        <v>163014039.1037835</v>
       </c>
       <c r="AA22" t="n">
         <v>3.84126071669241e-07</v>
@@ -8862,12 +8592,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -8922,10 +8652,8 @@
       <c r="K2" t="n">
         <v>84.08290098419012</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 9.649x + -5985.534</t>
-        </is>
+      <c r="W2" t="n">
+        <v>9.64863735957964</v>
       </c>
       <c r="X2" t="n">
         <v>-5985.534406047734</v>
@@ -8934,7 +8662,7 @@
         <v>517.0072749278866</v>
       </c>
       <c r="Z2" t="n">
-        <v>493.3709999999999</v>
+        <v>424364260.9700205</v>
       </c>
       <c r="AA2" t="n">
         <v>7.372089456214138e-07</v>
@@ -8974,10 +8702,8 @@
       <c r="K3" t="n">
         <v>85.38886327510725</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 12.399x + -6817.849</t>
-        </is>
+      <c r="W3" t="n">
+        <v>12.39868361975104</v>
       </c>
       <c r="X3" t="n">
         <v>-6817.848939904364</v>
@@ -8986,7 +8712,7 @@
         <v>487.5256646728903</v>
       </c>
       <c r="Z3" t="n">
-        <v>369.8169999999999</v>
+        <v>401099383.0753671</v>
       </c>
       <c r="AA3" t="n">
         <v>5.505983538172226e-07</v>
@@ -9026,10 +8752,8 @@
       <c r="K4" t="n">
         <v>86.04545356274795</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 14.466x + -7736.705</t>
-        </is>
+      <c r="W4" t="n">
+        <v>14.46557039402282</v>
       </c>
       <c r="X4" t="n">
         <v>-7736.704617183487</v>
@@ -9038,7 +8762,7 @@
         <v>477.6740464688352</v>
       </c>
       <c r="Z4" t="n">
-        <v>316.712</v>
+        <v>264626087.1599844</v>
       </c>
       <c r="AA4" t="n">
         <v>4.957459364143968e-07</v>
@@ -9078,10 +8802,8 @@
       <c r="K5" t="n">
         <v>86.37443048586742</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 15.782x + -8310.461</t>
-        </is>
+      <c r="W5" t="n">
+        <v>15.78215113178104</v>
       </c>
       <c r="X5" t="n">
         <v>-8310.46069717217</v>
@@ -9090,7 +8812,7 @@
         <v>470.9872411527926</v>
       </c>
       <c r="Z5" t="n">
-        <v>290.949</v>
+        <v>257756903.5772153</v>
       </c>
       <c r="AA5" t="n">
         <v>4.690264968634016e-07</v>
@@ -9130,10 +8852,8 @@
       <c r="K6" t="n">
         <v>86.62510124543059</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 16.957x + -8818.705</t>
-        </is>
+      <c r="W6" t="n">
+        <v>16.95739764315634</v>
       </c>
       <c r="X6" t="n">
         <v>-8818.705085613392</v>
@@ -9142,7 +8862,7 @@
         <v>464.8602776880605</v>
       </c>
       <c r="Z6" t="n">
-        <v>272.147</v>
+        <v>254079897.3065849</v>
       </c>
       <c r="AA6" t="n">
         <v>4.517866403552614e-07</v>
@@ -9182,10 +8902,8 @@
       <c r="K7" t="n">
         <v>86.73955288943954</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 17.554x + -8990.702</t>
-        </is>
+      <c r="W7" t="n">
+        <v>17.55400973710982</v>
       </c>
       <c r="X7" t="n">
         <v>-8990.702303374113</v>
@@ -9194,7 +8912,7 @@
         <v>440.5670897046683</v>
       </c>
       <c r="Z7" t="n">
-        <v>261.033</v>
+        <v>3760.852508810734</v>
       </c>
       <c r="AA7" t="n">
         <v>1.58174486006174e-06</v>
@@ -9234,10 +8952,8 @@
       <c r="K8" t="n">
         <v>86.83360894459653</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 18.077x + -9110.545</t>
-        </is>
+      <c r="W8" t="n">
+        <v>18.07655388747258</v>
       </c>
       <c r="X8" t="n">
         <v>-9110.545228760877</v>
@@ -9246,7 +8962,7 @@
         <v>452.7456342089746</v>
       </c>
       <c r="Z8" t="n">
-        <v>249.523</v>
+        <v>246904518.6869225</v>
       </c>
       <c r="AA8" t="n">
         <v>4.294520224850721e-07</v>
@@ -9286,10 +9002,8 @@
       <c r="K9" t="n">
         <v>86.75578467338379</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 17.642x + -8721.405</t>
-        </is>
+      <c r="W9" t="n">
+        <v>17.64202714084421</v>
       </c>
       <c r="X9" t="n">
         <v>-8721.405395930318</v>
@@ -9298,7 +9012,7 @@
         <v>447.0348010388421</v>
       </c>
       <c r="Z9" t="n">
-        <v>251.2169999999999</v>
+        <v>121838407.0186928</v>
       </c>
       <c r="AA9" t="n">
         <v>4.240480861238635e-07</v>
@@ -9338,10 +9052,8 @@
       <c r="K10" t="n">
         <v>86.88368510113125</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 18.368x + -8980.525</t>
-        </is>
+      <c r="W10" t="n">
+        <v>18.3676141474842</v>
       </c>
       <c r="X10" t="n">
         <v>-8980.525195986682</v>
@@ -9350,7 +9062,7 @@
         <v>441.8132763859897</v>
       </c>
       <c r="Z10" t="n">
-        <v>244.867</v>
+        <v>126501952.0246875</v>
       </c>
       <c r="AA10" t="n">
         <v>4.183775092728076e-07</v>
@@ -9390,10 +9102,8 @@
       <c r="K11" t="n">
         <v>86.86890944232314</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 18.281x + -8798.414</t>
-        </is>
+      <c r="W11" t="n">
+        <v>18.28076554225826</v>
       </c>
       <c r="X11" t="n">
         <v>-8798.41393372084</v>
@@ -9402,7 +9112,7 @@
         <v>437.2092957584164</v>
       </c>
       <c r="Z11" t="n">
-        <v>238.592</v>
+        <v>357233911.4357943</v>
       </c>
       <c r="AA11" t="n">
         <v>4.123806631877916e-07</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 45.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 45.xlsx
@@ -428,7 +428,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -559,7 +559,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-273.0309999999999</v>
@@ -609,7 +609,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-253.042</v>
@@ -659,7 +659,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>-244.425</v>
@@ -709,7 +709,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>-237.049</v>
@@ -759,7 +759,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>-232.828</v>
@@ -809,7 +809,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>-226.1440000000001</v>
@@ -859,7 +859,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>-222.697</v>
@@ -909,7 +909,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>-232.307</v>
@@ -959,7 +959,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>-223.849</v>
@@ -1009,7 +1009,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>-217.3030000000001</v>
@@ -1074,7 +1074,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -2270,7 +2270,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -3466,7 +3466,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -3597,7 +3597,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-460.1</v>
@@ -3647,7 +3647,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-364.144</v>
@@ -3697,7 +3697,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>-319.514</v>
@@ -3747,7 +3747,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>-292.909</v>
@@ -3797,7 +3797,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>-277.218</v>
@@ -3847,7 +3847,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>-267.169</v>
@@ -3897,7 +3897,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>-255.1600000000001</v>
@@ -3947,7 +3947,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>-251.974</v>
@@ -3997,7 +3997,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>-247.93</v>
@@ -4047,7 +4047,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>-235.55</v>
@@ -4112,7 +4112,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -5308,7 +5308,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -5439,7 +5439,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-562.266</v>
@@ -5489,7 +5489,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-405.046</v>
@@ -5539,7 +5539,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>-350.2140000000001</v>
@@ -5589,7 +5589,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>-313.629</v>
@@ -5639,7 +5639,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>-293.726</v>
@@ -5689,7 +5689,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>-278.4590000000001</v>
@@ -5739,7 +5739,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>-264.2569999999999</v>
@@ -5789,7 +5789,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>-259.361</v>
@@ -5839,7 +5839,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>-248.358</v>
@@ -5889,7 +5889,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>-243.711</v>
@@ -5954,7 +5954,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -7150,7 +7150,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -7296,7 +7296,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -8492,7 +8492,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -8623,7 +8623,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-493.3709999999999</v>
@@ -8673,7 +8673,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-369.8169999999999</v>
@@ -8723,7 +8723,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>-316.712</v>
@@ -8773,7 +8773,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>-290.949</v>
@@ -8823,7 +8823,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>-272.147</v>
@@ -8873,7 +8873,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>-261.033</v>
@@ -8923,7 +8923,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>-249.523</v>
@@ -8973,7 +8973,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>-251.2169999999999</v>
@@ -9023,7 +9023,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>-244.867</v>
@@ -9073,7 +9073,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>-238.592</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 45.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 45.xlsx
@@ -562,7 +562,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-273.0309999999999</v>
+        <v>107.8630000000001</v>
       </c>
       <c r="D2" t="n">
         <v>2.64063e-07</v>
@@ -612,7 +612,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-253.042</v>
+        <v>101.1759999999999</v>
       </c>
       <c r="D3" t="n">
         <v>2.631e-07</v>
@@ -662,7 +662,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-244.425</v>
+        <v>97.33999999999997</v>
       </c>
       <c r="D4" t="n">
         <v>2.6245e-07</v>
@@ -712,7 +712,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-237.049</v>
+        <v>94.54599999999999</v>
       </c>
       <c r="D5" t="n">
         <v>2.62147e-07</v>
@@ -762,7 +762,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-232.828</v>
+        <v>90.08799999999997</v>
       </c>
       <c r="D6" t="n">
         <v>2.61719e-07</v>
@@ -812,7 +812,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>-226.1440000000001</v>
+        <v>88.339</v>
       </c>
       <c r="D7" t="n">
         <v>2.61617e-07</v>
@@ -862,7 +862,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>-222.697</v>
+        <v>86.74099999999999</v>
       </c>
       <c r="D8" t="n">
         <v>2.61431e-07</v>
@@ -912,7 +912,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-232.307</v>
+        <v>75.55000000000001</v>
       </c>
       <c r="D9" t="n">
         <v>2.6122e-07</v>
@@ -962,7 +962,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-223.849</v>
+        <v>81.28800000000001</v>
       </c>
       <c r="D10" t="n">
         <v>2.61242e-07</v>
@@ -1012,7 +1012,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-217.3030000000001</v>
+        <v>80.596</v>
       </c>
       <c r="D11" t="n">
         <v>2.61085e-07</v>
@@ -1208,7 +1208,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-302.203</v>
+        <v>123.117</v>
       </c>
       <c r="D2" t="n">
         <v>2.72644e-07</v>
@@ -1258,7 +1258,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-264.968</v>
+        <v>103.567</v>
       </c>
       <c r="D3" t="n">
         <v>2.70903e-07</v>
@@ -1308,7 +1308,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-259.959</v>
+        <v>95.75399999999996</v>
       </c>
       <c r="D4" t="n">
         <v>2.70055e-07</v>
@@ -1358,7 +1358,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-249.0699999999999</v>
+        <v>96.40000000000003</v>
       </c>
       <c r="D5" t="n">
         <v>2.69345e-07</v>
@@ -1408,7 +1408,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-242.599</v>
+        <v>93.21000000000004</v>
       </c>
       <c r="D6" t="n">
         <v>2.69164e-07</v>
@@ -1458,7 +1458,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-243.597</v>
+        <v>89.90199999999999</v>
       </c>
       <c r="D7" t="n">
         <v>2.68755e-07</v>
@@ -1508,7 +1508,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-239.779</v>
+        <v>86.86799999999999</v>
       </c>
       <c r="D8" t="n">
         <v>2.68598e-07</v>
@@ -1558,7 +1558,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>-240.252</v>
+        <v>83.68000000000001</v>
       </c>
       <c r="D9" t="n">
         <v>2.6826e-07</v>
@@ -1608,7 +1608,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>-234.1440000000001</v>
+        <v>83.89999999999998</v>
       </c>
       <c r="D10" t="n">
         <v>2.67996e-07</v>
@@ -1658,7 +1658,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>-235.8550000000001</v>
+        <v>80.892</v>
       </c>
       <c r="D11" t="n">
         <v>2.67899e-07</v>
@@ -1708,7 +1708,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>-232.321</v>
+        <v>79.81299999999999</v>
       </c>
       <c r="D12" t="n">
         <v>2.67688e-07</v>
@@ -1758,7 +1758,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>-229.193</v>
+        <v>79.834</v>
       </c>
       <c r="D13" t="n">
         <v>2.67488e-07</v>
@@ -1808,7 +1808,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>-226.787</v>
+        <v>79.64600000000002</v>
       </c>
       <c r="D14" t="n">
         <v>2.67391e-07</v>
@@ -1858,7 +1858,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-228.5439999999999</v>
+        <v>74.56900000000002</v>
       </c>
       <c r="D15" t="n">
         <v>2.67161e-07</v>
@@ -1908,7 +1908,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>-227.6300000000001</v>
+        <v>72.36599999999999</v>
       </c>
       <c r="D16" t="n">
         <v>2.67154e-07</v>
@@ -1958,7 +1958,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>-220.461</v>
+        <v>74.714</v>
       </c>
       <c r="D17" t="n">
         <v>2.67023e-07</v>
@@ -2008,7 +2008,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>-220.907</v>
+        <v>71.79700000000003</v>
       </c>
       <c r="D18" t="n">
         <v>2.66962e-07</v>
@@ -2058,7 +2058,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>-220.714</v>
+        <v>72.14000000000004</v>
       </c>
       <c r="D19" t="n">
         <v>2.66831e-07</v>
@@ -2108,7 +2108,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>-220.716</v>
+        <v>67.97899999999998</v>
       </c>
       <c r="D20" t="n">
         <v>2.6676e-07</v>
@@ -2158,7 +2158,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>-215.333</v>
+        <v>67.697</v>
       </c>
       <c r="D21" t="n">
         <v>2.66757e-07</v>
@@ -2208,7 +2208,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>-213.279</v>
+        <v>67.423</v>
       </c>
       <c r="D22" t="n">
         <v>2.66694e-07</v>
@@ -2404,7 +2404,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-347.697</v>
+        <v>127.235</v>
       </c>
       <c r="D2" t="n">
         <v>2.76249e-07</v>
@@ -2454,7 +2454,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-271.207</v>
+        <v>103.22</v>
       </c>
       <c r="D3" t="n">
         <v>2.69663e-07</v>
@@ -2504,7 +2504,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-245.1329999999999</v>
+        <v>98.11100000000005</v>
       </c>
       <c r="D4" t="n">
         <v>2.67466e-07</v>
@@ -2554,7 +2554,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-233.96</v>
+        <v>94.24499999999995</v>
       </c>
       <c r="D5" t="n">
         <v>2.66165e-07</v>
@@ -2604,7 +2604,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-226.484</v>
+        <v>90.20500000000004</v>
       </c>
       <c r="D6" t="n">
         <v>2.65327e-07</v>
@@ -2654,7 +2654,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-225.373</v>
+        <v>88.66500000000002</v>
       </c>
       <c r="D7" t="n">
         <v>2.64548e-07</v>
@@ -2704,7 +2704,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-223.033</v>
+        <v>85.44799999999998</v>
       </c>
       <c r="D8" t="n">
         <v>2.64146e-07</v>
@@ -2754,7 +2754,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>-214.4809999999999</v>
+        <v>86.50400000000002</v>
       </c>
       <c r="D9" t="n">
         <v>2.63749e-07</v>
@@ -2804,7 +2804,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>-213.393</v>
+        <v>82.78000000000003</v>
       </c>
       <c r="D10" t="n">
         <v>2.63693e-07</v>
@@ -2854,7 +2854,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>-209.535</v>
+        <v>81.62599999999998</v>
       </c>
       <c r="D11" t="n">
         <v>2.63424e-07</v>
@@ -2904,7 +2904,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>-208.582</v>
+        <v>80.48199999999997</v>
       </c>
       <c r="D12" t="n">
         <v>2.63247e-07</v>
@@ -2954,7 +2954,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>-213.7740000000001</v>
+        <v>76.88</v>
       </c>
       <c r="D13" t="n">
         <v>2.6306e-07</v>
@@ -3004,7 +3004,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>-206.2859999999999</v>
+        <v>78.01499999999999</v>
       </c>
       <c r="D14" t="n">
         <v>2.6299e-07</v>
@@ -3054,7 +3054,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-210.5310000000001</v>
+        <v>73.17599999999999</v>
       </c>
       <c r="D15" t="n">
         <v>2.62701e-07</v>
@@ -3104,7 +3104,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>-206.84</v>
+        <v>71.80000000000001</v>
       </c>
       <c r="D16" t="n">
         <v>2.62774e-07</v>
@@ -3154,7 +3154,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>-212.756</v>
+        <v>63.90500000000003</v>
       </c>
       <c r="D17" t="n">
         <v>2.62665e-07</v>
@@ -3204,7 +3204,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>-202.6950000000001</v>
+        <v>70.37099999999998</v>
       </c>
       <c r="D18" t="n">
         <v>2.62561e-07</v>
@@ -3254,7 +3254,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>-201.413</v>
+        <v>70.33600000000001</v>
       </c>
       <c r="D19" t="n">
         <v>2.62665e-07</v>
@@ -3304,7 +3304,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>-202.188</v>
+        <v>67.50400000000002</v>
       </c>
       <c r="D20" t="n">
         <v>2.62544e-07</v>
@@ -3354,7 +3354,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>-201.159</v>
+        <v>65.69799999999998</v>
       </c>
       <c r="D21" t="n">
         <v>2.62416e-07</v>
@@ -3404,7 +3404,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>-203.246</v>
+        <v>65.69800000000004</v>
       </c>
       <c r="D22" t="n">
         <v>2.62309e-07</v>
@@ -3600,7 +3600,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-460.1</v>
+        <v>176.22</v>
       </c>
       <c r="D2" t="n">
         <v>2.79854e-07</v>
@@ -3650,7 +3650,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-364.144</v>
+        <v>133.565</v>
       </c>
       <c r="D3" t="n">
         <v>2.81243e-07</v>
@@ -3700,7 +3700,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-319.514</v>
+        <v>121.0210000000001</v>
       </c>
       <c r="D4" t="n">
         <v>2.78511e-07</v>
@@ -3750,7 +3750,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-292.909</v>
+        <v>115.665</v>
       </c>
       <c r="D5" t="n">
         <v>2.76359e-07</v>
@@ -3800,7 +3800,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-277.218</v>
+        <v>111.664</v>
       </c>
       <c r="D6" t="n">
         <v>2.74397e-07</v>
@@ -3850,7 +3850,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>-267.169</v>
+        <v>106.525</v>
       </c>
       <c r="D7" t="n">
         <v>2.73123e-07</v>
@@ -3900,7 +3900,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>-255.1600000000001</v>
+        <v>106.549</v>
       </c>
       <c r="D8" t="n">
         <v>2.71946e-07</v>
@@ -3950,7 +3950,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-251.974</v>
+        <v>99.30899999999997</v>
       </c>
       <c r="D9" t="n">
         <v>2.71109e-07</v>
@@ -4000,7 +4000,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-247.93</v>
+        <v>96.35899999999998</v>
       </c>
       <c r="D10" t="n">
         <v>2.70458e-07</v>
@@ -4050,7 +4050,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-235.55</v>
+        <v>97.024</v>
       </c>
       <c r="D11" t="n">
         <v>2.69936e-07</v>
@@ -4246,7 +4246,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-332.0350000000001</v>
+        <v>122.251</v>
       </c>
       <c r="D2" t="n">
         <v>2.76224e-07</v>
@@ -4296,7 +4296,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-280.237</v>
+        <v>100.185</v>
       </c>
       <c r="D3" t="n">
         <v>2.73656e-07</v>
@@ -4346,7 +4346,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-257.74</v>
+        <v>96.005</v>
       </c>
       <c r="D4" t="n">
         <v>2.7226e-07</v>
@@ -4396,7 +4396,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-258.3969999999999</v>
+        <v>83.81100000000004</v>
       </c>
       <c r="D5" t="n">
         <v>2.71316e-07</v>
@@ -4446,7 +4446,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-239.8799999999999</v>
+        <v>89.99099999999999</v>
       </c>
       <c r="D6" t="n">
         <v>2.70379e-07</v>
@@ -4496,7 +4496,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-231.3179999999999</v>
+        <v>88.84500000000003</v>
       </c>
       <c r="D7" t="n">
         <v>2.69961e-07</v>
@@ -4546,7 +4546,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-228.917</v>
+        <v>86.53199999999998</v>
       </c>
       <c r="D8" t="n">
         <v>2.69501e-07</v>
@@ -4596,7 +4596,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>-225.077</v>
+        <v>84.29000000000002</v>
       </c>
       <c r="D9" t="n">
         <v>2.69065e-07</v>
@@ -4646,7 +4646,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>-219.884</v>
+        <v>82.62300000000005</v>
       </c>
       <c r="D10" t="n">
         <v>2.68862e-07</v>
@@ -4696,7 +4696,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>-220.128</v>
+        <v>79.98599999999999</v>
       </c>
       <c r="D11" t="n">
         <v>2.685e-07</v>
@@ -4746,7 +4746,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>-218.152</v>
+        <v>78.154</v>
       </c>
       <c r="D12" t="n">
         <v>2.68248e-07</v>
@@ -4796,7 +4796,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>-212.123</v>
+        <v>78.22499999999997</v>
       </c>
       <c r="D13" t="n">
         <v>2.68049e-07</v>
@@ -4846,7 +4846,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>-210.152</v>
+        <v>77.61399999999998</v>
       </c>
       <c r="D14" t="n">
         <v>2.6773e-07</v>
@@ -4896,7 +4896,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-216.568</v>
+        <v>70.72300000000001</v>
       </c>
       <c r="D15" t="n">
         <v>2.67571e-07</v>
@@ -4946,7 +4946,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>-211.1</v>
+        <v>73.56799999999998</v>
       </c>
       <c r="D16" t="n">
         <v>2.67374e-07</v>
@@ -4996,7 +4996,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>-207.197</v>
+        <v>73.66899999999998</v>
       </c>
       <c r="D17" t="n">
         <v>2.67279e-07</v>
@@ -5046,7 +5046,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>-203.219</v>
+        <v>73.53999999999996</v>
       </c>
       <c r="D18" t="n">
         <v>2.67075e-07</v>
@@ -5096,7 +5096,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>-205.833</v>
+        <v>69.43700000000001</v>
       </c>
       <c r="D19" t="n">
         <v>2.66953e-07</v>
@@ -5146,7 +5146,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>-205.568</v>
+        <v>69.13500000000005</v>
       </c>
       <c r="D20" t="n">
         <v>2.66861e-07</v>
@@ -5196,7 +5196,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>-200.7020000000001</v>
+        <v>70.59499999999997</v>
       </c>
       <c r="D21" t="n">
         <v>2.66724e-07</v>
@@ -5246,7 +5246,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>-199.958</v>
+        <v>66.67299999999994</v>
       </c>
       <c r="D22" t="n">
         <v>2.66594e-07</v>
@@ -5442,7 +5442,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-562.266</v>
+        <v>203.4469999999999</v>
       </c>
       <c r="D2" t="n">
         <v>2.84316e-07</v>
@@ -5492,7 +5492,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-405.046</v>
+        <v>140.4449999999999</v>
       </c>
       <c r="D3" t="n">
         <v>2.87624e-07</v>
@@ -5542,7 +5542,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-350.2140000000001</v>
+        <v>125.5309999999999</v>
       </c>
       <c r="D4" t="n">
         <v>2.84392e-07</v>
@@ -5592,7 +5592,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-313.629</v>
+        <v>119.874</v>
       </c>
       <c r="D5" t="n">
         <v>2.81587e-07</v>
@@ -5642,7 +5642,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-293.726</v>
+        <v>115.61</v>
       </c>
       <c r="D6" t="n">
         <v>2.79529e-07</v>
@@ -5692,7 +5692,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>-278.4590000000001</v>
+        <v>112.884</v>
       </c>
       <c r="D7" t="n">
         <v>2.78141e-07</v>
@@ -5742,7 +5742,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>-264.2569999999999</v>
+        <v>110.67</v>
       </c>
       <c r="D8" t="n">
         <v>2.76923e-07</v>
@@ -5792,7 +5792,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-259.361</v>
+        <v>104.707</v>
       </c>
       <c r="D9" t="n">
         <v>2.75833e-07</v>
@@ -5842,7 +5842,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-248.358</v>
+        <v>101.419</v>
       </c>
       <c r="D10" t="n">
         <v>2.75131e-07</v>
@@ -5892,7 +5892,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-243.711</v>
+        <v>97.31200000000001</v>
       </c>
       <c r="D11" t="n">
         <v>2.74475e-07</v>
@@ -6088,7 +6088,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-402.6819999999999</v>
+        <v>125.5210000000001</v>
       </c>
       <c r="D2" t="n">
         <v>2.93977e-07</v>
@@ -6138,7 +6138,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-304.586</v>
+        <v>103.521</v>
       </c>
       <c r="D3" t="n">
         <v>2.84886e-07</v>
@@ -6188,7 +6188,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-275.384</v>
+        <v>97.38899999999995</v>
       </c>
       <c r="D4" t="n">
         <v>2.81455e-07</v>
@@ -6238,7 +6238,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-261.417</v>
+        <v>94.255</v>
       </c>
       <c r="D5" t="n">
         <v>2.79294e-07</v>
@@ -6288,7 +6288,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-250.0599999999999</v>
+        <v>92.601</v>
       </c>
       <c r="D6" t="n">
         <v>2.78271e-07</v>
@@ -6338,7 +6338,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-244.102</v>
+        <v>88.86799999999999</v>
       </c>
       <c r="D7" t="n">
         <v>2.77066e-07</v>
@@ -6388,7 +6388,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-239.6659999999999</v>
+        <v>85.39500000000004</v>
       </c>
       <c r="D8" t="n">
         <v>2.76493e-07</v>
@@ -6438,7 +6438,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>-234.5579999999999</v>
+        <v>83.005</v>
       </c>
       <c r="D9" t="n">
         <v>2.75846e-07</v>
@@ -6488,7 +6488,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>-227.726</v>
+        <v>79.952</v>
       </c>
       <c r="D10" t="n">
         <v>2.75517e-07</v>
@@ -6538,7 +6538,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>-226.396</v>
+        <v>80.97499999999997</v>
       </c>
       <c r="D11" t="n">
         <v>2.74867e-07</v>
@@ -6588,7 +6588,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>-218.4560000000001</v>
+        <v>80.16699999999997</v>
       </c>
       <c r="D12" t="n">
         <v>2.74698e-07</v>
@@ -6638,7 +6638,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>-218.275</v>
+        <v>78.42199999999997</v>
       </c>
       <c r="D13" t="n">
         <v>2.74453e-07</v>
@@ -6688,7 +6688,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>-216.824</v>
+        <v>77.54300000000001</v>
       </c>
       <c r="D14" t="n">
         <v>2.74151e-07</v>
@@ -6738,7 +6738,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-211.552</v>
+        <v>75.66800000000001</v>
       </c>
       <c r="D15" t="n">
         <v>2.73748e-07</v>
@@ -6788,7 +6788,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>-210.8699999999999</v>
+        <v>76.363</v>
       </c>
       <c r="D16" t="n">
         <v>2.73534e-07</v>
@@ -6838,7 +6838,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>-209.307</v>
+        <v>73.23899999999998</v>
       </c>
       <c r="D17" t="n">
         <v>2.73386e-07</v>
@@ -6888,7 +6888,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>-205.398</v>
+        <v>72.40800000000002</v>
       </c>
       <c r="D18" t="n">
         <v>2.73301e-07</v>
@@ -6938,7 +6938,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>-206.718</v>
+        <v>72.01900000000001</v>
       </c>
       <c r="D19" t="n">
         <v>2.73065e-07</v>
@@ -6988,7 +6988,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>-203.48</v>
+        <v>69.64600000000002</v>
       </c>
       <c r="D20" t="n">
         <v>2.73002e-07</v>
@@ -7038,7 +7038,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>-202.8820000000001</v>
+        <v>68.39400000000001</v>
       </c>
       <c r="D21" t="n">
         <v>2.7283e-07</v>
@@ -7088,7 +7088,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>-202.72</v>
+        <v>67.209</v>
       </c>
       <c r="D22" t="n">
         <v>2.72657e-07</v>
@@ -7430,7 +7430,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-366.1239999999999</v>
+        <v>118.316</v>
       </c>
       <c r="D2" t="n">
         <v>2.90962e-07</v>
@@ -7480,7 +7480,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-296.5</v>
+        <v>101.064</v>
       </c>
       <c r="D3" t="n">
         <v>2.84504e-07</v>
@@ -7530,7 +7530,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-273.1660000000001</v>
+        <v>95.32999999999998</v>
       </c>
       <c r="D4" t="n">
         <v>2.81687e-07</v>
@@ -7580,7 +7580,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-257.358</v>
+        <v>92.99799999999999</v>
       </c>
       <c r="D5" t="n">
         <v>2.80065e-07</v>
@@ -7630,7 +7630,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-247.627</v>
+        <v>90.89699999999999</v>
       </c>
       <c r="D6" t="n">
         <v>2.78988e-07</v>
@@ -7680,7 +7680,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-238.378</v>
+        <v>87.29400000000004</v>
       </c>
       <c r="D7" t="n">
         <v>2.78413e-07</v>
@@ -7730,7 +7730,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-237.4060000000001</v>
+        <v>88.53699999999998</v>
       </c>
       <c r="D8" t="n">
         <v>2.77561e-07</v>
@@ -7780,7 +7780,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>-231.886</v>
+        <v>84.02199999999999</v>
       </c>
       <c r="D9" t="n">
         <v>2.77305e-07</v>
@@ -7830,7 +7830,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>-228.221</v>
+        <v>82.19300000000004</v>
       </c>
       <c r="D10" t="n">
         <v>2.76884e-07</v>
@@ -7880,7 +7880,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>-223.821</v>
+        <v>79.88600000000002</v>
       </c>
       <c r="D11" t="n">
         <v>2.76525e-07</v>
@@ -7930,7 +7930,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>-219.738</v>
+        <v>79.03700000000003</v>
       </c>
       <c r="D12" t="n">
         <v>2.76262e-07</v>
@@ -7980,7 +7980,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>-216.857</v>
+        <v>77.45600000000002</v>
       </c>
       <c r="D13" t="n">
         <v>2.76021e-07</v>
@@ -8030,7 +8030,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>-214.232</v>
+        <v>75.98400000000004</v>
       </c>
       <c r="D14" t="n">
         <v>2.75885e-07</v>
@@ -8080,7 +8080,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-221.498</v>
+        <v>66.12299999999999</v>
       </c>
       <c r="D15" t="n">
         <v>2.75449e-07</v>
@@ -8130,7 +8130,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>-211.868</v>
+        <v>73.81999999999999</v>
       </c>
       <c r="D16" t="n">
         <v>2.75362e-07</v>
@@ -8180,7 +8180,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>-209.069</v>
+        <v>73.86700000000002</v>
       </c>
       <c r="D17" t="n">
         <v>2.75127e-07</v>
@@ -8230,7 +8230,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>-208.9879999999999</v>
+        <v>69.31600000000003</v>
       </c>
       <c r="D18" t="n">
         <v>2.752e-07</v>
@@ -8280,7 +8280,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>-201.794</v>
+        <v>71.404</v>
       </c>
       <c r="D19" t="n">
         <v>2.75054e-07</v>
@@ -8330,7 +8330,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>-205.635</v>
+        <v>66.90200000000004</v>
       </c>
       <c r="D20" t="n">
         <v>2.74906e-07</v>
@@ -8380,7 +8380,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>-204.341</v>
+        <v>68.47899999999998</v>
       </c>
       <c r="D21" t="n">
         <v>2.74804e-07</v>
@@ -8430,7 +8430,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>-203.105</v>
+        <v>63.71500000000003</v>
       </c>
       <c r="D22" t="n">
         <v>2.74796e-07</v>
@@ -8626,7 +8626,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-493.3709999999999</v>
+        <v>175.804</v>
       </c>
       <c r="D2" t="n">
         <v>2.85579e-07</v>
@@ -8676,7 +8676,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-369.8169999999999</v>
+        <v>119.131</v>
       </c>
       <c r="D3" t="n">
         <v>2.84088e-07</v>
@@ -8726,7 +8726,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-316.712</v>
+        <v>108.834</v>
       </c>
       <c r="D4" t="n">
         <v>2.80278e-07</v>
@@ -8776,7 +8776,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-290.949</v>
+        <v>104.93</v>
       </c>
       <c r="D5" t="n">
         <v>2.77441e-07</v>
@@ -8826,7 +8826,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-272.147</v>
+        <v>102.597</v>
       </c>
       <c r="D6" t="n">
         <v>2.75699e-07</v>
@@ -8876,7 +8876,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>-261.033</v>
+        <v>98.27800000000002</v>
       </c>
       <c r="D7" t="n">
         <v>2.74648e-07</v>
@@ -8926,7 +8926,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>-249.523</v>
+        <v>95.08199999999999</v>
       </c>
       <c r="D8" t="n">
         <v>2.7384e-07</v>
@@ -8976,7 +8976,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-251.2169999999999</v>
+        <v>89.55800000000005</v>
       </c>
       <c r="D9" t="n">
         <v>2.73324e-07</v>
@@ -9026,7 +9026,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-244.867</v>
+        <v>87.34300000000002</v>
       </c>
       <c r="D10" t="n">
         <v>2.73061e-07</v>
@@ -9076,7 +9076,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-238.592</v>
+        <v>83.30200000000002</v>
       </c>
       <c r="D11" t="n">
         <v>2.72774e-07</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 45.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 45.xlsx
@@ -438,7 +438,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -564,6 +564,9 @@
       <c r="B2" t="n">
         <v>107.8630000000001</v>
       </c>
+      <c r="C2" t="n">
+        <v>1248.029358834179</v>
+      </c>
       <c r="D2" t="n">
         <v>2.64063e-07</v>
       </c>
@@ -614,6 +617,9 @@
       <c r="B3" t="n">
         <v>101.1759999999999</v>
       </c>
+      <c r="C3" t="n">
+        <v>1166.83280439228</v>
+      </c>
       <c r="D3" t="n">
         <v>2.631e-07</v>
       </c>
@@ -664,6 +670,9 @@
       <c r="B4" t="n">
         <v>97.33999999999997</v>
       </c>
+      <c r="C4" t="n">
+        <v>1216.407403903457</v>
+      </c>
       <c r="D4" t="n">
         <v>2.6245e-07</v>
       </c>
@@ -714,6 +723,9 @@
       <c r="B5" t="n">
         <v>94.54599999999999</v>
       </c>
+      <c r="C5" t="n">
+        <v>1187.651258806375</v>
+      </c>
       <c r="D5" t="n">
         <v>2.62147e-07</v>
       </c>
@@ -764,6 +776,9 @@
       <c r="B6" t="n">
         <v>90.08799999999997</v>
       </c>
+      <c r="C6" t="n">
+        <v>1105.388444731782</v>
+      </c>
       <c r="D6" t="n">
         <v>2.61719e-07</v>
       </c>
@@ -814,6 +829,9 @@
       <c r="B7" t="n">
         <v>88.339</v>
       </c>
+      <c r="C7" t="n">
+        <v>1279.22109889874</v>
+      </c>
       <c r="D7" t="n">
         <v>2.61617e-07</v>
       </c>
@@ -864,6 +882,9 @@
       <c r="B8" t="n">
         <v>86.74099999999999</v>
       </c>
+      <c r="C8" t="n">
+        <v>1250.247842130406</v>
+      </c>
       <c r="D8" t="n">
         <v>2.61431e-07</v>
       </c>
@@ -914,6 +935,9 @@
       <c r="B9" t="n">
         <v>75.55000000000001</v>
       </c>
+      <c r="C9" t="n">
+        <v>887.6808016878061</v>
+      </c>
       <c r="D9" t="n">
         <v>2.6122e-07</v>
       </c>
@@ -964,6 +988,9 @@
       <c r="B10" t="n">
         <v>81.28800000000001</v>
       </c>
+      <c r="C10" t="n">
+        <v>1157.716315494703</v>
+      </c>
       <c r="D10" t="n">
         <v>2.61242e-07</v>
       </c>
@@ -1013,6 +1040,9 @@
       </c>
       <c r="B11" t="n">
         <v>80.596</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1425.967181650261</v>
       </c>
       <c r="D11" t="n">
         <v>2.61085e-07</v>
@@ -1084,7 +1114,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -1210,6 +1240,9 @@
       <c r="B2" t="n">
         <v>123.117</v>
       </c>
+      <c r="C2" t="n">
+        <v>2041.000587068997</v>
+      </c>
       <c r="D2" t="n">
         <v>2.72644e-07</v>
       </c>
@@ -1260,6 +1293,9 @@
       <c r="B3" t="n">
         <v>103.567</v>
       </c>
+      <c r="C3" t="n">
+        <v>1202.000444526864</v>
+      </c>
       <c r="D3" t="n">
         <v>2.70903e-07</v>
       </c>
@@ -1310,6 +1346,9 @@
       <c r="B4" t="n">
         <v>95.75399999999996</v>
       </c>
+      <c r="C4" t="n">
+        <v>978.1090729161624</v>
+      </c>
       <c r="D4" t="n">
         <v>2.70055e-07</v>
       </c>
@@ -1360,6 +1399,9 @@
       <c r="B5" t="n">
         <v>96.40000000000003</v>
       </c>
+      <c r="C5" t="n">
+        <v>1184.717710036321</v>
+      </c>
       <c r="D5" t="n">
         <v>2.69345e-07</v>
       </c>
@@ -1410,6 +1452,9 @@
       <c r="B6" t="n">
         <v>93.21000000000004</v>
       </c>
+      <c r="C6" t="n">
+        <v>1159.48784159667</v>
+      </c>
       <c r="D6" t="n">
         <v>2.69164e-07</v>
       </c>
@@ -1460,6 +1505,9 @@
       <c r="B7" t="n">
         <v>89.90199999999999</v>
       </c>
+      <c r="C7" t="n">
+        <v>1096.504198591751</v>
+      </c>
       <c r="D7" t="n">
         <v>2.68755e-07</v>
       </c>
@@ -1510,6 +1558,9 @@
       <c r="B8" t="n">
         <v>86.86799999999999</v>
       </c>
+      <c r="C8" t="n">
+        <v>1076.456784454768</v>
+      </c>
       <c r="D8" t="n">
         <v>2.68598e-07</v>
       </c>
@@ -1560,6 +1611,9 @@
       <c r="B9" t="n">
         <v>83.68000000000001</v>
       </c>
+      <c r="C9" t="n">
+        <v>1036.68428274126</v>
+      </c>
       <c r="D9" t="n">
         <v>2.6826e-07</v>
       </c>
@@ -1610,6 +1664,9 @@
       <c r="B10" t="n">
         <v>83.89999999999998</v>
       </c>
+      <c r="C10" t="n">
+        <v>1160.319110418423</v>
+      </c>
       <c r="D10" t="n">
         <v>2.67996e-07</v>
       </c>
@@ -1660,6 +1717,9 @@
       <c r="B11" t="n">
         <v>80.892</v>
       </c>
+      <c r="C11" t="n">
+        <v>1147.566718997316</v>
+      </c>
       <c r="D11" t="n">
         <v>2.67899e-07</v>
       </c>
@@ -1710,6 +1770,9 @@
       <c r="B12" t="n">
         <v>79.81299999999999</v>
       </c>
+      <c r="C12" t="n">
+        <v>1105.155850821311</v>
+      </c>
       <c r="D12" t="n">
         <v>2.67688e-07</v>
       </c>
@@ -1760,6 +1823,9 @@
       <c r="B13" t="n">
         <v>79.834</v>
       </c>
+      <c r="C13" t="n">
+        <v>1354.636139517809</v>
+      </c>
       <c r="D13" t="n">
         <v>2.67488e-07</v>
       </c>
@@ -1810,6 +1876,9 @@
       <c r="B14" t="n">
         <v>79.64600000000002</v>
       </c>
+      <c r="C14" t="n">
+        <v>1528.40126424197</v>
+      </c>
       <c r="D14" t="n">
         <v>2.67391e-07</v>
       </c>
@@ -1860,6 +1929,9 @@
       <c r="B15" t="n">
         <v>74.56900000000002</v>
       </c>
+      <c r="C15" t="n">
+        <v>1139.289523396569</v>
+      </c>
       <c r="D15" t="n">
         <v>2.67161e-07</v>
       </c>
@@ -1910,6 +1982,9 @@
       <c r="B16" t="n">
         <v>72.36599999999999</v>
       </c>
+      <c r="C16" t="n">
+        <v>1084.388580300227</v>
+      </c>
       <c r="D16" t="n">
         <v>2.67154e-07</v>
       </c>
@@ -1960,6 +2035,9 @@
       <c r="B17" t="n">
         <v>74.714</v>
       </c>
+      <c r="C17" t="n">
+        <v>1409.623082602064</v>
+      </c>
       <c r="D17" t="n">
         <v>2.67023e-07</v>
       </c>
@@ -2010,6 +2088,9 @@
       <c r="B18" t="n">
         <v>71.79700000000003</v>
       </c>
+      <c r="C18" t="n">
+        <v>1278.934043768995</v>
+      </c>
       <c r="D18" t="n">
         <v>2.66962e-07</v>
       </c>
@@ -2060,6 +2141,9 @@
       <c r="B19" t="n">
         <v>72.14000000000004</v>
       </c>
+      <c r="C19" t="n">
+        <v>1584.414576363821</v>
+      </c>
       <c r="D19" t="n">
         <v>2.66831e-07</v>
       </c>
@@ -2110,6 +2194,9 @@
       <c r="B20" t="n">
         <v>67.97899999999998</v>
       </c>
+      <c r="C20" t="n">
+        <v>1128.676562504201</v>
+      </c>
       <c r="D20" t="n">
         <v>2.6676e-07</v>
       </c>
@@ -2160,6 +2247,9 @@
       <c r="B21" t="n">
         <v>67.697</v>
       </c>
+      <c r="C21" t="n">
+        <v>1372.149299879956</v>
+      </c>
       <c r="D21" t="n">
         <v>2.66757e-07</v>
       </c>
@@ -2209,6 +2299,9 @@
       </c>
       <c r="B22" t="n">
         <v>67.423</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1460.925774212316</v>
       </c>
       <c r="D22" t="n">
         <v>2.66694e-07</v>
@@ -2280,7 +2373,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -2406,6 +2499,9 @@
       <c r="B2" t="n">
         <v>127.235</v>
       </c>
+      <c r="C2" t="n">
+        <v>2586.212812919433</v>
+      </c>
       <c r="D2" t="n">
         <v>2.76249e-07</v>
       </c>
@@ -2456,6 +2552,9 @@
       <c r="B3" t="n">
         <v>103.22</v>
       </c>
+      <c r="C3" t="n">
+        <v>1159.030521839782</v>
+      </c>
       <c r="D3" t="n">
         <v>2.69663e-07</v>
       </c>
@@ -2506,6 +2605,9 @@
       <c r="B4" t="n">
         <v>98.11100000000005</v>
       </c>
+      <c r="C4" t="n">
+        <v>1113.051029798632</v>
+      </c>
       <c r="D4" t="n">
         <v>2.67466e-07</v>
       </c>
@@ -2556,6 +2658,9 @@
       <c r="B5" t="n">
         <v>94.24499999999995</v>
       </c>
+      <c r="C5" t="n">
+        <v>1149.862309491787</v>
+      </c>
       <c r="D5" t="n">
         <v>2.66165e-07</v>
       </c>
@@ -2606,6 +2711,9 @@
       <c r="B6" t="n">
         <v>90.20500000000004</v>
       </c>
+      <c r="C6" t="n">
+        <v>1021.840160489777</v>
+      </c>
       <c r="D6" t="n">
         <v>2.65327e-07</v>
       </c>
@@ -2656,6 +2764,9 @@
       <c r="B7" t="n">
         <v>88.66500000000002</v>
       </c>
+      <c r="C7" t="n">
+        <v>1101.746923166582</v>
+      </c>
       <c r="D7" t="n">
         <v>2.64548e-07</v>
       </c>
@@ -2706,6 +2817,9 @@
       <c r="B8" t="n">
         <v>85.44799999999998</v>
       </c>
+      <c r="C8" t="n">
+        <v>1049.571623158748</v>
+      </c>
       <c r="D8" t="n">
         <v>2.64146e-07</v>
       </c>
@@ -2756,6 +2870,9 @@
       <c r="B9" t="n">
         <v>86.50400000000002</v>
       </c>
+      <c r="C9" t="n">
+        <v>1306.950579478831</v>
+      </c>
       <c r="D9" t="n">
         <v>2.63749e-07</v>
       </c>
@@ -2806,6 +2923,9 @@
       <c r="B10" t="n">
         <v>82.78000000000003</v>
       </c>
+      <c r="C10" t="n">
+        <v>1162.271947841235</v>
+      </c>
       <c r="D10" t="n">
         <v>2.63693e-07</v>
       </c>
@@ -2856,6 +2976,9 @@
       <c r="B11" t="n">
         <v>81.62599999999998</v>
       </c>
+      <c r="C11" t="n">
+        <v>1275.515577500727</v>
+      </c>
       <c r="D11" t="n">
         <v>2.63424e-07</v>
       </c>
@@ -2906,6 +3029,9 @@
       <c r="B12" t="n">
         <v>80.48199999999997</v>
       </c>
+      <c r="C12" t="n">
+        <v>1340.808776300246</v>
+      </c>
       <c r="D12" t="n">
         <v>2.63247e-07</v>
       </c>
@@ -2956,6 +3082,9 @@
       <c r="B13" t="n">
         <v>76.88</v>
       </c>
+      <c r="C13" t="n">
+        <v>1139.670042063237</v>
+      </c>
       <c r="D13" t="n">
         <v>2.6306e-07</v>
       </c>
@@ -3006,6 +3135,9 @@
       <c r="B14" t="n">
         <v>78.01499999999999</v>
       </c>
+      <c r="C14" t="n">
+        <v>1579.548196473024</v>
+      </c>
       <c r="D14" t="n">
         <v>2.6299e-07</v>
       </c>
@@ -3056,6 +3188,9 @@
       <c r="B15" t="n">
         <v>73.17599999999999</v>
       </c>
+      <c r="C15" t="n">
+        <v>1158.237863090533</v>
+      </c>
       <c r="D15" t="n">
         <v>2.62701e-07</v>
       </c>
@@ -3106,6 +3241,9 @@
       <c r="B16" t="n">
         <v>71.80000000000001</v>
       </c>
+      <c r="C16" t="n">
+        <v>1111.868495126394</v>
+      </c>
       <c r="D16" t="n">
         <v>2.62774e-07</v>
       </c>
@@ -3156,6 +3294,9 @@
       <c r="B17" t="n">
         <v>63.90500000000003</v>
       </c>
+      <c r="C17" t="n">
+        <v>871.381342517173</v>
+      </c>
       <c r="D17" t="n">
         <v>2.62665e-07</v>
       </c>
@@ -3206,6 +3347,9 @@
       <c r="B18" t="n">
         <v>70.37099999999998</v>
       </c>
+      <c r="C18" t="n">
+        <v>1323.961131520585</v>
+      </c>
       <c r="D18" t="n">
         <v>2.62561e-07</v>
       </c>
@@ -3256,6 +3400,9 @@
       <c r="B19" t="n">
         <v>70.33600000000001</v>
       </c>
+      <c r="C19" t="n">
+        <v>1550.686136580121</v>
+      </c>
       <c r="D19" t="n">
         <v>2.62665e-07</v>
       </c>
@@ -3306,6 +3453,9 @@
       <c r="B20" t="n">
         <v>67.50400000000002</v>
       </c>
+      <c r="C20" t="n">
+        <v>1250.437060771369</v>
+      </c>
       <c r="D20" t="n">
         <v>2.62544e-07</v>
       </c>
@@ -3356,6 +3506,9 @@
       <c r="B21" t="n">
         <v>65.69799999999998</v>
       </c>
+      <c r="C21" t="n">
+        <v>1202.949647855174</v>
+      </c>
       <c r="D21" t="n">
         <v>2.62416e-07</v>
       </c>
@@ -3405,6 +3558,9 @@
       </c>
       <c r="B22" t="n">
         <v>65.69800000000004</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1491.110636291105</v>
       </c>
       <c r="D22" t="n">
         <v>2.62309e-07</v>
@@ -3476,7 +3632,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -3602,6 +3758,9 @@
       <c r="B2" t="n">
         <v>176.22</v>
       </c>
+      <c r="C2" t="n">
+        <v>2635.239028489558</v>
+      </c>
       <c r="D2" t="n">
         <v>2.79854e-07</v>
       </c>
@@ -3652,6 +3811,9 @@
       <c r="B3" t="n">
         <v>133.565</v>
       </c>
+      <c r="C3" t="n">
+        <v>1215.826072554044</v>
+      </c>
       <c r="D3" t="n">
         <v>2.81243e-07</v>
       </c>
@@ -3702,6 +3864,9 @@
       <c r="B4" t="n">
         <v>121.0210000000001</v>
       </c>
+      <c r="C4" t="n">
+        <v>1041.04672888471</v>
+      </c>
       <c r="D4" t="n">
         <v>2.78511e-07</v>
       </c>
@@ -3752,6 +3917,9 @@
       <c r="B5" t="n">
         <v>115.665</v>
       </c>
+      <c r="C5" t="n">
+        <v>979.7952431635265</v>
+      </c>
       <c r="D5" t="n">
         <v>2.76359e-07</v>
       </c>
@@ -3802,6 +3970,9 @@
       <c r="B6" t="n">
         <v>111.664</v>
       </c>
+      <c r="C6" t="n">
+        <v>995.02190658779</v>
+      </c>
       <c r="D6" t="n">
         <v>2.74397e-07</v>
       </c>
@@ -3852,6 +4023,9 @@
       <c r="B7" t="n">
         <v>106.525</v>
       </c>
+      <c r="C7" t="n">
+        <v>982.9181314317373</v>
+      </c>
       <c r="D7" t="n">
         <v>2.73123e-07</v>
       </c>
@@ -3902,6 +4076,9 @@
       <c r="B8" t="n">
         <v>106.549</v>
       </c>
+      <c r="C8" t="n">
+        <v>1114.771364220516</v>
+      </c>
       <c r="D8" t="n">
         <v>2.71946e-07</v>
       </c>
@@ -3952,6 +4129,9 @@
       <c r="B9" t="n">
         <v>99.30899999999997</v>
       </c>
+      <c r="C9" t="n">
+        <v>981.7589436192243</v>
+      </c>
       <c r="D9" t="n">
         <v>2.71109e-07</v>
       </c>
@@ -4002,6 +4182,9 @@
       <c r="B10" t="n">
         <v>96.35899999999998</v>
       </c>
+      <c r="C10" t="n">
+        <v>983.1096099877034</v>
+      </c>
       <c r="D10" t="n">
         <v>2.70458e-07</v>
       </c>
@@ -4051,6 +4234,9 @@
       </c>
       <c r="B11" t="n">
         <v>97.024</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1132.297131039089</v>
       </c>
       <c r="D11" t="n">
         <v>2.69936e-07</v>
@@ -4122,7 +4308,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -4248,6 +4434,9 @@
       <c r="B2" t="n">
         <v>122.251</v>
       </c>
+      <c r="C2" t="n">
+        <v>2071.129000891164</v>
+      </c>
       <c r="D2" t="n">
         <v>2.76224e-07</v>
       </c>
@@ -4298,6 +4487,9 @@
       <c r="B3" t="n">
         <v>100.185</v>
       </c>
+      <c r="C3" t="n">
+        <v>1070.006645330949</v>
+      </c>
       <c r="D3" t="n">
         <v>2.73656e-07</v>
       </c>
@@ -4348,6 +4540,9 @@
       <c r="B4" t="n">
         <v>96.005</v>
       </c>
+      <c r="C4" t="n">
+        <v>1028.069869692912</v>
+      </c>
       <c r="D4" t="n">
         <v>2.7226e-07</v>
       </c>
@@ -4398,6 +4593,9 @@
       <c r="B5" t="n">
         <v>83.81100000000004</v>
       </c>
+      <c r="C5" t="n">
+        <v>780.5624334017402</v>
+      </c>
       <c r="D5" t="n">
         <v>2.71316e-07</v>
       </c>
@@ -4448,6 +4646,9 @@
       <c r="B6" t="n">
         <v>89.99099999999999</v>
       </c>
+      <c r="C6" t="n">
+        <v>1105.687811972319</v>
+      </c>
       <c r="D6" t="n">
         <v>2.70379e-07</v>
       </c>
@@ -4498,6 +4699,9 @@
       <c r="B7" t="n">
         <v>88.84500000000003</v>
       </c>
+      <c r="C7" t="n">
+        <v>1145.362233957521</v>
+      </c>
       <c r="D7" t="n">
         <v>2.69961e-07</v>
       </c>
@@ -4548,6 +4752,9 @@
       <c r="B8" t="n">
         <v>86.53199999999998</v>
       </c>
+      <c r="C8" t="n">
+        <v>1089.61742367896</v>
+      </c>
       <c r="D8" t="n">
         <v>2.69501e-07</v>
       </c>
@@ -4598,6 +4805,9 @@
       <c r="B9" t="n">
         <v>84.29000000000002</v>
       </c>
+      <c r="C9" t="n">
+        <v>1163.8042330788</v>
+      </c>
       <c r="D9" t="n">
         <v>2.69065e-07</v>
       </c>
@@ -4648,6 +4858,9 @@
       <c r="B10" t="n">
         <v>82.62300000000005</v>
       </c>
+      <c r="C10" t="n">
+        <v>1138.155710573946</v>
+      </c>
       <c r="D10" t="n">
         <v>2.68862e-07</v>
       </c>
@@ -4698,6 +4911,9 @@
       <c r="B11" t="n">
         <v>79.98599999999999</v>
       </c>
+      <c r="C11" t="n">
+        <v>1117.753121679628</v>
+      </c>
       <c r="D11" t="n">
         <v>2.685e-07</v>
       </c>
@@ -4748,6 +4964,9 @@
       <c r="B12" t="n">
         <v>78.154</v>
       </c>
+      <c r="C12" t="n">
+        <v>1056.623211221279</v>
+      </c>
       <c r="D12" t="n">
         <v>2.68248e-07</v>
       </c>
@@ -4798,6 +5017,9 @@
       <c r="B13" t="n">
         <v>78.22499999999997</v>
       </c>
+      <c r="C13" t="n">
+        <v>1158.946581049302</v>
+      </c>
       <c r="D13" t="n">
         <v>2.68049e-07</v>
       </c>
@@ -4848,6 +5070,9 @@
       <c r="B14" t="n">
         <v>77.61399999999998</v>
       </c>
+      <c r="C14" t="n">
+        <v>1265.306162161252</v>
+      </c>
       <c r="D14" t="n">
         <v>2.6773e-07</v>
       </c>
@@ -4898,6 +5123,9 @@
       <c r="B15" t="n">
         <v>70.72300000000001</v>
       </c>
+      <c r="C15" t="n">
+        <v>841.8951208112268</v>
+      </c>
       <c r="D15" t="n">
         <v>2.67571e-07</v>
       </c>
@@ -4948,6 +5176,9 @@
       <c r="B16" t="n">
         <v>73.56799999999998</v>
       </c>
+      <c r="C16" t="n">
+        <v>1151.32314085616</v>
+      </c>
       <c r="D16" t="n">
         <v>2.67374e-07</v>
       </c>
@@ -4998,6 +5229,9 @@
       <c r="B17" t="n">
         <v>73.66899999999998</v>
       </c>
+      <c r="C17" t="n">
+        <v>1333.291066661545</v>
+      </c>
       <c r="D17" t="n">
         <v>2.67279e-07</v>
       </c>
@@ -5048,6 +5282,9 @@
       <c r="B18" t="n">
         <v>73.53999999999996</v>
       </c>
+      <c r="C18" t="n">
+        <v>1450.53164419885</v>
+      </c>
       <c r="D18" t="n">
         <v>2.67075e-07</v>
       </c>
@@ -5098,6 +5335,9 @@
       <c r="B19" t="n">
         <v>69.43700000000001</v>
       </c>
+      <c r="C19" t="n">
+        <v>1041.712351240576</v>
+      </c>
       <c r="D19" t="n">
         <v>2.66953e-07</v>
       </c>
@@ -5148,6 +5388,9 @@
       <c r="B20" t="n">
         <v>69.13500000000005</v>
       </c>
+      <c r="C20" t="n">
+        <v>1211.447361577304</v>
+      </c>
       <c r="D20" t="n">
         <v>2.66861e-07</v>
       </c>
@@ -5198,6 +5441,9 @@
       <c r="B21" t="n">
         <v>70.59499999999997</v>
       </c>
+      <c r="C21" t="n">
+        <v>1532.503127564351</v>
+      </c>
       <c r="D21" t="n">
         <v>2.66724e-07</v>
       </c>
@@ -5247,6 +5493,9 @@
       </c>
       <c r="B22" t="n">
         <v>66.67299999999994</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1297.68069844646</v>
       </c>
       <c r="D22" t="n">
         <v>2.66594e-07</v>
@@ -5318,7 +5567,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -5444,6 +5693,9 @@
       <c r="B2" t="n">
         <v>203.4469999999999</v>
       </c>
+      <c r="C2" t="n">
+        <v>3658.577788260438</v>
+      </c>
       <c r="D2" t="n">
         <v>2.84316e-07</v>
       </c>
@@ -5494,6 +5746,9 @@
       <c r="B3" t="n">
         <v>140.4449999999999</v>
       </c>
+      <c r="C3" t="n">
+        <v>1135.786094047378</v>
+      </c>
       <c r="D3" t="n">
         <v>2.87624e-07</v>
       </c>
@@ -5544,6 +5799,9 @@
       <c r="B4" t="n">
         <v>125.5309999999999</v>
       </c>
+      <c r="C4" t="n">
+        <v>951.7623487726468</v>
+      </c>
       <c r="D4" t="n">
         <v>2.84392e-07</v>
       </c>
@@ -5594,6 +5852,9 @@
       <c r="B5" t="n">
         <v>119.874</v>
       </c>
+      <c r="C5" t="n">
+        <v>946.0863655456129</v>
+      </c>
       <c r="D5" t="n">
         <v>2.81587e-07</v>
       </c>
@@ -5644,6 +5905,9 @@
       <c r="B6" t="n">
         <v>115.61</v>
       </c>
+      <c r="C6" t="n">
+        <v>963.0878134928013</v>
+      </c>
       <c r="D6" t="n">
         <v>2.79529e-07</v>
       </c>
@@ -5694,6 +5958,9 @@
       <c r="B7" t="n">
         <v>112.884</v>
       </c>
+      <c r="C7" t="n">
+        <v>986.4307862151077</v>
+      </c>
       <c r="D7" t="n">
         <v>2.78141e-07</v>
       </c>
@@ -5744,6 +6011,9 @@
       <c r="B8" t="n">
         <v>110.67</v>
       </c>
+      <c r="C8" t="n">
+        <v>1071.806574982334</v>
+      </c>
       <c r="D8" t="n">
         <v>2.76923e-07</v>
       </c>
@@ -5794,6 +6064,9 @@
       <c r="B9" t="n">
         <v>104.707</v>
       </c>
+      <c r="C9" t="n">
+        <v>1001.688998626273</v>
+      </c>
       <c r="D9" t="n">
         <v>2.75833e-07</v>
       </c>
@@ -5844,6 +6117,9 @@
       <c r="B10" t="n">
         <v>101.419</v>
       </c>
+      <c r="C10" t="n">
+        <v>1000.612791883113</v>
+      </c>
       <c r="D10" t="n">
         <v>2.75131e-07</v>
       </c>
@@ -5893,6 +6169,9 @@
       </c>
       <c r="B11" t="n">
         <v>97.31200000000001</v>
+      </c>
+      <c r="C11" t="n">
+        <v>989.9729950892493</v>
       </c>
       <c r="D11" t="n">
         <v>2.74475e-07</v>
@@ -5964,7 +6243,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -6090,6 +6369,9 @@
       <c r="B2" t="n">
         <v>125.5210000000001</v>
       </c>
+      <c r="C2" t="n">
+        <v>2478.609899888871</v>
+      </c>
       <c r="D2" t="n">
         <v>2.93977e-07</v>
       </c>
@@ -6140,6 +6422,9 @@
       <c r="B3" t="n">
         <v>103.521</v>
       </c>
+      <c r="C3" t="n">
+        <v>1146.28105107472</v>
+      </c>
       <c r="D3" t="n">
         <v>2.84886e-07</v>
       </c>
@@ -6190,6 +6475,9 @@
       <c r="B4" t="n">
         <v>97.38899999999995</v>
       </c>
+      <c r="C4" t="n">
+        <v>1096.741930382429</v>
+      </c>
       <c r="D4" t="n">
         <v>2.81455e-07</v>
       </c>
@@ -6240,6 +6528,9 @@
       <c r="B5" t="n">
         <v>94.255</v>
       </c>
+      <c r="C5" t="n">
+        <v>1084.882553370524</v>
+      </c>
       <c r="D5" t="n">
         <v>2.79294e-07</v>
       </c>
@@ -6290,6 +6581,9 @@
       <c r="B6" t="n">
         <v>92.601</v>
       </c>
+      <c r="C6" t="n">
+        <v>1111.50397580101</v>
+      </c>
       <c r="D6" t="n">
         <v>2.78271e-07</v>
       </c>
@@ -6340,6 +6634,9 @@
       <c r="B7" t="n">
         <v>88.86799999999999</v>
       </c>
+      <c r="C7" t="n">
+        <v>1054.161982132104</v>
+      </c>
       <c r="D7" t="n">
         <v>2.77066e-07</v>
       </c>
@@ -6390,6 +6687,9 @@
       <c r="B8" t="n">
         <v>85.39500000000004</v>
       </c>
+      <c r="C8" t="n">
+        <v>1013.327057023328</v>
+      </c>
       <c r="D8" t="n">
         <v>2.76493e-07</v>
       </c>
@@ -6440,6 +6740,9 @@
       <c r="B9" t="n">
         <v>83.005</v>
       </c>
+      <c r="C9" t="n">
+        <v>991.7783538055976</v>
+      </c>
       <c r="D9" t="n">
         <v>2.75846e-07</v>
       </c>
@@ -6490,6 +6793,9 @@
       <c r="B10" t="n">
         <v>79.952</v>
       </c>
+      <c r="C10" t="n">
+        <v>947.4534114483696</v>
+      </c>
       <c r="D10" t="n">
         <v>2.75517e-07</v>
       </c>
@@ -6540,6 +6846,9 @@
       <c r="B11" t="n">
         <v>80.97499999999997</v>
       </c>
+      <c r="C11" t="n">
+        <v>1069.019106746909</v>
+      </c>
       <c r="D11" t="n">
         <v>2.74867e-07</v>
       </c>
@@ -6590,6 +6899,9 @@
       <c r="B12" t="n">
         <v>80.16699999999997</v>
       </c>
+      <c r="C12" t="n">
+        <v>1185.70813221656</v>
+      </c>
       <c r="D12" t="n">
         <v>2.74698e-07</v>
       </c>
@@ -6640,6 +6952,9 @@
       <c r="B13" t="n">
         <v>78.42199999999997</v>
       </c>
+      <c r="C13" t="n">
+        <v>1109.68627446145</v>
+      </c>
       <c r="D13" t="n">
         <v>2.74453e-07</v>
       </c>
@@ -6690,6 +7005,9 @@
       <c r="B14" t="n">
         <v>77.54300000000001</v>
       </c>
+      <c r="C14" t="n">
+        <v>1211.656903211732</v>
+      </c>
       <c r="D14" t="n">
         <v>2.74151e-07</v>
       </c>
@@ -6740,6 +7058,9 @@
       <c r="B15" t="n">
         <v>75.66800000000001</v>
       </c>
+      <c r="C15" t="n">
+        <v>1128.892526466224</v>
+      </c>
       <c r="D15" t="n">
         <v>2.73748e-07</v>
       </c>
@@ -6790,6 +7111,9 @@
       <c r="B16" t="n">
         <v>76.363</v>
       </c>
+      <c r="C16" t="n">
+        <v>1333.86003807952</v>
+      </c>
       <c r="D16" t="n">
         <v>2.73534e-07</v>
       </c>
@@ -6840,6 +7164,9 @@
       <c r="B17" t="n">
         <v>73.23899999999998</v>
       </c>
+      <c r="C17" t="n">
+        <v>1166.157899106196</v>
+      </c>
       <c r="D17" t="n">
         <v>2.73386e-07</v>
       </c>
@@ -6890,6 +7217,9 @@
       <c r="B18" t="n">
         <v>72.40800000000002</v>
       </c>
+      <c r="C18" t="n">
+        <v>1197.188233985904</v>
+      </c>
       <c r="D18" t="n">
         <v>2.73301e-07</v>
       </c>
@@ -6940,6 +7270,9 @@
       <c r="B19" t="n">
         <v>72.01900000000001</v>
       </c>
+      <c r="C19" t="n">
+        <v>1298.149178707205</v>
+      </c>
       <c r="D19" t="n">
         <v>2.73065e-07</v>
       </c>
@@ -6990,6 +7323,9 @@
       <c r="B20" t="n">
         <v>69.64600000000002</v>
       </c>
+      <c r="C20" t="n">
+        <v>1195.222838806978</v>
+      </c>
       <c r="D20" t="n">
         <v>2.73002e-07</v>
       </c>
@@ -7040,6 +7376,9 @@
       <c r="B21" t="n">
         <v>68.39400000000001</v>
       </c>
+      <c r="C21" t="n">
+        <v>1202.488746601807</v>
+      </c>
       <c r="D21" t="n">
         <v>2.7283e-07</v>
       </c>
@@ -7089,6 +7428,9 @@
       </c>
       <c r="B22" t="n">
         <v>67.209</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1177.49969119494</v>
       </c>
       <c r="D22" t="n">
         <v>2.72657e-07</v>
@@ -7160,7 +7502,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -7306,7 +7648,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -7432,6 +7774,9 @@
       <c r="B2" t="n">
         <v>118.316</v>
       </c>
+      <c r="C2" t="n">
+        <v>1672.290138218241</v>
+      </c>
       <c r="D2" t="n">
         <v>2.90962e-07</v>
       </c>
@@ -7482,6 +7827,9 @@
       <c r="B3" t="n">
         <v>101.064</v>
       </c>
+      <c r="C3" t="n">
+        <v>1098.834575786059</v>
+      </c>
       <c r="D3" t="n">
         <v>2.84504e-07</v>
       </c>
@@ -7532,6 +7880,9 @@
       <c r="B4" t="n">
         <v>95.32999999999998</v>
       </c>
+      <c r="C4" t="n">
+        <v>1017.286921415541</v>
+      </c>
       <c r="D4" t="n">
         <v>2.81687e-07</v>
       </c>
@@ -7582,6 +7933,9 @@
       <c r="B5" t="n">
         <v>92.99799999999999</v>
       </c>
+      <c r="C5" t="n">
+        <v>1040.355902008638</v>
+      </c>
       <c r="D5" t="n">
         <v>2.80065e-07</v>
       </c>
@@ -7632,6 +7986,9 @@
       <c r="B6" t="n">
         <v>90.89699999999999</v>
       </c>
+      <c r="C6" t="n">
+        <v>1072.857682168924</v>
+      </c>
       <c r="D6" t="n">
         <v>2.78988e-07</v>
       </c>
@@ -7682,6 +8039,9 @@
       <c r="B7" t="n">
         <v>87.29400000000004</v>
       </c>
+      <c r="C7" t="n">
+        <v>997.1212722705529</v>
+      </c>
       <c r="D7" t="n">
         <v>2.78413e-07</v>
       </c>
@@ -7732,6 +8092,9 @@
       <c r="B8" t="n">
         <v>88.53699999999998</v>
       </c>
+      <c r="C8" t="n">
+        <v>1230.553507425333</v>
+      </c>
       <c r="D8" t="n">
         <v>2.77561e-07</v>
       </c>
@@ -7782,6 +8145,9 @@
       <c r="B9" t="n">
         <v>84.02199999999999</v>
       </c>
+      <c r="C9" t="n">
+        <v>1118.888373515422</v>
+      </c>
       <c r="D9" t="n">
         <v>2.77305e-07</v>
       </c>
@@ -7832,6 +8198,9 @@
       <c r="B10" t="n">
         <v>82.19300000000004</v>
       </c>
+      <c r="C10" t="n">
+        <v>1106.79165121209</v>
+      </c>
       <c r="D10" t="n">
         <v>2.76884e-07</v>
       </c>
@@ -7882,6 +8251,9 @@
       <c r="B11" t="n">
         <v>79.88600000000002</v>
       </c>
+      <c r="C11" t="n">
+        <v>1025.532207037964</v>
+      </c>
       <c r="D11" t="n">
         <v>2.76525e-07</v>
       </c>
@@ -7932,6 +8304,9 @@
       <c r="B12" t="n">
         <v>79.03700000000003</v>
       </c>
+      <c r="C12" t="n">
+        <v>1111.226650450044</v>
+      </c>
       <c r="D12" t="n">
         <v>2.76262e-07</v>
       </c>
@@ -7982,6 +8357,9 @@
       <c r="B13" t="n">
         <v>77.45600000000002</v>
       </c>
+      <c r="C13" t="n">
+        <v>1142.3548446192</v>
+      </c>
       <c r="D13" t="n">
         <v>2.76021e-07</v>
       </c>
@@ -8032,6 +8410,9 @@
       <c r="B14" t="n">
         <v>75.98400000000004</v>
       </c>
+      <c r="C14" t="n">
+        <v>1178.923355097134</v>
+      </c>
       <c r="D14" t="n">
         <v>2.75885e-07</v>
       </c>
@@ -8082,6 +8463,9 @@
       <c r="B15" t="n">
         <v>66.12299999999999</v>
       </c>
+      <c r="C15" t="n">
+        <v>797.4729970405186</v>
+      </c>
       <c r="D15" t="n">
         <v>2.75449e-07</v>
       </c>
@@ -8132,6 +8516,9 @@
       <c r="B16" t="n">
         <v>73.81999999999999</v>
       </c>
+      <c r="C16" t="n">
+        <v>1172.26114802531</v>
+      </c>
       <c r="D16" t="n">
         <v>2.75362e-07</v>
       </c>
@@ -8182,6 +8569,9 @@
       <c r="B17" t="n">
         <v>73.86700000000002</v>
       </c>
+      <c r="C17" t="n">
+        <v>1337.034338347031</v>
+      </c>
       <c r="D17" t="n">
         <v>2.75127e-07</v>
       </c>
@@ -8232,6 +8622,9 @@
       <c r="B18" t="n">
         <v>69.31600000000003</v>
       </c>
+      <c r="C18" t="n">
+        <v>1020.084472025237</v>
+      </c>
       <c r="D18" t="n">
         <v>2.752e-07</v>
       </c>
@@ -8282,6 +8675,9 @@
       <c r="B19" t="n">
         <v>71.404</v>
       </c>
+      <c r="C19" t="n">
+        <v>1474.85698748639</v>
+      </c>
       <c r="D19" t="n">
         <v>2.75054e-07</v>
       </c>
@@ -8332,6 +8728,9 @@
       <c r="B20" t="n">
         <v>66.90200000000004</v>
       </c>
+      <c r="C20" t="n">
+        <v>1043.121285100443</v>
+      </c>
       <c r="D20" t="n">
         <v>2.74906e-07</v>
       </c>
@@ -8382,6 +8781,9 @@
       <c r="B21" t="n">
         <v>68.47899999999998</v>
       </c>
+      <c r="C21" t="n">
+        <v>1557.422037080431</v>
+      </c>
       <c r="D21" t="n">
         <v>2.74804e-07</v>
       </c>
@@ -8431,6 +8833,9 @@
       </c>
       <c r="B22" t="n">
         <v>63.71500000000003</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1061.022850069246</v>
       </c>
       <c r="D22" t="n">
         <v>2.74796e-07</v>
@@ -8502,7 +8907,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -8628,6 +9033,9 @@
       <c r="B2" t="n">
         <v>175.804</v>
       </c>
+      <c r="C2" t="n">
+        <v>4997.975715959094</v>
+      </c>
       <c r="D2" t="n">
         <v>2.85579e-07</v>
       </c>
@@ -8678,6 +9086,9 @@
       <c r="B3" t="n">
         <v>119.131</v>
       </c>
+      <c r="C3" t="n">
+        <v>1096.942042425906</v>
+      </c>
       <c r="D3" t="n">
         <v>2.84088e-07</v>
       </c>
@@ -8728,6 +9139,9 @@
       <c r="B4" t="n">
         <v>108.834</v>
       </c>
+      <c r="C4" t="n">
+        <v>988.9897267160436</v>
+      </c>
       <c r="D4" t="n">
         <v>2.80278e-07</v>
       </c>
@@ -8778,6 +9192,9 @@
       <c r="B5" t="n">
         <v>104.93</v>
       </c>
+      <c r="C5" t="n">
+        <v>1043.286614551929</v>
+      </c>
       <c r="D5" t="n">
         <v>2.77441e-07</v>
       </c>
@@ -8828,6 +9245,9 @@
       <c r="B6" t="n">
         <v>102.597</v>
       </c>
+      <c r="C6" t="n">
+        <v>1115.729764617504</v>
+      </c>
       <c r="D6" t="n">
         <v>2.75699e-07</v>
       </c>
@@ -8878,6 +9298,9 @@
       <c r="B7" t="n">
         <v>98.27800000000002</v>
       </c>
+      <c r="C7" t="n">
+        <v>1139.613659268496</v>
+      </c>
       <c r="D7" t="n">
         <v>2.74648e-07</v>
       </c>
@@ -8928,6 +9351,9 @@
       <c r="B8" t="n">
         <v>95.08199999999999</v>
       </c>
+      <c r="C8" t="n">
+        <v>1124.949113929093</v>
+      </c>
       <c r="D8" t="n">
         <v>2.7384e-07</v>
       </c>
@@ -8978,6 +9404,9 @@
       <c r="B9" t="n">
         <v>89.55800000000005</v>
       </c>
+      <c r="C9" t="n">
+        <v>1030.071202337699</v>
+      </c>
       <c r="D9" t="n">
         <v>2.73324e-07</v>
       </c>
@@ -9028,6 +9457,9 @@
       <c r="B10" t="n">
         <v>87.34300000000002</v>
       </c>
+      <c r="C10" t="n">
+        <v>1084.0731959497</v>
+      </c>
       <c r="D10" t="n">
         <v>2.73061e-07</v>
       </c>
@@ -9077,6 +9509,9 @@
       </c>
       <c r="B11" t="n">
         <v>83.30200000000002</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1045.541931314833</v>
       </c>
       <c r="D11" t="n">
         <v>2.72774e-07</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 45.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 45.xlsx
@@ -565,7 +565,7 @@
         <v>107.8630000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>1248.029358834179</v>
+        <v>107.8630000000001</v>
       </c>
       <c r="D2" t="n">
         <v>2.64063e-07</v>
@@ -597,11 +597,10 @@
       <c r="X2" t="n">
         <v>-9599.322190146206</v>
       </c>
-      <c r="Y2" t="n">
-        <v>479.6053667238517</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>149743442.3326762</v>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA2" t="n">
         <v>4.26998522159083e-07</v>
@@ -618,7 +617,7 @@
         <v>101.1759999999999</v>
       </c>
       <c r="C3" t="n">
-        <v>1166.83280439228</v>
+        <v>322.5225745905415</v>
       </c>
       <c r="D3" t="n">
         <v>2.631e-07</v>
@@ -651,16 +650,13 @@
         <v>-9898.387345826271</v>
       </c>
       <c r="Y3" t="n">
-        <v>451.5456264712489</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>3879.482615407804</v>
+        <v>196.6038275660232</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.643783049026739e-06</v>
+        <v>3.19835178925394e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.8272660883542078</v>
+        <v>0.9531833137658476</v>
       </c>
     </row>
     <row r="4">
@@ -671,7 +667,7 @@
         <v>97.33999999999997</v>
       </c>
       <c r="C4" t="n">
-        <v>1216.407403903457</v>
+        <v>97.33999999999997</v>
       </c>
       <c r="D4" t="n">
         <v>2.6245e-07</v>
@@ -703,11 +699,10 @@
       <c r="X4" t="n">
         <v>-9985.674568337905</v>
       </c>
-      <c r="Y4" t="n">
-        <v>446.2200620584686</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>3829.841406571698</v>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA4" t="n">
         <v>1.351528210561691e-06</v>
@@ -724,7 +719,7 @@
         <v>94.54599999999999</v>
       </c>
       <c r="C5" t="n">
-        <v>1187.651258806375</v>
+        <v>292.7528309902486</v>
       </c>
       <c r="D5" t="n">
         <v>2.62147e-07</v>
@@ -757,16 +752,13 @@
         <v>-10105.93471235811</v>
       </c>
       <c r="Y5" t="n">
-        <v>444.7545958425873</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>7629.382468145198</v>
+        <v>212.8954931796348</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.588868257132026e-07</v>
+        <v>3.180351202254403e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.9999755699729936</v>
+        <v>0.9631485769281766</v>
       </c>
     </row>
     <row r="6">
@@ -777,7 +769,7 @@
         <v>90.08799999999997</v>
       </c>
       <c r="C6" t="n">
-        <v>1105.388444731782</v>
+        <v>295.7764811491053</v>
       </c>
       <c r="D6" t="n">
         <v>2.61719e-07</v>
@@ -810,16 +802,13 @@
         <v>-9813.14555680553</v>
       </c>
       <c r="Y6" t="n">
-        <v>457.025911920714</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>746705934.7151682</v>
+        <v>203.5830804596798</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.916622015651721e-07</v>
+        <v>3.042652857361922e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.9384871503513036</v>
+        <v>0.9642278860578373</v>
       </c>
     </row>
     <row r="7">
@@ -830,7 +819,7 @@
         <v>88.339</v>
       </c>
       <c r="C7" t="n">
-        <v>1279.22109889874</v>
+        <v>288.5476913772789</v>
       </c>
       <c r="D7" t="n">
         <v>2.61617e-07</v>
@@ -863,16 +852,13 @@
         <v>-10212.2407737871</v>
       </c>
       <c r="Y7" t="n">
-        <v>452.1017489174236</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>184651142.0570834</v>
+        <v>205.2885692830164</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.870928133099566e-07</v>
+        <v>3.035692624654456e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.940198540333773</v>
+        <v>0.9690429443664929</v>
       </c>
     </row>
     <row r="8">
@@ -883,7 +869,7 @@
         <v>86.74099999999999</v>
       </c>
       <c r="C8" t="n">
-        <v>1250.247842130406</v>
+        <v>279.1673700266779</v>
       </c>
       <c r="D8" t="n">
         <v>2.61431e-07</v>
@@ -916,16 +902,13 @@
         <v>-10390.98297151223</v>
       </c>
       <c r="Y8" t="n">
-        <v>447.5255461435086</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>186251969.6700453</v>
+        <v>209.7779686162477</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.837286484855732e-07</v>
+        <v>2.988565085512058e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.9414129971822996</v>
+        <v>0.9741591695207212</v>
       </c>
     </row>
     <row r="9">
@@ -936,7 +919,7 @@
         <v>75.55000000000001</v>
       </c>
       <c r="C9" t="n">
-        <v>887.6808016878061</v>
+        <v>270.5031388763601</v>
       </c>
       <c r="D9" t="n">
         <v>2.6122e-07</v>
@@ -969,16 +952,13 @@
         <v>-8486.174645203593</v>
       </c>
       <c r="Y9" t="n">
-        <v>443.1919386320271</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>603072528.4740071</v>
+        <v>213.2948459020328</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.8122141057872e-07</v>
+        <v>2.961304040078978e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.9423048378955623</v>
+        <v>0.9780791324344728</v>
       </c>
     </row>
     <row r="10">
@@ -989,7 +969,7 @@
         <v>81.28800000000001</v>
       </c>
       <c r="C10" t="n">
-        <v>1157.716315494703</v>
+        <v>81.28800000000001</v>
       </c>
       <c r="D10" t="n">
         <v>2.61242e-07</v>
@@ -1021,11 +1001,10 @@
       <c r="X10" t="n">
         <v>-10047.85629252543</v>
       </c>
-      <c r="Y10" t="n">
-        <v>438.9914340641202</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>239030133.4983007</v>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA10" t="n">
         <v>3.792017074982107e-07</v>
@@ -1042,7 +1021,7 @@
         <v>80.596</v>
       </c>
       <c r="C11" t="n">
-        <v>1425.967181650261</v>
+        <v>259.2571686859554</v>
       </c>
       <c r="D11" t="n">
         <v>2.61085e-07</v>
@@ -1075,16 +1054,13 @@
         <v>-10438.64831531955</v>
       </c>
       <c r="Y11" t="n">
-        <v>435.0729141741307</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>118307610.4016054</v>
+        <v>215.1496792817575</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.755259302377786e-07</v>
+        <v>2.896819842384782e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.9445047767300254</v>
+        <v>0.9841219456287496</v>
       </c>
     </row>
   </sheetData>
@@ -1241,7 +1217,7 @@
         <v>123.117</v>
       </c>
       <c r="C2" t="n">
-        <v>2041.000587068997</v>
+        <v>321.402776633894</v>
       </c>
       <c r="D2" t="n">
         <v>2.72644e-07</v>
@@ -1274,16 +1250,13 @@
         <v>-8360.98103653289</v>
       </c>
       <c r="Y2" t="n">
-        <v>480.9179802226254</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>32722752.40087609</v>
+        <v>205.4262152339841</v>
       </c>
       <c r="AA2" t="n">
-        <v>4.76354489356448e-07</v>
+        <v>3.054023043952894e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.9151183199761981</v>
+        <v>0.9570999626100983</v>
       </c>
     </row>
     <row r="3">
@@ -1294,7 +1267,7 @@
         <v>103.567</v>
       </c>
       <c r="C3" t="n">
-        <v>1202.000444526864</v>
+        <v>298.8130768324517</v>
       </c>
       <c r="D3" t="n">
         <v>2.70903e-07</v>
@@ -1327,16 +1300,13 @@
         <v>-9099.215171842827</v>
       </c>
       <c r="Y3" t="n">
-        <v>467.4573120364058</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>184552953.7433971</v>
+        <v>214.0880238171488</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.383445486220268e-07</v>
+        <v>3.415398829678572e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.9266667270381466</v>
+        <v>0.956657759485756</v>
       </c>
     </row>
     <row r="4">
@@ -1347,7 +1317,7 @@
         <v>95.75399999999996</v>
       </c>
       <c r="C4" t="n">
-        <v>978.1090729161624</v>
+        <v>290.6848276806795</v>
       </c>
       <c r="D4" t="n">
         <v>2.70055e-07</v>
@@ -1380,16 +1350,13 @@
         <v>-8852.895054964198</v>
       </c>
       <c r="Y4" t="n">
-        <v>454.0172810323862</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>3786.052574500075</v>
+        <v>216.2954593594942</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.329909910929096e-06</v>
+        <v>3.465882598306991e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.8414651222984563</v>
+        <v>0.9603081372144887</v>
       </c>
     </row>
     <row r="5">
@@ -1400,7 +1367,7 @@
         <v>96.40000000000003</v>
       </c>
       <c r="C5" t="n">
-        <v>1184.717710036321</v>
+        <v>284.1902500700844</v>
       </c>
       <c r="D5" t="n">
         <v>2.69345e-07</v>
@@ -1433,16 +1400,13 @@
         <v>-9578.119360771974</v>
       </c>
       <c r="Y5" t="n">
-        <v>437.8876006493587</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>3750.519568057159</v>
+        <v>216.7643268856545</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.369126947661995e-06</v>
+        <v>3.392131179092535e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.8634281974415232</v>
+        <v>0.9642447875621984</v>
       </c>
     </row>
     <row r="6">
@@ -1453,7 +1417,7 @@
         <v>93.21000000000004</v>
       </c>
       <c r="C6" t="n">
-        <v>1159.48784159667</v>
+        <v>93.21000000000004</v>
       </c>
       <c r="D6" t="n">
         <v>2.69164e-07</v>
@@ -1485,11 +1449,10 @@
       <c r="X6" t="n">
         <v>-9651.181865898097</v>
       </c>
-      <c r="Y6" t="n">
-        <v>452.6898605286162</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>372708633.2520003</v>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA6" t="n">
         <v>4.145001707610471e-07</v>
@@ -1506,7 +1469,7 @@
         <v>89.90199999999999</v>
       </c>
       <c r="C7" t="n">
-        <v>1096.504198591751</v>
+        <v>285.3255967460265</v>
       </c>
       <c r="D7" t="n">
         <v>2.68755e-07</v>
@@ -1539,16 +1502,13 @@
         <v>-9335.073827635899</v>
       </c>
       <c r="Y7" t="n">
-        <v>448.2409320277739</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>213847128.618784</v>
+        <v>205.6331673845985</v>
       </c>
       <c r="AA7" t="n">
-        <v>4.107660705107558e-07</v>
+        <v>3.237270670726093e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.935303220497161</v>
+        <v>0.966159951561589</v>
       </c>
     </row>
     <row r="8">
@@ -1559,7 +1519,7 @@
         <v>86.86799999999999</v>
       </c>
       <c r="C8" t="n">
-        <v>1076.456784454768</v>
+        <v>86.86799999999999</v>
       </c>
       <c r="D8" t="n">
         <v>2.68598e-07</v>
@@ -1591,11 +1551,10 @@
       <c r="X8" t="n">
         <v>-9296.228995134883</v>
       </c>
-      <c r="Y8" t="n">
-        <v>443.9565030544216</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>181463160.9333132</v>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA8" t="n">
         <v>4.064278669403648e-07</v>
@@ -1612,7 +1571,7 @@
         <v>83.68000000000001</v>
       </c>
       <c r="C9" t="n">
-        <v>1036.68428274126</v>
+        <v>272.0211356902333</v>
       </c>
       <c r="D9" t="n">
         <v>2.6826e-07</v>
@@ -1645,16 +1604,13 @@
         <v>-9000.956083669631</v>
       </c>
       <c r="Y9" t="n">
-        <v>439.8959858391522</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>239754015.1150077</v>
+        <v>208.8089194013856</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.030579782766424e-07</v>
+        <v>3.138147437366153e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.9379010583485747</v>
+        <v>0.9716960190708679</v>
       </c>
     </row>
     <row r="10">
@@ -1665,7 +1621,7 @@
         <v>83.89999999999998</v>
       </c>
       <c r="C10" t="n">
-        <v>1160.319110418423</v>
+        <v>266.8839953771854</v>
       </c>
       <c r="D10" t="n">
         <v>2.67996e-07</v>
@@ -1698,16 +1654,13 @@
         <v>-9552.484276580579</v>
       </c>
       <c r="Y10" t="n">
-        <v>436.1400784512594</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>178248817.8884017</v>
+        <v>210.1638982217008</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.991627777082239e-07</v>
+        <v>3.151916879162522e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.9392278592739676</v>
+        <v>0.9750368063868143</v>
       </c>
     </row>
     <row r="11">
@@ -1718,7 +1671,7 @@
         <v>80.892</v>
       </c>
       <c r="C11" t="n">
-        <v>1147.566718997316</v>
+        <v>263.5442154903696</v>
       </c>
       <c r="D11" t="n">
         <v>2.67899e-07</v>
@@ -1751,16 +1704,13 @@
         <v>-9255.033440822186</v>
       </c>
       <c r="Y11" t="n">
-        <v>432.6308624506758</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>118712714.3928932</v>
+        <v>208.3422900152539</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.972024883721081e-07</v>
+        <v>2.98571001451132e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.9399227166687285</v>
+        <v>0.9779969130476638</v>
       </c>
     </row>
     <row r="12">
@@ -1771,7 +1721,7 @@
         <v>79.81299999999999</v>
       </c>
       <c r="C12" t="n">
-        <v>1105.155850821311</v>
+        <v>79.81299999999999</v>
       </c>
       <c r="D12" t="n">
         <v>2.67688e-07</v>
@@ -1803,11 +1753,10 @@
       <c r="X12" t="n">
         <v>-9391.598627738556</v>
       </c>
-      <c r="Y12" t="n">
-        <v>429.2544068328343</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>117731880.7618263</v>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA12" t="n">
         <v>3.941020955067442e-07</v>
@@ -1824,7 +1773,7 @@
         <v>79.834</v>
       </c>
       <c r="C13" t="n">
-        <v>1354.636139517809</v>
+        <v>255.6253435220658</v>
       </c>
       <c r="D13" t="n">
         <v>2.67488e-07</v>
@@ -1857,16 +1806,13 @@
         <v>-9755.401357545546</v>
       </c>
       <c r="Y13" t="n">
-        <v>426.0092985316125</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>115910342.4364102</v>
+        <v>209.283666804612</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.916201313707369e-07</v>
+        <v>2.932628784245715e-09</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.9418383531316091</v>
+        <v>0.9840684482731586</v>
       </c>
     </row>
     <row r="14">
@@ -1877,7 +1823,7 @@
         <v>79.64600000000002</v>
       </c>
       <c r="C14" t="n">
-        <v>1528.40126424197</v>
+        <v>292.3778707083775</v>
       </c>
       <c r="D14" t="n">
         <v>2.67391e-07</v>
@@ -1910,16 +1856,13 @@
         <v>-9907.355670692714</v>
       </c>
       <c r="Y14" t="n">
-        <v>422.7582751157986</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>115113235.4057532</v>
+        <v>168.8802381912911</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.894681968248368e-07</v>
+        <v>2.711537928833161e-09</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.9426184644425313</v>
+        <v>0.9717103869597031</v>
       </c>
     </row>
     <row r="15">
@@ -1930,7 +1873,7 @@
         <v>74.56900000000002</v>
       </c>
       <c r="C15" t="n">
-        <v>1139.289523396569</v>
+        <v>375.1629628756303</v>
       </c>
       <c r="D15" t="n">
         <v>2.67161e-07</v>
@@ -1963,16 +1906,13 @@
         <v>-9230.947039114715</v>
       </c>
       <c r="Y15" t="n">
-        <v>419.5445726516589</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>228489614.6300777</v>
+        <v>81.98508481685084</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.870198928759991e-07</v>
+        <v>2.209917632442655e-09</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.943446300867181</v>
+        <v>0.9529286919212562</v>
       </c>
     </row>
     <row r="16">
@@ -1983,7 +1923,7 @@
         <v>72.36599999999999</v>
       </c>
       <c r="C16" t="n">
-        <v>1084.388580300227</v>
+        <v>72.36599999999999</v>
       </c>
       <c r="D16" t="n">
         <v>2.67154e-07</v>
@@ -2015,11 +1955,10 @@
       <c r="X16" t="n">
         <v>-9039.394937021554</v>
       </c>
-      <c r="Y16" t="n">
-        <v>416.4026218088894</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>113897961.7652397</v>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA16" t="n">
         <v>3.852111742265167e-07</v>
@@ -2036,7 +1975,7 @@
         <v>74.714</v>
       </c>
       <c r="C17" t="n">
-        <v>1409.623082602064</v>
+        <v>300.9773256111691</v>
       </c>
       <c r="D17" t="n">
         <v>2.67023e-07</v>
@@ -2069,16 +2008,13 @@
         <v>-9725.303200891476</v>
       </c>
       <c r="Y17" t="n">
-        <v>413.2448694439817</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>225034438.3059394</v>
+        <v>148.6439560096277</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.824649422397493e-07</v>
+        <v>2.489580359789973e-09</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.9451590446040621</v>
+        <v>0.9703009642891506</v>
       </c>
     </row>
     <row r="18">
@@ -2089,7 +2025,7 @@
         <v>71.79700000000003</v>
       </c>
       <c r="C18" t="n">
-        <v>1278.934043768995</v>
+        <v>71.79700000000003</v>
       </c>
       <c r="D18" t="n">
         <v>2.66962e-07</v>
@@ -2121,11 +2057,10 @@
       <c r="X18" t="n">
         <v>-9479.464339063117</v>
       </c>
-      <c r="Y18" t="n">
-        <v>410.0939754555842</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>111547416.8222765</v>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA18" t="n">
         <v>3.80791102093921e-07</v>
@@ -2142,7 +2077,7 @@
         <v>72.14000000000004</v>
       </c>
       <c r="C19" t="n">
-        <v>1584.414576363821</v>
+        <v>72.14000000000004</v>
       </c>
       <c r="D19" t="n">
         <v>2.66831e-07</v>
@@ -2174,11 +2109,10 @@
       <c r="X19" t="n">
         <v>-9689.716375442036</v>
       </c>
-      <c r="Y19" t="n">
-        <v>406.9299068987231</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>166188766.2632105</v>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA19" t="n">
         <v>3.795864383290239e-07</v>
@@ -2195,7 +2129,7 @@
         <v>67.97899999999998</v>
       </c>
       <c r="C20" t="n">
-        <v>1128.676562504201</v>
+        <v>259.298973178047</v>
       </c>
       <c r="D20" t="n">
         <v>2.6676e-07</v>
@@ -2228,16 +2162,13 @@
         <v>-9112.604359247525</v>
       </c>
       <c r="Y20" t="n">
-        <v>403.8097827662983</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>110186319.4424782</v>
+        <v>180.0947226192888</v>
       </c>
       <c r="AA20" t="n">
-        <v>3.773386297485312e-07</v>
+        <v>2.560503052061468e-09</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.9470588941999227</v>
+        <v>0.9883849659134706</v>
       </c>
     </row>
     <row r="21">
@@ -2248,7 +2179,7 @@
         <v>67.697</v>
       </c>
       <c r="C21" t="n">
-        <v>1372.149299879956</v>
+        <v>67.697</v>
       </c>
       <c r="D21" t="n">
         <v>2.66757e-07</v>
@@ -2280,11 +2211,10 @@
       <c r="X21" t="n">
         <v>-9365.318451994282</v>
       </c>
-      <c r="Y21" t="n">
-        <v>400.5999790302465</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>174014444.5471484</v>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA21" t="n">
         <v>3.749404704529664e-07</v>
@@ -2301,7 +2231,7 @@
         <v>67.423</v>
       </c>
       <c r="C22" t="n">
-        <v>1460.925774212316</v>
+        <v>251.226710645646</v>
       </c>
       <c r="D22" t="n">
         <v>2.66694e-07</v>
@@ -2334,16 +2264,13 @@
         <v>-9532.753076700101</v>
       </c>
       <c r="Y22" t="n">
-        <v>397.4150777577553</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>108186090.8757237</v>
+        <v>180.2399021969108</v>
       </c>
       <c r="AA22" t="n">
-        <v>3.73254825807647e-07</v>
+        <v>2.448464186610658e-09</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.9486615081080416</v>
+        <v>0.9941180490747477</v>
       </c>
     </row>
   </sheetData>
@@ -2500,7 +2427,7 @@
         <v>127.235</v>
       </c>
       <c r="C2" t="n">
-        <v>2586.212812919433</v>
+        <v>311.8203438103901</v>
       </c>
       <c r="D2" t="n">
         <v>2.76249e-07</v>
@@ -2533,16 +2460,13 @@
         <v>-7751.373462847805</v>
       </c>
       <c r="Y2" t="n">
-        <v>489.3266483925309</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>107266965.1809667</v>
+        <v>224.8049189095018</v>
       </c>
       <c r="AA2" t="n">
-        <v>5.117874468168567e-07</v>
+        <v>3.256997233637986e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.9064835283478637</v>
+        <v>0.9551582904690579</v>
       </c>
     </row>
     <row r="3">
@@ -2553,7 +2477,7 @@
         <v>103.22</v>
       </c>
       <c r="C3" t="n">
-        <v>1159.030521839782</v>
+        <v>103.22</v>
       </c>
       <c r="D3" t="n">
         <v>2.69663e-07</v>
@@ -2585,11 +2509,10 @@
       <c r="X3" t="n">
         <v>-9142.691276745545</v>
       </c>
-      <c r="Y3" t="n">
-        <v>473.6761094560357</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>193739339.0518807</v>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA3" t="n">
         <v>4.361934590012305e-07</v>
@@ -2606,7 +2529,7 @@
         <v>98.11100000000005</v>
       </c>
       <c r="C4" t="n">
-        <v>1113.051029798632</v>
+        <v>302.2430431724609</v>
       </c>
       <c r="D4" t="n">
         <v>2.67466e-07</v>
@@ -2639,16 +2562,13 @@
         <v>-9826.40835573673</v>
       </c>
       <c r="Y4" t="n">
-        <v>443.9702341850466</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>3830.162915425468</v>
+        <v>209.5102998264315</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.663103739688245e-06</v>
+        <v>3.34247232173712e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.8227840406122269</v>
+        <v>0.9573863392555503</v>
       </c>
     </row>
     <row r="5">
@@ -2659,7 +2579,7 @@
         <v>94.24499999999995</v>
       </c>
       <c r="C5" t="n">
-        <v>1149.862309491787</v>
+        <v>94.24499999999995</v>
       </c>
       <c r="D5" t="n">
         <v>2.66165e-07</v>
@@ -2691,11 +2611,10 @@
       <c r="X5" t="n">
         <v>-10144.97169018693</v>
       </c>
-      <c r="Y5" t="n">
-        <v>461.9480378828465</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>188865975.5467272</v>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA5" t="n">
         <v>4.05022007432776e-07</v>
@@ -2712,7 +2631,7 @@
         <v>90.20500000000004</v>
       </c>
       <c r="C6" t="n">
-        <v>1021.840160489777</v>
+        <v>90.20500000000004</v>
       </c>
       <c r="D6" t="n">
         <v>2.65327e-07</v>
@@ -2744,11 +2663,10 @@
       <c r="X6" t="n">
         <v>-9944.378389610323</v>
       </c>
-      <c r="Y6" t="n">
-        <v>457.2780540802589</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>186916035.996489</v>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA6" t="n">
         <v>3.974253091366641e-07</v>
@@ -2765,7 +2683,7 @@
         <v>88.66500000000002</v>
       </c>
       <c r="C7" t="n">
-        <v>1101.746923166582</v>
+        <v>278.3399754802228</v>
       </c>
       <c r="D7" t="n">
         <v>2.64548e-07</v>
@@ -2798,16 +2716,13 @@
         <v>-10269.29342203443</v>
       </c>
       <c r="Y7" t="n">
-        <v>452.8080354240732</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>370275443.9422262</v>
+        <v>217.3011836480284</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.930978807543943e-07</v>
+        <v>3.246698665830911e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.9395936313795407</v>
+        <v>0.9697832236769369</v>
       </c>
     </row>
     <row r="8">
@@ -2818,7 +2733,7 @@
         <v>85.44799999999998</v>
       </c>
       <c r="C8" t="n">
-        <v>1049.571623158748</v>
+        <v>271.6278766491395</v>
       </c>
       <c r="D8" t="n">
         <v>2.64146e-07</v>
@@ -2851,16 +2766,13 @@
         <v>-9938.273876717878</v>
       </c>
       <c r="Y8" t="n">
-        <v>448.5791766810402</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>122673713.7347551</v>
+        <v>218.9167356284906</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.888280687482529e-07</v>
+        <v>3.230033604263431e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.9410154735253821</v>
+        <v>0.9719565266017115</v>
       </c>
     </row>
     <row r="9">
@@ -2871,7 +2783,7 @@
         <v>86.50400000000002</v>
       </c>
       <c r="C9" t="n">
-        <v>1306.950579478831</v>
+        <v>270.632445255155</v>
       </c>
       <c r="D9" t="n">
         <v>2.63749e-07</v>
@@ -2904,16 +2816,13 @@
         <v>-10810.29347620989</v>
       </c>
       <c r="Y9" t="n">
-        <v>444.5332927489689</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>968286450.4794898</v>
+        <v>214.2745901883827</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.844328084949008e-07</v>
+        <v>3.094554235943757e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.9425036085232681</v>
+        <v>0.9726984257445165</v>
       </c>
     </row>
     <row r="10">
@@ -2924,7 +2833,7 @@
         <v>82.78000000000003</v>
       </c>
       <c r="C10" t="n">
-        <v>1162.271947841235</v>
+        <v>82.78000000000003</v>
       </c>
       <c r="D10" t="n">
         <v>2.63693e-07</v>
@@ -2956,11 +2865,10 @@
       <c r="X10" t="n">
         <v>-10413.43311909305</v>
       </c>
-      <c r="Y10" t="n">
-        <v>440.5873702632053</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>184768244.8321308</v>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA10" t="n">
         <v>3.815704047326536e-07</v>
@@ -2977,7 +2885,7 @@
         <v>81.62599999999998</v>
       </c>
       <c r="C11" t="n">
-        <v>1275.515577500727</v>
+        <v>273.931822756834</v>
       </c>
       <c r="D11" t="n">
         <v>2.63424e-07</v>
@@ -3010,16 +2918,13 @@
         <v>-10691.8405558676</v>
       </c>
       <c r="Y11" t="n">
-        <v>436.8161075249475</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>356645226.2740096</v>
+        <v>202.6447225581472</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.783203121129007e-07</v>
+        <v>2.934167877457859e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.9447429738066498</v>
+        <v>0.97619521660496</v>
       </c>
     </row>
     <row r="12">
@@ -3030,7 +2935,7 @@
         <v>80.48199999999997</v>
       </c>
       <c r="C12" t="n">
-        <v>1340.808776300246</v>
+        <v>263.1916753154977</v>
       </c>
       <c r="D12" t="n">
         <v>2.63247e-07</v>
@@ -3063,16 +2968,13 @@
         <v>-10800.42748218264</v>
       </c>
       <c r="Y12" t="n">
-        <v>433.1057700019758</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>117833105.0114324</v>
+        <v>208.8295789926936</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.76118759844843e-07</v>
+        <v>2.914191425989571e-09</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.9455323355146705</v>
+        <v>0.9812823881140623</v>
       </c>
     </row>
     <row r="13">
@@ -3083,7 +2985,7 @@
         <v>76.88</v>
       </c>
       <c r="C13" t="n">
-        <v>1139.670042063237</v>
+        <v>76.88</v>
       </c>
       <c r="D13" t="n">
         <v>2.6306e-07</v>
@@ -3115,11 +3017,10 @@
       <c r="X13" t="n">
         <v>-10161.85739058252</v>
       </c>
-      <c r="Y13" t="n">
-        <v>429.4439812672068</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>175380791.5834915</v>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA13" t="n">
         <v>3.749219490547249e-07</v>
@@ -3136,7 +3037,7 @@
         <v>78.01499999999999</v>
       </c>
       <c r="C14" t="n">
-        <v>1579.548196473024</v>
+        <v>78.01499999999999</v>
       </c>
       <c r="D14" t="n">
         <v>2.6299e-07</v>
@@ -3168,11 +3069,10 @@
       <c r="X14" t="n">
         <v>-10932.96353878005</v>
       </c>
-      <c r="Y14" t="n">
-        <v>425.9360495064776</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>231850658.248151</v>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA14" t="n">
         <v>3.720419380982052e-07</v>
@@ -3189,7 +3089,7 @@
         <v>73.17599999999999</v>
       </c>
       <c r="C15" t="n">
-        <v>1158.237863090533</v>
+        <v>73.17599999999999</v>
       </c>
       <c r="D15" t="n">
         <v>2.62701e-07</v>
@@ -3221,11 +3121,10 @@
       <c r="X15" t="n">
         <v>-10062.84740667248</v>
       </c>
-      <c r="Y15" t="n">
-        <v>422.5053683915358</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>115035712.5850869</v>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA15" t="n">
         <v>3.700733224478628e-07</v>
@@ -3242,7 +3141,7 @@
         <v>71.80000000000001</v>
       </c>
       <c r="C16" t="n">
-        <v>1111.868495126394</v>
+        <v>71.80000000000001</v>
       </c>
       <c r="D16" t="n">
         <v>2.62774e-07</v>
@@ -3274,11 +3173,10 @@
       <c r="X16" t="n">
         <v>-10140.97625424357</v>
       </c>
-      <c r="Y16" t="n">
-        <v>419.1506147717284</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>194254551.8520578</v>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA16" t="n">
         <v>3.680147787927724e-07</v>
@@ -3295,7 +3193,7 @@
         <v>63.90500000000003</v>
       </c>
       <c r="C17" t="n">
-        <v>871.381342517173</v>
+        <v>63.90500000000003</v>
       </c>
       <c r="D17" t="n">
         <v>2.62665e-07</v>
@@ -3327,11 +3225,10 @@
       <c r="X17" t="n">
         <v>-8545.572680046193</v>
       </c>
-      <c r="Y17" t="n">
-        <v>415.8752996081886</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>113149192.4884365</v>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA17" t="n">
         <v>3.662335020716312e-07</v>
@@ -3348,7 +3245,7 @@
         <v>70.37099999999998</v>
       </c>
       <c r="C18" t="n">
-        <v>1323.961131520585</v>
+        <v>70.37099999999998</v>
       </c>
       <c r="D18" t="n">
         <v>2.62561e-07</v>
@@ -3380,11 +3277,10 @@
       <c r="X18" t="n">
         <v>-10518.96137799515</v>
       </c>
-      <c r="Y18" t="n">
-        <v>412.6466910559025</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>224736200.9780773</v>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA18" t="n">
         <v>3.643023645097892e-07</v>
@@ -3401,7 +3297,7 @@
         <v>70.33600000000001</v>
       </c>
       <c r="C19" t="n">
-        <v>1550.686136580121</v>
+        <v>70.33600000000001</v>
       </c>
       <c r="D19" t="n">
         <v>2.62665e-07</v>
@@ -3433,11 +3329,10 @@
       <c r="X19" t="n">
         <v>-10802.08755314234</v>
       </c>
-      <c r="Y19" t="n">
-        <v>409.4551609776633</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>222919474.3622769</v>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA19" t="n">
         <v>3.633735453588941e-07</v>
@@ -3454,7 +3349,7 @@
         <v>67.50400000000002</v>
       </c>
       <c r="C20" t="n">
-        <v>1250.437060771369</v>
+        <v>67.50400000000002</v>
       </c>
       <c r="D20" t="n">
         <v>2.62544e-07</v>
@@ -3486,11 +3381,10 @@
       <c r="X20" t="n">
         <v>-10333.87876575362</v>
       </c>
-      <c r="Y20" t="n">
-        <v>406.3600839261352</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>663848237.5938212</v>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA20" t="n">
         <v>3.617354002147274e-07</v>
@@ -3507,7 +3401,7 @@
         <v>65.69799999999998</v>
       </c>
       <c r="C21" t="n">
-        <v>1202.949647855174</v>
+        <v>337.9518830409297</v>
       </c>
       <c r="D21" t="n">
         <v>2.62416e-07</v>
@@ -3540,16 +3434,13 @@
         <v>-10176.64596798434</v>
       </c>
       <c r="Y21" t="n">
-        <v>403.2808176775151</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>109812062.8511681</v>
+        <v>99.66359498637289</v>
       </c>
       <c r="AA21" t="n">
-        <v>3.599258221389223e-07</v>
+        <v>2.0752372489021e-09</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.9517534265592323</v>
+        <v>0.96840244442288</v>
       </c>
     </row>
     <row r="22">
@@ -3560,7 +3451,7 @@
         <v>65.69800000000004</v>
       </c>
       <c r="C22" t="n">
-        <v>1491.110636291105</v>
+        <v>253.4849512926001</v>
       </c>
       <c r="D22" t="n">
         <v>2.62309e-07</v>
@@ -3593,16 +3484,13 @@
         <v>-10345.33052685845</v>
       </c>
       <c r="Y22" t="n">
-        <v>400.2005045956716</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>870186794.0575885</v>
+        <v>180.98746229842</v>
       </c>
       <c r="AA22" t="n">
-        <v>3.594996674257935e-07</v>
+        <v>2.43105433794594e-09</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.9518836743788911</v>
+        <v>0.9939080897666923</v>
       </c>
     </row>
   </sheetData>
@@ -3759,7 +3647,7 @@
         <v>176.22</v>
       </c>
       <c r="C2" t="n">
-        <v>2635.239028489558</v>
+        <v>442.7387460738697</v>
       </c>
       <c r="D2" t="n">
         <v>2.79854e-07</v>
@@ -3792,16 +3680,13 @@
         <v>-6757.919165589063</v>
       </c>
       <c r="Y2" t="n">
-        <v>536.6848260996646</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>589286338.9800715</v>
+        <v>150.0046541522291</v>
       </c>
       <c r="AA2" t="n">
-        <v>6.871695977063213e-07</v>
+        <v>2.663338815567681e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.8642186898387478</v>
+        <v>0.930935082071441</v>
       </c>
     </row>
     <row r="3">
@@ -3812,7 +3697,7 @@
         <v>133.565</v>
       </c>
       <c r="C3" t="n">
-        <v>1215.826072554044</v>
+        <v>369.9274596601722</v>
       </c>
       <c r="D3" t="n">
         <v>2.81243e-07</v>
@@ -3845,16 +3730,13 @@
         <v>-7718.58434488335</v>
       </c>
       <c r="Y3" t="n">
-        <v>512.4986315999361</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>48174490.39845841</v>
+        <v>198.1229987553611</v>
       </c>
       <c r="AA3" t="n">
-        <v>5.584673222971136e-07</v>
+        <v>4.062100530834641e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.8960328445951323</v>
+        <v>0.9233217790353742</v>
       </c>
     </row>
     <row r="4">
@@ -3865,7 +3747,7 @@
         <v>121.0210000000001</v>
       </c>
       <c r="C4" t="n">
-        <v>1041.04672888471</v>
+        <v>414.5212612480102</v>
       </c>
       <c r="D4" t="n">
         <v>2.78511e-07</v>
@@ -3898,16 +3780,13 @@
         <v>-8224.407501363354</v>
       </c>
       <c r="Y4" t="n">
-        <v>503.443943654204</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>37943666.38081218</v>
+        <v>141.4992196163157</v>
       </c>
       <c r="AA4" t="n">
-        <v>5.082483036017803e-07</v>
+        <v>3.500981176660617e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.9086717044287616</v>
+        <v>0.9168284063498134</v>
       </c>
     </row>
     <row r="5">
@@ -3918,7 +3797,7 @@
         <v>115.665</v>
       </c>
       <c r="C5" t="n">
-        <v>979.7952431635265</v>
+        <v>423.001674061831</v>
       </c>
       <c r="D5" t="n">
         <v>2.76359e-07</v>
@@ -3951,16 +3830,13 @@
         <v>-8750.737407184411</v>
       </c>
       <c r="Y5" t="n">
-        <v>497.1263969792354</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>36136651.60595468</v>
+        <v>125.0068834456386</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.812910557211444e-07</v>
+        <v>3.327909644301807e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.9156698053745044</v>
+        <v>0.9165340856834941</v>
       </c>
     </row>
     <row r="6">
@@ -3971,7 +3847,7 @@
         <v>111.664</v>
       </c>
       <c r="C6" t="n">
-        <v>995.02190658779</v>
+        <v>315.214014663866</v>
       </c>
       <c r="D6" t="n">
         <v>2.74397e-07</v>
@@ -4004,16 +3880,13 @@
         <v>-9159.621420920957</v>
       </c>
       <c r="Y6" t="n">
-        <v>491.2163573691311</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>134309084.697485</v>
+        <v>226.5890297600529</v>
       </c>
       <c r="AA6" t="n">
-        <v>4.631455767424235e-07</v>
+        <v>4.165648408251593e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.9203777368027308</v>
+        <v>0.9410193869540328</v>
       </c>
     </row>
     <row r="7">
@@ -4024,7 +3897,7 @@
         <v>106.525</v>
       </c>
       <c r="C7" t="n">
-        <v>982.9181314317373</v>
+        <v>304.4091474298356</v>
       </c>
       <c r="D7" t="n">
         <v>2.73123e-07</v>
@@ -4057,16 +3930,13 @@
         <v>-9169.78964253145</v>
       </c>
       <c r="Y7" t="n">
-        <v>485.4364083442069</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>265477180.1549042</v>
+        <v>229.5252936546995</v>
       </c>
       <c r="AA7" t="n">
-        <v>4.500455495922638e-07</v>
+        <v>3.848689010004373e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.9239989877368346</v>
+        <v>0.9485918810563725</v>
       </c>
     </row>
     <row r="8">
@@ -4077,7 +3947,7 @@
         <v>106.549</v>
       </c>
       <c r="C8" t="n">
-        <v>1114.771364220516</v>
+        <v>293.8644231531741</v>
       </c>
       <c r="D8" t="n">
         <v>2.71946e-07</v>
@@ -4110,16 +3980,13 @@
         <v>-9885.402018134655</v>
       </c>
       <c r="Y8" t="n">
-        <v>479.7942909356152</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>131023940.34062</v>
+        <v>233.694384966184</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.389724878764684e-07</v>
+        <v>3.925830398464447e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.9271133873023493</v>
+        <v>0.9526061728951756</v>
       </c>
     </row>
     <row r="9">
@@ -4130,7 +3997,7 @@
         <v>99.30899999999997</v>
       </c>
       <c r="C9" t="n">
-        <v>981.7589436192243</v>
+        <v>294.8076902070335</v>
       </c>
       <c r="D9" t="n">
         <v>2.71109e-07</v>
@@ -4163,16 +4030,13 @@
         <v>-9258.92408894535</v>
       </c>
       <c r="Y9" t="n">
-        <v>464.4180728158482</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>3892.381706851974</v>
+        <v>226.3813638178644</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.172201301024176e-06</v>
+        <v>3.804104360018542e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.8860525156364467</v>
+        <v>0.9521398391556299</v>
       </c>
     </row>
     <row r="10">
@@ -4183,7 +4047,7 @@
         <v>96.35899999999998</v>
       </c>
       <c r="C10" t="n">
-        <v>983.1096099877034</v>
+        <v>282.5669926435706</v>
       </c>
       <c r="D10" t="n">
         <v>2.70458e-07</v>
@@ -4216,16 +4080,13 @@
         <v>-9296.456844935376</v>
       </c>
       <c r="Y10" t="n">
-        <v>450.9331247486803</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>3850.192004271824</v>
+        <v>232.6866487214249</v>
       </c>
       <c r="AA10" t="n">
-        <v>9.042976841967091e-07</v>
+        <v>3.690855315928129e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.9131653180518182</v>
+        <v>0.9613586079873644</v>
       </c>
     </row>
     <row r="11">
@@ -4236,7 +4097,7 @@
         <v>97.024</v>
       </c>
       <c r="C11" t="n">
-        <v>1132.297131039089</v>
+        <v>284.6341105243151</v>
       </c>
       <c r="D11" t="n">
         <v>2.69936e-07</v>
@@ -4269,16 +4130,13 @@
         <v>-10002.05164744971</v>
       </c>
       <c r="Y11" t="n">
-        <v>451.1993374767339</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>7672.813938747323</v>
+        <v>225.5531258644423</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.584885292294679e-07</v>
+        <v>3.719531512160598e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.9999959218011779</v>
+        <v>0.959207052369758</v>
       </c>
     </row>
   </sheetData>
@@ -4435,7 +4293,7 @@
         <v>122.251</v>
       </c>
       <c r="C2" t="n">
-        <v>2071.129000891164</v>
+        <v>371.1302526460128</v>
       </c>
       <c r="D2" t="n">
         <v>2.76224e-07</v>
@@ -4468,16 +4326,13 @@
         <v>-7763.767418940207</v>
       </c>
       <c r="Y2" t="n">
-        <v>480.2951757214407</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>58206032.58323675</v>
+        <v>154.9282210469704</v>
       </c>
       <c r="AA2" t="n">
-        <v>4.992013584057573e-07</v>
+        <v>2.775127738980829e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.9101550712502147</v>
+        <v>0.9423162248084451</v>
       </c>
     </row>
     <row r="3">
@@ -4488,7 +4343,7 @@
         <v>100.185</v>
       </c>
       <c r="C3" t="n">
-        <v>1070.006645330949</v>
+        <v>293.5717942110369</v>
       </c>
       <c r="D3" t="n">
         <v>2.73656e-07</v>
@@ -4521,16 +4376,13 @@
         <v>-8434.634266655097</v>
       </c>
       <c r="Y3" t="n">
-        <v>466.0520934308912</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>516752350.111385</v>
+        <v>218.5030673679464</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.480406649797358e-07</v>
+        <v>3.555761999522446e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.9249675534955195</v>
+        <v>0.9574689393513774</v>
       </c>
     </row>
     <row r="4">
@@ -4541,7 +4393,7 @@
         <v>96.005</v>
       </c>
       <c r="C4" t="n">
-        <v>1028.069869692912</v>
+        <v>293.9620819484975</v>
       </c>
       <c r="D4" t="n">
         <v>2.7226e-07</v>
@@ -4574,16 +4426,13 @@
         <v>-9104.597151980255</v>
       </c>
       <c r="Y4" t="n">
-        <v>440.2287237932851</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>3771.878876273001</v>
+        <v>210.4424909159111</v>
       </c>
       <c r="AA4" t="n">
-        <v>9.89915647613028e-07</v>
+        <v>3.45745774056418e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.9048746537960295</v>
+        <v>0.958654833657449</v>
       </c>
     </row>
     <row r="5">
@@ -4594,7 +4443,7 @@
         <v>83.81100000000004</v>
       </c>
       <c r="C5" t="n">
-        <v>780.5624334017402</v>
+        <v>83.81100000000004</v>
       </c>
       <c r="D5" t="n">
         <v>2.71316e-07</v>
@@ -4626,11 +4475,10 @@
       <c r="X5" t="n">
         <v>-7782.179053414251</v>
       </c>
-      <c r="Y5" t="n">
-        <v>455.2898977755081</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>233476585.7749151</v>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA5" t="n">
         <v>4.214796704370467e-07</v>
@@ -4647,7 +4495,7 @@
         <v>89.99099999999999</v>
       </c>
       <c r="C6" t="n">
-        <v>1105.687811972319</v>
+        <v>309.1481524226048</v>
       </c>
       <c r="D6" t="n">
         <v>2.70379e-07</v>
@@ -4680,16 +4528,13 @@
         <v>-9593.136762940996</v>
       </c>
       <c r="Y6" t="n">
-        <v>450.9861210411568</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>126545179.3254542</v>
+        <v>185.1971522685739</v>
       </c>
       <c r="AA6" t="n">
-        <v>4.129222500315576e-07</v>
+        <v>3.157655628746171e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.9354617326991671</v>
+        <v>0.9581210886649902</v>
       </c>
     </row>
     <row r="7">
@@ -4700,7 +4545,7 @@
         <v>88.84500000000003</v>
       </c>
       <c r="C7" t="n">
-        <v>1145.362233957521</v>
+        <v>288.029130813907</v>
       </c>
       <c r="D7" t="n">
         <v>2.69961e-07</v>
@@ -4733,16 +4578,13 @@
         <v>-9806.389472830584</v>
       </c>
       <c r="Y7" t="n">
-        <v>446.8889649155186</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>122458875.3100242</v>
+        <v>201.0756620235954</v>
       </c>
       <c r="AA7" t="n">
-        <v>4.067916761251468e-07</v>
+        <v>3.204622496837388e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.9374812448816695</v>
+        <v>0.9654061452331031</v>
       </c>
     </row>
     <row r="8">
@@ -4753,7 +4595,7 @@
         <v>86.53199999999998</v>
       </c>
       <c r="C8" t="n">
-        <v>1089.61742367896</v>
+        <v>280.5610312198099</v>
       </c>
       <c r="D8" t="n">
         <v>2.69501e-07</v>
@@ -4786,16 +4628,13 @@
         <v>-9869.027485010618</v>
       </c>
       <c r="Y8" t="n">
-        <v>442.8712218178521</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>122392902.8602818</v>
+        <v>203.5594313894652</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.024624242343295e-07</v>
+        <v>3.171923987511151e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.9388505881348892</v>
+        <v>0.9672949867260522</v>
       </c>
     </row>
     <row r="9">
@@ -4806,7 +4645,7 @@
         <v>84.29000000000002</v>
       </c>
       <c r="C9" t="n">
-        <v>1163.8042330788</v>
+        <v>84.29000000000002</v>
       </c>
       <c r="D9" t="n">
         <v>2.69065e-07</v>
@@ -4838,11 +4677,10 @@
       <c r="X9" t="n">
         <v>-9966.373567261111</v>
       </c>
-      <c r="Y9" t="n">
-        <v>439.1164588465697</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>358891114.3223209</v>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA9" t="n">
         <v>3.981809757220652e-07</v>
@@ -4859,7 +4697,7 @@
         <v>82.62300000000005</v>
       </c>
       <c r="C10" t="n">
-        <v>1138.155710573946</v>
+        <v>82.62300000000005</v>
       </c>
       <c r="D10" t="n">
         <v>2.68862e-07</v>
@@ -4891,11 +4729,10 @@
       <c r="X10" t="n">
         <v>-10037.10526332246</v>
       </c>
-      <c r="Y10" t="n">
-        <v>435.6279289492796</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>135088959.5285163</v>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA10" t="n">
         <v>3.942594878233831e-07</v>
@@ -4912,7 +4749,7 @@
         <v>79.98599999999999</v>
       </c>
       <c r="C11" t="n">
-        <v>1117.753121679628</v>
+        <v>79.98599999999999</v>
       </c>
       <c r="D11" t="n">
         <v>2.685e-07</v>
@@ -4944,11 +4781,10 @@
       <c r="X11" t="n">
         <v>-9852.044214779651</v>
       </c>
-      <c r="Y11" t="n">
-        <v>432.426126761333</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>353362037.112519</v>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA11" t="n">
         <v>3.915712377291921e-07</v>
@@ -4965,7 +4801,7 @@
         <v>78.154</v>
       </c>
       <c r="C12" t="n">
-        <v>1056.623211221279</v>
+        <v>263.3905282117934</v>
       </c>
       <c r="D12" t="n">
         <v>2.68248e-07</v>
@@ -4998,16 +4834,13 @@
         <v>-9738.146833238899</v>
       </c>
       <c r="Y12" t="n">
-        <v>429.3655616654337</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>350392262.7494087</v>
+        <v>204.2833436307353</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.887829210702251e-07</v>
+        <v>2.964121245558477e-09</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.9433874120046737</v>
+        <v>0.9786758717370597</v>
       </c>
     </row>
     <row r="13">
@@ -5018,7 +4851,7 @@
         <v>78.22499999999997</v>
       </c>
       <c r="C13" t="n">
-        <v>1158.946581049302</v>
+        <v>258.9733323338668</v>
       </c>
       <c r="D13" t="n">
         <v>2.68049e-07</v>
@@ -5051,16 +4884,13 @@
         <v>-10018.55328220722</v>
       </c>
       <c r="Y13" t="n">
-        <v>426.3164300355821</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>580420486.7926364</v>
+        <v>206.0807715082621</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.855688000858838e-07</v>
+        <v>2.980051866028077e-09</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.944520693151338</v>
+        <v>0.9812405777337895</v>
       </c>
     </row>
     <row r="14">
@@ -5071,7 +4901,7 @@
         <v>77.61399999999998</v>
       </c>
       <c r="C14" t="n">
-        <v>1265.306162161252</v>
+        <v>254.4256969508972</v>
       </c>
       <c r="D14" t="n">
         <v>2.6773e-07</v>
@@ -5104,16 +4934,13 @@
         <v>-10335.15395494345</v>
       </c>
       <c r="Y14" t="n">
-        <v>423.2760786268939</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>119273868.8902068</v>
+        <v>207.1560855920462</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.831347269447549e-07</v>
+        <v>2.946670623475948e-09</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.9453085696818081</v>
+        <v>0.9838192920285174</v>
       </c>
     </row>
     <row r="15">
@@ -5124,7 +4951,7 @@
         <v>70.72300000000001</v>
       </c>
       <c r="C15" t="n">
-        <v>841.8951208112268</v>
+        <v>249.3184055109992</v>
       </c>
       <c r="D15" t="n">
         <v>2.67571e-07</v>
@@ -5157,16 +4984,13 @@
         <v>-8970.084037679289</v>
       </c>
       <c r="Y15" t="n">
-        <v>420.1909075974667</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>114419301.9815577</v>
+        <v>207.9274160689047</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.815828381615512e-07</v>
+        <v>2.883406127495331e-09</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.9458411130672405</v>
+        <v>0.9858299501431627</v>
       </c>
     </row>
     <row r="16">
@@ -5177,7 +5001,7 @@
         <v>73.56799999999998</v>
       </c>
       <c r="C16" t="n">
-        <v>1151.32314085616</v>
+        <v>73.56799999999998</v>
       </c>
       <c r="D16" t="n">
         <v>2.67374e-07</v>
@@ -5209,11 +5033,10 @@
       <c r="X16" t="n">
         <v>-9770.701640971984</v>
       </c>
-      <c r="Y16" t="n">
-        <v>417.1214845417246</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>170335906.1875667</v>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA16" t="n">
         <v>3.79570601572069e-07</v>
@@ -5230,7 +5053,7 @@
         <v>73.66899999999998</v>
       </c>
       <c r="C17" t="n">
-        <v>1333.291066661545</v>
+        <v>242.4036711160778</v>
       </c>
       <c r="D17" t="n">
         <v>2.67279e-07</v>
@@ -5263,16 +5086,13 @@
         <v>-10197.68748450432</v>
       </c>
       <c r="Y17" t="n">
-        <v>414.0538608169979</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>189662324.7506776</v>
+        <v>207.7190665652174</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.774134290660462e-07</v>
+        <v>2.799605684058503e-09</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.947336461795603</v>
+        <v>0.9912551803641145</v>
       </c>
     </row>
     <row r="18">
@@ -5283,7 +5103,7 @@
         <v>73.53999999999996</v>
       </c>
       <c r="C18" t="n">
-        <v>1450.53164419885</v>
+        <v>73.53999999999996</v>
       </c>
       <c r="D18" t="n">
         <v>2.67075e-07</v>
@@ -5315,11 +5135,10 @@
       <c r="X18" t="n">
         <v>-10453.6666009086</v>
       </c>
-      <c r="Y18" t="n">
-        <v>411.0115831455041</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>335463998.5325902</v>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA18" t="n">
         <v>3.75005320023306e-07</v>
@@ -5336,7 +5155,7 @@
         <v>69.43700000000001</v>
       </c>
       <c r="C19" t="n">
-        <v>1041.712351240576</v>
+        <v>69.43700000000001</v>
       </c>
       <c r="D19" t="n">
         <v>2.66953e-07</v>
@@ -5368,11 +5187,10 @@
       <c r="X19" t="n">
         <v>-9699.759956167509</v>
       </c>
-      <c r="Y19" t="n">
-        <v>407.8691435991047</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>166791579.8430284</v>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA19" t="n">
         <v>3.733618963832413e-07</v>
@@ -5389,7 +5207,7 @@
         <v>69.13500000000005</v>
       </c>
       <c r="C20" t="n">
-        <v>1211.447361577304</v>
+        <v>295.3282782537679</v>
       </c>
       <c r="D20" t="n">
         <v>2.66861e-07</v>
@@ -5422,16 +5240,13 @@
         <v>-9910.233625440118</v>
       </c>
       <c r="Y20" t="n">
-        <v>404.7743525593904</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>220966175.5117127</v>
+        <v>144.2515569162191</v>
       </c>
       <c r="AA20" t="n">
-        <v>3.722562336146518e-07</v>
+        <v>2.397901042999604e-09</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.9491914304127851</v>
+        <v>0.9755196704437346</v>
       </c>
     </row>
     <row r="21">
@@ -5442,7 +5257,7 @@
         <v>70.59499999999997</v>
       </c>
       <c r="C21" t="n">
-        <v>1532.503127564351</v>
+        <v>70.59499999999997</v>
       </c>
       <c r="D21" t="n">
         <v>2.66724e-07</v>
@@ -5474,11 +5289,10 @@
       <c r="X21" t="n">
         <v>-10659.97893321486</v>
       </c>
-      <c r="Y21" t="n">
-        <v>401.6864719294056</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>218430394.4754781</v>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA21" t="n">
         <v>3.70075288371997e-07</v>
@@ -5495,7 +5309,7 @@
         <v>66.67299999999994</v>
       </c>
       <c r="C22" t="n">
-        <v>1297.68069844646</v>
+        <v>66.67299999999994</v>
       </c>
       <c r="D22" t="n">
         <v>2.66594e-07</v>
@@ -5527,11 +5341,10 @@
       <c r="X22" t="n">
         <v>-9967.246164742723</v>
       </c>
-      <c r="Y22" t="n">
-        <v>398.5548574235218</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>433419073.6183606</v>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA22" t="n">
         <v>3.67800067085379e-07</v>
@@ -5694,7 +5507,7 @@
         <v>203.4469999999999</v>
       </c>
       <c r="C2" t="n">
-        <v>3658.577788260438</v>
+        <v>415.5327085246262</v>
       </c>
       <c r="D2" t="n">
         <v>2.84316e-07</v>
@@ -5727,16 +5540,13 @@
         <v>-5594.038148614398</v>
       </c>
       <c r="Y2" t="n">
-        <v>543.1549205509359</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>186265100.5781556</v>
+        <v>186.6668969395223</v>
       </c>
       <c r="AA2" t="n">
-        <v>9.000562484580156e-07</v>
+        <v>2.572271554047037e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.8262717331236198</v>
+        <v>0.938911304287214</v>
       </c>
     </row>
     <row r="3">
@@ -5747,7 +5557,7 @@
         <v>140.4449999999999</v>
       </c>
       <c r="C3" t="n">
-        <v>1135.786094047378</v>
+        <v>366.1706152569249</v>
       </c>
       <c r="D3" t="n">
         <v>2.87624e-07</v>
@@ -5780,16 +5590,13 @@
         <v>-6793.990321478196</v>
       </c>
       <c r="Y3" t="n">
-        <v>510.9396929138588</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>280770929.6339918</v>
+        <v>201.3950181930518</v>
       </c>
       <c r="AA3" t="n">
-        <v>6.244166002873013e-07</v>
+        <v>3.975618856927215e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.8826192676113127</v>
+        <v>0.9272835811670955</v>
       </c>
     </row>
     <row r="4">
@@ -5800,7 +5607,7 @@
         <v>125.5309999999999</v>
       </c>
       <c r="C4" t="n">
-        <v>951.7623487726468</v>
+        <v>375.5439358635578</v>
       </c>
       <c r="D4" t="n">
         <v>2.84392e-07</v>
@@ -5833,16 +5640,13 @@
         <v>-7493.781817736216</v>
       </c>
       <c r="Y4" t="n">
-        <v>500.6049367462784</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>53375387.1332188</v>
+        <v>179.4005400322105</v>
       </c>
       <c r="AA4" t="n">
-        <v>5.527798103117413e-07</v>
+        <v>4.013424808418114e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.8991624134218938</v>
+        <v>0.9205809758583041</v>
       </c>
     </row>
     <row r="5">
@@ -5853,7 +5657,7 @@
         <v>119.874</v>
       </c>
       <c r="C5" t="n">
-        <v>946.0863655456129</v>
+        <v>347.7739808807816</v>
       </c>
       <c r="D5" t="n">
         <v>2.81587e-07</v>
@@ -5886,16 +5690,13 @@
         <v>-8129.460176005873</v>
       </c>
       <c r="Y5" t="n">
-        <v>494.0450278191379</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>46786109.65925075</v>
+        <v>199.3094209785422</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.137677306838621e-07</v>
+        <v>4.065767804653407e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.9086276890544402</v>
+        <v>0.9303064612826984</v>
       </c>
     </row>
     <row r="6">
@@ -5906,7 +5707,7 @@
         <v>115.61</v>
       </c>
       <c r="C6" t="n">
-        <v>963.0878134928013</v>
+        <v>344.5431679792791</v>
       </c>
       <c r="D6" t="n">
         <v>2.79529e-07</v>
@@ -5939,16 +5740,13 @@
         <v>-8528.742698678667</v>
       </c>
       <c r="Y6" t="n">
-        <v>487.943646383955</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>33367211.02390506</v>
+        <v>194.0300614241733</v>
       </c>
       <c r="AA6" t="n">
-        <v>4.901749361239819e-07</v>
+        <v>3.797769097365081e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.9145916029816222</v>
+        <v>0.9344079888545811</v>
       </c>
     </row>
     <row r="7">
@@ -5959,7 +5757,7 @@
         <v>112.884</v>
       </c>
       <c r="C7" t="n">
-        <v>986.4307862151077</v>
+        <v>337.7569877718033</v>
       </c>
       <c r="D7" t="n">
         <v>2.78141e-07</v>
@@ -5992,16 +5790,13 @@
         <v>-8919.202352188366</v>
       </c>
       <c r="Y7" t="n">
-        <v>481.8661609590969</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>792603942.9823534</v>
+        <v>195.0194154104938</v>
       </c>
       <c r="AA7" t="n">
-        <v>4.73924482176603e-07</v>
+        <v>3.957792547492014e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.9189140062896058</v>
+        <v>0.9353854739980608</v>
       </c>
     </row>
     <row r="8">
@@ -6012,7 +5807,7 @@
         <v>110.67</v>
       </c>
       <c r="C8" t="n">
-        <v>1071.806574982334</v>
+        <v>303.9509120285736</v>
       </c>
       <c r="D8" t="n">
         <v>2.76923e-07</v>
@@ -6045,16 +5840,13 @@
         <v>-9365.715433468496</v>
       </c>
       <c r="Y8" t="n">
-        <v>475.8994573007008</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>130349566.0779665</v>
+        <v>219.55007937401</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.59654215334174e-07</v>
+        <v>3.787443146573083e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.9228651803233946</v>
+        <v>0.9486950212711025</v>
       </c>
     </row>
     <row r="9">
@@ -6065,7 +5857,7 @@
         <v>104.707</v>
       </c>
       <c r="C9" t="n">
-        <v>1001.688998626273</v>
+        <v>312.3779167183858</v>
       </c>
       <c r="D9" t="n">
         <v>2.75833e-07</v>
@@ -6098,16 +5890,13 @@
         <v>-9178.008238206097</v>
       </c>
       <c r="Y9" t="n">
-        <v>470.2342682494343</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>192582098.4404453</v>
+        <v>205.1482171028925</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.488018763383606e-07</v>
+        <v>3.634220492126294e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.9258881672677145</v>
+        <v>0.9499441529603132</v>
       </c>
     </row>
     <row r="10">
@@ -6118,7 +5907,7 @@
         <v>101.419</v>
       </c>
       <c r="C10" t="n">
-        <v>1000.612791883113</v>
+        <v>288.0152578296328</v>
       </c>
       <c r="D10" t="n">
         <v>2.75131e-07</v>
@@ -6151,16 +5940,13 @@
         <v>-9343.367392363531</v>
       </c>
       <c r="Y10" t="n">
-        <v>443.8763524390018</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>3816.204478538165</v>
+        <v>224.1732257160687</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.679564945875143e-06</v>
+        <v>3.800356597337321e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.826458868524758</v>
+        <v>0.957496570548547</v>
       </c>
     </row>
     <row r="11">
@@ -6171,7 +5957,7 @@
         <v>97.31200000000001</v>
       </c>
       <c r="C11" t="n">
-        <v>989.9729950892493</v>
+        <v>97.31200000000001</v>
       </c>
       <c r="D11" t="n">
         <v>2.74475e-07</v>
@@ -6203,11 +5989,10 @@
       <c r="X11" t="n">
         <v>-9412.102212550497</v>
       </c>
-      <c r="Y11" t="n">
-        <v>439.9090000652595</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>3778.608686157441</v>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA11" t="n">
         <v>1.073043167800002e-06</v>
@@ -6370,7 +6155,7 @@
         <v>125.5210000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>2478.609899888871</v>
+        <v>405.3857065638215</v>
       </c>
       <c r="D2" t="n">
         <v>2.93977e-07</v>
@@ -6403,16 +6188,13 @@
         <v>-6270.929668642305</v>
       </c>
       <c r="Y2" t="n">
-        <v>480.7329810792613</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>74281673.71447983</v>
+        <v>121.8358773643241</v>
       </c>
       <c r="AA2" t="n">
-        <v>6.10816213591845e-07</v>
+        <v>2.615643179912395e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.8894009714299091</v>
+        <v>0.9354954801747274</v>
       </c>
     </row>
     <row r="3">
@@ -6423,7 +6205,7 @@
         <v>103.521</v>
       </c>
       <c r="C3" t="n">
-        <v>1146.28105107472</v>
+        <v>297.9121641172151</v>
       </c>
       <c r="D3" t="n">
         <v>2.84886e-07</v>
@@ -6456,16 +6238,13 @@
         <v>-7908.507524896489</v>
       </c>
       <c r="Y3" t="n">
-        <v>466.6743280794358</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1146789125.444086</v>
+        <v>215.2388074861108</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.93953090122737e-07</v>
+        <v>3.823713161981205e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.9163984231004559</v>
+        <v>0.9485331697934489</v>
       </c>
     </row>
     <row r="4">
@@ -6476,7 +6255,7 @@
         <v>97.38899999999995</v>
       </c>
       <c r="C4" t="n">
-        <v>1096.741930382429</v>
+        <v>347.8931214451231</v>
       </c>
       <c r="D4" t="n">
         <v>2.81455e-07</v>
@@ -6509,16 +6288,13 @@
         <v>-8555.417740161829</v>
       </c>
       <c r="Y4" t="n">
-        <v>441.7462578815397</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>3784.671871658175</v>
+        <v>157.6042352353657</v>
       </c>
       <c r="AA4" t="n">
-        <v>9.920763789529094e-07</v>
+        <v>3.216838550327608e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.8841076497048745</v>
+        <v>0.9410180316194678</v>
       </c>
     </row>
     <row r="5">
@@ -6529,7 +6305,7 @@
         <v>94.255</v>
       </c>
       <c r="C5" t="n">
-        <v>1084.882553370524</v>
+        <v>291.2478942510287</v>
       </c>
       <c r="D5" t="n">
         <v>2.79294e-07</v>
@@ -6562,16 +6338,13 @@
         <v>-8769.937580096921</v>
       </c>
       <c r="Y5" t="n">
-        <v>456.5841396445374</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>124610153.8380714</v>
+        <v>209.3121854112009</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.478528728625239e-07</v>
+        <v>3.525626918630125e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.9281369151662501</v>
+        <v>0.9563581711741531</v>
       </c>
     </row>
     <row r="6">
@@ -6582,7 +6355,7 @@
         <v>92.601</v>
       </c>
       <c r="C6" t="n">
-        <v>1111.50397580101</v>
+        <v>92.601</v>
       </c>
       <c r="D6" t="n">
         <v>2.78271e-07</v>
@@ -6614,11 +6387,10 @@
       <c r="X6" t="n">
         <v>-9162.047188881685</v>
       </c>
-      <c r="Y6" t="n">
-        <v>452.2941937652293</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>370159327.3551711</v>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA6" t="n">
         <v>4.379485607529913e-07</v>
@@ -6635,7 +6407,7 @@
         <v>88.86799999999999</v>
       </c>
       <c r="C7" t="n">
-        <v>1054.161982132104</v>
+        <v>300.0706833703337</v>
       </c>
       <c r="D7" t="n">
         <v>2.77066e-07</v>
@@ -6668,16 +6440,13 @@
         <v>-9049.732686986781</v>
       </c>
       <c r="Y7" t="n">
-        <v>447.9608253751574</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>170780600.7147736</v>
+        <v>189.579177906469</v>
       </c>
       <c r="AA7" t="n">
-        <v>4.290502484936856e-07</v>
+        <v>3.195553307344356e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.9333986982988465</v>
+        <v>0.957182481430212</v>
       </c>
     </row>
     <row r="8">
@@ -6688,7 +6457,7 @@
         <v>85.39500000000004</v>
       </c>
       <c r="C8" t="n">
-        <v>1013.327057023328</v>
+        <v>85.39500000000004</v>
       </c>
       <c r="D8" t="n">
         <v>2.76493e-07</v>
@@ -6720,11 +6489,10 @@
       <c r="X8" t="n">
         <v>-8927.370516560044</v>
       </c>
-      <c r="Y8" t="n">
-        <v>443.8211181574397</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>363229513.4700153</v>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA8" t="n">
         <v>4.22975977742907e-07</v>
@@ -6741,7 +6509,7 @@
         <v>83.005</v>
       </c>
       <c r="C9" t="n">
-        <v>991.7783538055976</v>
+        <v>275.3660407745592</v>
       </c>
       <c r="D9" t="n">
         <v>2.75846e-07</v>
@@ -6774,16 +6542,13 @@
         <v>-8965.882849277941</v>
       </c>
       <c r="Y9" t="n">
-        <v>439.9561516169117</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>723148207.1356236</v>
+        <v>205.8523840482428</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.170676493982838e-07</v>
+        <v>3.283730475275384e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.9370133824139422</v>
+        <v>0.9677627404878894</v>
       </c>
     </row>
     <row r="10">
@@ -6794,7 +6559,7 @@
         <v>79.952</v>
       </c>
       <c r="C10" t="n">
-        <v>947.4534114483696</v>
+        <v>269.3672857783816</v>
       </c>
       <c r="D10" t="n">
         <v>2.75517e-07</v>
@@ -6827,16 +6592,13 @@
         <v>-8968.913603131734</v>
       </c>
       <c r="Y10" t="n">
-        <v>436.3600211278208</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>358460681.8910872</v>
+        <v>206.8959001718724</v>
       </c>
       <c r="AA10" t="n">
-        <v>4.115320442145009e-07</v>
+        <v>3.219122922390677e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.9388208224766018</v>
+        <v>0.9709782872640963</v>
       </c>
     </row>
     <row r="11">
@@ -6847,7 +6609,7 @@
         <v>80.97499999999997</v>
       </c>
       <c r="C11" t="n">
-        <v>1069.019106746909</v>
+        <v>272.4305633527943</v>
       </c>
       <c r="D11" t="n">
         <v>2.74867e-07</v>
@@ -6880,16 +6642,13 @@
         <v>-9466.037951180724</v>
       </c>
       <c r="Y11" t="n">
-        <v>432.97046668927</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>236014137.9245085</v>
+        <v>200.7267970224578</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.083913633849018e-07</v>
+        <v>3.17688850201871e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.9396582439700497</v>
+        <v>0.970887714769868</v>
       </c>
     </row>
     <row r="12">
@@ -6900,7 +6659,7 @@
         <v>80.16699999999997</v>
       </c>
       <c r="C12" t="n">
-        <v>1185.70813221656</v>
+        <v>271.452524826908</v>
       </c>
       <c r="D12" t="n">
         <v>2.74698e-07</v>
@@ -6933,16 +6692,13 @@
         <v>-9759.613103107598</v>
       </c>
       <c r="Y12" t="n">
-        <v>429.7823712461693</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>117324768.0826236</v>
+        <v>196.9601773108916</v>
       </c>
       <c r="AA12" t="n">
-        <v>4.040091939319597e-07</v>
+        <v>3.044740685015784e-09</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.9411799777512009</v>
+        <v>0.9713685662655376</v>
       </c>
     </row>
     <row r="13">
@@ -6953,7 +6709,7 @@
         <v>78.42199999999997</v>
       </c>
       <c r="C13" t="n">
-        <v>1109.68627446145</v>
+        <v>262.6311674888393</v>
       </c>
       <c r="D13" t="n">
         <v>2.74453e-07</v>
@@ -6986,16 +6742,13 @@
         <v>-9605.001358597106</v>
       </c>
       <c r="Y13" t="n">
-        <v>426.7265578770754</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>116197004.0089286</v>
+        <v>202.1012455968446</v>
       </c>
       <c r="AA13" t="n">
-        <v>4.017211680390725e-07</v>
+        <v>3.028402362316282e-09</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.9419093952397858</v>
+        <v>0.975506896952175</v>
       </c>
     </row>
     <row r="14">
@@ -7006,7 +6759,7 @@
         <v>77.54300000000001</v>
       </c>
       <c r="C14" t="n">
-        <v>1211.656903211732</v>
+        <v>257.744043877046</v>
       </c>
       <c r="D14" t="n">
         <v>2.74151e-07</v>
@@ -7039,16 +6792,13 @@
         <v>-9858.038022428444</v>
       </c>
       <c r="Y14" t="n">
-        <v>423.717404171028</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>174275636.4765854</v>
+        <v>204.3977224310647</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.993079744260538e-07</v>
+        <v>3.05001386034005e-09</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.9426626894254309</v>
+        <v>0.9794342435769583</v>
       </c>
     </row>
     <row r="15">
@@ -7059,7 +6809,7 @@
         <v>75.66800000000001</v>
       </c>
       <c r="C15" t="n">
-        <v>1128.892526466224</v>
+        <v>254.4315096756712</v>
       </c>
       <c r="D15" t="n">
         <v>2.73748e-07</v>
@@ -7092,16 +6842,13 @@
         <v>-9717.500210802407</v>
       </c>
       <c r="Y15" t="n">
-        <v>420.8301510651199</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>118699947.6321774</v>
+        <v>203.8928223453725</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.950350635438924e-07</v>
+        <v>2.989209394828137e-09</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.9440599332315927</v>
+        <v>0.9809711745479887</v>
       </c>
     </row>
     <row r="16">
@@ -7112,7 +6859,7 @@
         <v>76.363</v>
       </c>
       <c r="C16" t="n">
-        <v>1333.86003807952</v>
+        <v>76.363</v>
       </c>
       <c r="D16" t="n">
         <v>2.73534e-07</v>
@@ -7144,11 +6891,10 @@
       <c r="X16" t="n">
         <v>-10047.4484867406</v>
       </c>
-      <c r="Y16" t="n">
-        <v>417.8883155073642</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>113886404.4804137</v>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA16" t="n">
         <v>3.936691830738516e-07</v>
@@ -7165,7 +6911,7 @@
         <v>73.23899999999998</v>
       </c>
       <c r="C17" t="n">
-        <v>1166.157899106196</v>
+        <v>244.5955564915038</v>
       </c>
       <c r="D17" t="n">
         <v>2.73386e-07</v>
@@ -7198,16 +6944,13 @@
         <v>-9621.749888657463</v>
       </c>
       <c r="Y17" t="n">
-        <v>414.9342646853236</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>225863530.1406434</v>
+        <v>206.6729844924076</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.909898706607735e-07</v>
+        <v>2.918659223018812e-09</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.9454196979458092</v>
+        <v>0.9864064225147992</v>
       </c>
     </row>
     <row r="18">
@@ -7218,7 +6961,7 @@
         <v>72.40800000000002</v>
       </c>
       <c r="C18" t="n">
-        <v>1197.188233985904</v>
+        <v>241.0425060395608</v>
       </c>
       <c r="D18" t="n">
         <v>2.73301e-07</v>
@@ -7251,16 +6994,13 @@
         <v>-9796.620626035796</v>
       </c>
       <c r="Y18" t="n">
-        <v>411.9720116088964</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>224301672.8987534</v>
+        <v>206.4848258723064</v>
       </c>
       <c r="AA18" t="n">
-        <v>3.885281668279745e-07</v>
+        <v>2.86301780001747e-09</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.9463227911538287</v>
+        <v>0.9893006895905088</v>
       </c>
     </row>
     <row r="19">
@@ -7271,7 +7011,7 @@
         <v>72.01900000000001</v>
       </c>
       <c r="C19" t="n">
-        <v>1298.149178707205</v>
+        <v>72.01900000000001</v>
       </c>
       <c r="D19" t="n">
         <v>2.73065e-07</v>
@@ -7303,11 +7043,10 @@
       <c r="X19" t="n">
         <v>-9966.493890533791</v>
       </c>
-      <c r="Y19" t="n">
-        <v>408.9261837758424</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>336717429.4957645</v>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA19" t="n">
         <v>3.872646030629363e-07</v>
@@ -7324,7 +7063,7 @@
         <v>69.64600000000002</v>
       </c>
       <c r="C20" t="n">
-        <v>1195.222838806978</v>
+        <v>236.1196616454022</v>
       </c>
       <c r="D20" t="n">
         <v>2.73002e-07</v>
@@ -7357,16 +7096,13 @@
         <v>-9633.625039364226</v>
       </c>
       <c r="Y20" t="n">
-        <v>405.9261632735991</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>167472087.5035553</v>
+        <v>205.4424390750135</v>
       </c>
       <c r="AA20" t="n">
-        <v>3.846101172966364e-07</v>
+        <v>2.866193333496123e-09</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.9476994654770635</v>
+        <v>0.99200859706049</v>
       </c>
     </row>
     <row r="21">
@@ -7377,7 +7113,7 @@
         <v>68.39400000000001</v>
       </c>
       <c r="C21" t="n">
-        <v>1202.488746601807</v>
+        <v>68.39400000000001</v>
       </c>
       <c r="D21" t="n">
         <v>2.7283e-07</v>
@@ -7409,11 +7145,10 @@
       <c r="X21" t="n">
         <v>-9599.512453267755</v>
       </c>
-      <c r="Y21" t="n">
-        <v>402.8799496509758</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>164336307.8858424</v>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA21" t="n">
         <v>3.8283198706333e-07</v>
@@ -7430,7 +7165,7 @@
         <v>67.209</v>
       </c>
       <c r="C22" t="n">
-        <v>1177.49969119494</v>
+        <v>67.209</v>
       </c>
       <c r="D22" t="n">
         <v>2.72657e-07</v>
@@ -7462,11 +7197,10 @@
       <c r="X22" t="n">
         <v>-9575.315285342263</v>
       </c>
-      <c r="Y22" t="n">
-        <v>399.8123011185766</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>435006457.8718216</v>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA22" t="n">
         <v>3.81027561082448e-07</v>
@@ -7775,7 +7509,7 @@
         <v>118.316</v>
       </c>
       <c r="C2" t="n">
-        <v>1672.290138218241</v>
+        <v>369.5350152927466</v>
       </c>
       <c r="D2" t="n">
         <v>2.90962e-07</v>
@@ -7808,16 +7542,13 @@
         <v>-6748.482591283335</v>
       </c>
       <c r="Y2" t="n">
-        <v>481.3169627103698</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>16419334.8726047</v>
+        <v>159.0509250657501</v>
       </c>
       <c r="AA2" t="n">
-        <v>5.669450557150221e-07</v>
+        <v>2.963030700935378e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.8989682063270243</v>
+        <v>0.940373104250686</v>
       </c>
     </row>
     <row r="3">
@@ -7828,7 +7559,7 @@
         <v>101.064</v>
       </c>
       <c r="C3" t="n">
-        <v>1098.834575786059</v>
+        <v>355.8295593562266</v>
       </c>
       <c r="D3" t="n">
         <v>2.84504e-07</v>
@@ -7861,16 +7592,13 @@
         <v>-7954.308330172933</v>
       </c>
       <c r="Y3" t="n">
-        <v>468.5931932505256</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>159877891.2432903</v>
+        <v>159.6887983620639</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.873475088148432e-07</v>
+        <v>3.424431195194482e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.9182314914725673</v>
+        <v>0.9346305805070538</v>
       </c>
     </row>
     <row r="4">
@@ -7881,7 +7609,7 @@
         <v>95.32999999999998</v>
       </c>
       <c r="C4" t="n">
-        <v>1017.286921415541</v>
+        <v>95.32999999999998</v>
       </c>
       <c r="D4" t="n">
         <v>2.81687e-07</v>
@@ -7913,11 +7641,10 @@
       <c r="X4" t="n">
         <v>-8381.349611913041</v>
       </c>
-      <c r="Y4" t="n">
-        <v>442.0128795856027</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>3801.263534749723</v>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA4" t="n">
         <v>1.062851142884898e-06</v>
@@ -7934,7 +7661,7 @@
         <v>92.99799999999999</v>
       </c>
       <c r="C5" t="n">
-        <v>1040.355902008638</v>
+        <v>317.7733505329975</v>
       </c>
       <c r="D5" t="n">
         <v>2.80065e-07</v>
@@ -7967,16 +7694,13 @@
         <v>-8819.308046089296</v>
       </c>
       <c r="Y5" t="n">
-        <v>458.1390253610684</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>250286990.6666235</v>
+        <v>183.6347808140506</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.477011926842336e-07</v>
+        <v>3.274663858979854e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.9286061019103289</v>
+        <v>0.950857189668233</v>
       </c>
     </row>
     <row r="6">
@@ -7987,7 +7711,7 @@
         <v>90.89699999999999</v>
       </c>
       <c r="C6" t="n">
-        <v>1072.857682168924</v>
+        <v>286.7512002453175</v>
       </c>
       <c r="D6" t="n">
         <v>2.78988e-07</v>
@@ -8020,16 +7744,13 @@
         <v>-9051.57053567746</v>
       </c>
       <c r="Y6" t="n">
-        <v>453.4836180409301</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>185543068.2052857</v>
+        <v>209.1715136290948</v>
       </c>
       <c r="AA6" t="n">
-        <v>4.378649357911211e-07</v>
+        <v>3.411665790433054e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.9313778756816655</v>
+        <v>0.9589776822849928</v>
       </c>
     </row>
     <row r="7">
@@ -8040,7 +7761,7 @@
         <v>87.29400000000004</v>
       </c>
       <c r="C7" t="n">
-        <v>997.1212722705529</v>
+        <v>87.29400000000004</v>
       </c>
       <c r="D7" t="n">
         <v>2.78413e-07</v>
@@ -8072,11 +7793,10 @@
       <c r="X7" t="n">
         <v>-8990.707432323008</v>
       </c>
-      <c r="Y7" t="n">
-        <v>449.0052073497969</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>122834849.4659618</v>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA7" t="n">
         <v>4.295566039130984e-07</v>
@@ -8093,7 +7813,7 @@
         <v>88.53699999999998</v>
       </c>
       <c r="C8" t="n">
-        <v>1230.553507425333</v>
+        <v>269.9773985855614</v>
       </c>
       <c r="D8" t="n">
         <v>2.77561e-07</v>
@@ -8126,16 +7846,13 @@
         <v>-9667.665045701837</v>
       </c>
       <c r="Y8" t="n">
-        <v>444.7540789640374</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>181863100.6548848</v>
+        <v>216.3547258732697</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.254248137776638e-07</v>
+        <v>3.479188572772316e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.9349760936115415</v>
+        <v>0.964842238475587</v>
       </c>
     </row>
     <row r="9">
@@ -8146,7 +7863,7 @@
         <v>84.02199999999999</v>
       </c>
       <c r="C9" t="n">
-        <v>1118.888373515422</v>
+        <v>84.02199999999999</v>
       </c>
       <c r="D9" t="n">
         <v>2.77305e-07</v>
@@ -8178,11 +7895,10 @@
       <c r="X9" t="n">
         <v>-9336.989697992338</v>
       </c>
-      <c r="Y9" t="n">
-        <v>440.9192743489919</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>163536237.4030253</v>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA9" t="n">
         <v>4.197342568742096e-07</v>
@@ -8199,7 +7915,7 @@
         <v>82.19300000000004</v>
       </c>
       <c r="C10" t="n">
-        <v>1106.79165121209</v>
+        <v>274.5475740736072</v>
       </c>
       <c r="D10" t="n">
         <v>2.76884e-07</v>
@@ -8232,16 +7948,13 @@
         <v>-9355.328574205456</v>
       </c>
       <c r="Y10" t="n">
-        <v>437.2768084047943</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>180768141.8999214</v>
+        <v>203.1186071539383</v>
       </c>
       <c r="AA10" t="n">
-        <v>4.153048812850813e-07</v>
+        <v>3.23573904239515e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.9382300766782647</v>
+        <v>0.9686453122603983</v>
       </c>
     </row>
     <row r="11">
@@ -8252,7 +7965,7 @@
         <v>79.88600000000002</v>
       </c>
       <c r="C11" t="n">
-        <v>1025.532207037964</v>
+        <v>79.88600000000002</v>
       </c>
       <c r="D11" t="n">
         <v>2.76525e-07</v>
@@ -8284,11 +7997,10 @@
       <c r="X11" t="n">
         <v>-9268.527996519775</v>
       </c>
-      <c r="Y11" t="n">
-        <v>433.926388333696</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>354594046.7493199</v>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA11" t="n">
         <v>4.108080852274275e-07</v>
@@ -8305,7 +8017,7 @@
         <v>79.03700000000003</v>
       </c>
       <c r="C12" t="n">
-        <v>1111.226650450044</v>
+        <v>270.4001125787417</v>
       </c>
       <c r="D12" t="n">
         <v>2.76262e-07</v>
@@ -8338,16 +8050,13 @@
         <v>-9562.296871914776</v>
       </c>
       <c r="Y12" t="n">
-        <v>430.7946570849169</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>176191282.6818075</v>
+        <v>199.5883649360603</v>
       </c>
       <c r="AA12" t="n">
-        <v>4.07338253062954e-07</v>
+        <v>3.133842896208384e-09</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.9408160193881694</v>
+        <v>0.9717957570144885</v>
       </c>
     </row>
     <row r="13">
@@ -8358,7 +8067,7 @@
         <v>77.45600000000002</v>
       </c>
       <c r="C13" t="n">
-        <v>1142.3548446192</v>
+        <v>77.45600000000002</v>
       </c>
       <c r="D13" t="n">
         <v>2.76021e-07</v>
@@ -8390,11 +8099,10 @@
       <c r="X13" t="n">
         <v>-9433.776914746522</v>
       </c>
-      <c r="Y13" t="n">
-        <v>427.7582624629842</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>582235796.8971089</v>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA13" t="n">
         <v>4.042887200040525e-07</v>
@@ -8411,7 +8119,7 @@
         <v>75.98400000000004</v>
       </c>
       <c r="C14" t="n">
-        <v>1178.923355097134</v>
+        <v>75.98400000000004</v>
       </c>
       <c r="D14" t="n">
         <v>2.75885e-07</v>
@@ -8443,11 +8151,10 @@
       <c r="X14" t="n">
         <v>-9622.311120797718</v>
       </c>
-      <c r="Y14" t="n">
-        <v>424.742500254259</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>231370192.64752</v>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA14" t="n">
         <v>4.016765652232231e-07</v>
@@ -8464,7 +8171,7 @@
         <v>66.12299999999999</v>
       </c>
       <c r="C15" t="n">
-        <v>797.4729970405186</v>
+        <v>66.12299999999999</v>
       </c>
       <c r="D15" t="n">
         <v>2.75449e-07</v>
@@ -8496,11 +8203,10 @@
       <c r="X15" t="n">
         <v>-7835.619852268862</v>
       </c>
-      <c r="Y15" t="n">
-        <v>421.7272234711429</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>459203866.0416507</v>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA15" t="n">
         <v>3.987137550482963e-07</v>
@@ -8517,7 +8223,7 @@
         <v>73.81999999999999</v>
       </c>
       <c r="C16" t="n">
-        <v>1172.26114802531</v>
+        <v>247.9717159469945</v>
       </c>
       <c r="D16" t="n">
         <v>2.75362e-07</v>
@@ -8550,16 +8256,13 @@
         <v>-9609.411179678706</v>
       </c>
       <c r="Y16" t="n">
-        <v>418.6073312970457</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>341638582.3541558</v>
+        <v>207.9857742983415</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.968436105843079e-07</v>
+        <v>3.000877385603088e-09</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.9442829336644935</v>
+        <v>0.9843579474320026</v>
       </c>
     </row>
     <row r="17">
@@ -8570,7 +8273,7 @@
         <v>73.86700000000002</v>
       </c>
       <c r="C17" t="n">
-        <v>1337.034338347031</v>
+        <v>242.9896784929909</v>
       </c>
       <c r="D17" t="n">
         <v>2.75127e-07</v>
@@ -8603,16 +8306,13 @@
         <v>-9943.823040689851</v>
       </c>
       <c r="Y17" t="n">
-        <v>415.4988262863592</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>678122195.9628119</v>
+        <v>208.7061592560813</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.944747448839126e-07</v>
+        <v>2.934898745315521e-09</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.9450593510380562</v>
+        <v>0.9867490683189911</v>
       </c>
     </row>
     <row r="18">
@@ -8623,7 +8323,7 @@
         <v>69.31600000000003</v>
       </c>
       <c r="C18" t="n">
-        <v>1020.084472025237</v>
+        <v>239.3967595783767</v>
       </c>
       <c r="D18" t="n">
         <v>2.752e-07</v>
@@ -8656,16 +8356,13 @@
         <v>-9214.62778707721</v>
       </c>
       <c r="Y18" t="n">
-        <v>412.3408510988346</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1009164193.7573</v>
+        <v>208.3155993653169</v>
       </c>
       <c r="AA18" t="n">
-        <v>3.922775108507422e-07</v>
+        <v>2.884147173787239e-09</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.9459407386960953</v>
+        <v>0.9893611120511779</v>
       </c>
     </row>
     <row r="19">
@@ -8676,7 +8373,7 @@
         <v>71.404</v>
       </c>
       <c r="C19" t="n">
-        <v>1474.85698748639</v>
+        <v>236.3754229980884</v>
       </c>
       <c r="D19" t="n">
         <v>2.75054e-07</v>
@@ -8709,16 +8406,13 @@
         <v>-10016.93989251047</v>
       </c>
       <c r="Y19" t="n">
-        <v>409.146220039869</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>111675322.944287</v>
+        <v>207.6202720540414</v>
       </c>
       <c r="AA19" t="n">
-        <v>3.89463031729073e-07</v>
+        <v>2.835822218598735e-09</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.9469428626333418</v>
+        <v>0.9916767324305956</v>
       </c>
     </row>
     <row r="20">
@@ -8729,7 +8423,7 @@
         <v>66.90200000000004</v>
       </c>
       <c r="C20" t="n">
-        <v>1043.121285100443</v>
+        <v>66.90200000000004</v>
       </c>
       <c r="D20" t="n">
         <v>2.74906e-07</v>
@@ -8761,11 +8455,10 @@
       <c r="X20" t="n">
         <v>-9168.849542788153</v>
       </c>
-      <c r="Y20" t="n">
-        <v>405.8704923241809</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>331483536.4798995</v>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA20" t="n">
         <v>3.879106575621827e-07</v>
@@ -8782,7 +8475,7 @@
         <v>68.47899999999998</v>
       </c>
       <c r="C21" t="n">
-        <v>1557.422037080431</v>
+        <v>359.5789682705087</v>
       </c>
       <c r="D21" t="n">
         <v>2.74804e-07</v>
@@ -8815,16 +8508,13 @@
         <v>-9813.809394455837</v>
       </c>
       <c r="Y21" t="n">
-        <v>402.6115395092147</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>328927971.9372172</v>
+        <v>77.18629528357988</v>
       </c>
       <c r="AA21" t="n">
-        <v>3.868962096896977e-07</v>
+        <v>2.086474433088637e-09</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.9478246627882296</v>
+        <v>0.9588283015147214</v>
       </c>
     </row>
     <row r="22">
@@ -8835,7 +8525,7 @@
         <v>63.71500000000003</v>
       </c>
       <c r="C22" t="n">
-        <v>1061.022850069246</v>
+        <v>286.0845554073265</v>
       </c>
       <c r="D22" t="n">
         <v>2.74796e-07</v>
@@ -8868,16 +8558,13 @@
         <v>-9099.907935646037</v>
       </c>
       <c r="Y22" t="n">
-        <v>399.4009964319251</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>163014039.1037835</v>
+        <v>147.32249618387</v>
       </c>
       <c r="AA22" t="n">
-        <v>3.84126071669241e-07</v>
+        <v>2.42546733860646e-09</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.948902603725772</v>
+        <v>0.9770802734266457</v>
       </c>
     </row>
   </sheetData>
@@ -9034,7 +8721,7 @@
         <v>175.804</v>
       </c>
       <c r="C2" t="n">
-        <v>4997.975715959094</v>
+        <v>450.9873025173325</v>
       </c>
       <c r="D2" t="n">
         <v>2.85579e-07</v>
@@ -9067,16 +8754,13 @@
         <v>-5985.534406047734</v>
       </c>
       <c r="Y2" t="n">
-        <v>517.0072749278866</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>424364260.9700205</v>
+        <v>117.3173695326476</v>
       </c>
       <c r="AA2" t="n">
-        <v>7.372089456214138e-07</v>
+        <v>2.159399899675312e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.8567990274930191</v>
+        <v>0.9375264351296223</v>
       </c>
     </row>
     <row r="3">
@@ -9087,7 +8771,7 @@
         <v>119.131</v>
       </c>
       <c r="C3" t="n">
-        <v>1096.942042425906</v>
+        <v>325.0698715098383</v>
       </c>
       <c r="D3" t="n">
         <v>2.84088e-07</v>
@@ -9120,16 +8804,13 @@
         <v>-6817.848939904364</v>
       </c>
       <c r="Y3" t="n">
-        <v>487.5256646728903</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>401099383.0753671</v>
+        <v>213.153448464948</v>
       </c>
       <c r="AA3" t="n">
-        <v>5.505983538172226e-07</v>
+        <v>3.632816821607504e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.8996711595776918</v>
+        <v>0.9457522965899512</v>
       </c>
     </row>
     <row r="4">
@@ -9140,7 +8821,7 @@
         <v>108.834</v>
       </c>
       <c r="C4" t="n">
-        <v>988.9897267160436</v>
+        <v>294.4824401233031</v>
       </c>
       <c r="D4" t="n">
         <v>2.80278e-07</v>
@@ -9173,16 +8854,13 @@
         <v>-7736.704617183487</v>
       </c>
       <c r="Y4" t="n">
-        <v>477.6740464688352</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>264626087.1599844</v>
+        <v>231.3200934587096</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.957459364143968e-07</v>
+        <v>3.821241086520508e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.9133416400144007</v>
+        <v>0.9521152222408992</v>
       </c>
     </row>
     <row r="5">
@@ -9193,7 +8871,7 @@
         <v>104.93</v>
       </c>
       <c r="C5" t="n">
-        <v>1043.286614551929</v>
+        <v>104.93</v>
       </c>
       <c r="D5" t="n">
         <v>2.77441e-07</v>
@@ -9225,11 +8903,10 @@
       <c r="X5" t="n">
         <v>-8310.46069717217</v>
       </c>
-      <c r="Y5" t="n">
-        <v>470.9872411527926</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>257756903.5772153</v>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA5" t="n">
         <v>4.690264968634016e-07</v>
@@ -9246,7 +8923,7 @@
         <v>102.597</v>
       </c>
       <c r="C6" t="n">
-        <v>1115.729764617504</v>
+        <v>296.1167881260038</v>
       </c>
       <c r="D6" t="n">
         <v>2.75699e-07</v>
@@ -9279,16 +8956,13 @@
         <v>-8818.705085613392</v>
       </c>
       <c r="Y6" t="n">
-        <v>464.8602776880605</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>254079897.3065849</v>
+        <v>215.2670023435051</v>
       </c>
       <c r="AA6" t="n">
-        <v>4.517866403552614e-07</v>
+        <v>3.621003761594688e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.9248175910051529</v>
+        <v>0.9559966117070875</v>
       </c>
     </row>
     <row r="7">
@@ -9299,7 +8973,7 @@
         <v>98.27800000000002</v>
       </c>
       <c r="C7" t="n">
-        <v>1139.613659268496</v>
+        <v>290.1308306112169</v>
       </c>
       <c r="D7" t="n">
         <v>2.74648e-07</v>
@@ -9332,16 +9006,13 @@
         <v>-8990.702303374113</v>
       </c>
       <c r="Y7" t="n">
-        <v>440.5670897046683</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>3760.852508810734</v>
+        <v>212.5574818785006</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.58174486006174e-06</v>
+        <v>3.414761704890756e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.8362733134808182</v>
+        <v>0.9587342441696117</v>
       </c>
     </row>
     <row r="8">
@@ -9352,7 +9023,7 @@
         <v>95.08199999999999</v>
       </c>
       <c r="C8" t="n">
-        <v>1124.949113929093</v>
+        <v>345.9489321465711</v>
       </c>
       <c r="D8" t="n">
         <v>2.7384e-07</v>
@@ -9385,16 +9056,13 @@
         <v>-9110.545228760877</v>
       </c>
       <c r="Y8" t="n">
-        <v>452.7456342089746</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>246904518.6869225</v>
+        <v>149.1845983054319</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.294520224850721e-07</v>
+        <v>2.900780488906018e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.9314217339739586</v>
+        <v>0.9480522908624358</v>
       </c>
     </row>
     <row r="9">
@@ -9405,7 +9073,7 @@
         <v>89.55800000000005</v>
       </c>
       <c r="C9" t="n">
-        <v>1030.071202337699</v>
+        <v>285.008058431263</v>
       </c>
       <c r="D9" t="n">
         <v>2.73324e-07</v>
@@ -9438,16 +9106,13 @@
         <v>-8721.405395930318</v>
       </c>
       <c r="Y9" t="n">
-        <v>447.0348010388421</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>121838407.0186928</v>
+        <v>205.1288038006654</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.240480861238635e-07</v>
+        <v>3.308902799432964e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.9330733490802984</v>
+        <v>0.9647739575190577</v>
       </c>
     </row>
     <row r="10">
@@ -9458,7 +9123,7 @@
         <v>87.34300000000002</v>
       </c>
       <c r="C10" t="n">
-        <v>1084.0731959497</v>
+        <v>278.2940228376488</v>
       </c>
       <c r="D10" t="n">
         <v>2.73061e-07</v>
@@ -9491,16 +9156,13 @@
         <v>-8980.525195986682</v>
       </c>
       <c r="Y10" t="n">
-        <v>441.8132763859897</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>126501952.0246875</v>
+        <v>205.2202800737344</v>
       </c>
       <c r="AA10" t="n">
-        <v>4.183775092728076e-07</v>
+        <v>3.21658966442484e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.9349609149016714</v>
+        <v>0.968041685462972</v>
       </c>
     </row>
     <row r="11">
@@ -9511,7 +9173,7 @@
         <v>83.30200000000002</v>
       </c>
       <c r="C11" t="n">
-        <v>1045.541931314833</v>
+        <v>83.30200000000002</v>
       </c>
       <c r="D11" t="n">
         <v>2.72774e-07</v>
@@ -9543,11 +9205,10 @@
       <c r="X11" t="n">
         <v>-8798.41393372084</v>
       </c>
-      <c r="Y11" t="n">
-        <v>437.2092957584164</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>357233911.4357943</v>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA11" t="n">
         <v>4.123806631877916e-07</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 45.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 45.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AD11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,125 +438,693 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>normalized Rct_a</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>delta Rct-d</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>normalized Rct_d</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
         <is>
           <t>Cp1</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Ph1</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Slope 1</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Slope 2</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Slope 3</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Slope 4</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Slope 5</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Angle</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Cp_exp-a</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Cp_exp-b</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Ph_slope</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Ph_peak</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Area Cp</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Area Ph</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Area Slope</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Area Rs-direct</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
-      <c r="W1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>linear_eq_m</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>linear_eq_b</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Rs</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>delta Rct-i</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Q</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B2" t="n">
+        <v>107.8630000000001</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1222.881998380931</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>2.64063e-07</v>
+      </c>
+      <c r="G2" t="n">
+        <v>-82.324</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.4924579293767634</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.000017234335748</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1.556010042998564</v>
+      </c>
+      <c r="K2" t="n">
+        <v>2.39825309898576</v>
+      </c>
+      <c r="L2" t="n">
+        <v>25.68537325146842</v>
+      </c>
+      <c r="M2" t="n">
+        <v>86.78874740645739</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>17.82350396332755</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>-9599.322190146206</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>-617.2483626631367</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>4.26998522159083e-07</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.9268023972871524</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B3" t="n">
+        <v>101.1759999999999</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.938004691135977</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1147.345740482078</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.9382309511474847</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2.631e-07</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-82.649</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.407323822046795</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.9823134680563622</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1.596583349940528</v>
+      </c>
+      <c r="K3" t="n">
+        <v>2.523729445795916</v>
+      </c>
+      <c r="L3" t="n">
+        <v>28.66566303413096</v>
+      </c>
+      <c r="M3" t="n">
+        <v>86.94581505152189</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>18.7419890496679</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>-9898.387345826271</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>-561.4886336034604</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1.643783049026739e-06</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.8272660883542078</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B4" t="n">
+        <v>97.33999999999997</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.9024410594921328</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1134.818910529744</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9279872563601553</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2.6245e-07</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-82.824</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.3142806937342108</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.9343354005925628</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1.48290245110116</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2.273660235496234</v>
+      </c>
+      <c r="L4" t="n">
+        <v>29.27699521926877</v>
+      </c>
+      <c r="M4" t="n">
+        <v>87.01709364146427</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>19.19068129526032</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>-9985.674568337905</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>-558.4113668681046</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.351528210561691e-06</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.8650685767984596</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B5" t="n">
+        <v>94.54599999999999</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.8765378303959647</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1165.483636117922</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.9530630409647014</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2.62147e-07</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-82.971</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.3739565358041708</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.8913275871117444</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1.557116324463475</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2.389893365360842</v>
+      </c>
+      <c r="L5" t="n">
+        <v>30.37546324776115</v>
+      </c>
+      <c r="M5" t="n">
+        <v>87.09139200699965</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>19.68176973497182</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>-10105.93471235811</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>-593.2626273972858</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>3.588868257132026e-07</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.9999755699729936</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B6" t="n">
+        <v>90.08799999999997</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.8352076244866166</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1086.965916765387</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.8888559306658417</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2.61719e-07</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-83.101</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.1972190940341653</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.7763665983516556</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1.288509687719331</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2.056046379524496</v>
+      </c>
+      <c r="L6" t="n">
+        <v>30.40908416249143</v>
+      </c>
+      <c r="M6" t="n">
+        <v>87.05450951659333</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>19.43489429606497</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>-9813.14555680553</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>-530.1304184541336</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>3.916622015651721e-07</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.9384871503513036</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>9</v>
+      </c>
+      <c r="B7" t="n">
+        <v>88.339</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.8189926109972832</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1229.580759139218</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1.005477847222508</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2.61617e-07</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-83.221</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.2593616930651583</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.8290005632814033</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1.408463332803359</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2.172567118839585</v>
+      </c>
+      <c r="L7" t="n">
+        <v>31.3206243398632</v>
+      </c>
+      <c r="M7" t="n">
+        <v>87.196205066275</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>20.41876762439064</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>-10212.2407737871</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>-664.8064308613309</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>3.870928133099566e-07</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.940198540333773</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B8" t="n">
+        <v>86.74099999999999</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.8041775214855876</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1281.912940571164</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1.048271985578648</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2.61431e-07</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-83.304</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.6319168900716478</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.8630939836095451</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1.493971249342138</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2.44281625196101</v>
+      </c>
+      <c r="L8" t="n">
+        <v>32.69220281666847</v>
+      </c>
+      <c r="M8" t="n">
+        <v>87.27092498551941</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>20.97869894262035</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>-10390.98297151223</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>-717.6859974801409</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>3.837286484855732e-07</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.9414129971822996</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>12</v>
+      </c>
+      <c r="B9" t="n">
+        <v>75.55000000000001</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.7004255398051229</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1149.524458071477</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.9400125765146777</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2.6122e-07</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-83.35299999999999</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.7986966776689637</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1.791538494521635</v>
+      </c>
+      <c r="L9" t="n">
+        <v>30.10285341389156</v>
+      </c>
+      <c r="M9" t="n">
+        <v>86.75953266883968</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>17.66247594942411</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>-8486.174645203593</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>-604.3494735023893</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>3.8122141057872e-07</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0.9423048378955623</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B10" t="n">
+        <v>81.28800000000001</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.7536226509553783</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1177.411325716256</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.9628167944864039</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2.61242e-07</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-83.407</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.1202899337352879</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.000500774910222</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.456274285465032</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2.337962751536113</v>
+      </c>
+      <c r="L10" t="n">
+        <v>32.18886212165614</v>
+      </c>
+      <c r="M10" t="n">
+        <v>87.24643305816566</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>20.79181762396264</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>-10047.85629252543</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>-635.2635025417703</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>3.792017074982107e-07</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0.943130388630344</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>15</v>
+      </c>
+      <c r="B11" t="n">
+        <v>80.596</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.7472071053095126</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1385.583051570613</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1.133047222385393</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2.61085e-07</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-83.509</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.2858294528696655</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.9502442901448466</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1.518586120627437</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2.44874768511965</v>
+      </c>
+      <c r="L11" t="n">
+        <v>33.15944773050924</v>
+      </c>
+      <c r="M11" t="n">
+        <v>87.36798349326666</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>21.7534620588097</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>-10438.64831531955</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>-828.4386767217325</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>3.755259302377786e-07</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0.9445047767300254</v>
       </c>
     </row>
   </sheetData>
@@ -570,7 +1138,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AD22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -586,125 +1154,1309 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>normalized Rct_a</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>delta Rct-d</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>normalized Rct_d</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
         <is>
           <t>Cp1</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Ph1</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Slope 1</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Slope 2</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Slope 3</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Slope 4</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Slope 5</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Angle</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Cp_exp-a</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Cp_exp-b</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Ph_slope</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Ph_peak</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Area Cp</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Area Ph</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Area Slope</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Area Rs-direct</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
-      <c r="W1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>linear_eq_m</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>linear_eq_b</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Rs</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>delta Rct-i</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Q</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>123.117</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>321.402776633894</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>2.72644e-07</v>
+      </c>
+      <c r="G2" t="n">
+        <v>-81.66800000000001</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.3324985672437418</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.7394414943525438</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1.361079132107822</v>
+      </c>
+      <c r="K2" t="n">
+        <v>2.201343800322297</v>
+      </c>
+      <c r="L2" t="n">
+        <v>22.28309065067079</v>
+      </c>
+      <c r="M2" t="n">
+        <v>86.23659232903233</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>15.20254047159887</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>-8360.98103653289</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>205.4262152339841</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>3.054023043952894e-09</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.9570999626100983</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>103.567</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.8412079566591129</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1179.625519179557</v>
+      </c>
+      <c r="E3" t="n">
+        <v>3.670240598211305</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2.70903e-07</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-82.346</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.6659572099321607</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.048833820776525</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1.586446990618198</v>
+      </c>
+      <c r="K3" t="n">
+        <v>2.345168482408644</v>
+      </c>
+      <c r="L3" t="n">
+        <v>25.39547829567944</v>
+      </c>
+      <c r="M3" t="n">
+        <v>86.70513271440362</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>17.37023136307375</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>-9099.215171842827</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>-593.3444619426984</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>4.383445486220268e-07</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.9266667270381466</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>95.75399999999996</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.7777479958088643</v>
+      </c>
+      <c r="D4" t="n">
+        <v>966.7639839950861</v>
+      </c>
+      <c r="E4" t="n">
+        <v>3.007951561962749</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2.70055e-07</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-82.53400000000001</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.2065994235832161</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.6908149256288911</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1.464748598532261</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2.374217128379251</v>
+      </c>
+      <c r="L4" t="n">
+        <v>26.27564491304693</v>
+      </c>
+      <c r="M4" t="n">
+        <v>86.68945551792773</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>17.28779197790907</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>-8852.895054964198</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>-414.1502404941225</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.329909910929096e-06</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.8414651222984563</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>96.40000000000003</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.7829950372409985</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1160.211078560553</v>
+      </c>
+      <c r="E5" t="n">
+        <v>3.609835268729292</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2.69345e-07</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-82.68600000000001</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.6912967279279655</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1.198611813223144</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1.778678856535083</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2.59988802737649</v>
+      </c>
+      <c r="L5" t="n">
+        <v>28.11678770011679</v>
+      </c>
+      <c r="M5" t="n">
+        <v>86.9522145457658</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>18.78141653552514</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>-9578.119360771974</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>-593.4682633410224</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1.369126947661995e-06</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.8634281974415232</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>93.21000000000004</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.7570847242866543</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1160.025521391174</v>
+      </c>
+      <c r="E6" t="n">
+        <v>3.609257933426458</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2.69164e-07</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-82.818</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.5585690423399794</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.031679730211049</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1.876525158797712</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2.557353394756368</v>
+      </c>
+      <c r="L6" t="n">
+        <v>28.68694396703544</v>
+      </c>
+      <c r="M6" t="n">
+        <v>87.00985416806904</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>19.1441343721385</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>-9651.181865898097</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>-599.1738908571873</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>4.145001707610471e-07</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.9341455687278762</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>89.90199999999999</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.7302159734236537</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1075.754610710713</v>
+      </c>
+      <c r="E7" t="n">
+        <v>3.347060725415238</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2.68755e-07</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-82.883</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.2829153481239688</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.030556376765423</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1.715617314790859</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2.399803562555813</v>
+      </c>
+      <c r="L7" t="n">
+        <v>28.28943105105307</v>
+      </c>
+      <c r="M7" t="n">
+        <v>86.9539854200394</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>18.79235618526171</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>-9335.073827635899</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>-529.3180006892528</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>4.107660705107558e-07</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.935303220497161</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>86.86799999999999</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.7055727478739734</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1056.271900996974</v>
+      </c>
+      <c r="E8" t="n">
+        <v>3.286442986148066</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2.68598e-07</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-82.98399999999999</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.3906853287052123</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.8914368621230316</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1.468883588348177</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2.182733189467243</v>
+      </c>
+      <c r="L8" t="n">
+        <v>28.13442189504315</v>
+      </c>
+      <c r="M8" t="n">
+        <v>86.97806735020897</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>18.94239482524619</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>-9296.228995134883</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>-517.90592141103</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>4.064278669403648e-07</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.9368215071807625</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>83.68000000000001</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.6796786796299454</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1036.684282741261</v>
+      </c>
+      <c r="E9" t="n">
+        <v>3.225498838555885</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2.6826e-07</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-83.051</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.1343551314808551</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.6300344017212653</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.495542216537642</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2.470749574069002</v>
+      </c>
+      <c r="L9" t="n">
+        <v>29.05839633211262</v>
+      </c>
+      <c r="M9" t="n">
+        <v>86.92254155876262</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>18.59998158003243</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>-9000.956083669631</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>-505.6383923216868</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>4.030579782766424e-07</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0.9379010583485747</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>83.89999999999998</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.6814655977647276</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1185.00606703777</v>
+      </c>
+      <c r="E10" t="n">
+        <v>3.686981423896022</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2.67996e-07</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-83.143</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.3960606103374492</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.107020323807981</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.75865263571295</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2.651354532909224</v>
+      </c>
+      <c r="L10" t="n">
+        <v>30.14161298387466</v>
+      </c>
+      <c r="M10" t="n">
+        <v>87.11025620574966</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>19.81047228239968</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>-9552.484276580579</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>-643.8866275498301</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>3.991627777082239e-07</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0.9392278592739676</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>80.892</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.657033553449158</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1076.417096395307</v>
+      </c>
+      <c r="E11" t="n">
+        <v>3.349121957404371</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2.67899e-07</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-83.182</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.3126472516318443</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.8809811551360011</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1.651890857807161</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2.515392565456309</v>
+      </c>
+      <c r="L11" t="n">
+        <v>29.56037493256354</v>
+      </c>
+      <c r="M11" t="n">
+        <v>87.0544119031679</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>19.43424910969891</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>-9255.033440822186</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>-550.8676979068796</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>3.972024883721081e-07</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0.9399227166687285</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79.81299999999999</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.6482695322335662</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1102.362485309878</v>
+      </c>
+      <c r="E12" t="n">
+        <v>3.429847423395367</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2.67688e-07</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-83.258</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.3193440510416889</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1.123988181618426</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.585267034946885</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2.58428996961779</v>
+      </c>
+      <c r="L12" t="n">
+        <v>30.44305894452784</v>
+      </c>
+      <c r="M12" t="n">
+        <v>87.11923817397374</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>19.87234434365108</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-9391.598627738556</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-578.5316398579125</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>3.941020955067442e-07</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.9409913259040812</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79.834</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.6484401016918865</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1356.556854621175</v>
+      </c>
+      <c r="E13" t="n">
+        <v>4.220737819469472</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2.67488e-07</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-83.316</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.5158624171801967</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.280873663322011</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.604421231636899</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2.575176920347626</v>
+      </c>
+      <c r="L13" t="n">
+        <v>29.97653689912666</v>
+      </c>
+      <c r="M13" t="n">
+        <v>87.23740857856555</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>20.72379271336019</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-9755.401357545546</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>-812.0160587446607</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>3.916201313707369e-07</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.9418383531316091</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79.64600000000002</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.6469130989221635</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1474.992826046468</v>
+      </c>
+      <c r="E14" t="n">
+        <v>4.589234858187347</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2.67391e-07</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-83.373</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.9861774126466745</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.304360260794313</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.874176311080603</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2.810718427190251</v>
+      </c>
+      <c r="L14" t="n">
+        <v>31.00984725168055</v>
+      </c>
+      <c r="M14" t="n">
+        <v>87.29760709754886</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>21.18614449045294</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-9907.355670692714</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>-922.9449034751918</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>3.894681968248368e-07</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.9426184644425313</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>74.56900000000002</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.6056759017844815</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1137.799362420583</v>
+      </c>
+      <c r="E15" t="n">
+        <v>3.540104333686689</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2.67161e-07</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-83.43300000000001</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.1390085439308156</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.641765336270207</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.526971169942958</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2.211514049010288</v>
+      </c>
+      <c r="L15" t="n">
+        <v>29.73296890354945</v>
+      </c>
+      <c r="M15" t="n">
+        <v>87.14788086539058</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>20.07224940566364</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-9230.947039114715</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>-622.2631509525115</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>3.870198928759991e-07</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.943446300867181</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>72.36599999999999</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.5877823533711833</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1152.38370216259</v>
+      </c>
+      <c r="E16" t="n">
+        <v>3.585481476643423</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2.67154e-07</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-83.488</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.7845881925667021</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.367119214563877</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2.248802712732471</v>
+      </c>
+      <c r="L16" t="n">
+        <v>30.00706656580175</v>
+      </c>
+      <c r="M16" t="n">
+        <v>87.11724320036751</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>19.85856873896583</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-9039.394937021554</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>-638.9565004737317</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>3.852111742265167e-07</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.9441457628753107</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>74.714</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.6068536432824061</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1362.539900844115</v>
+      </c>
+      <c r="E17" t="n">
+        <v>4.239353234947835</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2.67023e-07</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-83.565</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.5472777647383407</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.097982380007562</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.639998117077041</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2.663054796785869</v>
+      </c>
+      <c r="L17" t="n">
+        <v>31.83879823197438</v>
+      </c>
+      <c r="M17" t="n">
+        <v>87.32277914582281</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>21.38563744612662</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-9725.303200891476</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>-832.9856661114804</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>3.824649422397493e-07</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.9451590446040621</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>71.79700000000003</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.5831607332862238</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1243.914973409662</v>
+      </c>
+      <c r="E18" t="n">
+        <v>3.870268285910269</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2.66962e-07</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-83.611</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.2356551103359827</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.103637347044258</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.725787522674725</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2.554197738215202</v>
+      </c>
+      <c r="L18" t="n">
+        <v>31.97879886202891</v>
+      </c>
+      <c r="M18" t="n">
+        <v>87.28332486828249</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>21.07459792476552</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-9479.464339063117</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>-729.6039828480266</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>3.80791102093921e-07</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.9457842968523634</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>72.14000000000004</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.5859467011054528</v>
+      </c>
+      <c r="D19" t="n">
+        <v>259.3172291982016</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.8068294615064473</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2.66831e-07</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-83.63800000000001</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.6330550368265632</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.105393231135166</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.821768013626504</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2.646129527231523</v>
+      </c>
+      <c r="L19" t="n">
+        <v>31.71668794179721</v>
+      </c>
+      <c r="M19" t="n">
+        <v>87.35643336487306</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>21.65828387251652</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-9689.716375442036</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>182.7074024379407</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>2.528419754708605e-09</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.9886619915612028</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>67.97899999999998</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.5521495812925914</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1271.407339760744</v>
+      </c>
+      <c r="E20" t="n">
+        <v>3.955806956854605</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2.6676e-07</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-83.705</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.2173800541936653</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.5995250439238596</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.575355738175434</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2.35627503580692</v>
+      </c>
+      <c r="L20" t="n">
+        <v>31.15370010076809</v>
+      </c>
+      <c r="M20" t="n">
+        <v>87.23143930517391</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>20.67904089367934</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-9112.604359247525</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>-761.7503826281744</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>3.773386297485312e-07</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.9470588941999227</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>67.697</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.5498590771380069</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1287.595040004948</v>
+      </c>
+      <c r="E21" t="n">
+        <v>4.006172732824993</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2.66757e-07</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-83.786</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.2509158592886808</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.8856038118946071</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1.654938574216668</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2.552729536040805</v>
+      </c>
+      <c r="L21" t="n">
+        <v>33.03580469276218</v>
+      </c>
+      <c r="M21" t="n">
+        <v>87.32353763478508</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>21.39170680144206</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-9365.318451994282</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>-780.2273909206376</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>3.749404704529664e-07</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0.9480103435088878</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>67.423</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.547633551824687</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1410.086256220752</v>
+      </c>
+      <c r="E22" t="n">
+        <v>4.387287101215569</v>
+      </c>
+      <c r="F22" t="n">
+        <v>2.66694e-07</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-83.834</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.4855452567875742</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1.096834607655973</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1.769976167413208</v>
+      </c>
+      <c r="K22" t="n">
+        <v>2.541987523060316</v>
+      </c>
+      <c r="L22" t="n">
+        <v>32.85722396609565</v>
+      </c>
+      <c r="M22" t="n">
+        <v>87.38723037836647</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>21.91393308703115</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>-9532.753076700101</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>-895.0446830198503</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>3.73254825807647e-07</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0.9486615081080416</v>
       </c>
     </row>
   </sheetData>
@@ -718,7 +2470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AD22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -734,125 +2486,1309 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>normalized Rct_a</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>delta Rct-d</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>normalized Rct_d</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
         <is>
           <t>Cp1</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Ph1</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Slope 1</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Slope 2</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Slope 3</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Slope 4</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Slope 5</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Angle</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Cp_exp-a</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Cp_exp-b</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Ph_slope</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Ph_peak</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Area Cp</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Area Ph</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Area Slope</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Area Rs-direct</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
-      <c r="W1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>linear_eq_m</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>linear_eq_b</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Rs</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>delta Rct-i</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Q</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>127.235</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>311.8203438103901</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>2.76249e-07</v>
+      </c>
+      <c r="G2" t="n">
+        <v>-80.96899999999999</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.04343039752405262</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.8418040515083883</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1.314491415637336</v>
+      </c>
+      <c r="K2" t="n">
+        <v>2.038407936820749</v>
+      </c>
+      <c r="L2" t="n">
+        <v>18.18260956816588</v>
+      </c>
+      <c r="M2" t="n">
+        <v>85.87600810476651</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>13.86928060524225</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>-7751.373462847805</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>224.8049189095018</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>3.256997233637986e-09</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.9551582904690579</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>103.22</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.8112547648052817</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1142.125530947138</v>
+      </c>
+      <c r="E3" t="n">
+        <v>3.662767852124604</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2.69663e-07</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-82.26900000000001</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.1914147981042067</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.8150916579859183</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1.315918381934325</v>
+      </c>
+      <c r="K3" t="n">
+        <v>2.255889295085648</v>
+      </c>
+      <c r="L3" t="n">
+        <v>25.20742870161399</v>
+      </c>
+      <c r="M3" t="n">
+        <v>86.68721616396195</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>17.27607983040949</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>-9142.691276745545</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>-553.9258759056572</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>4.361934590012305e-07</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.9268027198490548</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>98.11100000000005</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.7711007191417458</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1093.490723263717</v>
+      </c>
+      <c r="E4" t="n">
+        <v>3.506797247098927</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2.67466e-07</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-82.681</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.2646475862435225</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.8565699563484701</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1.522194353988355</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2.446073873217861</v>
+      </c>
+      <c r="L4" t="n">
+        <v>28.77049235878962</v>
+      </c>
+      <c r="M4" t="n">
+        <v>86.97475332453027</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>18.92160570492989</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>-9826.40835573673</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>-523.5999161736368</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.663103739688245e-06</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.8227840406122269</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>94.24499999999995</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.7407159979565366</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1110.501712220133</v>
+      </c>
+      <c r="E5" t="n">
+        <v>3.561351060838417</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2.66165e-07</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-82.895</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.3351661003685886</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.8756985218762945</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1.568373431022961</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2.506700597572104</v>
+      </c>
+      <c r="L5" t="n">
+        <v>30.56301410612685</v>
+      </c>
+      <c r="M5" t="n">
+        <v>87.10637500562872</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>19.7838554817209</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>-10144.97169018693</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>-546.2286018913619</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>4.05022007432776e-07</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.9359848204513325</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>90.20500000000004</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.7089637285338156</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1073.425280004044</v>
+      </c>
+      <c r="E6" t="n">
+        <v>3.442447875231536</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2.65327e-07</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-83.065</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.1508564917214077</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.799194061895109</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1.418053411067973</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2.272384411112472</v>
+      </c>
+      <c r="L6" t="n">
+        <v>31.22483142127902</v>
+      </c>
+      <c r="M6" t="n">
+        <v>87.093586354596</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>19.69665505777763</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>-9944.378389610323</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>-519.5084179558846</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>3.974253091366641e-07</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.9383576063960247</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>88.66500000000002</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.6968601406845601</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1101.46898989985</v>
+      </c>
+      <c r="E7" t="n">
+        <v>3.532383347539456</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2.64548e-07</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-83.139</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.2463480940070178</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.9326952380695922</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1.429578443016108</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2.372350245621452</v>
+      </c>
+      <c r="L7" t="n">
+        <v>31.30864612221542</v>
+      </c>
+      <c r="M7" t="n">
+        <v>87.208357009784</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>20.50779169331176</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>-10269.29342203443</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>-550.3091909320802</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>3.930978807543943e-07</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.9395936313795407</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>85.44799999999998</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.6715762172358233</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1016.019246505042</v>
+      </c>
+      <c r="E8" t="n">
+        <v>3.258348169620573</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2.64146e-07</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-83.236</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.105649314740603</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.625763532184045</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1.355536378971123</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2.164654493749005</v>
+      </c>
+      <c r="L8" t="n">
+        <v>31.128494022466</v>
+      </c>
+      <c r="M8" t="n">
+        <v>87.15669685568162</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>20.1345885083383</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>-9938.273876717878</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>-478.987139726159</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>3.888280687482529e-07</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.9410154735253821</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>86.50400000000002</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.6798758203324557</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1271.782998660311</v>
+      </c>
+      <c r="E9" t="n">
+        <v>4.078576090063097</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2.63749e-07</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-83.346</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.4360353487768501</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.120755714236871</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.501267766137637</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2.447572537638714</v>
+      </c>
+      <c r="L9" t="n">
+        <v>32.95742830739476</v>
+      </c>
+      <c r="M9" t="n">
+        <v>87.39384097181849</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>21.96959541256436</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>-10810.29347620989</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>-714.5158237384464</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>3.844328084949008e-07</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0.9425036085232681</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>82.78000000000003</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.6506071442606203</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1116.318859956402</v>
+      </c>
+      <c r="E10" t="n">
+        <v>3.580006507321429</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2.63693e-07</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-83.42400000000001</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.4194633037955159</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.8070032550269018</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.533721079263632</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2.586691077604846</v>
+      </c>
+      <c r="L10" t="n">
+        <v>34.42595728458807</v>
+      </c>
+      <c r="M10" t="n">
+        <v>87.33204245290545</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>21.45999765158652</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>-10413.43311909305</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>-579.5001553026457</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>3.815704047326536e-07</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0.9435980953403028</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>81.62599999999998</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.6415373128463078</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1242.480855458714</v>
+      </c>
+      <c r="E11" t="n">
+        <v>3.984604853794385</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2.63424e-07</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-83.505</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.3467271827384857</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.9828524000414398</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1.640047320023245</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2.434250549018704</v>
+      </c>
+      <c r="L11" t="n">
+        <v>34.5404099508481</v>
+      </c>
+      <c r="M11" t="n">
+        <v>87.42074980966801</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>22.19911493592852</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>-10691.8405558676</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>-698.3461184728435</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>3.783203121129007e-07</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0.9447429738066498</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>80.48199999999997</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.6325460761582895</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1337.098906904267</v>
+      </c>
+      <c r="E12" t="n">
+        <v>4.288042565039702</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2.63247e-07</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-83.556</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.4731264239234456</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1.152051875921184</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.74960963116658</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2.73274829544289</v>
+      </c>
+      <c r="L12" t="n">
+        <v>35.06571559413162</v>
+      </c>
+      <c r="M12" t="n">
+        <v>87.46809368424151</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>22.6147702364912</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-10800.42748218264</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-788.3820535815166</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>3.76118759844843e-07</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.9455323355146705</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>76.88</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.6042362557472393</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1092.557355971152</v>
+      </c>
+      <c r="E13" t="n">
+        <v>3.503803961666812</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2.6306e-07</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-83.574</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.2326338549762718</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.6982633161749783</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.307001351254357</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2.189353317246665</v>
+      </c>
+      <c r="L13" t="n">
+        <v>32.80302195309584</v>
+      </c>
+      <c r="M13" t="n">
+        <v>87.34812609311159</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>21.59034050245337</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-10161.85739058252</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>-571.8582531923878</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>3.749219490547249e-07</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.9459274276735616</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>78.01499999999999</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.6131567571815929</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1381.532500439867</v>
+      </c>
+      <c r="E14" t="n">
+        <v>4.430539981958143</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2.6299e-07</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-83.66200000000001</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.6826025157403757</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.156997170608582</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.916585457249574</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2.980092831894027</v>
+      </c>
+      <c r="L14" t="n">
+        <v>35.58622275389752</v>
+      </c>
+      <c r="M14" t="n">
+        <v>87.54149542254061</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>23.29082960857156</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-10932.96353878005</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>-837.7793837372946</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>3.720419380982052e-07</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.9470460350531218</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>73.17599999999999</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.5751247691279914</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1158.202504931345</v>
+      </c>
+      <c r="E15" t="n">
+        <v>3.71432630333965</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2.62701e-07</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-83.7</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.8436189222789908</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.499790380353879</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2.287454373889161</v>
+      </c>
+      <c r="L15" t="n">
+        <v>33.92203510076359</v>
+      </c>
+      <c r="M15" t="n">
+        <v>87.37337984018964</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>21.79821705208842</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-10062.84740667248</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>-639.9241128250131</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>3.700733224478628e-07</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.9477029872925168</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>71.80000000000001</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.5643101347899556</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1187.6540011319</v>
+      </c>
+      <c r="E16" t="n">
+        <v>3.808776510919642</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2.62774e-07</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-83.77200000000001</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.1429580418353057</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.7701281964330922</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.374109121272471</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2.28657479494855</v>
+      </c>
+      <c r="L16" t="n">
+        <v>34.64877437114263</v>
+      </c>
+      <c r="M16" t="n">
+        <v>87.41554703304374</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>22.15436528183677</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-10140.97625424357</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>-670.8309867947038</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>3.680147787927724e-07</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.9485785014736785</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>63.90500000000003</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.5022595983809488</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1176.457813671851</v>
+      </c>
+      <c r="E17" t="n">
+        <v>3.772870619330806</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2.62665e-07</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-83.81999999999999</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.6061579902784883</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1.729433694712073</v>
+      </c>
+      <c r="L17" t="n">
+        <v>32.14037607902404</v>
+      </c>
+      <c r="M17" t="n">
+        <v>87.00610323156411</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>19.12010580011504</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-8545.572680046193</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>-664.7393103211614</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>3.662335020716312e-07</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.949257850232058</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>70.37099999999998</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.553078948402562</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1288.040229298836</v>
+      </c>
+      <c r="E18" t="n">
+        <v>4.130712619834902</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2.62561e-07</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-83.878</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.3912048887978243</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.8700773857977739</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.657233547782414</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2.501819561359755</v>
+      </c>
+      <c r="L18" t="n">
+        <v>35.6105177428725</v>
+      </c>
+      <c r="M18" t="n">
+        <v>87.54195876112072</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>23.29522530219045</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-10518.96137799515</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>-769.9522465150571</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>3.643023645097892e-07</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.9499978075269191</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>70.33600000000001</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.5528038668605337</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1554.02570976438</v>
+      </c>
+      <c r="E19" t="n">
+        <v>4.983721365881578</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2.62665e-07</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-83.913</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.5333541823910142</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.075086740893133</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.811626083946722</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2.572617737686896</v>
+      </c>
+      <c r="L19" t="n">
+        <v>35.61814551247041</v>
+      </c>
+      <c r="M19" t="n">
+        <v>87.61957944655116</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>24.05575344467231</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-10802.08755314234</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>-1015.472560120132</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>3.633735453588941e-07</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.9504444312633231</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>67.50400000000002</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.530545840374111</v>
+      </c>
+      <c r="D20" t="n">
+        <v>321.7711421805641</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1.031911960100413</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2.62544e-07</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-83.959</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.2908092961987711</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.8500583952511908</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.679482118302269</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2.599995524394957</v>
+      </c>
+      <c r="L20" t="n">
+        <v>36.11289913370867</v>
+      </c>
+      <c r="M20" t="n">
+        <v>87.54282346394551</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>23.30343316986745</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-10333.87876575362</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>119.5516867572638</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.197145276428801e-09</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.971479365951204</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>65.69799999999998</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.5163516328054385</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1360.205729210209</v>
+      </c>
+      <c r="E21" t="n">
+        <v>4.362145563014692</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2.62416e-07</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-84.01300000000001</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.1072777898928834</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.7640302041180881</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1.46361278669187</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2.205173163820537</v>
+      </c>
+      <c r="L21" t="n">
+        <v>35.41312290823187</v>
+      </c>
+      <c r="M21" t="n">
+        <v>87.52906141133336</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>23.17348346630436</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-10176.64596798434</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>-846.4309046715292</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>3.599258221389223e-07</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0.9517534265592323</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>65.69800000000004</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.5163516328054389</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1436.289351969401</v>
+      </c>
+      <c r="E22" t="n">
+        <v>4.606143827622651</v>
+      </c>
+      <c r="F22" t="n">
+        <v>2.62309e-07</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-84.02</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.2293604959594025</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.8844101444669695</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1.560549621133494</v>
+      </c>
+      <c r="K22" t="n">
+        <v>2.407839855706039</v>
+      </c>
+      <c r="L22" t="n">
+        <v>34.74501701540667</v>
+      </c>
+      <c r="M22" t="n">
+        <v>87.58295513147668</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>23.69082520203667</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>-10345.33052685845</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>-919.8843263028816</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>3.594996674257935e-07</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0.9518836743788911</v>
       </c>
     </row>
   </sheetData>
@@ -866,7 +3802,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AD11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -882,125 +3818,693 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>normalized Rct_a</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>delta Rct-d</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>normalized Rct_d</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
         <is>
           <t>Cp1</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Ph1</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Slope 1</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Slope 2</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Slope 3</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Slope 4</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Slope 5</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Angle</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Cp_exp-a</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Cp_exp-b</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Ph_slope</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Ph_peak</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Area Cp</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Area Ph</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Area Slope</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Area Rs-direct</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
-      <c r="W1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>linear_eq_m</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>linear_eq_b</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Rs</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>delta Rct-i</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Q</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B2" t="n">
+        <v>176.22</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>442.7387460738697</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>2.79854e-07</v>
+      </c>
+      <c r="G2" t="n">
+        <v>-78.821</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.5481798751735231</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.7263531403530465</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1.179289579195842</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1.896337896148187</v>
+      </c>
+      <c r="L2" t="n">
+        <v>13.24664818956317</v>
+      </c>
+      <c r="M2" t="n">
+        <v>84.60611152146957</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>10.5909525989069</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>-6757.919165589063</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>150.0046541522291</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>2.663338815567681e-09</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.930935082071441</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B3" t="n">
+        <v>133.565</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.7579446146861876</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1196.766216359756</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2.703097993957996</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2.81243e-07</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-80.351</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.5418256152046087</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.9010682330957922</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1.475204226091361</v>
+      </c>
+      <c r="K3" t="n">
+        <v>2.33219979671676</v>
+      </c>
+      <c r="L3" t="n">
+        <v>17.23871188001938</v>
+      </c>
+      <c r="M3" t="n">
+        <v>85.66777575705275</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>13.20027447754708</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>-7718.58434488335</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>-546.4129549561276</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>5.584673222971136e-07</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.8960328445951323</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B4" t="n">
+        <v>121.0210000000001</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.686760867097946</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1004.782878100348</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2.269471301101581</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2.78511e-07</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-81.10299999999999</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.0275019636966087</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.5816810453513427</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1.475904541060932</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2.069702158372602</v>
+      </c>
+      <c r="L4" t="n">
+        <v>19.65098299046176</v>
+      </c>
+      <c r="M4" t="n">
+        <v>86.06107784966113</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>14.52313237965902</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>-8224.407501363354</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>-396.409918092351</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>5.082483036017803e-07</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.9086717044287616</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B5" t="n">
+        <v>115.665</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.6563670411985015</v>
+      </c>
+      <c r="D5" t="n">
+        <v>968.9229310325121</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2.18847557306595</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2.76359e-07</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-81.548</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.2203867314408416</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.7012511749719063</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1.426403407443023</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2.056537876143126</v>
+      </c>
+      <c r="L5" t="n">
+        <v>21.90434294057446</v>
+      </c>
+      <c r="M5" t="n">
+        <v>86.35405494977601</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>15.6937152902109</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>-8750.737407184411</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>-374.1297666354274</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>4.812910557211444e-07</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.9156698053745044</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B6" t="n">
+        <v>111.664</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.6336624673703327</v>
+      </c>
+      <c r="D6" t="n">
+        <v>995.1849059884513</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2.247792665118149</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2.74397e-07</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-81.848</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.3164895967107017</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.9415504384226792</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1.506193361917312</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2.216134587374894</v>
+      </c>
+      <c r="L6" t="n">
+        <v>23.84829695047509</v>
+      </c>
+      <c r="M6" t="n">
+        <v>86.56163916493065</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>16.64368175398435</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>-9159.621420920957</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>-405.2875774307696</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>4.631455767424235e-07</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.9203777368027308</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>9</v>
+      </c>
+      <c r="B7" t="n">
+        <v>106.525</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.6045000567472478</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1162.349516158448</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2.6253620819636</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2.73123e-07</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-82.081</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.7123332046212697</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1.37181600158045</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2.207625158007089</v>
+      </c>
+      <c r="L7" t="n">
+        <v>25.18493337408912</v>
+      </c>
+      <c r="M7" t="n">
+        <v>86.62097055897429</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>16.93662005737464</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>-9169.78964253145</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>-561.4111691179689</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>4.500455495922638e-07</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.9239989877368346</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B8" t="n">
+        <v>106.549</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.6046362501418679</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1114.422041441262</v>
+      </c>
+      <c r="E8" t="n">
+        <v>2.517109810974899</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2.71946e-07</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-82.276</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.5263140168972354</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.466862357593779</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1.551702448414602</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2.379554499254712</v>
+      </c>
+      <c r="L8" t="n">
+        <v>26.2906876890817</v>
+      </c>
+      <c r="M8" t="n">
+        <v>86.88720245361314</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>18.38840987531621</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>-9885.402018134655</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>-526.361471191174</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>4.389724878764684e-07</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.9271133873023493</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>12</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99.30899999999997</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.5635512427647257</v>
+      </c>
+      <c r="D9" t="n">
+        <v>959.0771913942996</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2.166237312408795</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2.71109e-07</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-82.44199999999999</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.07132121822165173</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.6796286447944158</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.403179545867203</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2.237145134177287</v>
+      </c>
+      <c r="L9" t="n">
+        <v>27.30665783007737</v>
+      </c>
+      <c r="M9" t="n">
+        <v>86.74861304721674</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>17.60303050451797</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>-9258.92408894535</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>-395.272394972675</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.172201301024176e-06</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0.8860525156364467</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B10" t="n">
+        <v>96.35899999999998</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.546810804675973</v>
+      </c>
+      <c r="D10" t="n">
+        <v>961.2081953427482</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2.171050543614209</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2.70458e-07</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-82.56999999999999</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.1163231533897849</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.6260359228828783</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.327437304529981</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2.16106049180579</v>
+      </c>
+      <c r="L10" t="n">
+        <v>27.57286682831236</v>
+      </c>
+      <c r="M10" t="n">
+        <v>86.80272453991049</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>17.90158382468181</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>-9296.456844935376</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>-403.7582045733692</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>9.042976841967091e-07</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0.9131653180518182</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>15</v>
+      </c>
+      <c r="B11" t="n">
+        <v>97.024</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.5505844966519123</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1090.861368925641</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2.46389406529067</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2.69936e-07</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-82.73699999999999</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.2728817483206419</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.9138021539933532</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1.630666832634549</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2.235788488584801</v>
+      </c>
+      <c r="L11" t="n">
+        <v>28.88389101858023</v>
+      </c>
+      <c r="M11" t="n">
+        <v>87.04481260445652</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>19.37100952744106</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>-10002.05164744971</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>-525.8263464214272</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>3.584885292294679e-07</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0.9999959218011779</v>
       </c>
     </row>
   </sheetData>
@@ -1014,7 +4518,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AD22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1030,125 +4534,1309 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>normalized Rct_a</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>delta Rct-d</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>normalized Rct_d</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
         <is>
           <t>Cp1</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Ph1</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Slope 1</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Slope 2</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Slope 3</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Slope 4</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Slope 5</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Angle</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Cp_exp-a</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Cp_exp-b</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Ph_slope</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Ph_peak</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Area Cp</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Area Ph</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Area Slope</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Area Rs-direct</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
-      <c r="W1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>linear_eq_m</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>linear_eq_b</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Rs</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>delta Rct-i</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Q</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>122.251</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>371.1302526460128</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>2.76224e-07</v>
+      </c>
+      <c r="G2" t="n">
+        <v>-81.25700000000001</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.330533986844334</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.5877378281273548</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1.298060770326512</v>
+      </c>
+      <c r="K2" t="n">
+        <v>2.010056679955588</v>
+      </c>
+      <c r="L2" t="n">
+        <v>19.28371356972924</v>
+      </c>
+      <c r="M2" t="n">
+        <v>85.95626256722102</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>14.14548245783472</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>-7763.767418940207</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>154.9282210469704</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>2.775127738980829e-09</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.9423162248084451</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>100.185</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.819502498957064</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1040.947955095718</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2.804804910605287</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2.73656e-07</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-82.15600000000001</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.08386181951354808</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.6501778611598134</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1.29584434663318</v>
+      </c>
+      <c r="K3" t="n">
+        <v>2.223420237279577</v>
+      </c>
+      <c r="L3" t="n">
+        <v>23.83488154240947</v>
+      </c>
+      <c r="M3" t="n">
+        <v>86.48127321041933</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>16.26262353659398</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>-8434.634266655097</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>-472.4873431757055</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>4.480406649797358e-07</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.9249675534955195</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>96.005</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.7853105496069563</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1013.380858740757</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2.730526146860164</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2.7226e-07</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-82.504</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.1348066623443797</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.740179005066733</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1.480561527749616</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2.313516128215868</v>
+      </c>
+      <c r="L4" t="n">
+        <v>26.24863934026049</v>
+      </c>
+      <c r="M4" t="n">
+        <v>86.78649210241561</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>17.81096882872391</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>-9104.597151980255</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>-458.6884857145841</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>9.89915647613028e-07</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.9048746537960295</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>83.81100000000004</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.6855649442540351</v>
+      </c>
+      <c r="D5" t="n">
+        <v>913.260656169433</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2.460755084389493</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2.71316e-07</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-82.673</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.59305345371442</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1.713764778757748</v>
+      </c>
+      <c r="L5" t="n">
+        <v>25.21912274842513</v>
+      </c>
+      <c r="M5" t="n">
+        <v>86.35824109805462</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>15.71180374738322</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>-7782.179053414251</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>-375.7026330630589</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>4.214796704370467e-07</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.9328901449854846</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>89.99099999999999</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.7361166779821842</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1089.022814217741</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2.934341262813894</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2.70379e-07</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-82.851</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.3779501970894521</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.030186041264169</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1.767613475431259</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2.52143372850762</v>
+      </c>
+      <c r="L6" t="n">
+        <v>29.13872742400114</v>
+      </c>
+      <c r="M6" t="n">
+        <v>87.01682231696586</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>19.1889327159228</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>-9593.136762940996</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>-539.0461410029877</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>4.129222500315576e-07</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.9354617326991671</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>88.84500000000003</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.7267425215335666</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1123.578190914356</v>
+      </c>
+      <c r="E7" t="n">
+        <v>3.027449750872329</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2.69961e-07</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-82.991</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.448810581471758</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.128325434466154</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1.581702138578309</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2.476534749288193</v>
+      </c>
+      <c r="L7" t="n">
+        <v>30.31672463756461</v>
+      </c>
+      <c r="M7" t="n">
+        <v>87.11128161283676</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>19.81751633429429</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>-9806.389472830584</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>-575.7878673236623</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>4.067916761251468e-07</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.9374812448816695</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>86.53199999999998</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.7078224309003607</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1089.956399068956</v>
+      </c>
+      <c r="E8" t="n">
+        <v>2.9368567808687</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2.69501e-07</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-83.08</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.4950521832648156</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.9881042457549121</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1.67893185350079</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2.517252900989067</v>
+      </c>
+      <c r="L8" t="n">
+        <v>30.77767099983682</v>
+      </c>
+      <c r="M8" t="n">
+        <v>87.15781820780296</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>20.14254544709857</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>-9869.027485010618</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>-550.5535689678708</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>4.024624242343295e-07</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.9388505881348892</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>84.29000000000002</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.6894831126125761</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1140.983223647905</v>
+      </c>
+      <c r="E9" t="n">
+        <v>3.074347120756509</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2.69065e-07</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-83.175</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.4777027867347912</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.956899369371179</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.699034982422144</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2.490957032654544</v>
+      </c>
+      <c r="L9" t="n">
+        <v>31.46402998335893</v>
+      </c>
+      <c r="M9" t="n">
+        <v>87.21211455630632</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>20.53547611323334</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>-9966.373567261111</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>-601.8452908097837</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>3.981809757220652e-07</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0.9402256101603299</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>82.62300000000005</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.6758472323334783</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1114.760587997812</v>
+      </c>
+      <c r="E10" t="n">
+        <v>3.00369096846729</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2.68862e-07</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-83.27500000000001</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.5569813971787919</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.9256174962347529</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.624419420570391</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2.511422546735022</v>
+      </c>
+      <c r="L10" t="n">
+        <v>31.88114884056025</v>
+      </c>
+      <c r="M10" t="n">
+        <v>87.25805920057836</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>20.88011291202754</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>-10037.10526332246</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>-582.950222603053</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>3.942594878233831e-07</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0.9416011267882688</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79.98599999999999</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.6542768566310296</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1059.935901410297</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2.855967396495895</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2.685e-07</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-83.33</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.3114787340900936</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.9543286886739243</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1.720521367487621</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2.638531994005457</v>
+      </c>
+      <c r="L11" t="n">
+        <v>32.48496036065949</v>
+      </c>
+      <c r="M11" t="n">
+        <v>87.23514555078835</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>20.70680400200393</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>-9852.044214779651</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>-537.6712598958597</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>3.915712377291921e-07</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0.9424435530314343</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>78.154</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.6392912941407434</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1038.133128703909</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2.797220440269765</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2.68248e-07</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-83.396</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.2604359614596863</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.6804501382612789</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.486805657384116</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2.327269215728609</v>
+      </c>
+      <c r="L12" t="n">
+        <v>31.64516494426261</v>
+      </c>
+      <c r="M12" t="n">
+        <v>87.22943828442875</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>20.66408230488827</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-9738.146833238899</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-521.6903502515428</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>3.887829210702251e-07</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.9433874120046737</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>78.22499999999997</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.6398720664861636</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1107.335620098692</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2.983684601844835</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2.68049e-07</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-83.486</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.2269760579253861</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.9987665889543645</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.602335496143361</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2.626349416462623</v>
+      </c>
+      <c r="L13" t="n">
+        <v>33.86317524998702</v>
+      </c>
+      <c r="M13" t="n">
+        <v>87.3222287501108</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>21.38123538406983</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-10018.55328220722</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>-587.8074351467726</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>3.855688000858838e-07</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.944520693151338</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>77.61399999999998</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.6348741523586718</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1232.241741846284</v>
+      </c>
+      <c r="E14" t="n">
+        <v>3.320240624580951</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2.6773e-07</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-83.53700000000001</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.6305025851687559</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.9964186962867626</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.912712004248301</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2.683603967450868</v>
+      </c>
+      <c r="L14" t="n">
+        <v>33.97227132522889</v>
+      </c>
+      <c r="M14" t="n">
+        <v>87.41672760765853</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>22.16450373431897</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-10335.15395494345</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>-704.3154703716659</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>3.831347269447549e-07</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.9453085696818081</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>70.72300000000001</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.5785065152841288</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1502.298777220812</v>
+      </c>
+      <c r="E15" t="n">
+        <v>4.047901690875407</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2.67571e-07</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-83.574</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.01892620484260812</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.208705692684379</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.0716699838771</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1.940687293254324</v>
+      </c>
+      <c r="L15" t="n">
+        <v>31.05210348518892</v>
+      </c>
+      <c r="M15" t="n">
+        <v>87.08785412480184</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>19.65781776517757</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-8970.084037679289</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>-952.4806994721499</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>3.815828381615512e-07</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.9458411130672405</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>73.56799999999998</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.6017783085618932</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1085.282837682996</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2.924264001507169</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2.67374e-07</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-83.628</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.1876909474431176</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.8003300417552056</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.61157141227288</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2.526243468095973</v>
+      </c>
+      <c r="L16" t="n">
+        <v>33.83314000141182</v>
+      </c>
+      <c r="M16" t="n">
+        <v>87.32531571405592</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>21.4059483032814</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-9770.701640971984</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>-578.5028063672166</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>3.79570601572069e-07</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.9465298135882735</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>73.66899999999998</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.6026044776729842</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1262.560004319287</v>
+      </c>
+      <c r="E17" t="n">
+        <v>3.401932327849133</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2.67279e-07</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-83.69</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.2957751868366115</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.9636503420793484</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.634190566495614</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2.392784020934656</v>
+      </c>
+      <c r="L17" t="n">
+        <v>33.49245672902483</v>
+      </c>
+      <c r="M17" t="n">
+        <v>87.44751334825065</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>22.43219200770721</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-10197.68748450432</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>-742.7700921882181</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>3.774134290660462e-07</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.947336461795603</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>73.53999999999996</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.6015492715806003</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1357.128652157507</v>
+      </c>
+      <c r="E18" t="n">
+        <v>3.656744882643529</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2.67075e-07</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-83.759</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.5951039828724957</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.073613451235428</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.874587208278521</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2.748564575002348</v>
+      </c>
+      <c r="L18" t="n">
+        <v>35.30980551628979</v>
+      </c>
+      <c r="M18" t="n">
+        <v>87.52417100540225</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>23.12765295142246</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-10453.6666009086</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>-831.865799298183</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>3.75005320023306e-07</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.948182704905459</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>69.43700000000001</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.5679871739290479</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1113.909590429736</v>
+      </c>
+      <c r="E19" t="n">
+        <v>3.001397979517969</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2.66953e-07</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-83.803</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.1242211930156695</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.631517199390349</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.431943269044873</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2.321296160162953</v>
+      </c>
+      <c r="L19" t="n">
+        <v>33.81777975569447</v>
+      </c>
+      <c r="M19" t="n">
+        <v>87.37354170745235</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>21.79956234889971</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-9699.759956167509</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>-614.8522174445186</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>3.733618963832413e-07</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.9487873349115972</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>69.13500000000005</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.5655168464879637</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1211.447361577307</v>
+      </c>
+      <c r="E20" t="n">
+        <v>3.26421075334108</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2.66861e-07</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-83.834</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.3188206966877221</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.7984307653834289</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.671405747267264</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2.27978211544319</v>
+      </c>
+      <c r="L20" t="n">
+        <v>33.65501553687267</v>
+      </c>
+      <c r="M20" t="n">
+        <v>87.44335165990118</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>22.39562869768338</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-9910.233625440118</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>-707.2753955044894</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>3.722562336146518e-07</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.9491914304127851</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>70.59499999999997</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.5774594890839337</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1657.77317527988</v>
+      </c>
+      <c r="E21" t="n">
+        <v>4.466823072117157</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2.66724e-07</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-83.895</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.7173799805031622</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.316235481668363</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1.739407420553176</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2.618405736056628</v>
+      </c>
+      <c r="L21" t="n">
+        <v>34.88228354389916</v>
+      </c>
+      <c r="M21" t="n">
+        <v>87.6263570578039</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>24.12452033487193</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-10659.97893321486</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>-1115.902302769691</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>3.70075288371997e-07</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0.9500074306874754</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>66.67299999999994</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.5453779519185934</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1262.278685295418</v>
+      </c>
+      <c r="E22" t="n">
+        <v>3.401174321672423</v>
+      </c>
+      <c r="F22" t="n">
+        <v>2.66594e-07</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-83.96599999999999</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.4115843471558466</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.9389535320322314</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1.611043353358093</v>
+      </c>
+      <c r="K22" t="n">
+        <v>2.606017068382955</v>
+      </c>
+      <c r="L22" t="n">
+        <v>36.02166506229121</v>
+      </c>
+      <c r="M22" t="n">
+        <v>87.50042163574763</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>22.90763392616027</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>-9967.246164742723</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>-760.3784048609194</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>3.67800067085379e-07</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0.9508641339490165</v>
       </c>
     </row>
   </sheetData>
@@ -1162,7 +5850,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AD11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1178,125 +5866,693 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>normalized Rct_a</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>delta Rct-d</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>normalized Rct_d</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
         <is>
           <t>Cp1</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Ph1</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Slope 1</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Slope 2</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Slope 3</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Slope 4</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Slope 5</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Angle</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Cp_exp-a</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Cp_exp-b</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Ph_slope</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Ph_peak</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Area Cp</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Area Ph</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Area Slope</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Area Rs-direct</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
-      <c r="W1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>linear_eq_m</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>linear_eq_b</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Rs</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>delta Rct-i</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Q</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B2" t="n">
+        <v>203.4469999999999</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>415.5327085246262</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>2.84316e-07</v>
+      </c>
+      <c r="G2" t="n">
+        <v>-77.22</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.08978648883415256</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.4588389627428508</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.967997851505038</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1.680153160535744</v>
+      </c>
+      <c r="L2" t="n">
+        <v>10.51397226609207</v>
+      </c>
+      <c r="M2" t="n">
+        <v>83.2286754759028</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>8.422101355625013</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>-5594.038148614398</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>186.6668969395223</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>2.572271554047037e-09</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.938911304287214</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B3" t="n">
+        <v>140.4449999999999</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.6903272105265743</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1121.467977719676</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2.698868114862763</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2.87624e-07</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-79.655</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.3596651333256907</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.7502398108834016</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1.458388893159746</v>
+      </c>
+      <c r="K3" t="n">
+        <v>2.304195474805894</v>
+      </c>
+      <c r="L3" t="n">
+        <v>15.06963432387406</v>
+      </c>
+      <c r="M3" t="n">
+        <v>85.0734179252637</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>11.60124906408612</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>-6793.990321478196</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>-472.6731776653691</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>6.244166002873013e-07</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.8826192676113127</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B4" t="n">
+        <v>125.5309999999999</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.6170206491125452</v>
+      </c>
+      <c r="D4" t="n">
+        <v>943.2031818020457</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2.269865073079193</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2.84392e-07</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-80.584</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.4120581683184186</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.7372488032528489</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1.3682177871806</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2.171282251502486</v>
+      </c>
+      <c r="L4" t="n">
+        <v>17.43515295685487</v>
+      </c>
+      <c r="M4" t="n">
+        <v>85.68063584767771</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>13.23972577131781</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>-7493.781817736216</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>-339.512298175683</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>5.527798103117413e-07</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.8991624134218938</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B5" t="n">
+        <v>119.874</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.5892148815170536</v>
+      </c>
+      <c r="D5" t="n">
+        <v>925.0936317207684</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2.226283545777584</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2.81587e-07</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-81.169</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.2220249874761634</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.8108045526750352</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1.575293000320209</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2.21423370452061</v>
+      </c>
+      <c r="L5" t="n">
+        <v>19.9532080972912</v>
+      </c>
+      <c r="M5" t="n">
+        <v>86.08381995169948</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>14.60773689230128</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>-8129.460176005873</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>-333.7548071037525</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>5.137677306838621e-07</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.9086276890544402</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B6" t="n">
+        <v>115.61</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.5682561060128681</v>
+      </c>
+      <c r="D6" t="n">
+        <v>952.8001598665713</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2.292960675104363</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2.79529e-07</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-81.532</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.2913970905464736</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.753727737783691</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1.54670286844977</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2.167709406308663</v>
+      </c>
+      <c r="L6" t="n">
+        <v>21.73132486399051</v>
+      </c>
+      <c r="M6" t="n">
+        <v>86.32011709446074</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>15.54858614599184</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>-8528.742698678667</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>-366.5285160124305</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>4.901749361239819e-07</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.9145916029816222</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>9</v>
+      </c>
+      <c r="B7" t="n">
+        <v>112.884</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.5548570389339729</v>
+      </c>
+      <c r="D7" t="n">
+        <v>973.8540596952689</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2.343627925592178</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2.78141e-07</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-81.807</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.4629487547650173</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.044311552568128</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1.66867415449035</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2.49605929445957</v>
+      </c>
+      <c r="L7" t="n">
+        <v>23.85104886284417</v>
+      </c>
+      <c r="M7" t="n">
+        <v>86.52516603865126</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>16.46856123014045</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>-8919.202352188366</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>-392.8741474049283</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>4.73924482176603e-07</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.9189140062896058</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B8" t="n">
+        <v>110.67</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.5439745978068</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1052.069384466093</v>
+      </c>
+      <c r="E8" t="n">
+        <v>2.531856970300914</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2.76923e-07</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-82.05200000000001</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.7921775406142562</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.013640151941362</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1.876557889961799</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2.37590768450577</v>
+      </c>
+      <c r="L8" t="n">
+        <v>24.90528374330481</v>
+      </c>
+      <c r="M8" t="n">
+        <v>86.72920435807227</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>17.49835000588874</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>-9365.715433468496</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>-470.1810552379338</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>4.59654215334174e-07</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.9228651803233946</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>12</v>
+      </c>
+      <c r="B9" t="n">
+        <v>104.707</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.5146647529823494</v>
+      </c>
+      <c r="D9" t="n">
+        <v>988.0854681183581</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2.377876513323379</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2.75833e-07</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-82.236</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.2993758409746031</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.9043058464767185</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.591753687542244</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2.306192192620498</v>
+      </c>
+      <c r="L9" t="n">
+        <v>25.07201326729235</v>
+      </c>
+      <c r="M9" t="n">
+        <v>86.72363030343634</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>17.46851540983855</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>-9178.008238206097</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>-421.4502052960082</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>4.488018763383606e-07</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0.9258881672677145</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B10" t="n">
+        <v>101.419</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.4985032956986341</v>
+      </c>
+      <c r="D10" t="n">
+        <v>985.8590759485415</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2.372518590531401</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2.75131e-07</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-82.438</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.1965352671732684</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.8598913346408041</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.621214801029556</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2.558268819927799</v>
+      </c>
+      <c r="L10" t="n">
+        <v>27.73301992254679</v>
+      </c>
+      <c r="M10" t="n">
+        <v>86.82480654129405</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>18.02633899289433</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>-9343.367392363531</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>-426.5521051765032</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.679564945875143e-06</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0.826458868524758</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>15</v>
+      </c>
+      <c r="B11" t="n">
+        <v>97.31200000000001</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.4783162199491761</v>
+      </c>
+      <c r="D11" t="n">
+        <v>940.3522230414053</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2.263004099918349</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2.74475e-07</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-82.578</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.3162668118101436</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.9570668073881924</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1.68957947960506</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2.411477381060497</v>
+      </c>
+      <c r="L11" t="n">
+        <v>28.05607358596687</v>
+      </c>
+      <c r="M11" t="n">
+        <v>86.88813597581999</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>18.39393704756781</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>-9412.102212550497</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>-392.5744355680042</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.073043167800002e-06</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0.8926826976604159</v>
       </c>
     </row>
   </sheetData>
@@ -1310,7 +6566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AD22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1326,125 +6582,1309 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>normalized Rct_a</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>delta Rct-d</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>normalized Rct_d</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
         <is>
           <t>Cp1</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Ph1</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Slope 1</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Slope 2</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Slope 3</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Slope 4</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Slope 5</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Angle</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Cp_exp-a</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Cp_exp-b</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Ph_slope</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Ph_peak</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Area Cp</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Area Ph</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Area Slope</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Area Rs-direct</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
-      <c r="W1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>linear_eq_m</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>linear_eq_b</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Rs</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>delta Rct-i</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Q</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>125.5210000000001</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>405.3857065638215</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>2.93977e-07</v>
+      </c>
+      <c r="G2" t="n">
+        <v>-79.83799999999999</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.2391044109163905</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.7136005494002059</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1.243429740364458</v>
+      </c>
+      <c r="K2" t="n">
+        <v>2.049380985192579</v>
+      </c>
+      <c r="L2" t="n">
+        <v>14.65458637159623</v>
+      </c>
+      <c r="M2" t="n">
+        <v>84.97403041664072</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>11.37069061908078</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>-6270.929668642305</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>121.8358773643241</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>2.615643179912395e-09</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.9354954801747274</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>103.521</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.824730523179388</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1146.565042166093</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2.828331200635423</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2.84886e-07</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-81.52</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.4649729785824099</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.9275681081264546</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1.623548140619627</v>
+      </c>
+      <c r="K3" t="n">
+        <v>2.307936484269805</v>
+      </c>
+      <c r="L3" t="n">
+        <v>20.57984087140361</v>
+      </c>
+      <c r="M3" t="n">
+        <v>86.21937729737456</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>15.13311587404684</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>-7908.507524896489</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>-565.6887190885853</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>4.93953090122737e-07</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.9163984231004559</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>97.38899999999995</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.7758781399128425</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1078.587580289879</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2.660645313403699</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2.81455e-07</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-82.027</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.5400442856502823</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.004924751475929</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1.562905831973823</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2.46533442115506</v>
+      </c>
+      <c r="L4" t="n">
+        <v>23.42731796260284</v>
+      </c>
+      <c r="M4" t="n">
+        <v>86.56353036166978</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>16.6528633143862</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>-8555.417740161829</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>-516.3670651784987</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>9.920763789529094e-07</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.8841076497048745</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>94.255</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.7509102062603066</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1032.789144989676</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2.547670350155968</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2.79294e-07</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-82.303</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.3643220811514742</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.9542164653254016</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1.706124634932756</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2.557466640050853</v>
+      </c>
+      <c r="L5" t="n">
+        <v>25.57066790162908</v>
+      </c>
+      <c r="M5" t="n">
+        <v>86.69176337968138</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>17.29987900364074</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>-8769.937580096921</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>-481.5837848715981</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>4.478528728625239e-07</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.9281369151662501</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>92.601</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.737733128321157</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1071.254183162644</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2.642555388158442</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2.78271e-07</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-82.5</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.4038505141133135</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.191843074366935</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1.61408324282019</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2.427137666739247</v>
+      </c>
+      <c r="L6" t="n">
+        <v>26.19734474223249</v>
+      </c>
+      <c r="M6" t="n">
+        <v>86.86121345923347</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>18.23585350489639</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>-9162.047188881685</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>-521.5038801240548</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>4.379485607529913e-07</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.9309405666265033</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>88.86799999999999</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.7079930848224596</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1018.455294596793</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2.51231180109813</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2.77066e-07</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-82.661</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.1492253332338421</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.7377444389760996</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1.550429218871968</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2.420052258613789</v>
+      </c>
+      <c r="L7" t="n">
+        <v>26.8792209452552</v>
+      </c>
+      <c r="M7" t="n">
+        <v>86.86744460857412</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>18.27220011263456</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>-9049.732686986781</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>-479.7410486108045</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>4.290502484936856e-07</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.9333986982988465</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>85.39500000000004</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.6803244078680061</v>
+      </c>
+      <c r="D8" t="n">
+        <v>952.8610339279178</v>
+      </c>
+      <c r="E8" t="n">
+        <v>2.350504762500562</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2.76493e-07</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-82.78700000000001</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.07170453227870047</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.9006459460884192</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1.410516855309734</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2.356001495963845</v>
+      </c>
+      <c r="L8" t="n">
+        <v>27.71404091806502</v>
+      </c>
+      <c r="M8" t="n">
+        <v>86.86641320059545</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>18.26617388483119</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>-8927.370516560044</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>-426.3495748725411</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>4.22975977742907e-07</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.9352353544685039</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>83.005</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.6612837692497665</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1043.478335741616</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2.574038301908744</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2.75846e-07</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-82.91</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.04359110091901515</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.6539034218664624</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.507416497338782</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2.093907073931078</v>
+      </c>
+      <c r="L9" t="n">
+        <v>27.72395612532735</v>
+      </c>
+      <c r="M9" t="n">
+        <v>86.91368979123239</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>18.5465325606511</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>-8965.882849277941</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>-512.8964082705451</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>4.170676493982838e-07</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0.9370133824139422</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79.952</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.6369611459437062</v>
+      </c>
+      <c r="D10" t="n">
+        <v>991.8055552344614</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2.446572583037822</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2.75517e-07</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-83.04600000000001</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.04799330266948247</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.5089520950458595</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.328541868980331</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2.276765500046405</v>
+      </c>
+      <c r="L10" t="n">
+        <v>29.34774855306356</v>
+      </c>
+      <c r="M10" t="n">
+        <v>86.94806930354042</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>18.75585872139407</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>-8968.913603131734</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>-471.3586055370186</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>4.115320442145009e-07</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0.9388208224766018</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>80.97499999999997</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.6451111766158645</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1069.677066978048</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2.638664979199617</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2.74867e-07</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-83.09099999999999</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.251142230750293</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.001559869725202</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1.617462083210003</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2.388396257881872</v>
+      </c>
+      <c r="L11" t="n">
+        <v>29.59671202286416</v>
+      </c>
+      <c r="M11" t="n">
+        <v>87.11608184377877</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>19.85055815957696</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>-9466.037951180724</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>-545.8962549955997</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>4.083913633849018e-07</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0.9396582439700497</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>80.16699999999997</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.6386740067399075</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1160.498537446534</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2.862702159095075</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2.74698e-07</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-83.209</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.538528885055742</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1.197607868959394</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.673785067309329</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2.645207520751798</v>
+      </c>
+      <c r="L12" t="n">
+        <v>31.71356509395545</v>
+      </c>
+      <c r="M12" t="n">
+        <v>87.22113248913811</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>20.60222261724563</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-9759.613103107598</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-632.0797298057973</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>4.040091939319597e-07</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.9411799777512009</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>78.42199999999997</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.6247719505102726</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1086.038955565593</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2.67902626555634</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2.74453e-07</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-83.25700000000001</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.3159914689799611</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.7606565528292796</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.532980626709601</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2.379374168915587</v>
+      </c>
+      <c r="L13" t="n">
+        <v>30.45819316920828</v>
+      </c>
+      <c r="M13" t="n">
+        <v>87.20388616141652</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>20.47494874847089</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-9605.001358597106</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>-568.3870217097557</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>4.017211680390725e-07</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.9419093952397858</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>77.54300000000001</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.6177691382318493</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1210.144025696469</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2.985166980735545</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2.74151e-07</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-83.309</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.6882018617424399</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.240996384041292</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.838074607032267</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2.844247579126824</v>
+      </c>
+      <c r="L14" t="n">
+        <v>32.33648522574576</v>
+      </c>
+      <c r="M14" t="n">
+        <v>87.28877204326189</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>21.11700272736227</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-9858.038022428444</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>-684.4150291705306</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>3.993079744260538e-07</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.9426626894254309</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>75.66800000000001</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.6028313987300927</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1105.476830800402</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2.726975354337911</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2.73748e-07</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-83.417</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.3134838763771157</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.042939328728132</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.762795303259463</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2.697678128525368</v>
+      </c>
+      <c r="L15" t="n">
+        <v>33.13060500710547</v>
+      </c>
+      <c r="M15" t="n">
+        <v>87.27853165704568</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>21.03742435549335</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-9717.500210802407</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>-593.3234985105496</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>3.950350635438924e-07</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.9440599332315927</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>76.363</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.6083683208387438</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1255.083621829614</v>
+      </c>
+      <c r="E16" t="n">
+        <v>3.096023371095401</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2.73534e-07</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-83.444</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.8348889911401127</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.162140258504048</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.817230276788898</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2.500076677676967</v>
+      </c>
+      <c r="L16" t="n">
+        <v>32.04735124593791</v>
+      </c>
+      <c r="M16" t="n">
+        <v>87.37663320905385</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>21.82528800418178</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-10047.4484867406</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>-731.7342709361276</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>3.936691830738516e-07</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.9444756568646714</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>73.23899999999998</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.5834800551302167</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1089.17127217829</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2.686753021981099</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2.73386e-07</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-83.521</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.1647945491312554</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.9837396176996254</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.647799806128335</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2.36922966697612</v>
+      </c>
+      <c r="L17" t="n">
+        <v>32.74818385103877</v>
+      </c>
+      <c r="M17" t="n">
+        <v>87.29573909794998</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>21.17148818119123</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-9621.749888657463</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>-585.0291552274996</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>3.909898706607735e-07</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.9454196979458092</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>72.40800000000002</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.5768596489830385</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1169.599698695776</v>
+      </c>
+      <c r="E18" t="n">
+        <v>2.885152781062944</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2.73301e-07</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-83.593</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.3214774842710523</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.209466696147226</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.839286975016417</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2.696931366100376</v>
+      </c>
+      <c r="L18" t="n">
+        <v>34.32470239710515</v>
+      </c>
+      <c r="M18" t="n">
+        <v>87.36062890868665</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>21.69276074669611</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-9796.620626035796</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>-661.2284984972958</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>3.885281668279745e-07</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.9463227911538287</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>72.01900000000001</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.5737605659610739</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1261.058472689659</v>
+      </c>
+      <c r="E19" t="n">
+        <v>3.110762052709733</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2.73065e-07</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-83.61199999999999</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.4950083851407024</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.175182459718676</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.651556081778543</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2.664032826976464</v>
+      </c>
+      <c r="L19" t="n">
+        <v>33.45708075385323</v>
+      </c>
+      <c r="M19" t="n">
+        <v>87.42040333435118</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>22.19612925718187</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-9966.493890533791</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>-747.838874172656</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>3.872646030629363e-07</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.9467052719556901</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>69.64600000000002</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.5548553628476508</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1132.602972835435</v>
+      </c>
+      <c r="E20" t="n">
+        <v>2.79388975609362</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2.73002e-07</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-83.694</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.3197724061545827</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.7992640451359035</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.667099980053784</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2.35736918713577</v>
+      </c>
+      <c r="L20" t="n">
+        <v>33.04256991738124</v>
+      </c>
+      <c r="M20" t="n">
+        <v>87.36357714126802</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>21.71705344331145</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-9633.625039364226</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>-634.9207040180563</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>3.846101172966364e-07</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.9476994654770635</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>68.39400000000001</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.5448809362576778</v>
+      </c>
+      <c r="D21" t="n">
+        <v>319.8996590417691</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.7891241695553122</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2.7283e-07</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-83.73999999999999</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.1456315529338118</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.8252817968348364</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1.68344162422929</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2.325128961003513</v>
+      </c>
+      <c r="L21" t="n">
+        <v>33.18595231170661</v>
+      </c>
+      <c r="M21" t="n">
+        <v>87.37559569964908</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>21.81664770973818</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-9599.512453267755</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>117.6086023247421</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>2.285483970405988e-09</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0.9679148829285911</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>67.209</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.5354402848925675</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1148.930834496155</v>
+      </c>
+      <c r="E22" t="n">
+        <v>2.834167105285629</v>
+      </c>
+      <c r="F22" t="n">
+        <v>2.72657e-07</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-83.786</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.3344382195167493</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.8663366712060335</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1.660336650775057</v>
+      </c>
+      <c r="K22" t="n">
+        <v>2.628745819131058</v>
+      </c>
+      <c r="L22" t="n">
+        <v>34.60014319776201</v>
+      </c>
+      <c r="M22" t="n">
+        <v>87.39131217537374</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>21.94826922092168</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>-9575.315285342263</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>-656.5089153167586</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>3.81027561082448e-07</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0.9489411211194251</v>
       </c>
     </row>
   </sheetData>
@@ -1458,7 +7898,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AD1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1474,122 +7914,130 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>normalized Rct_a</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>delta Rct-d</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>normalized Rct_d</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
         <is>
           <t>Cp1</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Ph1</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Slope 1</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Slope 2</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Slope 3</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Slope 4</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Slope 5</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Angle</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Cp_exp-a</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Cp_exp-b</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Ph_slope</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Ph_peak</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Area Cp</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Area Ph</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Area Slope</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Area Rs-direct</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
-      <c r="W1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>linear_eq_m</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>linear_eq_b</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Rs</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>delta Rct-i</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Q</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>n</t>
         </is>
@@ -1606,7 +8054,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AD22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1622,125 +8070,1309 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>normalized Rct_a</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>delta Rct-d</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>normalized Rct_d</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
         <is>
           <t>Cp1</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Ph1</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Slope 1</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Slope 2</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Slope 3</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Slope 4</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Slope 5</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Angle</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Cp_exp-a</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Cp_exp-b</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Ph_slope</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Ph_peak</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Area Cp</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Area Ph</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Area Slope</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Area Rs-direct</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
-      <c r="W1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>linear_eq_m</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>linear_eq_b</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Rs</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>delta Rct-i</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Q</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>118.316</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1673.428943731583</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>2.90962e-07</v>
+      </c>
+      <c r="G2" t="n">
+        <v>-80.413</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.05632165463573149</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.6030178703272474</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1.291296933946665</v>
+      </c>
+      <c r="K2" t="n">
+        <v>2.092727964739502</v>
+      </c>
+      <c r="L2" t="n">
+        <v>16.61522318530226</v>
+      </c>
+      <c r="M2" t="n">
+        <v>85.36780758400076</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>12.34208059193906</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>-6748.482591283335</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>-989.2711043607978</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>5.669450557150221e-07</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.8989682063270243</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>101.064</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.8541870921937856</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1063.97416431176</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.6358048056341145</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2.84504e-07</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-81.617</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.3018543265036266</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.7948109934005042</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1.450497006712002</v>
+      </c>
+      <c r="K3" t="n">
+        <v>2.347110374287388</v>
+      </c>
+      <c r="L3" t="n">
+        <v>21.37036557361384</v>
+      </c>
+      <c r="M3" t="n">
+        <v>86.24270524471871</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>15.22734540983481</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>-7954.308330172933</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>-492.076803122459</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>4.873475088148432e-07</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.9182314914725673</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>95.32999999999998</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.8057236552959867</v>
+      </c>
+      <c r="D4" t="n">
+        <v>974.7631682837783</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.5824945074214815</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2.81687e-07</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-82.045</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.0543188916675581</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.9187364282398158</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1.498707011918256</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2.289753805255692</v>
+      </c>
+      <c r="L4" t="n">
+        <v>23.14132603398336</v>
+      </c>
+      <c r="M4" t="n">
+        <v>86.49591963575499</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>16.33076923701559</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>-8381.349611913041</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>-422.4252394555306</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.062851142884898e-06</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.9015750434924876</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>92.99799999999999</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.786013725954224</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1025.52639569973</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.6128293642471049</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2.80065e-07</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-82.316</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.2822353297111492</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.9998832862542856</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1.644037359117712</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2.466855875220816</v>
+      </c>
+      <c r="L5" t="n">
+        <v>25.6597756595014</v>
+      </c>
+      <c r="M5" t="n">
+        <v>86.70390905726283</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>17.36376851073928</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>-8819.308046089296</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>-474.0564110993898</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>4.477011926842336e-07</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.9286061019103289</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>90.89699999999999</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.7682561952736736</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1054.783575052516</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.6303127354188415</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2.78988e-07</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-82.503</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.4369707905749145</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.9786950025844137</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1.598157331735448</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2.490136468821365</v>
+      </c>
+      <c r="L6" t="n">
+        <v>26.90238682115092</v>
+      </c>
+      <c r="M6" t="n">
+        <v>86.82408465951286</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>18.02223322550936</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>-9051.57053567746</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>-506.51117763558</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>4.378649357911211e-07</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.9313778756816655</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>87.29400000000004</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.7378038473241152</v>
+      </c>
+      <c r="D7" t="n">
+        <v>968.1862332091104</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.5785642926972148</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2.78413e-07</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-82.687</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.1281494067318574</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.7198944617762969</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1.488134384064884</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2.441531922837453</v>
+      </c>
+      <c r="L7" t="n">
+        <v>27.99171628122713</v>
+      </c>
+      <c r="M7" t="n">
+        <v>86.84822348474556</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>18.16054395931161</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>-8990.707432323008</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>-434.4667920596235</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>4.295566039130984e-07</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.9339426762883472</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>88.53699999999998</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.7483096115487335</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1263.616588506356</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.7551062106578693</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2.77561e-07</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-82.736</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.8914811866735203</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.257392073300633</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1.862314840617542</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2.422520428958181</v>
+      </c>
+      <c r="L8" t="n">
+        <v>27.77002464045712</v>
+      </c>
+      <c r="M8" t="n">
+        <v>87.07437942212684</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>19.56712211995582</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>-9667.665045701837</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>-706.2831264454267</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>4.254248137776638e-07</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.9349760936115415</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>84.02199999999999</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.7101490922614014</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1056.788388932611</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.6315107629106</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2.77305e-07</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-82.873</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.3707102807844357</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.042678878766388</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.664121299461529</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2.452585515216535</v>
+      </c>
+      <c r="L9" t="n">
+        <v>28.84182331349882</v>
+      </c>
+      <c r="M9" t="n">
+        <v>87.01837713022248</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>19.19895718333372</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>-9336.989697992338</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>-525.0837529260702</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>4.197342568742096e-07</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0.9368559410857729</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>82.19300000000004</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.6946904898745734</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1065.403944689762</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.6366592072406826</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2.76884e-07</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-82.96899999999999</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.3011969081534984</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.064876016727608</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.729454618817764</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2.321924199199953</v>
+      </c>
+      <c r="L10" t="n">
+        <v>29.13686104294803</v>
+      </c>
+      <c r="M10" t="n">
+        <v>87.05324217330423</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>19.42652097738906</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>-9355.328574205456</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>-537.6329311317322</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>4.153048812850813e-07</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0.9382300766782647</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79.88600000000002</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.6751918590892187</v>
+      </c>
+      <c r="D11" t="n">
+        <v>992.2784996992277</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.5929612389077865</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2.76525e-07</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-83.074</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.1863187019911016</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.785036998776084</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1.603038143482963</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2.366914462988277</v>
+      </c>
+      <c r="L11" t="n">
+        <v>29.90548607814235</v>
+      </c>
+      <c r="M11" t="n">
+        <v>87.05817622417544</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>19.4591607757565</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>-9268.527996519775</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>-475.8337559207615</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>4.108080852274275e-07</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0.939677337286614</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79.03700000000003</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.6680161601135942</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1111.473797982237</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.6641894190641636</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2.76262e-07</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-83.155</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.2965496547716178</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1.17144045888976</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.619530577406423</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2.461145959607075</v>
+      </c>
+      <c r="L12" t="n">
+        <v>30.46447517675472</v>
+      </c>
+      <c r="M12" t="n">
+        <v>87.16366452366474</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>20.18413181362069</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-9562.296871914776</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-588.064336523564</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>4.07338253062954e-07</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.9408160193881694</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>77.45600000000002</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.6546536394063356</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1032.268560235175</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.6168583160354074</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2.76021e-07</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-83.23</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.2612641244370062</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.8618077240652429</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.57390425567196</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2.491843768907402</v>
+      </c>
+      <c r="L13" t="n">
+        <v>31.51168575287774</v>
+      </c>
+      <c r="M13" t="n">
+        <v>87.15239682727612</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>20.10413422417657</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-9433.776914746522</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>-519.9453361865951</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>4.042887200040525e-07</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.941817274399396</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>75.98400000000004</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.6422123804050173</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1107.254170114177</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.6616678731784744</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2.75885e-07</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-83.29600000000001</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.3627986000509496</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.006275397997277</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.489633957647103</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2.341879768411624</v>
+      </c>
+      <c r="L14" t="n">
+        <v>31.02200798893481</v>
+      </c>
+      <c r="M14" t="n">
+        <v>87.22555644851892</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>20.63512520391754</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-9622.311120797718</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>-591.4631384823169</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>4.016765652232231e-07</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.9427223175330037</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>66.12299999999999</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.5588677778153417</v>
+      </c>
+      <c r="D15" t="n">
+        <v>983.9117922644982</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.5879615002179126</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2.75449e-07</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-83.358</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.5284105134071867</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1.645140983711813</v>
+      </c>
+      <c r="L15" t="n">
+        <v>28.54794017829548</v>
+      </c>
+      <c r="M15" t="n">
+        <v>86.68831508228989</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>17.2818253563226</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-7835.619852268862</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>-483.0485352067577</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>3.987137550482963e-07</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.9436113417893272</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>73.81999999999999</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.6239223773623176</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1168.524713587353</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.6982816437856376</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2.75362e-07</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-83.404</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.2567416298007419</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.039574621431789</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.901466951544447</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2.654389688558586</v>
+      </c>
+      <c r="L16" t="n">
+        <v>32.82564847444672</v>
+      </c>
+      <c r="M16" t="n">
+        <v>87.26625806343664</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>20.94283077297428</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-9609.411179678706</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>-654.1993830628451</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>3.968436105843079e-07</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.9442829336644935</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>73.86700000000002</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.6243196186483654</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1337.277504920916</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.7991241635506307</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2.75127e-07</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-83.46299999999999</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.6545810269870269</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.373625820132056</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.855074542768117</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2.859874240445463</v>
+      </c>
+      <c r="L17" t="n">
+        <v>33.53952021722319</v>
+      </c>
+      <c r="M17" t="n">
+        <v>87.36962013998401</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>21.76701631896348</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-9943.823040689851</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>-810.651811934684</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>3.944747448839126e-07</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.9450593510380562</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>69.31600000000003</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.5858548294398054</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1101.58013923501</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.6582772118059548</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2.752e-07</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-83.532</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.01972741828231752</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.6329222072146139</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.359612831196749</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2.342528833365068</v>
+      </c>
+      <c r="L18" t="n">
+        <v>31.92717052037846</v>
+      </c>
+      <c r="M18" t="n">
+        <v>87.20830633647073</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>20.50741885717805</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-9214.62778707721</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>-600.4447574485557</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>3.922775108507422e-07</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.9459407386960953</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>71.404</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.6035024848710232</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1425.594858736097</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.8519004431446967</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2.75054e-07</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-83.613</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.6193574318054983</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.224288964249634</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.757157908479477</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2.812775319975381</v>
+      </c>
+      <c r="L19" t="n">
+        <v>34.53731380715769</v>
+      </c>
+      <c r="M19" t="n">
+        <v>87.43245571536816</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>22.30046132747842</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-10016.93989251047</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>-898.650580828344</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>3.89463031729073e-07</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.9469428626333418</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>66.90200000000004</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.5654518408330237</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1136.629358682779</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.6792217637566412</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2.74906e-07</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-83.65000000000001</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.06680426372917281</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.6254671828461726</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.558258670953845</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2.418485407083224</v>
+      </c>
+      <c r="L20" t="n">
+        <v>33.6102473676049</v>
+      </c>
+      <c r="M20" t="n">
+        <v>87.24302465416277</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>20.76607339002453</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-9168.849542788153</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>-639.6596004768631</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>3.879106575621827e-07</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.9474793052485463</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>68.47899999999998</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.5787805537712564</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1396.660641082037</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.8346100659449698</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2.74804e-07</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-83.673</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.5907969911891308</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.248602594578701</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1.661483957986553</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2.549052190523509</v>
+      </c>
+      <c r="L21" t="n">
+        <v>33.20916565104123</v>
+      </c>
+      <c r="M21" t="n">
+        <v>87.42690252177401</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>22.25226847656322</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-9813.809394455837</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>-879.8485153942045</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>3.868962096896977e-07</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0.9478246627882296</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>63.71500000000003</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.5385155008620982</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1250.206767451459</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.747092831240041</v>
+      </c>
+      <c r="F22" t="n">
+        <v>2.74796e-07</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-83.76000000000001</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.6192578126582722</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1.366398932951824</v>
+      </c>
+      <c r="K22" t="n">
+        <v>2.324959367663667</v>
+      </c>
+      <c r="L22" t="n">
+        <v>33.37604744936927</v>
+      </c>
+      <c r="M22" t="n">
+        <v>87.27172274305212</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>20.98484247191181</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>-9099.907935646037</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>-750.7996544272796</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>3.84126071669241e-07</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0.948902603725772</v>
       </c>
     </row>
   </sheetData>
@@ -1754,7 +9386,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AD11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1770,125 +9402,693 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>normalized Rct_a</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>delta Rct-d</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>normalized Rct_d</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
         <is>
           <t>Cp1</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Ph1</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Slope 1</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Slope 2</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Slope 3</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Slope 4</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Slope 5</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Angle</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Cp_exp-a</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Cp_exp-b</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Ph_slope</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Ph_peak</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Area Cp</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Area Ph</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Area Slope</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Area Rs-direct</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
-      <c r="W1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>linear_eq_m</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>linear_eq_b</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Rs</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>delta Rct-i</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Q</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B2" t="n">
+        <v>175.804</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>450.9873025173325</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>2.85579e-07</v>
+      </c>
+      <c r="G2" t="n">
+        <v>-78.413</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.2263665679697882</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.6638822971646808</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1.293211094585357</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1.919426546576553</v>
+      </c>
+      <c r="L2" t="n">
+        <v>12.17773641243749</v>
+      </c>
+      <c r="M2" t="n">
+        <v>84.08290098419012</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>9.64863735957964</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>-5985.534406047734</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>117.3173695326476</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>2.159399899675312e-09</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.9375264351296223</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B3" t="n">
+        <v>119.131</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.6776353211531023</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1236.592133890851</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2.741966629633271</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2.84088e-07</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-80.55500000000001</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.551288982656042</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1.208455215704146</v>
+      </c>
+      <c r="K3" t="n">
+        <v>2.165342448054973</v>
+      </c>
+      <c r="L3" t="n">
+        <v>16.81992527759554</v>
+      </c>
+      <c r="M3" t="n">
+        <v>85.38886327510725</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>12.39868361975104</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>-6817.848939904364</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>-605.8544985072681</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>5.505983538172226e-07</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.8996711595776918</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B4" t="n">
+        <v>108.834</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.6190644126413505</v>
+      </c>
+      <c r="D4" t="n">
+        <v>965.3796183233129</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2.140591570837432</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2.80278e-07</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-81.40900000000001</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.06199560623364564</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.7243401381040071</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1.279808995644383</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2.217647669909073</v>
+      </c>
+      <c r="L4" t="n">
+        <v>20.02949988549155</v>
+      </c>
+      <c r="M4" t="n">
+        <v>86.04545356274795</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>14.46557039402282</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>-7736.704617183487</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>-388.7452794521322</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>4.957459364143968e-07</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.9133416400144007</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B5" t="n">
+        <v>104.93</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.5968578644399444</v>
+      </c>
+      <c r="D5" t="n">
+        <v>982.5105099527518</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2.178576878924416</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2.77441e-07</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-81.84999999999999</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.1304386430923389</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.8333450844142718</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1.58987825015285</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2.428335461406494</v>
+      </c>
+      <c r="L5" t="n">
+        <v>22.85414558827944</v>
+      </c>
+      <c r="M5" t="n">
+        <v>86.37443048586742</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>15.78215113178104</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>-8310.46069717217</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>-413.7158403279214</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>4.690264968634016e-07</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.9201326074386598</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B6" t="n">
+        <v>102.597</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.5835874041546265</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1073.324834721886</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2.379944687424179</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2.75699e-07</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-82.163</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.3225886190486932</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.9964592631470622</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1.757523654227942</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2.356567263269973</v>
+      </c>
+      <c r="L6" t="n">
+        <v>24.3758272005061</v>
+      </c>
+      <c r="M6" t="n">
+        <v>86.62510124543059</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>16.95739764315634</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>-8818.705085613392</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>-502.6845875195099</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>4.517866403552614e-07</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.9248175910051529</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>9</v>
+      </c>
+      <c r="B7" t="n">
+        <v>98.27800000000002</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.5590202725762782</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1097.665248777675</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2.433916082893463</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2.74648e-07</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-82.39400000000001</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.540467568610694</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.127642102626859</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1.53951753724565</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2.347522683678398</v>
+      </c>
+      <c r="L7" t="n">
+        <v>25.41078565163649</v>
+      </c>
+      <c r="M7" t="n">
+        <v>86.73955288943954</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>17.55400973710982</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>-8990.702303374113</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>-532.1645451137668</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.58174486006174e-06</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.8362733134808182</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B8" t="n">
+        <v>95.08199999999999</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.5408409364974629</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1103.259195102659</v>
+      </c>
+      <c r="E8" t="n">
+        <v>2.446319860768714</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2.7384e-07</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-82.613</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.3803279486330484</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.010963154993154</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1.642251469051127</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2.451493371399361</v>
+      </c>
+      <c r="L8" t="n">
+        <v>27.78480334468127</v>
+      </c>
+      <c r="M8" t="n">
+        <v>86.83360894459653</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>18.07655388747258</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>-9110.545228760877</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>-545.1034649052626</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>4.294520224850721e-07</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.9314217339739586</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>12</v>
+      </c>
+      <c r="B9" t="n">
+        <v>89.55800000000005</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.5094195808969081</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1002.1039226646</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2.222022476178443</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2.73324e-07</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-82.708</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.1068662504930662</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.7170961197232232</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.338398208661787</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2.16448637641308</v>
+      </c>
+      <c r="L9" t="n">
+        <v>26.71414690001193</v>
+      </c>
+      <c r="M9" t="n">
+        <v>86.75578467338379</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>17.64202714084421</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>-8721.405395930318</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>-462.4547437242704</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>4.240480861238635e-07</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0.9330733490802984</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B10" t="n">
+        <v>87.34300000000002</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.496820322632022</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1082.36022321853</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2.399979372317102</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2.73061e-07</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-82.834</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.4841724412663034</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.8789033583930339</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.561033290041177</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2.231645556879763</v>
+      </c>
+      <c r="L10" t="n">
+        <v>27.03093700069163</v>
+      </c>
+      <c r="M10" t="n">
+        <v>86.88368510113125</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>18.3676141474842</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>-8980.525195986682</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>-541.8561788930012</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>4.183775092728076e-07</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0.9349609149016714</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>15</v>
+      </c>
+      <c r="B11" t="n">
+        <v>83.30200000000002</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.4738344975085891</v>
+      </c>
+      <c r="D11" t="n">
+        <v>999.4223982786633</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2.216076578431503</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2.72774e-07</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-82.97799999999999</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.08315385594277053</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.7646753249610921</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1.466099350365916</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2.373176587681221</v>
+      </c>
+      <c r="L11" t="n">
+        <v>28.8931875628394</v>
+      </c>
+      <c r="M11" t="n">
+        <v>86.86890944232314</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>18.28076554225826</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>-8798.41393372084</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>-473.338552547877</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>4.123806631877916e-07</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0.9369762446723572</v>
       </c>
     </row>
   </sheetData>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 45.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 45.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1124,6 +1124,566 @@
         <v>3.755259302377786e-07</v>
       </c>
       <c r="AD11" t="n">
+        <v>0.9445047767300254</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B12" t="n">
+        <v>107.8630000000001</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1222.881998380931</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2.64063e-07</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-82.324</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.4924579293767634</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1.000017234335748</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.556010042998564</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2.39825309898576</v>
+      </c>
+      <c r="L12" t="n">
+        <v>25.68537325146842</v>
+      </c>
+      <c r="M12" t="n">
+        <v>86.78874740645739</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>17.82350396332755</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-9599.322190146206</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-617.2483626631367</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>4.26998522159083e-07</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.9268023972871524</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>101.1759999999999</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.938004691135977</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1147.345740482078</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.9382309511474847</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2.631e-07</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-82.649</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.407323822046795</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.9823134680563622</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.596583349940528</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2.523729445795916</v>
+      </c>
+      <c r="L13" t="n">
+        <v>28.66566303413096</v>
+      </c>
+      <c r="M13" t="n">
+        <v>86.94581505152189</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>18.7419890496679</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-9898.387345826271</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>-561.4886336034604</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.643783049026739e-06</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.8272660883542078</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B14" t="n">
+        <v>97.33999999999997</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.9024410594921328</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1134.818910529744</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.9279872563601553</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2.6245e-07</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-82.824</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.3142806937342108</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.9343354005925628</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.48290245110116</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2.273660235496234</v>
+      </c>
+      <c r="L14" t="n">
+        <v>29.27699521926877</v>
+      </c>
+      <c r="M14" t="n">
+        <v>87.01709364146427</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>19.19068129526032</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-9985.674568337905</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>-558.4113668681046</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.351528210561691e-06</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.8650685767984596</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" t="n">
+        <v>94.54599999999999</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.8765378303959647</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1165.483636117922</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.9530630409647014</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2.62147e-07</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-82.971</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.3739565358041708</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.8913275871117444</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.557116324463475</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2.389893365360842</v>
+      </c>
+      <c r="L15" t="n">
+        <v>30.37546324776115</v>
+      </c>
+      <c r="M15" t="n">
+        <v>87.09139200699965</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>19.68176973497182</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-10105.93471235811</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>-593.2626273972858</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>3.588868257132026e-07</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.9999755699729936</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B16" t="n">
+        <v>90.08799999999997</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.8352076244866166</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1086.965916765387</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.8888559306658417</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2.61719e-07</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-83.101</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.1972190940341653</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.7763665983516556</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.288509687719331</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2.056046379524496</v>
+      </c>
+      <c r="L16" t="n">
+        <v>30.40908416249143</v>
+      </c>
+      <c r="M16" t="n">
+        <v>87.05450951659333</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>19.43489429606497</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-9813.14555680553</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>-530.1304184541336</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>3.916622015651721e-07</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.9384871503513036</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" t="n">
+        <v>88.339</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.8189926109972832</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1229.580759139218</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1.005477847222508</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2.61617e-07</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-83.221</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.2593616930651583</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.8290005632814033</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.408463332803359</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2.172567118839585</v>
+      </c>
+      <c r="L17" t="n">
+        <v>31.3206243398632</v>
+      </c>
+      <c r="M17" t="n">
+        <v>87.196205066275</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>20.41876762439064</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-10212.2407737871</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>-664.8064308613309</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>3.870928133099566e-07</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.940198540333773</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B18" t="n">
+        <v>86.74099999999999</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.8041775214855876</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1281.912940571164</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1.048271985578648</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2.61431e-07</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-83.304</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.6319168900716478</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.8630939836095451</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.493971249342138</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2.44281625196101</v>
+      </c>
+      <c r="L18" t="n">
+        <v>32.69220281666847</v>
+      </c>
+      <c r="M18" t="n">
+        <v>87.27092498551941</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>20.97869894262035</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-10390.98297151223</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>-717.6859974801409</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>3.837286484855732e-07</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.9414129971822996</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" t="n">
+        <v>75.55000000000001</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.7004255398051229</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1149.524458071477</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.9400125765146777</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2.6122e-07</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-83.35299999999999</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.7986966776689637</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1.791538494521635</v>
+      </c>
+      <c r="L19" t="n">
+        <v>30.10285341389156</v>
+      </c>
+      <c r="M19" t="n">
+        <v>86.75953266883968</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>17.66247594942411</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-8486.174645203593</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>-604.3494735023893</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>3.8122141057872e-07</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.9423048378955623</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B20" t="n">
+        <v>81.28800000000001</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.7536226509553783</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1177.411325716256</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.9628167944864039</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2.61242e-07</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-83.407</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.1202899337352879</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.000500774910222</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.456274285465032</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2.337962751536113</v>
+      </c>
+      <c r="L20" t="n">
+        <v>32.18886212165614</v>
+      </c>
+      <c r="M20" t="n">
+        <v>87.24643305816566</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>20.79181762396264</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-10047.85629252543</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>-635.2635025417703</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>3.792017074982107e-07</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.943130388630344</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" t="n">
+        <v>80.596</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.7472071053095126</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1385.583051570613</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1.133047222385393</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2.61085e-07</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-83.509</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.2858294528696655</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.9502442901448466</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1.518586120627437</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2.44874768511965</v>
+      </c>
+      <c r="L21" t="n">
+        <v>33.15944773050924</v>
+      </c>
+      <c r="M21" t="n">
+        <v>87.36798349326666</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>21.7534620588097</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-10438.64831531955</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>-828.4386767217325</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>3.755259302377786e-07</v>
+      </c>
+      <c r="AD21" t="n">
         <v>0.9445047767300254</v>
       </c>
     </row>
@@ -1138,7 +1698,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2456,6 +3016,1182 @@
         <v>3.73254825807647e-07</v>
       </c>
       <c r="AD22" t="n">
+        <v>0.9486615081080416</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B23" t="n">
+        <v>123.117</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>321.402776633894</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>2.72644e-07</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-81.66800000000001</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.3324985672437418</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.7394414943525438</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.361079132107822</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2.201343800322297</v>
+      </c>
+      <c r="L23" t="n">
+        <v>22.28309065067079</v>
+      </c>
+      <c r="M23" t="n">
+        <v>86.23659232903233</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>15.20254047159887</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-8360.98103653289</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>205.4262152339841</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>3.054023043952894e-09</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.9570999626100983</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B24" t="n">
+        <v>103.567</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.8412079566591129</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1179.625519179557</v>
+      </c>
+      <c r="E24" t="n">
+        <v>3.670240598211305</v>
+      </c>
+      <c r="F24" t="n">
+        <v>2.70903e-07</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-82.346</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.6659572099321607</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1.048833820776525</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.586446990618198</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2.345168482408644</v>
+      </c>
+      <c r="L24" t="n">
+        <v>25.39547829567944</v>
+      </c>
+      <c r="M24" t="n">
+        <v>86.70513271440362</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>17.37023136307375</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-9099.215171842827</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>-593.3444619426984</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>4.383445486220268e-07</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.9266667270381466</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B25" t="n">
+        <v>95.75399999999996</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.7777479958088643</v>
+      </c>
+      <c r="D25" t="n">
+        <v>966.7639839950861</v>
+      </c>
+      <c r="E25" t="n">
+        <v>3.007951561962749</v>
+      </c>
+      <c r="F25" t="n">
+        <v>2.70055e-07</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-82.53400000000001</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.2065994235832161</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.6908149256288911</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1.464748598532261</v>
+      </c>
+      <c r="K25" t="n">
+        <v>2.374217128379251</v>
+      </c>
+      <c r="L25" t="n">
+        <v>26.27564491304693</v>
+      </c>
+      <c r="M25" t="n">
+        <v>86.68945551792773</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>17.28779197790907</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-8852.895054964198</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>-414.1502404941225</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.329909910929096e-06</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.8414651222984563</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B26" t="n">
+        <v>96.40000000000003</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.7829950372409985</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1160.211078560553</v>
+      </c>
+      <c r="E26" t="n">
+        <v>3.609835268729292</v>
+      </c>
+      <c r="F26" t="n">
+        <v>2.69345e-07</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-82.68600000000001</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.6912967279279655</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1.198611813223144</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1.778678856535083</v>
+      </c>
+      <c r="K26" t="n">
+        <v>2.59988802737649</v>
+      </c>
+      <c r="L26" t="n">
+        <v>28.11678770011679</v>
+      </c>
+      <c r="M26" t="n">
+        <v>86.9522145457658</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>18.78141653552514</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-9578.119360771974</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>-593.4682633410224</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.369126947661995e-06</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.8634281974415232</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B27" t="n">
+        <v>93.21000000000004</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.7570847242866543</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1160.025521391174</v>
+      </c>
+      <c r="E27" t="n">
+        <v>3.609257933426458</v>
+      </c>
+      <c r="F27" t="n">
+        <v>2.69164e-07</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-82.818</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.5585690423399794</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1.031679730211049</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1.876525158797712</v>
+      </c>
+      <c r="K27" t="n">
+        <v>2.557353394756368</v>
+      </c>
+      <c r="L27" t="n">
+        <v>28.68694396703544</v>
+      </c>
+      <c r="M27" t="n">
+        <v>87.00985416806904</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>19.1441343721385</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-9651.181865898097</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>-599.1738908571873</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>4.145001707610471e-07</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.9341455687278762</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B28" t="n">
+        <v>89.90199999999999</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.7302159734236537</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1075.754610710713</v>
+      </c>
+      <c r="E28" t="n">
+        <v>3.347060725415238</v>
+      </c>
+      <c r="F28" t="n">
+        <v>2.68755e-07</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-82.883</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.2829153481239688</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1.030556376765423</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.715617314790859</v>
+      </c>
+      <c r="K28" t="n">
+        <v>2.399803562555813</v>
+      </c>
+      <c r="L28" t="n">
+        <v>28.28943105105307</v>
+      </c>
+      <c r="M28" t="n">
+        <v>86.9539854200394</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>18.79235618526171</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-9335.073827635899</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>-529.3180006892528</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>4.107660705107558e-07</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.935303220497161</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" t="n">
+        <v>86.86799999999999</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.7055727478739734</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1056.271900996974</v>
+      </c>
+      <c r="E29" t="n">
+        <v>3.286442986148066</v>
+      </c>
+      <c r="F29" t="n">
+        <v>2.68598e-07</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-82.98399999999999</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.3906853287052123</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.8914368621230316</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.468883588348177</v>
+      </c>
+      <c r="K29" t="n">
+        <v>2.182733189467243</v>
+      </c>
+      <c r="L29" t="n">
+        <v>28.13442189504315</v>
+      </c>
+      <c r="M29" t="n">
+        <v>86.97806735020897</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>18.94239482524619</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-9296.228995134883</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>-517.90592141103</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>4.064278669403648e-07</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.9368215071807625</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B30" t="n">
+        <v>83.68000000000001</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.6796786796299454</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1036.684282741261</v>
+      </c>
+      <c r="E30" t="n">
+        <v>3.225498838555885</v>
+      </c>
+      <c r="F30" t="n">
+        <v>2.6826e-07</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-83.051</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.1343551314808551</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.6300344017212653</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.495542216537642</v>
+      </c>
+      <c r="K30" t="n">
+        <v>2.470749574069002</v>
+      </c>
+      <c r="L30" t="n">
+        <v>29.05839633211262</v>
+      </c>
+      <c r="M30" t="n">
+        <v>86.92254155876262</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>18.59998158003243</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-9000.956083669631</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>-505.6383923216868</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>4.030579782766424e-07</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.9379010583485747</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B31" t="n">
+        <v>83.89999999999998</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.6814655977647276</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1185.00606703777</v>
+      </c>
+      <c r="E31" t="n">
+        <v>3.686981423896022</v>
+      </c>
+      <c r="F31" t="n">
+        <v>2.67996e-07</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-83.143</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.3960606103374492</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1.107020323807981</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1.75865263571295</v>
+      </c>
+      <c r="K31" t="n">
+        <v>2.651354532909224</v>
+      </c>
+      <c r="L31" t="n">
+        <v>30.14161298387466</v>
+      </c>
+      <c r="M31" t="n">
+        <v>87.11025620574966</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>19.81047228239968</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-9552.484276580579</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>-643.8866275498301</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>3.991627777082239e-07</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.9392278592739676</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B32" t="n">
+        <v>80.892</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.657033553449158</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1076.417096395307</v>
+      </c>
+      <c r="E32" t="n">
+        <v>3.349121957404371</v>
+      </c>
+      <c r="F32" t="n">
+        <v>2.67899e-07</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-83.182</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.3126472516318443</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.8809811551360011</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1.651890857807161</v>
+      </c>
+      <c r="K32" t="n">
+        <v>2.515392565456309</v>
+      </c>
+      <c r="L32" t="n">
+        <v>29.56037493256354</v>
+      </c>
+      <c r="M32" t="n">
+        <v>87.0544119031679</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>19.43424910969891</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>-9255.033440822186</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>-550.8676979068796</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>3.972024883721081e-07</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.9399227166687285</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B33" t="n">
+        <v>79.81299999999999</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.6482695322335662</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1102.362485309878</v>
+      </c>
+      <c r="E33" t="n">
+        <v>3.429847423395367</v>
+      </c>
+      <c r="F33" t="n">
+        <v>2.67688e-07</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-83.258</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.3193440510416889</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1.123988181618426</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1.585267034946885</v>
+      </c>
+      <c r="K33" t="n">
+        <v>2.58428996961779</v>
+      </c>
+      <c r="L33" t="n">
+        <v>30.44305894452784</v>
+      </c>
+      <c r="M33" t="n">
+        <v>87.11923817397374</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>19.87234434365108</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>-9391.598627738556</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>-578.5316398579125</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>3.941020955067442e-07</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.9409913259040812</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B34" t="n">
+        <v>79.834</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.6484401016918865</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1356.556854621175</v>
+      </c>
+      <c r="E34" t="n">
+        <v>4.220737819469472</v>
+      </c>
+      <c r="F34" t="n">
+        <v>2.67488e-07</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-83.316</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.5158624171801967</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1.280873663322011</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1.604421231636899</v>
+      </c>
+      <c r="K34" t="n">
+        <v>2.575176920347626</v>
+      </c>
+      <c r="L34" t="n">
+        <v>29.97653689912666</v>
+      </c>
+      <c r="M34" t="n">
+        <v>87.23740857856555</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>20.72379271336019</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>-9755.401357545546</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>-812.0160587446607</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>3.916201313707369e-07</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.9418383531316091</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B35" t="n">
+        <v>79.64600000000002</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.6469130989221635</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1474.992826046468</v>
+      </c>
+      <c r="E35" t="n">
+        <v>4.589234858187347</v>
+      </c>
+      <c r="F35" t="n">
+        <v>2.67391e-07</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-83.373</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.9861774126466745</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1.304360260794313</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1.874176311080603</v>
+      </c>
+      <c r="K35" t="n">
+        <v>2.810718427190251</v>
+      </c>
+      <c r="L35" t="n">
+        <v>31.00984725168055</v>
+      </c>
+      <c r="M35" t="n">
+        <v>87.29760709754886</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>21.18614449045294</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>-9907.355670692714</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>-922.9449034751918</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>3.894681968248368e-07</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.9426184644425313</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>20</v>
+      </c>
+      <c r="B36" t="n">
+        <v>74.56900000000002</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.6056759017844815</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1137.799362420583</v>
+      </c>
+      <c r="E36" t="n">
+        <v>3.540104333686689</v>
+      </c>
+      <c r="F36" t="n">
+        <v>2.67161e-07</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-83.43300000000001</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.1390085439308156</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.641765336270207</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1.526971169942958</v>
+      </c>
+      <c r="K36" t="n">
+        <v>2.211514049010288</v>
+      </c>
+      <c r="L36" t="n">
+        <v>29.73296890354945</v>
+      </c>
+      <c r="M36" t="n">
+        <v>87.14788086539058</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>20.07224940566364</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>-9230.947039114715</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>-622.2631509525115</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>3.870198928759991e-07</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.943446300867181</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B37" t="n">
+        <v>72.36599999999999</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.5877823533711833</v>
+      </c>
+      <c r="D37" t="n">
+        <v>1152.38370216259</v>
+      </c>
+      <c r="E37" t="n">
+        <v>3.585481476643423</v>
+      </c>
+      <c r="F37" t="n">
+        <v>2.67154e-07</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-83.488</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.7845881925667021</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1.367119214563877</v>
+      </c>
+      <c r="K37" t="n">
+        <v>2.248802712732471</v>
+      </c>
+      <c r="L37" t="n">
+        <v>30.00706656580175</v>
+      </c>
+      <c r="M37" t="n">
+        <v>87.11724320036751</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>19.85856873896583</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>-9039.394937021554</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>-638.9565004737317</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>3.852111742265167e-07</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.9441457628753107</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B38" t="n">
+        <v>74.714</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.6068536432824061</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1362.539900844115</v>
+      </c>
+      <c r="E38" t="n">
+        <v>4.239353234947835</v>
+      </c>
+      <c r="F38" t="n">
+        <v>2.67023e-07</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-83.565</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.5472777647383407</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1.097982380007562</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1.639998117077041</v>
+      </c>
+      <c r="K38" t="n">
+        <v>2.663054796785869</v>
+      </c>
+      <c r="L38" t="n">
+        <v>31.83879823197438</v>
+      </c>
+      <c r="M38" t="n">
+        <v>87.32277914582281</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>21.38563744612662</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>-9725.303200891476</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>-832.9856661114804</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>3.824649422397493e-07</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.9451590446040621</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B39" t="n">
+        <v>71.79700000000003</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.5831607332862238</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1243.914973409662</v>
+      </c>
+      <c r="E39" t="n">
+        <v>3.870268285910269</v>
+      </c>
+      <c r="F39" t="n">
+        <v>2.66962e-07</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-83.611</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.2356551103359827</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1.103637347044258</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1.725787522674725</v>
+      </c>
+      <c r="K39" t="n">
+        <v>2.554197738215202</v>
+      </c>
+      <c r="L39" t="n">
+        <v>31.97879886202891</v>
+      </c>
+      <c r="M39" t="n">
+        <v>87.28332486828249</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>21.07459792476552</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>-9479.464339063117</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>-729.6039828480266</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>3.80791102093921e-07</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.9457842968523634</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B40" t="n">
+        <v>72.14000000000004</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.5859467011054528</v>
+      </c>
+      <c r="D40" t="n">
+        <v>259.3172291982016</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.8068294615064473</v>
+      </c>
+      <c r="F40" t="n">
+        <v>2.66831e-07</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-83.63800000000001</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.6330550368265632</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1.105393231135166</v>
+      </c>
+      <c r="J40" t="n">
+        <v>1.821768013626504</v>
+      </c>
+      <c r="K40" t="n">
+        <v>2.646129527231523</v>
+      </c>
+      <c r="L40" t="n">
+        <v>31.71668794179721</v>
+      </c>
+      <c r="M40" t="n">
+        <v>87.35643336487306</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>21.65828387251652</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>-9689.716375442036</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>182.7074024379407</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>2.528419754708605e-09</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.9886619915612028</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B41" t="n">
+        <v>67.97899999999998</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.5521495812925914</v>
+      </c>
+      <c r="D41" t="n">
+        <v>1271.407339760744</v>
+      </c>
+      <c r="E41" t="n">
+        <v>3.955806956854605</v>
+      </c>
+      <c r="F41" t="n">
+        <v>2.6676e-07</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-83.705</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.2173800541936653</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.5995250439238596</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1.575355738175434</v>
+      </c>
+      <c r="K41" t="n">
+        <v>2.35627503580692</v>
+      </c>
+      <c r="L41" t="n">
+        <v>31.15370010076809</v>
+      </c>
+      <c r="M41" t="n">
+        <v>87.23143930517391</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>20.67904089367934</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>-9112.604359247525</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>-761.7503826281744</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>3.773386297485312e-07</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.9470588941999227</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B42" t="n">
+        <v>67.697</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.5498590771380069</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1287.595040004948</v>
+      </c>
+      <c r="E42" t="n">
+        <v>4.006172732824993</v>
+      </c>
+      <c r="F42" t="n">
+        <v>2.66757e-07</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-83.786</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.2509158592886808</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.8856038118946071</v>
+      </c>
+      <c r="J42" t="n">
+        <v>1.654938574216668</v>
+      </c>
+      <c r="K42" t="n">
+        <v>2.552729536040805</v>
+      </c>
+      <c r="L42" t="n">
+        <v>33.03580469276218</v>
+      </c>
+      <c r="M42" t="n">
+        <v>87.32353763478508</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>21.39170680144206</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>-9365.318451994282</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>-780.2273909206376</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>3.749404704529664e-07</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.9480103435088878</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>30</v>
+      </c>
+      <c r="B43" t="n">
+        <v>67.423</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.547633551824687</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1410.086256220752</v>
+      </c>
+      <c r="E43" t="n">
+        <v>4.387287101215569</v>
+      </c>
+      <c r="F43" t="n">
+        <v>2.66694e-07</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-83.834</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.4855452567875742</v>
+      </c>
+      <c r="I43" t="n">
+        <v>1.096834607655973</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1.769976167413208</v>
+      </c>
+      <c r="K43" t="n">
+        <v>2.541987523060316</v>
+      </c>
+      <c r="L43" t="n">
+        <v>32.85722396609565</v>
+      </c>
+      <c r="M43" t="n">
+        <v>87.38723037836647</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>21.91393308703115</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>-9532.753076700101</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>-895.0446830198503</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>3.73254825807647e-07</v>
+      </c>
+      <c r="AD43" t="n">
         <v>0.9486615081080416</v>
       </c>
     </row>
@@ -2470,7 +4206,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3788,6 +5524,1182 @@
         <v>3.594996674257935e-07</v>
       </c>
       <c r="AD22" t="n">
+        <v>0.9518836743788911</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B23" t="n">
+        <v>127.235</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>311.8203438103901</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>2.76249e-07</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-80.96899999999999</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.04343039752405262</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.8418040515083883</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.314491415637336</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2.038407936820749</v>
+      </c>
+      <c r="L23" t="n">
+        <v>18.18260956816588</v>
+      </c>
+      <c r="M23" t="n">
+        <v>85.87600810476651</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>13.86928060524225</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-7751.373462847805</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>224.8049189095018</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>3.256997233637986e-09</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.9551582904690579</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B24" t="n">
+        <v>103.22</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.8112547648052817</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1142.125530947138</v>
+      </c>
+      <c r="E24" t="n">
+        <v>3.662767852124604</v>
+      </c>
+      <c r="F24" t="n">
+        <v>2.69663e-07</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-82.26900000000001</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.1914147981042067</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.8150916579859183</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.315918381934325</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2.255889295085648</v>
+      </c>
+      <c r="L24" t="n">
+        <v>25.20742870161399</v>
+      </c>
+      <c r="M24" t="n">
+        <v>86.68721616396195</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>17.27607983040949</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-9142.691276745545</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>-553.9258759056572</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>4.361934590012305e-07</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.9268027198490548</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B25" t="n">
+        <v>98.11100000000005</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.7711007191417458</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1093.490723263717</v>
+      </c>
+      <c r="E25" t="n">
+        <v>3.506797247098927</v>
+      </c>
+      <c r="F25" t="n">
+        <v>2.67466e-07</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-82.681</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.2646475862435225</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.8565699563484701</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1.522194353988355</v>
+      </c>
+      <c r="K25" t="n">
+        <v>2.446073873217861</v>
+      </c>
+      <c r="L25" t="n">
+        <v>28.77049235878962</v>
+      </c>
+      <c r="M25" t="n">
+        <v>86.97475332453027</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>18.92160570492989</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-9826.40835573673</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>-523.5999161736368</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.663103739688245e-06</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.8227840406122269</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B26" t="n">
+        <v>94.24499999999995</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.7407159979565366</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1110.501712220133</v>
+      </c>
+      <c r="E26" t="n">
+        <v>3.561351060838417</v>
+      </c>
+      <c r="F26" t="n">
+        <v>2.66165e-07</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-82.895</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.3351661003685886</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.8756985218762945</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1.568373431022961</v>
+      </c>
+      <c r="K26" t="n">
+        <v>2.506700597572104</v>
+      </c>
+      <c r="L26" t="n">
+        <v>30.56301410612685</v>
+      </c>
+      <c r="M26" t="n">
+        <v>87.10637500562872</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>19.7838554817209</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-10144.97169018693</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>-546.2286018913619</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>4.05022007432776e-07</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.9359848204513325</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B27" t="n">
+        <v>90.20500000000004</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.7089637285338156</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1073.425280004044</v>
+      </c>
+      <c r="E27" t="n">
+        <v>3.442447875231536</v>
+      </c>
+      <c r="F27" t="n">
+        <v>2.65327e-07</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-83.065</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.1508564917214077</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.799194061895109</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1.418053411067973</v>
+      </c>
+      <c r="K27" t="n">
+        <v>2.272384411112472</v>
+      </c>
+      <c r="L27" t="n">
+        <v>31.22483142127902</v>
+      </c>
+      <c r="M27" t="n">
+        <v>87.093586354596</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>19.69665505777763</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-9944.378389610323</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>-519.5084179558846</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>3.974253091366641e-07</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.9383576063960247</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B28" t="n">
+        <v>88.66500000000002</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.6968601406845601</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1101.46898989985</v>
+      </c>
+      <c r="E28" t="n">
+        <v>3.532383347539456</v>
+      </c>
+      <c r="F28" t="n">
+        <v>2.64548e-07</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-83.139</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.2463480940070178</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.9326952380695922</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.429578443016108</v>
+      </c>
+      <c r="K28" t="n">
+        <v>2.372350245621452</v>
+      </c>
+      <c r="L28" t="n">
+        <v>31.30864612221542</v>
+      </c>
+      <c r="M28" t="n">
+        <v>87.208357009784</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>20.50779169331176</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-10269.29342203443</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>-550.3091909320802</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>3.930978807543943e-07</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.9395936313795407</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" t="n">
+        <v>85.44799999999998</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.6715762172358233</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1016.019246505042</v>
+      </c>
+      <c r="E29" t="n">
+        <v>3.258348169620573</v>
+      </c>
+      <c r="F29" t="n">
+        <v>2.64146e-07</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-83.236</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.105649314740603</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.625763532184045</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.355536378971123</v>
+      </c>
+      <c r="K29" t="n">
+        <v>2.164654493749005</v>
+      </c>
+      <c r="L29" t="n">
+        <v>31.128494022466</v>
+      </c>
+      <c r="M29" t="n">
+        <v>87.15669685568162</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>20.1345885083383</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-9938.273876717878</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>-478.987139726159</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>3.888280687482529e-07</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.9410154735253821</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B30" t="n">
+        <v>86.50400000000002</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.6798758203324557</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1271.782998660311</v>
+      </c>
+      <c r="E30" t="n">
+        <v>4.078576090063097</v>
+      </c>
+      <c r="F30" t="n">
+        <v>2.63749e-07</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-83.346</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.4360353487768501</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1.120755714236871</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.501267766137637</v>
+      </c>
+      <c r="K30" t="n">
+        <v>2.447572537638714</v>
+      </c>
+      <c r="L30" t="n">
+        <v>32.95742830739476</v>
+      </c>
+      <c r="M30" t="n">
+        <v>87.39384097181849</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>21.96959541256436</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-10810.29347620989</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>-714.5158237384464</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>3.844328084949008e-07</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.9425036085232681</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B31" t="n">
+        <v>82.78000000000003</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.6506071442606203</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1116.318859956402</v>
+      </c>
+      <c r="E31" t="n">
+        <v>3.580006507321429</v>
+      </c>
+      <c r="F31" t="n">
+        <v>2.63693e-07</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-83.42400000000001</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.4194633037955159</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.8070032550269018</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1.533721079263632</v>
+      </c>
+      <c r="K31" t="n">
+        <v>2.586691077604846</v>
+      </c>
+      <c r="L31" t="n">
+        <v>34.42595728458807</v>
+      </c>
+      <c r="M31" t="n">
+        <v>87.33204245290545</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>21.45999765158652</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-10413.43311909305</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>-579.5001553026457</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>3.815704047326536e-07</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.9435980953403028</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B32" t="n">
+        <v>81.62599999999998</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.6415373128463078</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1242.480855458714</v>
+      </c>
+      <c r="E32" t="n">
+        <v>3.984604853794385</v>
+      </c>
+      <c r="F32" t="n">
+        <v>2.63424e-07</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-83.505</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.3467271827384857</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.9828524000414398</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1.640047320023245</v>
+      </c>
+      <c r="K32" t="n">
+        <v>2.434250549018704</v>
+      </c>
+      <c r="L32" t="n">
+        <v>34.5404099508481</v>
+      </c>
+      <c r="M32" t="n">
+        <v>87.42074980966801</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>22.19911493592852</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>-10691.8405558676</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>-698.3461184728435</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>3.783203121129007e-07</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.9447429738066498</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B33" t="n">
+        <v>80.48199999999997</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.6325460761582895</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1337.098906904267</v>
+      </c>
+      <c r="E33" t="n">
+        <v>4.288042565039702</v>
+      </c>
+      <c r="F33" t="n">
+        <v>2.63247e-07</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-83.556</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.4731264239234456</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1.152051875921184</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1.74960963116658</v>
+      </c>
+      <c r="K33" t="n">
+        <v>2.73274829544289</v>
+      </c>
+      <c r="L33" t="n">
+        <v>35.06571559413162</v>
+      </c>
+      <c r="M33" t="n">
+        <v>87.46809368424151</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>22.6147702364912</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>-10800.42748218264</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>-788.3820535815166</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>3.76118759844843e-07</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.9455323355146705</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B34" t="n">
+        <v>76.88</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.6042362557472393</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1092.557355971152</v>
+      </c>
+      <c r="E34" t="n">
+        <v>3.503803961666812</v>
+      </c>
+      <c r="F34" t="n">
+        <v>2.6306e-07</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-83.574</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.2326338549762718</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.6982633161749783</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1.307001351254357</v>
+      </c>
+      <c r="K34" t="n">
+        <v>2.189353317246665</v>
+      </c>
+      <c r="L34" t="n">
+        <v>32.80302195309584</v>
+      </c>
+      <c r="M34" t="n">
+        <v>87.34812609311159</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>21.59034050245337</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>-10161.85739058252</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>-571.8582531923878</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>3.749219490547249e-07</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.9459274276735616</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B35" t="n">
+        <v>78.01499999999999</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.6131567571815929</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1381.532500439867</v>
+      </c>
+      <c r="E35" t="n">
+        <v>4.430539981958143</v>
+      </c>
+      <c r="F35" t="n">
+        <v>2.6299e-07</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-83.66200000000001</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.6826025157403757</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1.156997170608582</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1.916585457249574</v>
+      </c>
+      <c r="K35" t="n">
+        <v>2.980092831894027</v>
+      </c>
+      <c r="L35" t="n">
+        <v>35.58622275389752</v>
+      </c>
+      <c r="M35" t="n">
+        <v>87.54149542254061</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>23.29082960857156</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>-10932.96353878005</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>-837.7793837372946</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>3.720419380982052e-07</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.9470460350531218</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>20</v>
+      </c>
+      <c r="B36" t="n">
+        <v>73.17599999999999</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.5751247691279914</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1158.202504931345</v>
+      </c>
+      <c r="E36" t="n">
+        <v>3.71432630333965</v>
+      </c>
+      <c r="F36" t="n">
+        <v>2.62701e-07</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-83.7</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.8436189222789908</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1.499790380353879</v>
+      </c>
+      <c r="K36" t="n">
+        <v>2.287454373889161</v>
+      </c>
+      <c r="L36" t="n">
+        <v>33.92203510076359</v>
+      </c>
+      <c r="M36" t="n">
+        <v>87.37337984018964</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>21.79821705208842</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>-10062.84740667248</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>-639.9241128250131</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>3.700733224478628e-07</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.9477029872925168</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B37" t="n">
+        <v>71.80000000000001</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.5643101347899556</v>
+      </c>
+      <c r="D37" t="n">
+        <v>1187.6540011319</v>
+      </c>
+      <c r="E37" t="n">
+        <v>3.808776510919642</v>
+      </c>
+      <c r="F37" t="n">
+        <v>2.62774e-07</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-83.77200000000001</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.1429580418353057</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.7701281964330922</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1.374109121272471</v>
+      </c>
+      <c r="K37" t="n">
+        <v>2.28657479494855</v>
+      </c>
+      <c r="L37" t="n">
+        <v>34.64877437114263</v>
+      </c>
+      <c r="M37" t="n">
+        <v>87.41554703304374</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>22.15436528183677</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>-10140.97625424357</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>-670.8309867947038</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>3.680147787927724e-07</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.9485785014736785</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B38" t="n">
+        <v>63.90500000000003</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.5022595983809488</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1176.457813671851</v>
+      </c>
+      <c r="E38" t="n">
+        <v>3.772870619330806</v>
+      </c>
+      <c r="F38" t="n">
+        <v>2.62665e-07</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-83.81999999999999</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.6061579902784883</v>
+      </c>
+      <c r="K38" t="n">
+        <v>1.729433694712073</v>
+      </c>
+      <c r="L38" t="n">
+        <v>32.14037607902404</v>
+      </c>
+      <c r="M38" t="n">
+        <v>87.00610323156411</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>19.12010580011504</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>-8545.572680046193</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>-664.7393103211614</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>3.662335020716312e-07</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.949257850232058</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B39" t="n">
+        <v>70.37099999999998</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.553078948402562</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1288.040229298836</v>
+      </c>
+      <c r="E39" t="n">
+        <v>4.130712619834902</v>
+      </c>
+      <c r="F39" t="n">
+        <v>2.62561e-07</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-83.878</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.3912048887978243</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.8700773857977739</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1.657233547782414</v>
+      </c>
+      <c r="K39" t="n">
+        <v>2.501819561359755</v>
+      </c>
+      <c r="L39" t="n">
+        <v>35.6105177428725</v>
+      </c>
+      <c r="M39" t="n">
+        <v>87.54195876112072</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>23.29522530219045</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>-10518.96137799515</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>-769.9522465150571</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>3.643023645097892e-07</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.9499978075269191</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B40" t="n">
+        <v>70.33600000000001</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.5528038668605337</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1554.02570976438</v>
+      </c>
+      <c r="E40" t="n">
+        <v>4.983721365881578</v>
+      </c>
+      <c r="F40" t="n">
+        <v>2.62665e-07</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-83.913</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.5333541823910142</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1.075086740893133</v>
+      </c>
+      <c r="J40" t="n">
+        <v>1.811626083946722</v>
+      </c>
+      <c r="K40" t="n">
+        <v>2.572617737686896</v>
+      </c>
+      <c r="L40" t="n">
+        <v>35.61814551247041</v>
+      </c>
+      <c r="M40" t="n">
+        <v>87.61957944655116</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>24.05575344467231</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>-10802.08755314234</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>-1015.472560120132</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>3.633735453588941e-07</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.9504444312633231</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B41" t="n">
+        <v>67.50400000000002</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.530545840374111</v>
+      </c>
+      <c r="D41" t="n">
+        <v>321.7711421805641</v>
+      </c>
+      <c r="E41" t="n">
+        <v>1.031911960100413</v>
+      </c>
+      <c r="F41" t="n">
+        <v>2.62544e-07</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-83.959</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.2908092961987711</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.8500583952511908</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1.679482118302269</v>
+      </c>
+      <c r="K41" t="n">
+        <v>2.599995524394957</v>
+      </c>
+      <c r="L41" t="n">
+        <v>36.11289913370867</v>
+      </c>
+      <c r="M41" t="n">
+        <v>87.54282346394551</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>23.30343316986745</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>-10333.87876575362</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>119.5516867572638</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>2.197145276428801e-09</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.971479365951204</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B42" t="n">
+        <v>65.69799999999998</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.5163516328054385</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1360.205729210209</v>
+      </c>
+      <c r="E42" t="n">
+        <v>4.362145563014692</v>
+      </c>
+      <c r="F42" t="n">
+        <v>2.62416e-07</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-84.01300000000001</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.1072777898928834</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.7640302041180881</v>
+      </c>
+      <c r="J42" t="n">
+        <v>1.46361278669187</v>
+      </c>
+      <c r="K42" t="n">
+        <v>2.205173163820537</v>
+      </c>
+      <c r="L42" t="n">
+        <v>35.41312290823187</v>
+      </c>
+      <c r="M42" t="n">
+        <v>87.52906141133336</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>23.17348346630436</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>-10176.64596798434</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>-846.4309046715292</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>3.599258221389223e-07</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.9517534265592323</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>30</v>
+      </c>
+      <c r="B43" t="n">
+        <v>65.69800000000004</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.5163516328054389</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1436.289351969401</v>
+      </c>
+      <c r="E43" t="n">
+        <v>4.606143827622651</v>
+      </c>
+      <c r="F43" t="n">
+        <v>2.62309e-07</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-84.02</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.2293604959594025</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.8844101444669695</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1.560549621133494</v>
+      </c>
+      <c r="K43" t="n">
+        <v>2.407839855706039</v>
+      </c>
+      <c r="L43" t="n">
+        <v>34.74501701540667</v>
+      </c>
+      <c r="M43" t="n">
+        <v>87.58295513147668</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>23.69082520203667</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>-10345.33052685845</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>-919.8843263028816</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>3.594996674257935e-07</v>
+      </c>
+      <c r="AD43" t="n">
         <v>0.9518836743788911</v>
       </c>
     </row>
@@ -3802,7 +6714,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4504,6 +7416,566 @@
         <v>3.584885292294679e-07</v>
       </c>
       <c r="AD11" t="n">
+        <v>0.9999959218011779</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B12" t="n">
+        <v>176.22</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>442.7387460738697</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2.79854e-07</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-78.821</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.5481798751735231</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.7263531403530465</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.179289579195842</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1.896337896148187</v>
+      </c>
+      <c r="L12" t="n">
+        <v>13.24664818956317</v>
+      </c>
+      <c r="M12" t="n">
+        <v>84.60611152146957</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>10.5909525989069</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-6757.919165589063</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>150.0046541522291</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.663338815567681e-09</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.930935082071441</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>133.565</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.7579446146861876</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1196.766216359756</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2.703097993957996</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2.81243e-07</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-80.351</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.5418256152046087</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.9010682330957922</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.475204226091361</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2.33219979671676</v>
+      </c>
+      <c r="L13" t="n">
+        <v>17.23871188001938</v>
+      </c>
+      <c r="M13" t="n">
+        <v>85.66777575705275</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>13.20027447754708</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-7718.58434488335</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>-546.4129549561276</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>5.584673222971136e-07</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.8960328445951323</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B14" t="n">
+        <v>121.0210000000001</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.686760867097946</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1004.782878100348</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2.269471301101581</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2.78511e-07</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-81.10299999999999</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.0275019636966087</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.5816810453513427</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.475904541060932</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2.069702158372602</v>
+      </c>
+      <c r="L14" t="n">
+        <v>19.65098299046176</v>
+      </c>
+      <c r="M14" t="n">
+        <v>86.06107784966113</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>14.52313237965902</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-8224.407501363354</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>-396.409918092351</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>5.082483036017803e-07</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.9086717044287616</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" t="n">
+        <v>115.665</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.6563670411985015</v>
+      </c>
+      <c r="D15" t="n">
+        <v>968.9229310325121</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2.18847557306595</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2.76359e-07</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-81.548</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.2203867314408416</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.7012511749719063</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.426403407443023</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2.056537876143126</v>
+      </c>
+      <c r="L15" t="n">
+        <v>21.90434294057446</v>
+      </c>
+      <c r="M15" t="n">
+        <v>86.35405494977601</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>15.6937152902109</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-8750.737407184411</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>-374.1297666354274</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>4.812910557211444e-07</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.9156698053745044</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B16" t="n">
+        <v>111.664</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.6336624673703327</v>
+      </c>
+      <c r="D16" t="n">
+        <v>995.1849059884513</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2.247792665118149</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2.74397e-07</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-81.848</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.3164895967107017</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.9415504384226792</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.506193361917312</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2.216134587374894</v>
+      </c>
+      <c r="L16" t="n">
+        <v>23.84829695047509</v>
+      </c>
+      <c r="M16" t="n">
+        <v>86.56163916493065</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>16.64368175398435</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-9159.621420920957</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>-405.2875774307696</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>4.631455767424235e-07</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.9203777368027308</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" t="n">
+        <v>106.525</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.6045000567472478</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1162.349516158448</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2.6253620819636</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2.73123e-07</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-82.081</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.7123332046212697</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.37181600158045</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2.207625158007089</v>
+      </c>
+      <c r="L17" t="n">
+        <v>25.18493337408912</v>
+      </c>
+      <c r="M17" t="n">
+        <v>86.62097055897429</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>16.93662005737464</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-9169.78964253145</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>-561.4111691179689</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>4.500455495922638e-07</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.9239989877368346</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B18" t="n">
+        <v>106.549</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.6046362501418679</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1114.422041441262</v>
+      </c>
+      <c r="E18" t="n">
+        <v>2.517109810974899</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2.71946e-07</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-82.276</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.5263140168972354</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.466862357593779</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.551702448414602</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2.379554499254712</v>
+      </c>
+      <c r="L18" t="n">
+        <v>26.2906876890817</v>
+      </c>
+      <c r="M18" t="n">
+        <v>86.88720245361314</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>18.38840987531621</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-9885.402018134655</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>-526.361471191174</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>4.389724878764684e-07</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.9271133873023493</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" t="n">
+        <v>99.30899999999997</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.5635512427647257</v>
+      </c>
+      <c r="D19" t="n">
+        <v>959.0771913942996</v>
+      </c>
+      <c r="E19" t="n">
+        <v>2.166237312408795</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2.71109e-07</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-82.44199999999999</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.07132121822165173</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.6796286447944158</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.403179545867203</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2.237145134177287</v>
+      </c>
+      <c r="L19" t="n">
+        <v>27.30665783007737</v>
+      </c>
+      <c r="M19" t="n">
+        <v>86.74861304721674</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>17.60303050451797</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-9258.92408894535</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>-395.272394972675</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.172201301024176e-06</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.8860525156364467</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B20" t="n">
+        <v>96.35899999999998</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.546810804675973</v>
+      </c>
+      <c r="D20" t="n">
+        <v>961.2081953427482</v>
+      </c>
+      <c r="E20" t="n">
+        <v>2.171050543614209</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2.70458e-07</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-82.56999999999999</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.1163231533897849</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.6260359228828783</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.327437304529981</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2.16106049180579</v>
+      </c>
+      <c r="L20" t="n">
+        <v>27.57286682831236</v>
+      </c>
+      <c r="M20" t="n">
+        <v>86.80272453991049</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>17.90158382468181</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-9296.456844935376</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>-403.7582045733692</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>9.042976841967091e-07</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.9131653180518182</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" t="n">
+        <v>97.024</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.5505844966519123</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1090.861368925641</v>
+      </c>
+      <c r="E21" t="n">
+        <v>2.46389406529067</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2.69936e-07</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-82.73699999999999</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.2728817483206419</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.9138021539933532</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1.630666832634549</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2.235788488584801</v>
+      </c>
+      <c r="L21" t="n">
+        <v>28.88389101858023</v>
+      </c>
+      <c r="M21" t="n">
+        <v>87.04481260445652</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>19.37100952744106</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-10002.05164744971</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>-525.8263464214272</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>3.584885292294679e-07</v>
+      </c>
+      <c r="AD21" t="n">
         <v>0.9999959218011779</v>
       </c>
     </row>
@@ -4518,7 +7990,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5836,6 +9308,1182 @@
         <v>3.67800067085379e-07</v>
       </c>
       <c r="AD22" t="n">
+        <v>0.9508641339490165</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B23" t="n">
+        <v>122.251</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>371.1302526460128</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>2.76224e-07</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-81.25700000000001</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.330533986844334</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.5877378281273548</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.298060770326512</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2.010056679955588</v>
+      </c>
+      <c r="L23" t="n">
+        <v>19.28371356972924</v>
+      </c>
+      <c r="M23" t="n">
+        <v>85.95626256722102</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>14.14548245783472</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-7763.767418940207</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>154.9282210469704</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>2.775127738980829e-09</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.9423162248084451</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B24" t="n">
+        <v>100.185</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.819502498957064</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1040.947955095718</v>
+      </c>
+      <c r="E24" t="n">
+        <v>2.804804910605287</v>
+      </c>
+      <c r="F24" t="n">
+        <v>2.73656e-07</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-82.15600000000001</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.08386181951354808</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.6501778611598134</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.29584434663318</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2.223420237279577</v>
+      </c>
+      <c r="L24" t="n">
+        <v>23.83488154240947</v>
+      </c>
+      <c r="M24" t="n">
+        <v>86.48127321041933</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>16.26262353659398</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-8434.634266655097</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>-472.4873431757055</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>4.480406649797358e-07</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.9249675534955195</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B25" t="n">
+        <v>96.005</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.7853105496069563</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1013.380858740757</v>
+      </c>
+      <c r="E25" t="n">
+        <v>2.730526146860164</v>
+      </c>
+      <c r="F25" t="n">
+        <v>2.7226e-07</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-82.504</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.1348066623443797</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.740179005066733</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1.480561527749616</v>
+      </c>
+      <c r="K25" t="n">
+        <v>2.313516128215868</v>
+      </c>
+      <c r="L25" t="n">
+        <v>26.24863934026049</v>
+      </c>
+      <c r="M25" t="n">
+        <v>86.78649210241561</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>17.81096882872391</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-9104.597151980255</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>-458.6884857145841</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>9.89915647613028e-07</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.9048746537960295</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B26" t="n">
+        <v>83.81100000000004</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.6855649442540351</v>
+      </c>
+      <c r="D26" t="n">
+        <v>913.260656169433</v>
+      </c>
+      <c r="E26" t="n">
+        <v>2.460755084389493</v>
+      </c>
+      <c r="F26" t="n">
+        <v>2.71316e-07</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-82.673</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.59305345371442</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1.713764778757748</v>
+      </c>
+      <c r="L26" t="n">
+        <v>25.21912274842513</v>
+      </c>
+      <c r="M26" t="n">
+        <v>86.35824109805462</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>15.71180374738322</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-7782.179053414251</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>-375.7026330630589</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>4.214796704370467e-07</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.9328901449854846</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B27" t="n">
+        <v>89.99099999999999</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.7361166779821842</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1089.022814217741</v>
+      </c>
+      <c r="E27" t="n">
+        <v>2.934341262813894</v>
+      </c>
+      <c r="F27" t="n">
+        <v>2.70379e-07</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-82.851</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.3779501970894521</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1.030186041264169</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1.767613475431259</v>
+      </c>
+      <c r="K27" t="n">
+        <v>2.52143372850762</v>
+      </c>
+      <c r="L27" t="n">
+        <v>29.13872742400114</v>
+      </c>
+      <c r="M27" t="n">
+        <v>87.01682231696586</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>19.1889327159228</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-9593.136762940996</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>-539.0461410029877</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>4.129222500315576e-07</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.9354617326991671</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B28" t="n">
+        <v>88.84500000000003</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.7267425215335666</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1123.578190914356</v>
+      </c>
+      <c r="E28" t="n">
+        <v>3.027449750872329</v>
+      </c>
+      <c r="F28" t="n">
+        <v>2.69961e-07</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-82.991</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.448810581471758</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1.128325434466154</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.581702138578309</v>
+      </c>
+      <c r="K28" t="n">
+        <v>2.476534749288193</v>
+      </c>
+      <c r="L28" t="n">
+        <v>30.31672463756461</v>
+      </c>
+      <c r="M28" t="n">
+        <v>87.11128161283676</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>19.81751633429429</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-9806.389472830584</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>-575.7878673236623</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>4.067916761251468e-07</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.9374812448816695</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" t="n">
+        <v>86.53199999999998</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.7078224309003607</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1089.956399068956</v>
+      </c>
+      <c r="E29" t="n">
+        <v>2.9368567808687</v>
+      </c>
+      <c r="F29" t="n">
+        <v>2.69501e-07</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-83.08</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.4950521832648156</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.9881042457549121</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.67893185350079</v>
+      </c>
+      <c r="K29" t="n">
+        <v>2.517252900989067</v>
+      </c>
+      <c r="L29" t="n">
+        <v>30.77767099983682</v>
+      </c>
+      <c r="M29" t="n">
+        <v>87.15781820780296</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>20.14254544709857</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-9869.027485010618</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>-550.5535689678708</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>4.024624242343295e-07</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.9388505881348892</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B30" t="n">
+        <v>84.29000000000002</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.6894831126125761</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1140.983223647905</v>
+      </c>
+      <c r="E30" t="n">
+        <v>3.074347120756509</v>
+      </c>
+      <c r="F30" t="n">
+        <v>2.69065e-07</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-83.175</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.4777027867347912</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.956899369371179</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.699034982422144</v>
+      </c>
+      <c r="K30" t="n">
+        <v>2.490957032654544</v>
+      </c>
+      <c r="L30" t="n">
+        <v>31.46402998335893</v>
+      </c>
+      <c r="M30" t="n">
+        <v>87.21211455630632</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>20.53547611323334</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-9966.373567261111</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>-601.8452908097837</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>3.981809757220652e-07</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.9402256101603299</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B31" t="n">
+        <v>82.62300000000005</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.6758472323334783</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1114.760587997812</v>
+      </c>
+      <c r="E31" t="n">
+        <v>3.00369096846729</v>
+      </c>
+      <c r="F31" t="n">
+        <v>2.68862e-07</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-83.27500000000001</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.5569813971787919</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.9256174962347529</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1.624419420570391</v>
+      </c>
+      <c r="K31" t="n">
+        <v>2.511422546735022</v>
+      </c>
+      <c r="L31" t="n">
+        <v>31.88114884056025</v>
+      </c>
+      <c r="M31" t="n">
+        <v>87.25805920057836</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>20.88011291202754</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-10037.10526332246</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>-582.950222603053</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>3.942594878233831e-07</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.9416011267882688</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79.98599999999999</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.6542768566310296</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1059.935901410297</v>
+      </c>
+      <c r="E32" t="n">
+        <v>2.855967396495895</v>
+      </c>
+      <c r="F32" t="n">
+        <v>2.685e-07</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-83.33</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.3114787340900936</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.9543286886739243</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1.720521367487621</v>
+      </c>
+      <c r="K32" t="n">
+        <v>2.638531994005457</v>
+      </c>
+      <c r="L32" t="n">
+        <v>32.48496036065949</v>
+      </c>
+      <c r="M32" t="n">
+        <v>87.23514555078835</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>20.70680400200393</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>-9852.044214779651</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>-537.6712598958597</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>3.915712377291921e-07</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.9424435530314343</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B33" t="n">
+        <v>78.154</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.6392912941407434</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1038.133128703909</v>
+      </c>
+      <c r="E33" t="n">
+        <v>2.797220440269765</v>
+      </c>
+      <c r="F33" t="n">
+        <v>2.68248e-07</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-83.396</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.2604359614596863</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.6804501382612789</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1.486805657384116</v>
+      </c>
+      <c r="K33" t="n">
+        <v>2.327269215728609</v>
+      </c>
+      <c r="L33" t="n">
+        <v>31.64516494426261</v>
+      </c>
+      <c r="M33" t="n">
+        <v>87.22943828442875</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>20.66408230488827</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>-9738.146833238899</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>-521.6903502515428</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>3.887829210702251e-07</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.9433874120046737</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B34" t="n">
+        <v>78.22499999999997</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.6398720664861636</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1107.335620098692</v>
+      </c>
+      <c r="E34" t="n">
+        <v>2.983684601844835</v>
+      </c>
+      <c r="F34" t="n">
+        <v>2.68049e-07</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-83.486</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.2269760579253861</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.9987665889543645</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1.602335496143361</v>
+      </c>
+      <c r="K34" t="n">
+        <v>2.626349416462623</v>
+      </c>
+      <c r="L34" t="n">
+        <v>33.86317524998702</v>
+      </c>
+      <c r="M34" t="n">
+        <v>87.3222287501108</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>21.38123538406983</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>-10018.55328220722</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>-587.8074351467726</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>3.855688000858838e-07</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.944520693151338</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B35" t="n">
+        <v>77.61399999999998</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.6348741523586718</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1232.241741846284</v>
+      </c>
+      <c r="E35" t="n">
+        <v>3.320240624580951</v>
+      </c>
+      <c r="F35" t="n">
+        <v>2.6773e-07</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-83.53700000000001</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.6305025851687559</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.9964186962867626</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1.912712004248301</v>
+      </c>
+      <c r="K35" t="n">
+        <v>2.683603967450868</v>
+      </c>
+      <c r="L35" t="n">
+        <v>33.97227132522889</v>
+      </c>
+      <c r="M35" t="n">
+        <v>87.41672760765853</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>22.16450373431897</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>-10335.15395494345</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>-704.3154703716659</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>3.831347269447549e-07</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.9453085696818081</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>20</v>
+      </c>
+      <c r="B36" t="n">
+        <v>70.72300000000001</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.5785065152841288</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1502.298777220812</v>
+      </c>
+      <c r="E36" t="n">
+        <v>4.047901690875407</v>
+      </c>
+      <c r="F36" t="n">
+        <v>2.67571e-07</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-83.574</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.01892620484260812</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.208705692684379</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1.0716699838771</v>
+      </c>
+      <c r="K36" t="n">
+        <v>1.940687293254324</v>
+      </c>
+      <c r="L36" t="n">
+        <v>31.05210348518892</v>
+      </c>
+      <c r="M36" t="n">
+        <v>87.08785412480184</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>19.65781776517757</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>-8970.084037679289</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>-952.4806994721499</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>3.815828381615512e-07</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.9458411130672405</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B37" t="n">
+        <v>73.56799999999998</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.6017783085618932</v>
+      </c>
+      <c r="D37" t="n">
+        <v>1085.282837682996</v>
+      </c>
+      <c r="E37" t="n">
+        <v>2.924264001507169</v>
+      </c>
+      <c r="F37" t="n">
+        <v>2.67374e-07</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-83.628</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.1876909474431176</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.8003300417552056</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1.61157141227288</v>
+      </c>
+      <c r="K37" t="n">
+        <v>2.526243468095973</v>
+      </c>
+      <c r="L37" t="n">
+        <v>33.83314000141182</v>
+      </c>
+      <c r="M37" t="n">
+        <v>87.32531571405592</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>21.4059483032814</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>-9770.701640971984</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>-578.5028063672166</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>3.79570601572069e-07</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.9465298135882735</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B38" t="n">
+        <v>73.66899999999998</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.6026044776729842</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1262.560004319287</v>
+      </c>
+      <c r="E38" t="n">
+        <v>3.401932327849133</v>
+      </c>
+      <c r="F38" t="n">
+        <v>2.67279e-07</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-83.69</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.2957751868366115</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.9636503420793484</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1.634190566495614</v>
+      </c>
+      <c r="K38" t="n">
+        <v>2.392784020934656</v>
+      </c>
+      <c r="L38" t="n">
+        <v>33.49245672902483</v>
+      </c>
+      <c r="M38" t="n">
+        <v>87.44751334825065</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>22.43219200770721</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>-10197.68748450432</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>-742.7700921882181</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>3.774134290660462e-07</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.947336461795603</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B39" t="n">
+        <v>73.53999999999996</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.6015492715806003</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1357.128652157507</v>
+      </c>
+      <c r="E39" t="n">
+        <v>3.656744882643529</v>
+      </c>
+      <c r="F39" t="n">
+        <v>2.67075e-07</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-83.759</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.5951039828724957</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1.073613451235428</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1.874587208278521</v>
+      </c>
+      <c r="K39" t="n">
+        <v>2.748564575002348</v>
+      </c>
+      <c r="L39" t="n">
+        <v>35.30980551628979</v>
+      </c>
+      <c r="M39" t="n">
+        <v>87.52417100540225</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>23.12765295142246</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>-10453.6666009086</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>-831.865799298183</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>3.75005320023306e-07</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.948182704905459</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B40" t="n">
+        <v>69.43700000000001</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.5679871739290479</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1113.909590429736</v>
+      </c>
+      <c r="E40" t="n">
+        <v>3.001397979517969</v>
+      </c>
+      <c r="F40" t="n">
+        <v>2.66953e-07</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-83.803</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.1242211930156695</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.631517199390349</v>
+      </c>
+      <c r="J40" t="n">
+        <v>1.431943269044873</v>
+      </c>
+      <c r="K40" t="n">
+        <v>2.321296160162953</v>
+      </c>
+      <c r="L40" t="n">
+        <v>33.81777975569447</v>
+      </c>
+      <c r="M40" t="n">
+        <v>87.37354170745235</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>21.79956234889971</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>-9699.759956167509</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>-614.8522174445186</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>3.733618963832413e-07</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.9487873349115972</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B41" t="n">
+        <v>69.13500000000005</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.5655168464879637</v>
+      </c>
+      <c r="D41" t="n">
+        <v>1211.447361577307</v>
+      </c>
+      <c r="E41" t="n">
+        <v>3.26421075334108</v>
+      </c>
+      <c r="F41" t="n">
+        <v>2.66861e-07</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-83.834</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.3188206966877221</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.7984307653834289</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1.671405747267264</v>
+      </c>
+      <c r="K41" t="n">
+        <v>2.27978211544319</v>
+      </c>
+      <c r="L41" t="n">
+        <v>33.65501553687267</v>
+      </c>
+      <c r="M41" t="n">
+        <v>87.44335165990118</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>22.39562869768338</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>-9910.233625440118</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>-707.2753955044894</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>3.722562336146518e-07</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.9491914304127851</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B42" t="n">
+        <v>70.59499999999997</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.5774594890839337</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1657.77317527988</v>
+      </c>
+      <c r="E42" t="n">
+        <v>4.466823072117157</v>
+      </c>
+      <c r="F42" t="n">
+        <v>2.66724e-07</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-83.895</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.7173799805031622</v>
+      </c>
+      <c r="I42" t="n">
+        <v>1.316235481668363</v>
+      </c>
+      <c r="J42" t="n">
+        <v>1.739407420553176</v>
+      </c>
+      <c r="K42" t="n">
+        <v>2.618405736056628</v>
+      </c>
+      <c r="L42" t="n">
+        <v>34.88228354389916</v>
+      </c>
+      <c r="M42" t="n">
+        <v>87.6263570578039</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>24.12452033487193</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>-10659.97893321486</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>-1115.902302769691</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>3.70075288371997e-07</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.9500074306874754</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>30</v>
+      </c>
+      <c r="B43" t="n">
+        <v>66.67299999999994</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.5453779519185934</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1262.278685295418</v>
+      </c>
+      <c r="E43" t="n">
+        <v>3.401174321672423</v>
+      </c>
+      <c r="F43" t="n">
+        <v>2.66594e-07</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-83.96599999999999</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.4115843471558466</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.9389535320322314</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1.611043353358093</v>
+      </c>
+      <c r="K43" t="n">
+        <v>2.606017068382955</v>
+      </c>
+      <c r="L43" t="n">
+        <v>36.02166506229121</v>
+      </c>
+      <c r="M43" t="n">
+        <v>87.50042163574763</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>22.90763392616027</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>-9967.246164742723</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>-760.3784048609194</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>3.67800067085379e-07</v>
+      </c>
+      <c r="AD43" t="n">
         <v>0.9508641339490165</v>
       </c>
     </row>
@@ -5850,7 +10498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6552,6 +11200,566 @@
         <v>1.073043167800002e-06</v>
       </c>
       <c r="AD11" t="n">
+        <v>0.8926826976604159</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B12" t="n">
+        <v>203.4469999999999</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>415.5327085246262</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2.84316e-07</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-77.22</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.08978648883415256</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.4588389627428508</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.967997851505038</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1.680153160535744</v>
+      </c>
+      <c r="L12" t="n">
+        <v>10.51397226609207</v>
+      </c>
+      <c r="M12" t="n">
+        <v>83.2286754759028</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>8.422101355625013</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-5594.038148614398</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>186.6668969395223</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.572271554047037e-09</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.938911304287214</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>140.4449999999999</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.6903272105265743</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1121.467977719676</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2.698868114862763</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2.87624e-07</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-79.655</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.3596651333256907</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.7502398108834016</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.458388893159746</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2.304195474805894</v>
+      </c>
+      <c r="L13" t="n">
+        <v>15.06963432387406</v>
+      </c>
+      <c r="M13" t="n">
+        <v>85.0734179252637</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>11.60124906408612</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-6793.990321478196</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>-472.6731776653691</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>6.244166002873013e-07</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.8826192676113127</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B14" t="n">
+        <v>125.5309999999999</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.6170206491125452</v>
+      </c>
+      <c r="D14" t="n">
+        <v>943.2031818020457</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2.269865073079193</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2.84392e-07</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-80.584</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.4120581683184186</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.7372488032528489</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.3682177871806</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2.171282251502486</v>
+      </c>
+      <c r="L14" t="n">
+        <v>17.43515295685487</v>
+      </c>
+      <c r="M14" t="n">
+        <v>85.68063584767771</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>13.23972577131781</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-7493.781817736216</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>-339.512298175683</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>5.527798103117413e-07</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.8991624134218938</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" t="n">
+        <v>119.874</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.5892148815170536</v>
+      </c>
+      <c r="D15" t="n">
+        <v>925.0936317207684</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2.226283545777584</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2.81587e-07</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-81.169</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.2220249874761634</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.8108045526750352</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.575293000320209</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2.21423370452061</v>
+      </c>
+      <c r="L15" t="n">
+        <v>19.9532080972912</v>
+      </c>
+      <c r="M15" t="n">
+        <v>86.08381995169948</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>14.60773689230128</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-8129.460176005873</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>-333.7548071037525</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>5.137677306838621e-07</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.9086276890544402</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B16" t="n">
+        <v>115.61</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.5682561060128681</v>
+      </c>
+      <c r="D16" t="n">
+        <v>952.8001598665713</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2.292960675104363</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2.79529e-07</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-81.532</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.2913970905464736</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.753727737783691</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.54670286844977</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2.167709406308663</v>
+      </c>
+      <c r="L16" t="n">
+        <v>21.73132486399051</v>
+      </c>
+      <c r="M16" t="n">
+        <v>86.32011709446074</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>15.54858614599184</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-8528.742698678667</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>-366.5285160124305</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>4.901749361239819e-07</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.9145916029816222</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" t="n">
+        <v>112.884</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.5548570389339729</v>
+      </c>
+      <c r="D17" t="n">
+        <v>973.8540596952689</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2.343627925592178</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2.78141e-07</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-81.807</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.4629487547650173</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.044311552568128</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.66867415449035</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2.49605929445957</v>
+      </c>
+      <c r="L17" t="n">
+        <v>23.85104886284417</v>
+      </c>
+      <c r="M17" t="n">
+        <v>86.52516603865126</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>16.46856123014045</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-8919.202352188366</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>-392.8741474049283</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>4.73924482176603e-07</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.9189140062896058</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B18" t="n">
+        <v>110.67</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.5439745978068</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1052.069384466093</v>
+      </c>
+      <c r="E18" t="n">
+        <v>2.531856970300914</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2.76923e-07</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-82.05200000000001</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.7921775406142562</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.013640151941362</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.876557889961799</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2.37590768450577</v>
+      </c>
+      <c r="L18" t="n">
+        <v>24.90528374330481</v>
+      </c>
+      <c r="M18" t="n">
+        <v>86.72920435807227</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>17.49835000588874</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-9365.715433468496</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>-470.1810552379338</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>4.59654215334174e-07</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.9228651803233946</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" t="n">
+        <v>104.707</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.5146647529823494</v>
+      </c>
+      <c r="D19" t="n">
+        <v>988.0854681183581</v>
+      </c>
+      <c r="E19" t="n">
+        <v>2.377876513323379</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2.75833e-07</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-82.236</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.2993758409746031</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.9043058464767185</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.591753687542244</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2.306192192620498</v>
+      </c>
+      <c r="L19" t="n">
+        <v>25.07201326729235</v>
+      </c>
+      <c r="M19" t="n">
+        <v>86.72363030343634</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>17.46851540983855</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-9178.008238206097</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>-421.4502052960082</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>4.488018763383606e-07</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.9258881672677145</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B20" t="n">
+        <v>101.419</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.4985032956986341</v>
+      </c>
+      <c r="D20" t="n">
+        <v>985.8590759485415</v>
+      </c>
+      <c r="E20" t="n">
+        <v>2.372518590531401</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2.75131e-07</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-82.438</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.1965352671732684</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.8598913346408041</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.621214801029556</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2.558268819927799</v>
+      </c>
+      <c r="L20" t="n">
+        <v>27.73301992254679</v>
+      </c>
+      <c r="M20" t="n">
+        <v>86.82480654129405</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>18.02633899289433</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-9343.367392363531</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>-426.5521051765032</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.679564945875143e-06</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.826458868524758</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" t="n">
+        <v>97.31200000000001</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.4783162199491761</v>
+      </c>
+      <c r="D21" t="n">
+        <v>940.3522230414053</v>
+      </c>
+      <c r="E21" t="n">
+        <v>2.263004099918349</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2.74475e-07</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-82.578</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.3162668118101436</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.9570668073881924</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1.68957947960506</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2.411477381060497</v>
+      </c>
+      <c r="L21" t="n">
+        <v>28.05607358596687</v>
+      </c>
+      <c r="M21" t="n">
+        <v>86.88813597581999</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>18.39393704756781</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-9412.102212550497</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>-392.5744355680042</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.073043167800002e-06</v>
+      </c>
+      <c r="AD21" t="n">
         <v>0.8926826976604159</v>
       </c>
     </row>
@@ -6566,7 +11774,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7884,6 +13092,1182 @@
         <v>3.81027561082448e-07</v>
       </c>
       <c r="AD22" t="n">
+        <v>0.9489411211194251</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B23" t="n">
+        <v>125.5210000000001</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>405.3857065638215</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>2.93977e-07</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-79.83799999999999</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.2391044109163905</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.7136005494002059</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.243429740364458</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2.049380985192579</v>
+      </c>
+      <c r="L23" t="n">
+        <v>14.65458637159623</v>
+      </c>
+      <c r="M23" t="n">
+        <v>84.97403041664072</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>11.37069061908078</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-6270.929668642305</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>121.8358773643241</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>2.615643179912395e-09</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.9354954801747274</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B24" t="n">
+        <v>103.521</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.824730523179388</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1146.565042166093</v>
+      </c>
+      <c r="E24" t="n">
+        <v>2.828331200635423</v>
+      </c>
+      <c r="F24" t="n">
+        <v>2.84886e-07</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-81.52</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.4649729785824099</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.9275681081264546</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.623548140619627</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2.307936484269805</v>
+      </c>
+      <c r="L24" t="n">
+        <v>20.57984087140361</v>
+      </c>
+      <c r="M24" t="n">
+        <v>86.21937729737456</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>15.13311587404684</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-7908.507524896489</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>-565.6887190885853</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>4.93953090122737e-07</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.9163984231004559</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B25" t="n">
+        <v>97.38899999999995</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.7758781399128425</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1078.587580289879</v>
+      </c>
+      <c r="E25" t="n">
+        <v>2.660645313403699</v>
+      </c>
+      <c r="F25" t="n">
+        <v>2.81455e-07</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-82.027</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.5400442856502823</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1.004924751475929</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1.562905831973823</v>
+      </c>
+      <c r="K25" t="n">
+        <v>2.46533442115506</v>
+      </c>
+      <c r="L25" t="n">
+        <v>23.42731796260284</v>
+      </c>
+      <c r="M25" t="n">
+        <v>86.56353036166978</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>16.6528633143862</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-8555.417740161829</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>-516.3670651784987</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>9.920763789529094e-07</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.8841076497048745</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B26" t="n">
+        <v>94.255</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.7509102062603066</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1032.789144989676</v>
+      </c>
+      <c r="E26" t="n">
+        <v>2.547670350155968</v>
+      </c>
+      <c r="F26" t="n">
+        <v>2.79294e-07</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-82.303</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.3643220811514742</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.9542164653254016</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1.706124634932756</v>
+      </c>
+      <c r="K26" t="n">
+        <v>2.557466640050853</v>
+      </c>
+      <c r="L26" t="n">
+        <v>25.57066790162908</v>
+      </c>
+      <c r="M26" t="n">
+        <v>86.69176337968138</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>17.29987900364074</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-8769.937580096921</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>-481.5837848715981</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>4.478528728625239e-07</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.9281369151662501</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B27" t="n">
+        <v>92.601</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.737733128321157</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1071.254183162644</v>
+      </c>
+      <c r="E27" t="n">
+        <v>2.642555388158442</v>
+      </c>
+      <c r="F27" t="n">
+        <v>2.78271e-07</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-82.5</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.4038505141133135</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1.191843074366935</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1.61408324282019</v>
+      </c>
+      <c r="K27" t="n">
+        <v>2.427137666739247</v>
+      </c>
+      <c r="L27" t="n">
+        <v>26.19734474223249</v>
+      </c>
+      <c r="M27" t="n">
+        <v>86.86121345923347</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>18.23585350489639</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-9162.047188881685</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>-521.5038801240548</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>4.379485607529913e-07</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.9309405666265033</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B28" t="n">
+        <v>88.86799999999999</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.7079930848224596</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1018.455294596793</v>
+      </c>
+      <c r="E28" t="n">
+        <v>2.51231180109813</v>
+      </c>
+      <c r="F28" t="n">
+        <v>2.77066e-07</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-82.661</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.1492253332338421</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.7377444389760996</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.550429218871968</v>
+      </c>
+      <c r="K28" t="n">
+        <v>2.420052258613789</v>
+      </c>
+      <c r="L28" t="n">
+        <v>26.8792209452552</v>
+      </c>
+      <c r="M28" t="n">
+        <v>86.86744460857412</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>18.27220011263456</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-9049.732686986781</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>-479.7410486108045</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>4.290502484936856e-07</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.9333986982988465</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" t="n">
+        <v>85.39500000000004</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.6803244078680061</v>
+      </c>
+      <c r="D29" t="n">
+        <v>952.8610339279178</v>
+      </c>
+      <c r="E29" t="n">
+        <v>2.350504762500562</v>
+      </c>
+      <c r="F29" t="n">
+        <v>2.76493e-07</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-82.78700000000001</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.07170453227870047</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.9006459460884192</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.410516855309734</v>
+      </c>
+      <c r="K29" t="n">
+        <v>2.356001495963845</v>
+      </c>
+      <c r="L29" t="n">
+        <v>27.71404091806502</v>
+      </c>
+      <c r="M29" t="n">
+        <v>86.86641320059545</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>18.26617388483119</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-8927.370516560044</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>-426.3495748725411</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>4.22975977742907e-07</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.9352353544685039</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B30" t="n">
+        <v>83.005</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.6612837692497665</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1043.478335741616</v>
+      </c>
+      <c r="E30" t="n">
+        <v>2.574038301908744</v>
+      </c>
+      <c r="F30" t="n">
+        <v>2.75846e-07</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-82.91</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.04359110091901515</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.6539034218664624</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.507416497338782</v>
+      </c>
+      <c r="K30" t="n">
+        <v>2.093907073931078</v>
+      </c>
+      <c r="L30" t="n">
+        <v>27.72395612532735</v>
+      </c>
+      <c r="M30" t="n">
+        <v>86.91368979123239</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>18.5465325606511</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-8965.882849277941</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>-512.8964082705451</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>4.170676493982838e-07</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.9370133824139422</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79.952</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.6369611459437062</v>
+      </c>
+      <c r="D31" t="n">
+        <v>991.8055552344614</v>
+      </c>
+      <c r="E31" t="n">
+        <v>2.446572583037822</v>
+      </c>
+      <c r="F31" t="n">
+        <v>2.75517e-07</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-83.04600000000001</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.04799330266948247</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.5089520950458595</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1.328541868980331</v>
+      </c>
+      <c r="K31" t="n">
+        <v>2.276765500046405</v>
+      </c>
+      <c r="L31" t="n">
+        <v>29.34774855306356</v>
+      </c>
+      <c r="M31" t="n">
+        <v>86.94806930354042</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>18.75585872139407</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-8968.913603131734</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>-471.3586055370186</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>4.115320442145009e-07</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.9388208224766018</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B32" t="n">
+        <v>80.97499999999997</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.6451111766158645</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1069.677066978048</v>
+      </c>
+      <c r="E32" t="n">
+        <v>2.638664979199617</v>
+      </c>
+      <c r="F32" t="n">
+        <v>2.74867e-07</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-83.09099999999999</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.251142230750293</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1.001559869725202</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1.617462083210003</v>
+      </c>
+      <c r="K32" t="n">
+        <v>2.388396257881872</v>
+      </c>
+      <c r="L32" t="n">
+        <v>29.59671202286416</v>
+      </c>
+      <c r="M32" t="n">
+        <v>87.11608184377877</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>19.85055815957696</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>-9466.037951180724</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>-545.8962549955997</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>4.083913633849018e-07</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.9396582439700497</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B33" t="n">
+        <v>80.16699999999997</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.6386740067399075</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1160.498537446534</v>
+      </c>
+      <c r="E33" t="n">
+        <v>2.862702159095075</v>
+      </c>
+      <c r="F33" t="n">
+        <v>2.74698e-07</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-83.209</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.538528885055742</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1.197607868959394</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1.673785067309329</v>
+      </c>
+      <c r="K33" t="n">
+        <v>2.645207520751798</v>
+      </c>
+      <c r="L33" t="n">
+        <v>31.71356509395545</v>
+      </c>
+      <c r="M33" t="n">
+        <v>87.22113248913811</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>20.60222261724563</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>-9759.613103107598</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>-632.0797298057973</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>4.040091939319597e-07</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.9411799777512009</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B34" t="n">
+        <v>78.42199999999997</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.6247719505102726</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1086.038955565593</v>
+      </c>
+      <c r="E34" t="n">
+        <v>2.67902626555634</v>
+      </c>
+      <c r="F34" t="n">
+        <v>2.74453e-07</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-83.25700000000001</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.3159914689799611</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.7606565528292796</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1.532980626709601</v>
+      </c>
+      <c r="K34" t="n">
+        <v>2.379374168915587</v>
+      </c>
+      <c r="L34" t="n">
+        <v>30.45819316920828</v>
+      </c>
+      <c r="M34" t="n">
+        <v>87.20388616141652</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>20.47494874847089</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>-9605.001358597106</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>-568.3870217097557</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>4.017211680390725e-07</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.9419093952397858</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B35" t="n">
+        <v>77.54300000000001</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.6177691382318493</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1210.144025696469</v>
+      </c>
+      <c r="E35" t="n">
+        <v>2.985166980735545</v>
+      </c>
+      <c r="F35" t="n">
+        <v>2.74151e-07</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-83.309</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.6882018617424399</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1.240996384041292</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1.838074607032267</v>
+      </c>
+      <c r="K35" t="n">
+        <v>2.844247579126824</v>
+      </c>
+      <c r="L35" t="n">
+        <v>32.33648522574576</v>
+      </c>
+      <c r="M35" t="n">
+        <v>87.28877204326189</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>21.11700272736227</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>-9858.038022428444</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>-684.4150291705306</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>3.993079744260538e-07</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.9426626894254309</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>20</v>
+      </c>
+      <c r="B36" t="n">
+        <v>75.66800000000001</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.6028313987300927</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1105.476830800402</v>
+      </c>
+      <c r="E36" t="n">
+        <v>2.726975354337911</v>
+      </c>
+      <c r="F36" t="n">
+        <v>2.73748e-07</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-83.417</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.3134838763771157</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1.042939328728132</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1.762795303259463</v>
+      </c>
+      <c r="K36" t="n">
+        <v>2.697678128525368</v>
+      </c>
+      <c r="L36" t="n">
+        <v>33.13060500710547</v>
+      </c>
+      <c r="M36" t="n">
+        <v>87.27853165704568</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>21.03742435549335</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>-9717.500210802407</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>-593.3234985105496</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>3.950350635438924e-07</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.9440599332315927</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B37" t="n">
+        <v>76.363</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.6083683208387438</v>
+      </c>
+      <c r="D37" t="n">
+        <v>1255.083621829614</v>
+      </c>
+      <c r="E37" t="n">
+        <v>3.096023371095401</v>
+      </c>
+      <c r="F37" t="n">
+        <v>2.73534e-07</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-83.444</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.8348889911401127</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1.162140258504048</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1.817230276788898</v>
+      </c>
+      <c r="K37" t="n">
+        <v>2.500076677676967</v>
+      </c>
+      <c r="L37" t="n">
+        <v>32.04735124593791</v>
+      </c>
+      <c r="M37" t="n">
+        <v>87.37663320905385</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>21.82528800418178</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>-10047.4484867406</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>-731.7342709361276</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>3.936691830738516e-07</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.9444756568646714</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B38" t="n">
+        <v>73.23899999999998</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.5834800551302167</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1089.17127217829</v>
+      </c>
+      <c r="E38" t="n">
+        <v>2.686753021981099</v>
+      </c>
+      <c r="F38" t="n">
+        <v>2.73386e-07</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-83.521</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.1647945491312554</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.9837396176996254</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1.647799806128335</v>
+      </c>
+      <c r="K38" t="n">
+        <v>2.36922966697612</v>
+      </c>
+      <c r="L38" t="n">
+        <v>32.74818385103877</v>
+      </c>
+      <c r="M38" t="n">
+        <v>87.29573909794998</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>21.17148818119123</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>-9621.749888657463</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>-585.0291552274996</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>3.909898706607735e-07</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.9454196979458092</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B39" t="n">
+        <v>72.40800000000002</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.5768596489830385</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1169.599698695776</v>
+      </c>
+      <c r="E39" t="n">
+        <v>2.885152781062944</v>
+      </c>
+      <c r="F39" t="n">
+        <v>2.73301e-07</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-83.593</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.3214774842710523</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1.209466696147226</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1.839286975016417</v>
+      </c>
+      <c r="K39" t="n">
+        <v>2.696931366100376</v>
+      </c>
+      <c r="L39" t="n">
+        <v>34.32470239710515</v>
+      </c>
+      <c r="M39" t="n">
+        <v>87.36062890868665</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>21.69276074669611</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>-9796.620626035796</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>-661.2284984972958</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>3.885281668279745e-07</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.9463227911538287</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B40" t="n">
+        <v>72.01900000000001</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.5737605659610739</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1261.058472689659</v>
+      </c>
+      <c r="E40" t="n">
+        <v>3.110762052709733</v>
+      </c>
+      <c r="F40" t="n">
+        <v>2.73065e-07</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-83.61199999999999</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.4950083851407024</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1.175182459718676</v>
+      </c>
+      <c r="J40" t="n">
+        <v>1.651556081778543</v>
+      </c>
+      <c r="K40" t="n">
+        <v>2.664032826976464</v>
+      </c>
+      <c r="L40" t="n">
+        <v>33.45708075385323</v>
+      </c>
+      <c r="M40" t="n">
+        <v>87.42040333435118</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>22.19612925718187</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>-9966.493890533791</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>-747.838874172656</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>3.872646030629363e-07</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.9467052719556901</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B41" t="n">
+        <v>69.64600000000002</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.5548553628476508</v>
+      </c>
+      <c r="D41" t="n">
+        <v>1132.602972835435</v>
+      </c>
+      <c r="E41" t="n">
+        <v>2.79388975609362</v>
+      </c>
+      <c r="F41" t="n">
+        <v>2.73002e-07</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-83.694</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.3197724061545827</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.7992640451359035</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1.667099980053784</v>
+      </c>
+      <c r="K41" t="n">
+        <v>2.35736918713577</v>
+      </c>
+      <c r="L41" t="n">
+        <v>33.04256991738124</v>
+      </c>
+      <c r="M41" t="n">
+        <v>87.36357714126802</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>21.71705344331145</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>-9633.625039364226</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>-634.9207040180563</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>3.846101172966364e-07</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.9476994654770635</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B42" t="n">
+        <v>68.39400000000001</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.5448809362576778</v>
+      </c>
+      <c r="D42" t="n">
+        <v>319.8996590417691</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.7891241695553122</v>
+      </c>
+      <c r="F42" t="n">
+        <v>2.7283e-07</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-83.73999999999999</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.1456315529338118</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.8252817968348364</v>
+      </c>
+      <c r="J42" t="n">
+        <v>1.68344162422929</v>
+      </c>
+      <c r="K42" t="n">
+        <v>2.325128961003513</v>
+      </c>
+      <c r="L42" t="n">
+        <v>33.18595231170661</v>
+      </c>
+      <c r="M42" t="n">
+        <v>87.37559569964908</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>21.81664770973818</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>-9599.512453267755</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>117.6086023247421</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>2.285483970405988e-09</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.9679148829285911</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>30</v>
+      </c>
+      <c r="B43" t="n">
+        <v>67.209</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.5354402848925675</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1148.930834496155</v>
+      </c>
+      <c r="E43" t="n">
+        <v>2.834167105285629</v>
+      </c>
+      <c r="F43" t="n">
+        <v>2.72657e-07</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-83.786</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.3344382195167493</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.8663366712060335</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1.660336650775057</v>
+      </c>
+      <c r="K43" t="n">
+        <v>2.628745819131058</v>
+      </c>
+      <c r="L43" t="n">
+        <v>34.60014319776201</v>
+      </c>
+      <c r="M43" t="n">
+        <v>87.39131217537374</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>21.94826922092168</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>-9575.315285342263</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>-656.5089153167586</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>3.81027561082448e-07</v>
+      </c>
+      <c r="AD43" t="n">
         <v>0.9489411211194251</v>
       </c>
     </row>
@@ -8054,7 +14438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9372,6 +15756,1182 @@
         <v>3.84126071669241e-07</v>
       </c>
       <c r="AD22" t="n">
+        <v>0.948902603725772</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B23" t="n">
+        <v>118.316</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1673.428943731583</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>2.90962e-07</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-80.413</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.05632165463573149</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.6030178703272474</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.291296933946665</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2.092727964739502</v>
+      </c>
+      <c r="L23" t="n">
+        <v>16.61522318530226</v>
+      </c>
+      <c r="M23" t="n">
+        <v>85.36780758400076</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>12.34208059193906</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-6748.482591283335</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>-989.2711043607978</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>5.669450557150221e-07</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.8989682063270243</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B24" t="n">
+        <v>101.064</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.8541870921937856</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1063.97416431176</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.6358048056341145</v>
+      </c>
+      <c r="F24" t="n">
+        <v>2.84504e-07</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-81.617</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.3018543265036266</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.7948109934005042</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.450497006712002</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2.347110374287388</v>
+      </c>
+      <c r="L24" t="n">
+        <v>21.37036557361384</v>
+      </c>
+      <c r="M24" t="n">
+        <v>86.24270524471871</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>15.22734540983481</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-7954.308330172933</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>-492.076803122459</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>4.873475088148432e-07</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.9182314914725673</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B25" t="n">
+        <v>95.32999999999998</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.8057236552959867</v>
+      </c>
+      <c r="D25" t="n">
+        <v>974.7631682837783</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.5824945074214815</v>
+      </c>
+      <c r="F25" t="n">
+        <v>2.81687e-07</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-82.045</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.0543188916675581</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.9187364282398158</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1.498707011918256</v>
+      </c>
+      <c r="K25" t="n">
+        <v>2.289753805255692</v>
+      </c>
+      <c r="L25" t="n">
+        <v>23.14132603398336</v>
+      </c>
+      <c r="M25" t="n">
+        <v>86.49591963575499</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>16.33076923701559</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-8381.349611913041</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>-422.4252394555306</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.062851142884898e-06</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.9015750434924876</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B26" t="n">
+        <v>92.99799999999999</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.786013725954224</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1025.52639569973</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.6128293642471049</v>
+      </c>
+      <c r="F26" t="n">
+        <v>2.80065e-07</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-82.316</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.2822353297111492</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.9998832862542856</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1.644037359117712</v>
+      </c>
+      <c r="K26" t="n">
+        <v>2.466855875220816</v>
+      </c>
+      <c r="L26" t="n">
+        <v>25.6597756595014</v>
+      </c>
+      <c r="M26" t="n">
+        <v>86.70390905726283</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>17.36376851073928</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-8819.308046089296</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>-474.0564110993898</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>4.477011926842336e-07</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.9286061019103289</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B27" t="n">
+        <v>90.89699999999999</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.7682561952736736</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1054.783575052516</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.6303127354188415</v>
+      </c>
+      <c r="F27" t="n">
+        <v>2.78988e-07</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-82.503</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.4369707905749145</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.9786950025844137</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1.598157331735448</v>
+      </c>
+      <c r="K27" t="n">
+        <v>2.490136468821365</v>
+      </c>
+      <c r="L27" t="n">
+        <v>26.90238682115092</v>
+      </c>
+      <c r="M27" t="n">
+        <v>86.82408465951286</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>18.02223322550936</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-9051.57053567746</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>-506.51117763558</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>4.378649357911211e-07</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.9313778756816655</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B28" t="n">
+        <v>87.29400000000004</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.7378038473241152</v>
+      </c>
+      <c r="D28" t="n">
+        <v>968.1862332091104</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.5785642926972148</v>
+      </c>
+      <c r="F28" t="n">
+        <v>2.78413e-07</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-82.687</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.1281494067318574</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.7198944617762969</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.488134384064884</v>
+      </c>
+      <c r="K28" t="n">
+        <v>2.441531922837453</v>
+      </c>
+      <c r="L28" t="n">
+        <v>27.99171628122713</v>
+      </c>
+      <c r="M28" t="n">
+        <v>86.84822348474556</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>18.16054395931161</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-8990.707432323008</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>-434.4667920596235</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>4.295566039130984e-07</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.9339426762883472</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" t="n">
+        <v>88.53699999999998</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.7483096115487335</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1263.616588506356</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.7551062106578693</v>
+      </c>
+      <c r="F29" t="n">
+        <v>2.77561e-07</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-82.736</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.8914811866735203</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1.257392073300633</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.862314840617542</v>
+      </c>
+      <c r="K29" t="n">
+        <v>2.422520428958181</v>
+      </c>
+      <c r="L29" t="n">
+        <v>27.77002464045712</v>
+      </c>
+      <c r="M29" t="n">
+        <v>87.07437942212684</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>19.56712211995582</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-9667.665045701837</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>-706.2831264454267</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>4.254248137776638e-07</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.9349760936115415</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B30" t="n">
+        <v>84.02199999999999</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.7101490922614014</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1056.788388932611</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.6315107629106</v>
+      </c>
+      <c r="F30" t="n">
+        <v>2.77305e-07</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-82.873</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.3707102807844357</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1.042678878766388</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.664121299461529</v>
+      </c>
+      <c r="K30" t="n">
+        <v>2.452585515216535</v>
+      </c>
+      <c r="L30" t="n">
+        <v>28.84182331349882</v>
+      </c>
+      <c r="M30" t="n">
+        <v>87.01837713022248</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>19.19895718333372</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-9336.989697992338</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>-525.0837529260702</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>4.197342568742096e-07</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.9368559410857729</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B31" t="n">
+        <v>82.19300000000004</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.6946904898745734</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1065.403944689762</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.6366592072406826</v>
+      </c>
+      <c r="F31" t="n">
+        <v>2.76884e-07</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-82.96899999999999</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.3011969081534984</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1.064876016727608</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1.729454618817764</v>
+      </c>
+      <c r="K31" t="n">
+        <v>2.321924199199953</v>
+      </c>
+      <c r="L31" t="n">
+        <v>29.13686104294803</v>
+      </c>
+      <c r="M31" t="n">
+        <v>87.05324217330423</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>19.42652097738906</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-9355.328574205456</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>-537.6329311317322</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>4.153048812850813e-07</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.9382300766782647</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79.88600000000002</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.6751918590892187</v>
+      </c>
+      <c r="D32" t="n">
+        <v>992.2784996992277</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.5929612389077865</v>
+      </c>
+      <c r="F32" t="n">
+        <v>2.76525e-07</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-83.074</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.1863187019911016</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.785036998776084</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1.603038143482963</v>
+      </c>
+      <c r="K32" t="n">
+        <v>2.366914462988277</v>
+      </c>
+      <c r="L32" t="n">
+        <v>29.90548607814235</v>
+      </c>
+      <c r="M32" t="n">
+        <v>87.05817622417544</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>19.4591607757565</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>-9268.527996519775</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>-475.8337559207615</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>4.108080852274275e-07</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.939677337286614</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B33" t="n">
+        <v>79.03700000000003</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.6680161601135942</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1111.473797982237</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.6641894190641636</v>
+      </c>
+      <c r="F33" t="n">
+        <v>2.76262e-07</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-83.155</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.2965496547716178</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1.17144045888976</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1.619530577406423</v>
+      </c>
+      <c r="K33" t="n">
+        <v>2.461145959607075</v>
+      </c>
+      <c r="L33" t="n">
+        <v>30.46447517675472</v>
+      </c>
+      <c r="M33" t="n">
+        <v>87.16366452366474</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>20.18413181362069</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>-9562.296871914776</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>-588.064336523564</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>4.07338253062954e-07</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.9408160193881694</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B34" t="n">
+        <v>77.45600000000002</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.6546536394063356</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1032.268560235175</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.6168583160354074</v>
+      </c>
+      <c r="F34" t="n">
+        <v>2.76021e-07</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-83.23</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.2612641244370062</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.8618077240652429</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1.57390425567196</v>
+      </c>
+      <c r="K34" t="n">
+        <v>2.491843768907402</v>
+      </c>
+      <c r="L34" t="n">
+        <v>31.51168575287774</v>
+      </c>
+      <c r="M34" t="n">
+        <v>87.15239682727612</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>20.10413422417657</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>-9433.776914746522</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>-519.9453361865951</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>4.042887200040525e-07</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.941817274399396</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B35" t="n">
+        <v>75.98400000000004</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.6422123804050173</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1107.254170114177</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.6616678731784744</v>
+      </c>
+      <c r="F35" t="n">
+        <v>2.75885e-07</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-83.29600000000001</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.3627986000509496</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1.006275397997277</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1.489633957647103</v>
+      </c>
+      <c r="K35" t="n">
+        <v>2.341879768411624</v>
+      </c>
+      <c r="L35" t="n">
+        <v>31.02200798893481</v>
+      </c>
+      <c r="M35" t="n">
+        <v>87.22555644851892</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>20.63512520391754</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>-9622.311120797718</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>-591.4631384823169</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>4.016765652232231e-07</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.9427223175330037</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>20</v>
+      </c>
+      <c r="B36" t="n">
+        <v>66.12299999999999</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.5588677778153417</v>
+      </c>
+      <c r="D36" t="n">
+        <v>983.9117922644982</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.5879615002179126</v>
+      </c>
+      <c r="F36" t="n">
+        <v>2.75449e-07</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-83.358</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.5284105134071867</v>
+      </c>
+      <c r="K36" t="n">
+        <v>1.645140983711813</v>
+      </c>
+      <c r="L36" t="n">
+        <v>28.54794017829548</v>
+      </c>
+      <c r="M36" t="n">
+        <v>86.68831508228989</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>17.2818253563226</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>-7835.619852268862</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>-483.0485352067577</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>3.987137550482963e-07</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.9436113417893272</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B37" t="n">
+        <v>73.81999999999999</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.6239223773623176</v>
+      </c>
+      <c r="D37" t="n">
+        <v>1168.524713587353</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.6982816437856376</v>
+      </c>
+      <c r="F37" t="n">
+        <v>2.75362e-07</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-83.404</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.2567416298007419</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1.039574621431789</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1.901466951544447</v>
+      </c>
+      <c r="K37" t="n">
+        <v>2.654389688558586</v>
+      </c>
+      <c r="L37" t="n">
+        <v>32.82564847444672</v>
+      </c>
+      <c r="M37" t="n">
+        <v>87.26625806343664</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>20.94283077297428</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>-9609.411179678706</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>-654.1993830628451</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>3.968436105843079e-07</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.9442829336644935</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B38" t="n">
+        <v>73.86700000000002</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.6243196186483654</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1337.277504920916</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.7991241635506307</v>
+      </c>
+      <c r="F38" t="n">
+        <v>2.75127e-07</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-83.46299999999999</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.6545810269870269</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1.373625820132056</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1.855074542768117</v>
+      </c>
+      <c r="K38" t="n">
+        <v>2.859874240445463</v>
+      </c>
+      <c r="L38" t="n">
+        <v>33.53952021722319</v>
+      </c>
+      <c r="M38" t="n">
+        <v>87.36962013998401</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>21.76701631896348</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>-9943.823040689851</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>-810.651811934684</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>3.944747448839126e-07</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.9450593510380562</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B39" t="n">
+        <v>69.31600000000003</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.5858548294398054</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1101.58013923501</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.6582772118059548</v>
+      </c>
+      <c r="F39" t="n">
+        <v>2.752e-07</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-83.532</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.01972741828231752</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.6329222072146139</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1.359612831196749</v>
+      </c>
+      <c r="K39" t="n">
+        <v>2.342528833365068</v>
+      </c>
+      <c r="L39" t="n">
+        <v>31.92717052037846</v>
+      </c>
+      <c r="M39" t="n">
+        <v>87.20830633647073</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>20.50741885717805</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>-9214.62778707721</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>-600.4447574485557</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>3.922775108507422e-07</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.9459407386960953</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B40" t="n">
+        <v>71.404</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.6035024848710232</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1425.594858736097</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.8519004431446967</v>
+      </c>
+      <c r="F40" t="n">
+        <v>2.75054e-07</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-83.613</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.6193574318054983</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1.224288964249634</v>
+      </c>
+      <c r="J40" t="n">
+        <v>1.757157908479477</v>
+      </c>
+      <c r="K40" t="n">
+        <v>2.812775319975381</v>
+      </c>
+      <c r="L40" t="n">
+        <v>34.53731380715769</v>
+      </c>
+      <c r="M40" t="n">
+        <v>87.43245571536816</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>22.30046132747842</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>-10016.93989251047</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>-898.650580828344</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>3.89463031729073e-07</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.9469428626333418</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B41" t="n">
+        <v>66.90200000000004</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.5654518408330237</v>
+      </c>
+      <c r="D41" t="n">
+        <v>1136.629358682779</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.6792217637566412</v>
+      </c>
+      <c r="F41" t="n">
+        <v>2.74906e-07</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-83.65000000000001</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.06680426372917281</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.6254671828461726</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1.558258670953845</v>
+      </c>
+      <c r="K41" t="n">
+        <v>2.418485407083224</v>
+      </c>
+      <c r="L41" t="n">
+        <v>33.6102473676049</v>
+      </c>
+      <c r="M41" t="n">
+        <v>87.24302465416277</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>20.76607339002453</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>-9168.849542788153</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>-639.6596004768631</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>3.879106575621827e-07</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.9474793052485463</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B42" t="n">
+        <v>68.47899999999998</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.5787805537712564</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1396.660641082037</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.8346100659449698</v>
+      </c>
+      <c r="F42" t="n">
+        <v>2.74804e-07</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-83.673</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.5907969911891308</v>
+      </c>
+      <c r="I42" t="n">
+        <v>1.248602594578701</v>
+      </c>
+      <c r="J42" t="n">
+        <v>1.661483957986553</v>
+      </c>
+      <c r="K42" t="n">
+        <v>2.549052190523509</v>
+      </c>
+      <c r="L42" t="n">
+        <v>33.20916565104123</v>
+      </c>
+      <c r="M42" t="n">
+        <v>87.42690252177401</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>22.25226847656322</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>-9813.809394455837</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>-879.8485153942045</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>3.868962096896977e-07</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.9478246627882296</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>30</v>
+      </c>
+      <c r="B43" t="n">
+        <v>63.71500000000003</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.5385155008620982</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1250.206767451459</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.747092831240041</v>
+      </c>
+      <c r="F43" t="n">
+        <v>2.74796e-07</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-83.76000000000001</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.6192578126582722</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1.366398932951824</v>
+      </c>
+      <c r="K43" t="n">
+        <v>2.324959367663667</v>
+      </c>
+      <c r="L43" t="n">
+        <v>33.37604744936927</v>
+      </c>
+      <c r="M43" t="n">
+        <v>87.27172274305212</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>20.98484247191181</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>-9099.907935646037</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>-750.7996544272796</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>3.84126071669241e-07</v>
+      </c>
+      <c r="AD43" t="n">
         <v>0.948902603725772</v>
       </c>
     </row>
@@ -9386,7 +16946,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10091,6 +17651,566 @@
         <v>0.9369762446723572</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B12" t="n">
+        <v>175.804</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>450.9873025173325</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2.85579e-07</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-78.413</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.2263665679697882</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.6638822971646808</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.293211094585357</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1.919426546576553</v>
+      </c>
+      <c r="L12" t="n">
+        <v>12.17773641243749</v>
+      </c>
+      <c r="M12" t="n">
+        <v>84.08290098419012</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>9.64863735957964</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-5985.534406047734</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>117.3173695326476</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.159399899675312e-09</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.9375264351296223</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>119.131</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.6776353211531023</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1236.592133890851</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2.741966629633271</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2.84088e-07</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-80.55500000000001</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.551288982656042</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.208455215704146</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2.165342448054973</v>
+      </c>
+      <c r="L13" t="n">
+        <v>16.81992527759554</v>
+      </c>
+      <c r="M13" t="n">
+        <v>85.38886327510725</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>12.39868361975104</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-6817.848939904364</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>-605.8544985072681</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>5.505983538172226e-07</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.8996711595776918</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B14" t="n">
+        <v>108.834</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.6190644126413505</v>
+      </c>
+      <c r="D14" t="n">
+        <v>965.3796183233129</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2.140591570837432</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2.80278e-07</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-81.40900000000001</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.06199560623364564</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.7243401381040071</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.279808995644383</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2.217647669909073</v>
+      </c>
+      <c r="L14" t="n">
+        <v>20.02949988549155</v>
+      </c>
+      <c r="M14" t="n">
+        <v>86.04545356274795</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>14.46557039402282</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-7736.704617183487</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>-388.7452794521322</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>4.957459364143968e-07</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.9133416400144007</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" t="n">
+        <v>104.93</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.5968578644399444</v>
+      </c>
+      <c r="D15" t="n">
+        <v>982.5105099527518</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2.178576878924416</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2.77441e-07</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-81.84999999999999</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.1304386430923389</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.8333450844142718</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.58987825015285</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2.428335461406494</v>
+      </c>
+      <c r="L15" t="n">
+        <v>22.85414558827944</v>
+      </c>
+      <c r="M15" t="n">
+        <v>86.37443048586742</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>15.78215113178104</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-8310.46069717217</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>-413.7158403279214</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>4.690264968634016e-07</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.9201326074386598</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B16" t="n">
+        <v>102.597</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.5835874041546265</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1073.324834721886</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2.379944687424179</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2.75699e-07</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-82.163</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.3225886190486932</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.9964592631470622</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.757523654227942</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2.356567263269973</v>
+      </c>
+      <c r="L16" t="n">
+        <v>24.3758272005061</v>
+      </c>
+      <c r="M16" t="n">
+        <v>86.62510124543059</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>16.95739764315634</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-8818.705085613392</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>-502.6845875195099</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>4.517866403552614e-07</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.9248175910051529</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" t="n">
+        <v>98.27800000000002</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.5590202725762782</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1097.665248777675</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2.433916082893463</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2.74648e-07</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-82.39400000000001</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.540467568610694</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.127642102626859</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.53951753724565</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2.347522683678398</v>
+      </c>
+      <c r="L17" t="n">
+        <v>25.41078565163649</v>
+      </c>
+      <c r="M17" t="n">
+        <v>86.73955288943954</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>17.55400973710982</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-8990.702303374113</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>-532.1645451137668</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.58174486006174e-06</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.8362733134808182</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B18" t="n">
+        <v>95.08199999999999</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.5408409364974629</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1103.259195102659</v>
+      </c>
+      <c r="E18" t="n">
+        <v>2.446319860768714</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2.7384e-07</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-82.613</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.3803279486330484</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.010963154993154</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.642251469051127</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2.451493371399361</v>
+      </c>
+      <c r="L18" t="n">
+        <v>27.78480334468127</v>
+      </c>
+      <c r="M18" t="n">
+        <v>86.83360894459653</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>18.07655388747258</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-9110.545228760877</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>-545.1034649052626</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>4.294520224850721e-07</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.9314217339739586</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" t="n">
+        <v>89.55800000000005</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.5094195808969081</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1002.1039226646</v>
+      </c>
+      <c r="E19" t="n">
+        <v>2.222022476178443</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2.73324e-07</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-82.708</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.1068662504930662</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.7170961197232232</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.338398208661787</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2.16448637641308</v>
+      </c>
+      <c r="L19" t="n">
+        <v>26.71414690001193</v>
+      </c>
+      <c r="M19" t="n">
+        <v>86.75578467338379</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>17.64202714084421</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-8721.405395930318</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>-462.4547437242704</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>4.240480861238635e-07</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.9330733490802984</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B20" t="n">
+        <v>87.34300000000002</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.496820322632022</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1082.36022321853</v>
+      </c>
+      <c r="E20" t="n">
+        <v>2.399979372317102</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2.73061e-07</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-82.834</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.4841724412663034</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.8789033583930339</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.561033290041177</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2.231645556879763</v>
+      </c>
+      <c r="L20" t="n">
+        <v>27.03093700069163</v>
+      </c>
+      <c r="M20" t="n">
+        <v>86.88368510113125</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>18.3676141474842</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-8980.525195986682</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>-541.8561788930012</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>4.183775092728076e-07</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.9349609149016714</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" t="n">
+        <v>83.30200000000002</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.4738344975085891</v>
+      </c>
+      <c r="D21" t="n">
+        <v>999.4223982786633</v>
+      </c>
+      <c r="E21" t="n">
+        <v>2.216076578431503</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2.72774e-07</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-82.97799999999999</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.08315385594277053</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.7646753249610921</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1.466099350365916</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2.373176587681221</v>
+      </c>
+      <c r="L21" t="n">
+        <v>28.8931875628394</v>
+      </c>
+      <c r="M21" t="n">
+        <v>86.86890944232314</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>18.28076554225826</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-8798.41393372084</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>-473.338552547877</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>4.123806631877916e-07</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0.9369762446723572</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
